--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BBACA9-2766-4DE4-B61B-C7F75E880958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BC9603-A518-4323-B0AA-8E696DE3AF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7103" uniqueCount="1784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7105" uniqueCount="1784">
   <si>
     <t>NpcID</t>
   </si>
@@ -9979,8 +9979,8 @@
     <col min="7" max="7" width="25.5" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.75" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="80" width="9.125" style="23" customWidth="1"/>
-    <col min="81" max="16384" width="9.125" style="23"/>
+    <col min="10" max="81" width="9.125" style="23" customWidth="1"/>
+    <col min="82" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -12261,8 +12261,8 @@
     <col min="16" max="18" width="8.375" style="46" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.75" style="46" customWidth="1"/>
     <col min="20" max="20" width="10" style="46" bestFit="1" customWidth="1"/>
-    <col min="21" max="30" width="9" style="47" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="47"/>
+    <col min="21" max="31" width="9" style="47" customWidth="1"/>
+    <col min="32" max="16384" width="9" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="46" customFormat="1" ht="36" customHeight="1">
@@ -14514,7 +14514,9 @@
       <c r="B60" s="48" t="s">
         <v>452</v>
       </c>
-      <c r="C60" s="48"/>
+      <c r="C60" s="48" t="s">
+        <v>305</v>
+      </c>
       <c r="D60" s="48">
         <v>26</v>
       </c>
@@ -14562,8 +14564,8 @@
     <col min="9" max="9" width="48" style="10" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="64" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="66" customWidth="1"/>
-    <col min="12" max="54" width="8.875" style="36" customWidth="1"/>
-    <col min="55" max="16384" width="8.875" style="36"/>
+    <col min="12" max="55" width="8.875" style="36" customWidth="1"/>
+    <col min="56" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -24372,7 +24374,9 @@
         <v>471</v>
       </c>
       <c r="G359" s="55"/>
-      <c r="H359" s="55"/>
+      <c r="H359" s="55" t="s">
+        <v>638</v>
+      </c>
       <c r="I359" s="55"/>
       <c r="J359" s="56" t="s">
         <v>845</v>
@@ -27536,8 +27540,8 @@
     <col min="27" max="27" width="5.125" style="35" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" customWidth="1"/>
-    <col min="30" max="128" width="9" style="9" customWidth="1"/>
-    <col min="129" max="16384" width="9" style="9"/>
+    <col min="30" max="129" width="9" style="9" customWidth="1"/>
+    <col min="130" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -27697,10 +27701,10 @@
         <v>1.3</v>
       </c>
       <c r="D8" s="32">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E8" s="32">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="18" customHeight="1">
@@ -27714,7 +27718,7 @@
         <v>1.5</v>
       </c>
       <c r="E9" s="32">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="18" customHeight="1">
@@ -27728,7 +27732,7 @@
         <v>0.7</v>
       </c>
       <c r="E10" s="32">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="18" customHeight="1">
@@ -27736,13 +27740,13 @@
         <v>964</v>
       </c>
       <c r="B11" s="32">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="D11" s="32">
         <v>0.7</v>
       </c>
       <c r="E11" s="32">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="18" customHeight="1">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681A5B1D-D9D3-4112-A292-0ECAFF453B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D6D0AD-CCCC-4D1F-BAA4-FEA9EF49BEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7234" uniqueCount="1881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7238" uniqueCount="1877">
   <si>
     <t>NpcID</t>
   </si>
@@ -7623,6 +7623,29 @@
     <t>把脉</t>
   </si>
   <si>
+    <t>游戏中人体被划分为表、心、肝、脾、肺、肾六个区域；每个区域由气、血、寒热、湿燥四种属性构成；医者通过把脉确定病位和病性。
+【寸关尺】
+寸、关、尺是脉诊中的三个把脉位置，在手腕桡骨动脉上。医者通过按压这三个位置，感受脉象的强弱、快慢、沉浮、流畅程度，从而推测人体不同区域和脏腑的健康状况。
+【对应脏腑区域】
+浮脉：表
+左寸：心
+左关：肝
+左尺：肾阴
+右寸：肺
+右关：脾
+右尺：肾阳
+【脉象】
+游戏中脉象由波形图表示。
+波峰的高低反映气的强弱；
+波峰越高气滞程度越高，波峰越低气虚程度越高。
+波线的粗细反映血的状态；
+波线越粗血瘀程度越高，波线越细血虚程度越高。
+波宽的宽窄反映湿燥程度；
+波宽越宽越湿，波宽越窄越燥。
+波速的快慢反映寒热程度；
+波速越快越热，波速越慢越寒。</t>
+  </si>
+  <si>
     <t>kai_fang</t>
   </si>
   <si>
@@ -7654,672 +7677,88 @@
     <t>现在你可以预制方剂，开方时搜索并选取方剂名，可自动填入该方剂包含的的所有药材及剂量。</t>
   </si>
   <si>
+    <t>si_zhen</t>
+  </si>
+  <si>
+    <t>四诊</t>
+  </si>
+  <si>
+    <t>【四诊】
+四诊是中医收集患者病情资料的四种基本诊察方法，包括望诊、闻诊、问诊和切诊。医者通过观察、听闻、询问和触按患者所表现出的各种信息，了解疾病的病因、病位、性质以及正邪盛衰，为辨证和治疗提供依据。
+望诊是观察患者的神、色、形、态以及舌象和局部变化；闻诊包括听声音和嗅气味，如辨别说话、呼吸、咳嗽等声音及异常气味；问诊是询问疾病经过、主要症状、生活习惯及既往情况；切诊包括脉诊和按诊，通过切脉与触按身体了解脉象及局部变化。
+四诊各有侧重，也会相互补充。同一种疾病可能表现出不同征象，不同疾病也可能出现相似症状，因此不能仅凭舌象、脉象或某一个症状作出判断。医者需要将四诊所得资料结合起来分析，称为“四诊合参”。
+通过四诊合参，医者可进一步运用八纲、脏腑、气血津液等辨证方法，对病情作出综合判断。四诊是中医辨证论治的基础，其结果也会受到患者体质、年龄、环境和病程等因素影响。</t>
+  </si>
+  <si>
+    <t>ba_gang_bian_zheng</t>
+  </si>
+  <si>
+    <t>八纲辨证</t>
+  </si>
+  <si>
+    <t>【八纲辨证】
+八纲辨证是中医分析病情的基本方法。医者通过望、闻、问、切收集症状，再以阴、阳、表、里、寒、热、虚、实八项纲领进行归纳，从而判断疾病的位置、性质以及正邪力量的盛衰。
+表里：辨别病位的内外深浅。病在肌表、经络，多属表；病入脏腑、气血，多属里。
+寒热：辨别疾病的性质。寒证多见畏寒喜暖、口淡不渴；热证多见发热喜凉、口渴烦躁。
+虚实：辨别正邪盛衰。虚证多为正气不足、功能衰弱；实证多为邪气较盛、病理产物壅滞。
+阴阳：统摄其余六纲，是八纲的总纲。一般而言，表、热、实偏属阳，里、寒、虚偏属阴。
+八纲之间并非彼此孤立，一种病证可以同时具有多种性质，如表寒证、里热证或虚寒证。病情发展过程中，还可能发生表里出入、寒热转化和虚实变化。因此，医者必须四诊合参，方能把握疾病的整体情况。</t>
+  </si>
+  <si>
     <t>yin_yang</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>阴阳</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>【阴阳】
 阴阳是中医认识人体与自然变化的基本方法。阴代表相对安静、寒凉、内守的一面，阳代表相对活动、温热、外发的一面。二者相互对立，又彼此依存，并会随着时间与环境不断消长变化。
 人体中的寒热、表里、虚实、动静，都可以用阴阳来概括。阴阳保持协调，身体便能正常运行；若一方偏盛或偏衰，就可能出现疾病。医者诊病时，需要分辨阴阳变化，判断失衡所在，再采用相应的方法使其重新趋于协调。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>biao_li</t>
+  </si>
+  <si>
+    <t>表里</t>
+  </si>
+  <si>
+    <t>【表里】
+表里是中医八纲辨证中用来判断疾病部位深浅和病势进退的两项纲领。表证通常指病邪位于皮毛、肌腠和经络，多见于外邪侵袭人体的初期；里证通常指病邪深入脏腑、气血或骨髓，也可由饮食、情志、劳倦等内伤因素直接形成。这里的表里并不单纯指身体的外部和内部，而是对病位与病势的综合判断。
+表证：常见恶寒发热、头痛身痛、鼻塞流涕、咳嗽、舌苔薄白、脉浮等表现。由于病邪尚在体表，通常病程较短，起病较急。
+里证：临床表现较为复杂，可见但热不寒、口渴、烦躁、腹痛、呕吐、腹泻、便秘、小便异常、舌苔厚或脉沉等表现。由于病变涉及脏腑气血，其症状会随寒热、虚实及所病脏腑的不同而有所变化。
+表证和里证可以同时存在，称为表里同病；疾病由表入里，通常表示病邪逐渐深入；由里出表，则可能表示病邪向外透达。医者需要结合寒热、虚实以及望、闻、问、切所得信息进行判断，不可只凭一个症状确定表里。辨明疾病部位后，表证通常以解表为基本方向，里证则根据具体的寒热虚实采取相应治法。</t>
+  </si>
+  <si>
+    <t>han_re</t>
+  </si>
+  <si>
+    <t>寒热</t>
+  </si>
+  <si>
+    <t>【寒热】
+寒热是中医八纲辨证中用来判断疾病性质的两项纲领。寒证多由寒邪侵袭，或人体阳气不足所致；热证多由热邪侵袭、阳气偏盛，或阴液不足所致。这里的寒热并不只指体温高低，而是对患者整体表现的综合判断。
+寒证：常见畏寒喜暖、四肢发冷、面色苍白、口淡不渴、小便清长、大便稀溏、舌淡苔白、脉象迟缓等表现。
+热证：常见发热喜凉、面红烦躁、口渴喜冷饮、小便短黄、大便干结、舌红苔黄、脉象较数等表现。
+寒证又可分为实寒与虚寒，热证也可分为实热与虚热。医者需要结合表里、虚实以及望、闻、问、切所得信息进行判断，不可只凭一个症状确定寒热。辨明疾病性质后，通常遵循寒证用温法、热证用清法的基本方向。</t>
+  </si>
+  <si>
+    <t>xu_shi</t>
+  </si>
+  <si>
+    <t>虚实</t>
+  </si>
+  <si>
+    <t>【虚实】
+虚实是中医八纲辨证中用来判断人体正气强弱和病邪盛衰的两项纲领。虚证多由人体正气不足、脏腑功能衰退，或气血阴阳亏损所致；实证多由外邪侵袭，或痰饮、瘀血、食积等病理产物壅盛所致。这里的虚实并不单指身体强壮或虚弱，而是对正邪双方力量和病理状态的综合判断。
+虚证：常见精神疲倦、身体乏力、面色少华、声音低弱、气短、自汗或盗汗、疼痛喜按、舌质淡嫩或少苔、脉象细弱无力等表现。其具体症状会因气、血、阴、阳亏虚的不同而有所变化。
+实证：常见起病较急、精神烦躁、声音洪亮、呼吸气粗、腹胀拒按、疼痛明显、痰涎壅盛、便秘或小便不利、舌苔厚腻、脉象有力等表现。其具体症状会随寒热性质以及病邪种类的不同而有所变化。
+虚证又可分为气虚、血虚、阴虚和阳虚等类型，实证则可见气滞、血瘀、痰湿、食积等不同情况。虚实也可能同时存在，称为虚实夹杂；病程中还可能出现由实转虚或因虚致实。医者需要结合表里、寒热以及望、闻、问、切所得信息进行判断，不可只凭一个症状确定虚实。辨明正邪盛衰后，虚证通常以补虚扶正为基本方向，实证通常以祛邪泻实为基本方向。</t>
+  </si>
+  <si>
+    <t>wu_xing</t>
   </si>
   <si>
     <t>五行</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>wu_xing</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <r>
-      <t>游</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>戏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>中人体被划分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>表、心、肝、脾、肺、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>肾阴，肾阳七</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>个区域；每个区域由气、血、寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>、湿燥四种属性构成；医者通</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>把脉确定病位和病性。
-【寸关尺】
-寸、关、尺是脉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>诊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>中的三个把脉位置，在手腕</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>桡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>骨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>脉上。医者通</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>压这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>三个位置，感受脉象的强弱、快慢、沉浮、流</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>畅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>程度，从而推</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>人体不同区域和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>脏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>腑的健康状况。
-【</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对应脏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>腑区域】
-浮脉：表
-左寸：心
-左关：肝
-左尺：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>肾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>阴
-右寸：肺
-右关：脾
-右尺：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>肾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>阳
-【脉象】
-游</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>戏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>中脉象由波形</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>图</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>表示。
-波峰的高低反映气的强弱；
-波峰越高气滞程度越高，波峰越低气虚程度越高。
-波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的粗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>细</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>反映血的状</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>；
-波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>越粗血瘀程度越高，波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>越</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>细</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>血虚程度越高。
-波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>宽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>宽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>窄反映湿燥程度；
-波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>宽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>越</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>宽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>越湿，波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>宽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>越窄越燥。
-波速的快慢反映寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>程度；
-波速越快越</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，波速越慢越寒。</t>
-    </r>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>【五行】
@@ -8340,1138 +7779,201 @@
 五液：泪，汗，涎，涕，唾
 春季万物生发，属木，与风、酸味和肝相应；夏季气候炎热，属火，与暑、苦味和心相应；长夏湿气较盛，属土，与湿、甘味和脾相应；秋季万物收敛，属金，与燥、辛味和肺相应；冬季万物闭藏，属水，与寒、咸味和肾相应。
 这些对应关系并不是说五脏只会受到某一种季节、气候或味道影响，而是用来说明自然环境、饮食情志和人体功能之间可能存在的联系。医者可以据此观察疾病发生与传变的规律，但诊断时仍须结合患者的全部症状综合判断。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>寒热</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>表里</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>虚实</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>biao_li</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>han_re</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>xu_shi</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>八纲辨证</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>ba_gang_bian_zheng</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>【八纲辨证】
-八纲辨证是中医分析病情的基本方法。医者通过望、闻、问、切收集症状，再以阴、阳、表、里、寒、热、虚、实八项纲领进行归纳，从而判断疾病的位置、性质以及正邪力量的盛衰。
-表里：辨别病位的内外深浅。病在肌表、经络，多属表；病入脏腑、气血，多属里。
-寒热：辨别疾病的性质。寒证多见畏寒喜暖、口淡不渴；热证多见发热喜凉、口渴烦躁。
-虚实：辨别正邪盛衰。虚证多为正气不足、功能衰弱；实证多为邪气较盛、病理产物壅滞。
-阴阳：统摄其余六纲，是八纲的总纲。一般而言，表、热、实偏属阳，里、寒、虚偏属阴。
-八纲之间并非彼此孤立，一种病证可以同时具有多种性质，如表寒证、里热证或虚寒证。病情发展过程中，还可能发生表里出入、寒热转化和虚实变化。因此，医者必须四诊合参，方能把握疾病的整体情况。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <r>
-      <t>【寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>】
-寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>是中医八</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>纲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>辨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>中用来判断疾病性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>质</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的两</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>项纲领</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>多由寒邪侵</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>袭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，或人体阳气不足所致；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>多由</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>邪侵</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>袭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>、阳气偏盛，或阴液不足所致。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>里的寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>并不只指体温高低，而是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>患者整体表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>综</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>合判断。
-寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>：常见畏寒喜暖、四肢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>冷、面色</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>苍</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>白、口淡不渴、小便清长、大便稀溏、舌淡苔白、脉象</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>迟缓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>等表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>：常见</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>喜凉、面</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>红烦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>躁、口渴喜冷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>饮</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>、小便短黄、大便干</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>结</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>、舌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>红</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>苔黄、脉象</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>较</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>数等表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。
-寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>又可分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为实</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>寒与虚寒，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>也可分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为实热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>与虚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。医者需要</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>结</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>合表里、虚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>实</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>以及望、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>闻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>问</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>、切所得信息</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>进</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>行判断，不可只凭一个症状确定寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。辨明疾病性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>质</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>后，通常遵循寒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>用温法、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>热证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>用清法的基本方向。</t>
-    </r>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>【表里】
-表里是中医八纲辨证中用来判断疾病部位深浅和病势进退的两项纲领。表证通常指病邪位于皮毛、肌腠和经络，多见于外邪侵袭人体的初期；里证通常指病邪深入脏腑、气血或骨髓，也可由饮食、情志、劳倦等内伤因素直接形成。这里的表里并不单纯指身体的外部和内部，而是对病位与病势的综合判断。
-表证：常见恶寒发热、头痛身痛、鼻塞流涕、咳嗽、舌苔薄白、脉浮等表现。由于病邪尚在体表，通常病程较短，起病较急。
-里证：临床表现较为复杂，可见但热不寒、口渴、烦躁、腹痛、呕吐、腹泻、便秘、小便异常、舌苔厚或脉沉等表现。由于病变涉及脏腑气血，其症状会随寒热、虚实及所病脏腑的不同而有所变化。
-表证和里证可以同时存在，称为表里同病；疾病由表入里，通常表示病邪逐渐深入；由里出表，则可能表示病邪向外透达。医者需要结合寒热、虚实以及望、闻、问、切所得信息进行判断，不可只凭一个症状确定表里。辨明疾病部位后，表证通常以解表为基本方向，里证则根据具体的寒热虚实采取相应治法。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>【虚实】
-虚实是中医八纲辨证中用来判断人体正气强弱和病邪盛衰的两项纲领。虚证多由人体正气不足、脏腑功能衰退，或气血阴阳亏损所致；实证多由外邪侵袭，或痰饮、瘀血、食积等病理产物壅盛所致。这里的虚实并不单指身体强壮或虚弱，而是对正邪双方力量和病理状态的综合判断。
-虚证：常见精神疲倦、身体乏力、面色少华、声音低弱、气短、自汗或盗汗、疼痛喜按、舌质淡嫩或少苔、脉象细弱无力等表现。其具体症状会因气、血、阴、阳亏虚的不同而有所变化。
-实证：常见起病较急、精神烦躁、声音洪亮、呼吸气粗、腹胀拒按、疼痛明显、痰涎壅盛、便秘或小便不利、舌苔厚腻、脉象有力等表现。其具体症状会随寒热性质以及病邪种类的不同而有所变化。
-虚证又可分为气虚、血虚、阴虚和阳虚等类型，实证则可见气滞、血瘀、痰湿、食积等不同情况。虚实也可能同时存在，称为虚实夹杂；病程中还可能出现由实转虚或因虚致实。医者需要结合表里、寒热以及望、闻、问、切所得信息进行判断，不可只凭一个症状确定虚实。辨明正邪盛衰后，虚证通常以补虚扶正为基本方向，实证通常以祛邪泻实为基本方向。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>zang_xiang</t>
   </si>
   <si>
     <t>藏象</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>zang_xiang</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>【藏象】
 藏象是中医研究人体脏腑生理功能、病理变化及其相互关系的理论。“藏”指藏于体内的脏腑，“象”指脏腑功能表现于外的各种征象。中医通过观察人的面色、形体、情志、声音、舌象和脉象等外在变化，推断脏腑的功能状态。
 藏象学说将人体内脏分为五脏、六腑和奇恒之腑。五脏包括肝、心、脾、肺、肾，以化生和贮藏精气为主要特点；六腑包括胆、小肠、胃、大肠、膀胱、三焦，以受盛和传化水谷为主要特点。奇恒之腑包括脑、髓、骨、脉、胆和女子胞。
 藏象理论强调人体是一个相互联系的整体。各脏腑不仅具有各自的功能，还通过气血津液、经络以及五行生克关系彼此协调，并与形体、官窍、情志和自然环境相联系。中医所说的脏腑属于功能体系，不能与现代医学中的解剖器官完全等同。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>肝</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>gan</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>【肝】
 肝是五脏之一，在五行属木，与胆相表里。中医认为肝具有主疏泄和藏血的功能。主疏泄是指肝能够调畅全身气机，促进脾胃运化、胆汁排泄和情志活动；藏血是指肝能够贮藏血液，并根据人体活动和休息的需要调节血量。
 肝在体合筋，其华在爪，开窍于目，在志为怒，在液为泪。肝血充足时，筋脉得到濡养，肢体活动灵活，双目视物清晰，指甲坚韧润泽。若肝血不足，可能出现视物模糊、肢体麻木、筋脉拘急或指甲失养等表现。
 肝的疏泄功能失常，可见情志抑郁、急躁易怒、胸胁胀满、食欲不振等表现；肝阳偏亢或肝火上炎，则可能出现头晕、头痛、面红目赤等表现。判断肝的功能状态，需要结合气血阴阳及其他脏腑情况综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>xin</t>
   </si>
   <si>
     <t>心</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>脾</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>肺</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>肾</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>pi</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>xin</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>fei</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>shen</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>【心】
 心是五脏之一，在五行属火，与小肠相表里。中医认为心具有主血脉和藏神的功能。主血脉是指心气推动血液在脉中运行，以濡养全身；藏神是指心与人的精神、意识、思维、情志和睡眠等活动密切相关。
 心在体合脉，其华在面，开窍于舌，在志为喜，在液为汗。心气和心血充足时，血脉运行通畅，面色红润，精神充沛，意识清楚，语言表达正常。若心血不足或心神失养，可能出现心悸、失眠、多梦、健忘、面色少华等表现。
 心气不足或心阳不振，可见心悸气短、精神疲倦、畏寒肢冷等表现；心火偏盛，则可能出现心烦失眠、口舌生疮、舌尖红等表现。判断心的功能状态，需要结合血脉、神志、舌象和脉象综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>pi</t>
   </si>
   <si>
     <t>【脾】
 脾是五脏之一，在五行属土，与胃相表里。中医认为脾具有主运化、升清和统血的功能。主运化是指脾将饮食物转化为水谷精微，并输布至全身；升清是指将精微物质向上输送；统血是指脾气能够固摄血液，使其正常运行于脉中。
 脾在体合肉，主四肢，其华在唇，开窍于口，在志为思，在液为涎。脾气健运时，饮食消化正常，肌肉充实，四肢有力，口唇红润。若脾失健运，可能出现食欲不振、腹胀、便溏、身体困重、四肢乏力等表现。
 脾气不足可导致水谷精微化生不足，也可能使水湿停聚，形成痰湿；脾不统血时，则可能出现便血、皮下出血或女性月经过多等表现。判断脾的功能状态，需要结合胃的受纳、气血生成和水液代谢情况综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>fei</t>
   </si>
   <si>
     <t>【肺】
 肺是五脏之一，在五行属金，与大肠相表里。中医认为肺具有主气、司呼吸、主宣发肃降和通调水道的功能。肺吸入自然界的清气，并参与宗气的生成；宣发使气和津液向上、向外输布，肃降使气和津液向下运行，并维持呼吸通畅。
 肺在体合皮，其华在毛，开窍于鼻，在志为悲忧，在液为涕。肺气充足时，呼吸均匀，声音有力，皮肤和毛发得到濡养，人体抵御外邪的能力正常。若肺气不足，可能出现气短、咳嗽、声音低弱、自汗和容易感受外邪等表现。
 肺失宣降时，可见咳嗽、气喘、鼻塞或痰液增多；肺的通调水道功能失常，还可能出现水液停聚、小便不利或水肿等表现。判断肺的功能状态，需要结合呼吸、声音、皮毛、鼻窍和水液代谢情况综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>shen</t>
   </si>
   <si>
     <t>【肾】
 肾是五脏之一，在五行属水，与膀胱相表里。中医认为肾具有藏精、主生长发育与生殖、主水和主纳气的功能。肾精是人体生长、发育和生殖的重要物质基础；肾主水，是指肾参与调节全身水液代谢；肾主纳气，是指肾能够帮助肺维持呼吸的深度和稳定。
 肾在体合骨，生髓充脑，其华在发，开窍于耳及二阴，在志为恐，在液为唾。肾精充足时，骨骼坚固，牙齿强健，听觉正常，头发有光泽，生长发育和生殖功能正常。若肾精不足，可能出现腰膝酸软、耳鸣、健忘、牙齿松动或生长发育迟缓等表现。
 肾阳不足可见畏寒肢冷、水肿、夜尿增多等表现；肾阴不足则可能出现潮热盗汗、口咽干燥、头晕耳鸣等表现；肾不纳气时，可见呼吸短促、动则气喘等表现。判断肾的功能状态，需要结合精、气、阴、阳以及水液代谢情况综合分析。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>风邪</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>寒邪</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>署邪</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>湿邪</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>燥邪</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>热邪</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>feng_xie</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>han_xie</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>shu_xie</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>shi_xie</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>zao_xie</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>re_xie</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>qi</t>
+  </si>
+  <si>
+    <t>气</t>
+  </si>
+  <si>
+    <t>【气】
+气是中医生命理论中的基本概念，既指构成人体和维持生命活动的精微物质，也指脏腑经络所表现出的功能活动。人体之气主要由先天之精、水谷精微和自然界清气化生，并依靠肺、脾、肾等脏腑共同维持。
+气具有推动、温煦、防御、固摄和气化等作用。它能够推动血液和津液运行，温暖脏腑形体，抵御外邪，固摄血液、汗液和二便，并促进饮食物及水液的转化。根据来源、分布和功能的不同，气还可分为元气、宗气、营气和卫气等。
+气的生成不足或功能减退，可形成气虚，常见乏力、气短、声音低弱、自汗等表现；气机运行不畅可形成气滞，出现胀满或疼痛；气机上逆、下陷或闭塞时，还可分别形成气逆、气陷和气闭。判断气的状态，需要结合脏腑功能、气血津液及全身表现综合分析。</t>
+  </si>
+  <si>
+    <t>xue</t>
+  </si>
+  <si>
+    <t>血</t>
+  </si>
+  <si>
+    <t>【血】
+血是中医所说运行于脉中、具有濡养和滋润作用的红色液态物质，也是维持人体生命活动的重要基础。血主要由脾胃运化所得的水谷精微化生，并与营气、津液及肾精的作用密切相关。
+血在心气推动下循脉运行，由肝贮藏和调节，并依靠脾气固摄而不致逸出脉外。血能够濡养脏腑、经络、肌肉、皮肤和官窍，同时也是精神意识活动的重要物质基础。血液充足、运行通畅时，面色润泽，感觉和运动正常，精神安定。
+血液不足可形成血虚，常见面色淡白、头晕、心悸、肢体麻木等表现；血行不畅可形成血瘀，常见固定刺痛、肿块或面色晦暗；血热、血寒及血液逸出脉外，也会形成不同证候。判断血的状态，需要结合气、津液和相关脏腑功能综合分析。</t>
+  </si>
+  <si>
+    <t>津</t>
+  </si>
+  <si>
+    <t>【津】
+津是人体正常水液的一部分，与液合称“津液”。中医认为津的性质较为清稀、流动性较强，主要分布于皮肤、肌肉和孔窍，也可渗入血脉，参与血液的组成和运行。
+津具有滋润皮肤、肌肉、口鼻和其他官窍的作用，并参与汗液、尿液等的生成和排泄。津的输布与脾的运化、肺的宣发肃降、肾的气化以及三焦水道是否通畅密切相关。
+津液不足时，常见口渴、口鼻干燥、皮肤干涩、小便短少或大便干结等表现；津的输布和排泄失常时，则可能停聚为水湿、痰饮或形成水肿。津和液性质有所不同，但能够相互转化，临床上通常结合起来判断。</t>
+  </si>
+  <si>
+    <t>ye</t>
+  </si>
+  <si>
+    <t>液</t>
+  </si>
+  <si>
+    <t>【液】
+液是人体正常水液的一部分，与津合称“津液”。中医认为液的性质较为稠厚、流动性相对较小，主要分布于脏腑、关节、骨髓和脑髓等较深部位。
+液具有濡养脏腑、滑利关节、充养骨髓和脑髓等作用，使关节活动灵活，并维持深部组织的滋润。液的生成、输布与排泄同样依赖脾、肺、肾和三焦等脏腑的协调作用。
+液不足时，可能出现关节活动不利、肌肤失润、口干咽燥、眩晕或身体消瘦等表现；液的运行失常时，也可能停聚形成痰饮、水湿等病理产物。一般而言，津偏于清稀并滋润体表，液偏于稠厚并濡养体内，但二者之间没有绝对界限。</t>
+  </si>
+  <si>
+    <t>wai_gan_liu_xie</t>
   </si>
   <si>
     <t>外感六邪</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>wai_gan_liu_xie</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>【外感六邪】
 外感六邪是中医对风、寒、暑、湿、燥、热六类外来致病因素的统称，又称“六淫”。风、寒、暑、湿、燥、热原本是自然界正常的气候变化，称为“六气”；当气候变化过于强烈、反常，或人体正气不足、适应能力下降时，六气便可能成为致病因素。
 外感六邪通常从皮毛、口鼻侵入人体，具有一定的季节性和地域性。例如春季多风、冬季多寒、长夏多湿、秋季多燥。六邪既可单独致病，也可相互结合，形成风寒、风热、寒湿、湿热等证候，在一定条件下还可能相互转化。
 不同邪气具有不同的致病特点，但人体患病后的具体表现还会受到体质、环境、病程及脏腑状态的影响。医者需要结合表里、寒热、虚实以及望、闻、问、切所得信息综合判断，不能仅凭季节或单一症状确定邪气种类。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>feng_xie</t>
+  </si>
+  <si>
+    <t>风邪</t>
   </si>
   <si>
     <t>【风邪】
 风邪是外感六邪之一，在五行与春季相应，但其他季节也可出现。中医认为风为阳邪，性质轻扬开泄，容易侵袭人体上部、肌表和肺卫，因此风邪致病多见头面部及体表症状。
 风邪具有善行数变的特点。“善行”是指症状位置游走不定，如游走性关节疼痛；“数变”是指发病较急、症状变化较快。风邪还具有主动的特点，可能出现眩晕、震颤、抽搐或肢体活动异常等表现。
 风邪常见恶风、发热、头痛、鼻塞、咳嗽、汗出、皮肤瘙痒等表现。由于风邪容易与其他邪气结合，又被称为“百病之长”，临床上常见风寒、风热、风湿和风燥等不同证候。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>han_xie</t>
+  </si>
+  <si>
+    <t>寒邪</t>
   </si>
   <si>
     <t>【寒邪】
 寒邪是外感六邪之一，在五行与冬季相应，气温骤降、衣着不足或长时间处于寒冷环境时较易侵袭人体。中医认为寒为阴邪，容易损伤人体阳气，使温煦和推动功能受到影响。
 寒邪具有凝滞和收引的特点。凝滞是指寒邪可使气血运行不畅，容易引起较为明显的疼痛；收引是指寒邪可使腠理、筋脉和经络收缩，出现无汗、肢体拘急、关节屈伸不利等表现。
 寒邪侵袭肌表时，常见恶寒明显、发热较轻、无汗、头痛身痛、鼻流清涕、舌苔薄白、脉浮紧等表现；寒邪深入脏腑时，则可能出现脘腹冷痛、呕吐、腹泻或四肢发冷等表现。辨治时还需区分外寒、内寒以及寒邪所在部位。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>shu_xie</t>
+  </si>
+  <si>
+    <t>署邪</t>
   </si>
   <si>
     <t>【暑邪】
 暑邪是外感六邪之一，是夏季特有的致病邪气，多由天气炎热、长时间暴露于高温环境或劳作过度所致。中医认为暑为阳邪，性质炎热升散，容易使人体腠理开泄、汗液大量排出。
 暑邪容易耗气伤津，常见高热、面红、心烦、口渴、大量出汗、身体乏力、气短、小便短黄等表现。暑邪严重时还可能出现头晕、恶心、突然昏倒或意识异常等情况。
 暑季气候往往炎热而潮湿，因此暑邪常与湿邪同时侵袭人体，形成“暑湿”。除发热口渴外，还可见胸闷、恶心、食欲不振、身体困重、腹泻和舌苔腻等表现。辨治时需要根据暑热与湿邪所占比重分别判断。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>shi_xie</t>
+  </si>
+  <si>
+    <t>湿邪</t>
   </si>
   <si>
     <t>【湿邪】
 湿邪是外感六邪之一，在五行与长夏相应，常与气候潮湿、淋雨涉水或长期处于湿润环境有关。中医认为湿为阴邪，容易阻碍气机、损伤阳气，并与脾的运化功能关系密切。
 湿邪具有重浊、黏滞和趋下的特点。重浊是指患者常有身体沉重、头重如裹、四肢困倦等感觉；黏滞是指症状缠绵、病程较长、分泌物黏腻不爽；趋下是指湿邪引起的症状较易出现在人体下部。
 湿邪致病常见胸闷脘痞、食欲不振、恶心、腹胀、便溏、肢体沉重、关节酸痛、舌苔厚腻等表现。湿邪还常与风、寒、热等邪气结合，形成风湿、寒湿或湿热等不同证候。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>zao_xie</t>
+  </si>
+  <si>
+    <t>燥邪</t>
   </si>
   <si>
     <t>【燥邪】
 燥邪是外感六邪之一，在五行与秋季相应，常见于气候干燥或人体津液不足以适应环境变化时。中医认为燥邪性质干涩，最容易耗伤人体津液，并容易侵袭肺脏。
 燥邪损伤津液后，常见口鼻干燥、咽干口渴、皮肤干涩、毛发失润、大便干结、小便短少等表现。肺为娇脏，喜润恶燥，因此燥邪犯肺时还可能出现干咳少痰，或痰液黏稠、不易咳出等表现。
 燥邪可分为温燥与凉燥。温燥多带有热象，可见发热、微恶风、口渴等表现；凉燥多带有寒象，可见恶寒、头痛、无汗等表现。医者需要结合季节、寒热和津液受损程度综合判断。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>re_xie</t>
+  </si>
+  <si>
+    <t>热邪</t>
   </si>
   <si>
     <t>【热邪】
 热邪是外感六邪之一，又常称为火邪。中医认为热为阳邪，性质炎热升腾，容易使人体出现阳热偏盛的表现。热邪可由外界侵入，也可由其他邪气在体内转化而成；热邪发展至较严重程度时，常称为火邪。
 热邪容易耗气伤津，常见高热、口渴喜冷饮、汗多、身体乏力、小便短黄、大便干结等表现。热邪具有炎上的特点，容易出现面红、目赤、咽喉肿痛、口舌生疮等人体上部症状。
 热邪还可能生风、动血或腐肉成脓。热极生风时可见抽搐、颈项强直等表现；热迫血行时可见出血、皮疹等表现；热邪壅聚局部时可能形成红、肿、热、痛的疮疡。判断热邪时，需要结合病位、病程及津液损伤程度综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>qi_qing_nei_shang</t>
   </si>
   <si>
     <t>七情内伤</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>qi_qing_nei_shang</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>【七情内伤】
@@ -9479,188 +7981,94 @@
 中医认为七情分别与五脏关系密切，即喜与心相应、怒与肝相应、思与脾相应、忧悲与肺相应、恐与肾相应。某种情绪过度时，容易影响相应脏腑；脏腑功能失调后，也可能反过来导致情绪变化。
 七情主要通过影响气机而致病，常概括为“怒则气上、喜则气缓、悲则气消、恐则气下、惊则气乱、思则气结”。例如，过怒可能出现头痛、面红、胸胁胀满；过思可能出现食欲不振、腹胀、失眠；惊恐过度可能出现心悸、神志不安或二便异常等表现。
 七情内伤通常直接影响内在脏腑，也可能导致气滞、血瘀、痰湿或阴阳失调。由于不同情志能够相互影响，具体表现还会因个人体质、情绪强度和持续时间而有所不同。医者需要结合患者的情志变化、脏腑症状以及望、闻、问、切所得信息综合判断。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>xi</t>
   </si>
   <si>
     <t>喜</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>怒</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>忧</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>思</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>悲</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>恐</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>惊</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>xi</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>nu</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>you</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>si</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>bei</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>kong</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>jing</t>
-    <phoneticPr fontId="20"/>
   </si>
   <si>
     <t>【喜】
 喜是七情之一，是人在愿望得到满足或遇到愉快事物时产生的正常情绪。适度的喜悦能够使心情舒畅、气血和缓，对身心具有积极作用。中医认为喜与心相应，正常的喜悦有助于心气调畅。
 喜悦过度或突然大喜时，则可能使心气涣散、心神失守，称为“喜则气缓”。这里的“缓”既有气机舒缓的一面，也包含过度时气机弛缓、精神难以集中的含义。
 过喜伤心时，可能出现心悸、失眠、精神涣散、注意力不集中或情绪异常兴奋等表现；情况严重时，还可能出现神志恍惚。判断是否由喜伤心，需要结合情绪变化、心神表现及个人体质综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>nu</t>
+  </si>
+  <si>
+    <t>怒</t>
   </si>
   <si>
     <t>【怒】
 怒是七情之一，是人在受到挫折、压迫或不公平对待时产生的正常情绪。适度表达愤怒有助于情绪疏解，但长期压抑、频繁发怒或突然暴怒，都可能影响人体气机。
 中医认为怒与肝相应。肝主疏泄，负责调畅气机；愤怒过度容易使肝的疏泄功能失常，导致气机上逆，称为“怒则气上”。
 怒伤肝时，常见头胀头痛、面红目赤、急躁易怒、胸胁胀满、口苦或眩晕等表现。肝气长期郁滞还可能影响脾胃，出现食欲不振、腹胀等症状。判断时需要区分肝气郁结、肝火上炎和肝阳上亢等不同情况。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>you</t>
+  </si>
+  <si>
+    <t>忧</t>
   </si>
   <si>
     <t>【忧】
 忧是七情之一，主要指因担心、顾虑或处境不安而产生的忧愁情绪。短暂的忧虑属于正常心理活动，但长期忧心忡忡、反复担忧，则可能使气机受到抑制。
 中医认为忧与肺关系密切。忧愁过度容易损伤肺气，使肺的宣发肃降功能失常；长期忧虑也可能影响脾的运化，导致气血化生不足。
 忧伤肺时，可能出现胸闷、气短、呼吸不畅、声音低弱、精神疲倦或容易叹息等表现；影响脾胃时，还可能出现食欲减退、腹胀和身体乏力。判断时需要结合忧虑持续时间以及肺、脾的相关症状综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>思</t>
   </si>
   <si>
     <t>【思】
 思是七情之一，主要指思考、谋虑和注意力集中的精神活动。正常思考有助于学习和处理问题，但思虑过度、长期用脑或反复纠结同一件事，则可能影响人体气机。
 中医认为思与脾相应。思虑过度容易使气机郁结，称为“思则气结”，并可能影响脾的运化功能，使饮食物不能正常转化为气血津液。
 思伤脾时，常见食欲不振、腹胀、便溏、身体乏力、精神倦怠等表现；心脾同时受到影响时，还可能出现心悸、健忘、失眠、多梦等症状。判断时需要结合饮食、睡眠和精神状态综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>bei</t>
+  </si>
+  <si>
+    <t>悲</t>
   </si>
   <si>
     <t>【悲】
 悲是七情之一，是人在经历失去、离别或重大打击时产生的哀伤情绪。适度悲伤属于正常的情感反应，但悲伤过度或长期不能缓解时，可能消耗人体之气，使精神和身体逐渐衰弱。
 中医认为悲与肺相应，悲伤过度容易耗伤肺气，称为“悲则气消”。肺气受损后，肺主气、司呼吸以及宣发肃降的功能可能受到影响。
 悲伤过度时，常见精神低落、气短乏力、声音低弱、胸闷、哭泣、食欲下降等表现。长期悲伤还可能进一步影响心、脾等脏腑。忧与悲都和肺有关，但忧偏于担心和愁虑，悲则偏于哀痛和失落。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>kong</t>
+  </si>
+  <si>
+    <t>恐</t>
   </si>
   <si>
     <t>【恐】
 恐是七情之一，是人在面临危险、威胁或未知事物时产生的害怕情绪。适度恐惧能够使人提高警觉、躲避危险，但长期处于恐惧之中或突然受到强烈惊吓，则可能扰乱脏腑气机。
 中医认为恐与肾相应。恐惧过度容易使肾气不固、气机下陷，称为“恐则气下”，从而影响肾的封藏及对二便的固摄功能。
 恐伤肾时，可能出现腰膝酸软、精神不安、遗尿、尿失禁或二便异常等表现；长期恐惧还可能耗伤肾精，使人出现健忘、耳鸣和意志消沉等症状。判断时需要结合恐惧发生的原因、持续时间及肾的相关表现综合分析。</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>jing</t>
+  </si>
+  <si>
+    <t>惊</t>
   </si>
   <si>
     <t>【惊】
 惊是七情之一，是人在突然遇到意外、声响或危险时产生的急剧情绪反应。惊与恐有所不同：惊通常由突发刺激引起，事先没有心理准备；恐则多是对已知或预期危险产生的害怕。
 中医认为惊主要影响心神，可使气机紊乱，称为“惊则气乱”。受到突然惊吓后，心神失去安定，气血运行也可能暂时失常，并可进一步影响肾的封藏功能。
 惊伤心神时，常见心悸、失眠、神志不宁、精神恍惚、容易受惊或注意力难以集中等表现；情况严重时，还可能出现昏厥或神志异常。判断时需要结合刺激强度、持续影响及患者原有的身心状态综合分析。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>气</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>血</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>津</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>液</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>xue</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>jin</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>ye</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>qi</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>【气】
-气是中医生命理论中的基本概念，既指构成人体和维持生命活动的精微物质，也指脏腑经络所表现出的功能活动。人体之气主要由先天之精、水谷精微和自然界清气化生，并依靠肺、脾、肾等脏腑共同维持。
-气具有推动、温煦、防御、固摄和气化等作用。它能够推动血液和津液运行，温暖脏腑形体，抵御外邪，固摄血液、汗液和二便，并促进饮食物及水液的转化。根据来源、分布和功能的不同，气还可分为元气、宗气、营气和卫气等。
-气的生成不足或功能减退，可形成气虚，常见乏力、气短、声音低弱、自汗等表现；气机运行不畅可形成气滞，出现胀满或疼痛；气机上逆、下陷或闭塞时，还可分别形成气逆、气陷和气闭。判断气的状态，需要结合脏腑功能、气血津液及全身表现综合分析。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>【血】
-血是中医所说运行于脉中、具有濡养和滋润作用的红色液态物质，也是维持人体生命活动的重要基础。血主要由脾胃运化所得的水谷精微化生，并与营气、津液及肾精的作用密切相关。
-血在心气推动下循脉运行，由肝贮藏和调节，并依靠脾气固摄而不致逸出脉外。血能够濡养脏腑、经络、肌肉、皮肤和官窍，同时也是精神意识活动的重要物质基础。血液充足、运行通畅时，面色润泽，感觉和运动正常，精神安定。
-血液不足可形成血虚，常见面色淡白、头晕、心悸、肢体麻木等表现；血行不畅可形成血瘀，常见固定刺痛、肿块或面色晦暗；血热、血寒及血液逸出脉外，也会形成不同证候。判断血的状态，需要结合气、津液和相关脏腑功能综合分析。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>【津】
-津是人体正常水液的一部分，与液合称“津液”。中医认为津的性质较为清稀、流动性较强，主要分布于皮肤、肌肉和孔窍，也可渗入血脉，参与血液的组成和运行。
-津具有滋润皮肤、肌肉、口鼻和其他官窍的作用，并参与汗液、尿液等的生成和排泄。津的输布与脾的运化、肺的宣发肃降、肾的气化以及三焦水道是否通畅密切相关。
-津液不足时，常见口渴、口鼻干燥、皮肤干涩、小便短少或大便干结等表现；津的输布和排泄失常时，则可能停聚为水湿、痰饮或形成水肿。津和液性质有所不同，但能够相互转化，临床上通常结合起来判断。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>【液】
-液是人体正常水液的一部分，与津合称“津液”。中医认为液的性质较为稠厚、流动性相对较小，主要分布于脏腑、关节、骨髓和脑髓等较深部位。
-液具有濡养脏腑、滑利关节、充养骨髓和脑髓等作用，使关节活动灵活，并维持深部组织的滋润。液的生成、输布与排泄同样依赖脾、肺、肾和三焦等脏腑的协调作用。
-液不足时，可能出现关节活动不利、肌肤失润、口干咽燥、眩晕或身体消瘦等表现；液的运行失常时，也可能停聚形成痰饮、水湿等病理产物。一般而言，津偏于清稀并滋润体表，液偏于稠厚并濡养体内，但二者之间没有绝对界限。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>四诊</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>【四诊】
-四诊是中医收集患者病情资料的四种基本诊察方法，包括望诊、闻诊、问诊和切诊。医者通过观察、听闻、询问和触按患者所表现出的各种信息，了解疾病的病因、病位、性质以及正邪盛衰，为辨证和治疗提供依据。
-望诊是观察患者的神、色、形、态以及舌象和局部变化；闻诊包括听声音和嗅气味，如辨别说话、呼吸、咳嗽等声音及异常气味；问诊是询问疾病经过、主要症状、生活习惯及既往情况；切诊包括脉诊和按诊，通过切脉与触按身体了解脉象及局部变化。
-四诊各有侧重，也会相互补充。同一种疾病可能表现出不同征象，不同疾病也可能出现相似症状，因此不能仅凭舌象、脉象或某一个症状作出判断。医者需要将四诊所得资料结合起来分析，称为“四诊合参”。
-通过四诊合参，医者可进一步运用八纲、脏腑、气血津液等辨证方法，对病情作出综合判断。四诊是中医辨证论治的基础，其结果也会受到患者体质、年龄、环境和病程等因素影响。</t>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>si_zhen</t>
-    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>sort_index</t>
+    <phoneticPr fontId="19"/>
   </si>
 </sst>
 </file>
@@ -9803,17 +8211,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="6"/>
+      <name val="BIZ UDGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="BIZ UDGothic"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="13">
@@ -9934,7 +8342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -10135,10 +8543,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -11984,8 +10393,8 @@
     <col min="7" max="7" width="25.5" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.75" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="82" width="9.125" style="23" customWidth="1"/>
-    <col min="83" max="16384" width="9.125" style="23"/>
+    <col min="10" max="83" width="9.125" style="23" customWidth="1"/>
+    <col min="84" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -14076,24 +12485,25 @@
       <c r="I81" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="11.125" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14.25" customWidth="1"/>
+    <col min="5" max="5" width="11.375" style="83" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>1773</v>
       </c>
@@ -14106,11 +12516,14 @@
       <c r="D1" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="85" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1">
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>1775</v>
       </c>
@@ -14123,16 +12536,19 @@
       <c r="D2" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E2" s="86" t="s">
-        <v>1789</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1">
+      <c r="E2" s="86">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="C3" s="7">
         <v>0</v>
@@ -14140,11 +12556,14 @@
       <c r="D3" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E3" s="74" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1">
+      <c r="E3" s="86">
+        <v>2</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>1728</v>
       </c>
@@ -14157,16 +12576,19 @@
       <c r="D4" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1">
+      <c r="E4" s="86">
+        <v>3</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="C5" s="7">
         <v>0</v>
@@ -14174,16 +12596,19 @@
       <c r="D5" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+      <c r="E5" s="86">
+        <v>4</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18" customHeight="1">
       <c r="A6" s="48" t="s">
-        <v>1880</v>
+        <v>1785</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>1878</v>
+        <v>1786</v>
       </c>
       <c r="C6" s="7">
         <v>0</v>
@@ -14191,16 +12616,19 @@
       <c r="D6" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E6" s="87" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1">
+      <c r="E6" s="86">
+        <v>5</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18" customHeight="1">
       <c r="A7" s="74" t="s">
-        <v>1798</v>
+        <v>1788</v>
       </c>
       <c r="B7" s="74" t="s">
-        <v>1797</v>
+        <v>1789</v>
       </c>
       <c r="C7" s="7">
         <v>10</v>
@@ -14208,16 +12636,19 @@
       <c r="D7" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E7" s="85" t="s">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1">
+      <c r="E7" s="86">
+        <v>6</v>
+      </c>
+      <c r="F7" s="74" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18" customHeight="1">
       <c r="A8" s="74" t="s">
-        <v>1784</v>
+        <v>1791</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>1785</v>
+        <v>1792</v>
       </c>
       <c r="C8" s="7">
         <v>10</v>
@@ -14225,16 +12656,19 @@
       <c r="D8" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E8" s="85" t="s">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1">
+      <c r="E8" s="86">
+        <v>7</v>
+      </c>
+      <c r="F8" s="74" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>1794</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="C9" s="7">
         <v>10</v>
@@ -14242,16 +12676,19 @@
       <c r="D9" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E9" s="86" t="s">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1">
+      <c r="E9" s="86">
+        <v>8</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1791</v>
+        <v>1798</v>
       </c>
       <c r="C10" s="7">
         <v>10</v>
@@ -14259,16 +12696,19 @@
       <c r="D10" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E10" s="86" t="s">
+      <c r="E10" s="86">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18" customHeight="1">
+      <c r="A11" s="7" t="s">
         <v>1800</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>1796</v>
-      </c>
       <c r="B11" s="7" t="s">
-        <v>1793</v>
+        <v>1801</v>
       </c>
       <c r="C11" s="7">
         <v>10</v>
@@ -14276,16 +12716,19 @@
       <c r="D11" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E11" s="86" t="s">
+      <c r="E11" s="86">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>1802</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1">
+    <row r="12" spans="1:6" ht="18" customHeight="1">
       <c r="A12" s="74" t="s">
-        <v>1788</v>
+        <v>1803</v>
       </c>
       <c r="B12" s="74" t="s">
-        <v>1787</v>
+        <v>1804</v>
       </c>
       <c r="C12" s="7">
         <v>20</v>
@@ -14293,16 +12736,19 @@
       <c r="D12" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E12" s="86" t="s">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1">
+      <c r="E12" s="86">
+        <v>11</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="C13" s="7">
         <v>40</v>
@@ -14310,16 +12756,19 @@
       <c r="D13" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E13" s="86" t="s">
-        <v>1805</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1">
+      <c r="E13" s="86">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1806</v>
+        <v>1619</v>
       </c>
       <c r="C14" s="7">
         <v>40</v>
@@ -14327,16 +12776,19 @@
       <c r="D14" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E14" s="86" t="s">
-        <v>1808</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1">
+      <c r="E14" s="86">
+        <v>13</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="C15" s="7">
         <v>40</v>
@@ -14344,16 +12796,19 @@
       <c r="D15" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E15" s="86" t="s">
-        <v>1817</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1">
+      <c r="E15" s="86">
+        <v>14</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1810</v>
+        <v>1595</v>
       </c>
       <c r="C16" s="7">
         <v>40</v>
@@ -14361,16 +12816,19 @@
       <c r="D16" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E16" s="86" t="s">
-        <v>1818</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1">
+      <c r="E16" s="86">
+        <v>15</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1811</v>
+        <v>1565</v>
       </c>
       <c r="C17" s="7">
         <v>40</v>
@@ -14378,16 +12836,19 @@
       <c r="D17" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E17" s="86" t="s">
-        <v>1819</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1">
+      <c r="E17" s="86">
+        <v>16</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1812</v>
+        <v>1614</v>
       </c>
       <c r="C18" s="7">
         <v>40</v>
@@ -14395,16 +12856,19 @@
       <c r="D18" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E18" s="86" t="s">
+      <c r="E18" s="86">
+        <v>17</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="18" customHeight="1">
+      <c r="A19" s="48" t="s">
         <v>1820</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1">
-      <c r="A19" s="48" t="s">
-        <v>1873</v>
-      </c>
       <c r="B19" s="48" t="s">
-        <v>1866</v>
+        <v>1821</v>
       </c>
       <c r="C19" s="7">
         <v>40</v>
@@ -14412,16 +12876,19 @@
       <c r="D19" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E19" s="87" t="s">
-        <v>1874</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1">
+      <c r="E19" s="86">
+        <v>18</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1">
       <c r="A20" s="48" t="s">
-        <v>1870</v>
+        <v>1823</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>1867</v>
+        <v>1824</v>
       </c>
       <c r="C20" s="7">
         <v>40</v>
@@ -14429,16 +12896,19 @@
       <c r="D20" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E20" s="87" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1">
+      <c r="E20" s="86">
+        <v>19</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18" customHeight="1">
       <c r="A21" s="48" t="s">
-        <v>1871</v>
+        <v>1352</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>1868</v>
+        <v>1826</v>
       </c>
       <c r="C21" s="7">
         <v>40</v>
@@ -14446,16 +12916,19 @@
       <c r="D21" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E21" s="87" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1">
+      <c r="E21" s="86">
+        <v>20</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1">
       <c r="A22" s="48" t="s">
-        <v>1872</v>
+        <v>1828</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>1869</v>
+        <v>1829</v>
       </c>
       <c r="C22" s="7">
         <v>40</v>
@@ -14463,16 +12936,19 @@
       <c r="D22" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E22" s="87" t="s">
-        <v>1877</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="18" customHeight="1">
+      <c r="E22" s="86">
+        <v>21</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="18" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="C23" s="7">
         <v>60</v>
@@ -14480,16 +12956,19 @@
       <c r="D23" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E23" s="86" t="s">
+      <c r="E23" s="86">
+        <v>22</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>1835</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="18" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>1827</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>1821</v>
       </c>
       <c r="C24" s="7">
         <v>60</v>
@@ -14497,16 +12976,19 @@
       <c r="D24" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E24" s="86" t="s">
+      <c r="E24" s="86">
+        <v>23</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>1836</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18" customHeight="1">
+    <row r="25" spans="1:6" ht="18" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>1828</v>
+        <v>1837</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1822</v>
+        <v>1838</v>
       </c>
       <c r="C25" s="7">
         <v>60</v>
@@ -14514,16 +12996,19 @@
       <c r="D25" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E25" s="86" t="s">
-        <v>1837</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="18" customHeight="1">
+      <c r="E25" s="86">
+        <v>24</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="18" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>1829</v>
+        <v>1840</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1823</v>
+        <v>1841</v>
       </c>
       <c r="C26" s="7">
         <v>60</v>
@@ -14531,16 +13016,19 @@
       <c r="D26" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E26" s="86" t="s">
-        <v>1838</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="18" customHeight="1">
+      <c r="E26" s="86">
+        <v>25</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="18" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>1830</v>
+        <v>1843</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>1824</v>
+        <v>1844</v>
       </c>
       <c r="C27" s="7">
         <v>60</v>
@@ -14548,16 +13036,19 @@
       <c r="D27" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E27" s="86" t="s">
-        <v>1839</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="18" customHeight="1">
+      <c r="E27" s="86">
+        <v>26</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>1831</v>
+        <v>1846</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>1825</v>
+        <v>1847</v>
       </c>
       <c r="C28" s="7">
         <v>60</v>
@@ -14565,16 +13056,19 @@
       <c r="D28" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E28" s="86" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="18" customHeight="1">
+      <c r="E28" s="86">
+        <v>27</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="18" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>1832</v>
+        <v>1849</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1826</v>
+        <v>1850</v>
       </c>
       <c r="C29" s="7">
         <v>60</v>
@@ -14582,16 +13076,19 @@
       <c r="D29" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E29" s="86" t="s">
-        <v>1841</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="18" customHeight="1">
+      <c r="E29" s="86">
+        <v>28</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>1843</v>
+        <v>1852</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1842</v>
+        <v>1853</v>
       </c>
       <c r="C30" s="7">
         <v>80</v>
@@ -14599,16 +13096,19 @@
       <c r="D30" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E30" s="86" t="s">
-        <v>1844</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="18" customHeight="1">
+      <c r="E30" s="86">
+        <v>29</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="18" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1845</v>
+        <v>1856</v>
       </c>
       <c r="C31" s="7">
         <v>80</v>
@@ -14616,16 +13116,19 @@
       <c r="D31" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E31" s="86" t="s">
+      <c r="E31" s="86">
+        <v>30</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18" customHeight="1">
+      <c r="A32" s="7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>1859</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="18" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>1846</v>
       </c>
       <c r="C32" s="7">
         <v>80</v>
@@ -14633,16 +13136,19 @@
       <c r="D32" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E32" s="86" t="s">
+      <c r="E32" s="86">
+        <v>31</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>1860</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="18" customHeight="1">
+    <row r="33" spans="1:6" ht="18" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>1854</v>
+        <v>1861</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>1847</v>
+        <v>1862</v>
       </c>
       <c r="C33" s="7">
         <v>80</v>
@@ -14650,16 +13156,19 @@
       <c r="D33" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E33" s="86" t="s">
-        <v>1861</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="18" customHeight="1">
+      <c r="E33" s="86">
+        <v>32</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="18" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>1855</v>
+        <v>1864</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>1848</v>
+        <v>1865</v>
       </c>
       <c r="C34" s="7">
         <v>80</v>
@@ -14667,16 +13176,19 @@
       <c r="D34" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E34" s="86" t="s">
-        <v>1862</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="18" customHeight="1">
+      <c r="E34" s="86">
+        <v>33</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="18" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>1856</v>
+        <v>1867</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>1849</v>
+        <v>1868</v>
       </c>
       <c r="C35" s="7">
         <v>80</v>
@@ -14684,16 +13196,19 @@
       <c r="D35" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E35" s="86" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="18" customHeight="1">
+      <c r="E35" s="86">
+        <v>34</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="18" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>1857</v>
+        <v>1870</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>1850</v>
+        <v>1871</v>
       </c>
       <c r="C36" s="7">
         <v>80</v>
@@ -14701,16 +13216,19 @@
       <c r="D36" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E36" s="86" t="s">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="18" customHeight="1">
+      <c r="E36" s="86">
+        <v>35</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1">
       <c r="A37" s="7" t="s">
-        <v>1858</v>
+        <v>1873</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>1851</v>
+        <v>1874</v>
       </c>
       <c r="C37" s="7">
         <v>80</v>
@@ -14718,110 +13236,125 @@
       <c r="D37" s="7" t="s">
         <v>1731</v>
       </c>
-      <c r="E37" s="86" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="18" customHeight="1">
+      <c r="E37" s="86">
+        <v>36</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-    </row>
-    <row r="39" spans="1:5" ht="18" customHeight="1">
+      <c r="E38" s="86"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" customHeight="1">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-    </row>
-    <row r="40" spans="1:5" ht="18" customHeight="1">
+      <c r="E39" s="86"/>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:6" ht="18" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" spans="1:5" ht="18" customHeight="1">
+      <c r="E40" s="86"/>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:6" ht="18" customHeight="1">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-    </row>
-    <row r="42" spans="1:5" ht="18" customHeight="1">
+      <c r="E41" s="86"/>
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" customHeight="1">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-    </row>
-    <row r="43" spans="1:5" ht="18" customHeight="1">
+      <c r="E42" s="86"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:6" ht="18" customHeight="1">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:5" ht="18" customHeight="1">
+      <c r="E43" s="86"/>
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="1:6" ht="18" customHeight="1">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-    </row>
-    <row r="45" spans="1:5" ht="18" customHeight="1">
+      <c r="E44" s="86"/>
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" spans="1:6" ht="18" customHeight="1">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46" spans="1:5" ht="18" customHeight="1">
+      <c r="E45" s="86"/>
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:6" ht="18" customHeight="1">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47" spans="1:5" ht="18" customHeight="1">
+      <c r="E46" s="86"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" spans="1:6" ht="18" customHeight="1">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-    </row>
-    <row r="48" spans="1:5" ht="18" customHeight="1">
+      <c r="E47" s="86"/>
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-    </row>
-    <row r="49" spans="1:5" ht="18" customHeight="1">
+      <c r="E48" s="86"/>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" ht="18" customHeight="1">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50" spans="1:5" ht="18" customHeight="1">
+      <c r="E49" s="86"/>
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6" ht="18" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-    </row>
-    <row r="51" spans="1:5" ht="18" customHeight="1">
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="1:6" ht="18" customHeight="1">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14845,8 +13378,8 @@
     <col min="16" max="18" width="8.375" style="46" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.75" style="46" customWidth="1"/>
     <col min="20" max="20" width="10" style="46" bestFit="1" customWidth="1"/>
-    <col min="21" max="32" width="9" style="47" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="47"/>
+    <col min="21" max="33" width="9" style="47" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="46" customFormat="1" ht="36" customHeight="1">
@@ -17127,7 +15660,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AA60" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17148,8 +15681,8 @@
     <col min="9" max="9" width="48" style="10" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="64" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="66" customWidth="1"/>
-    <col min="12" max="56" width="8.875" style="36" customWidth="1"/>
-    <col min="57" max="16384" width="8.875" style="36"/>
+    <col min="12" max="57" width="8.875" style="36" customWidth="1"/>
+    <col min="58" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -28911,14 +27444,14 @@
       <c r="K430" s="55"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="37" style="3" customWidth="1"/>
@@ -28926,10 +27459,11 @@
     <col min="3" max="3" width="29.5" style="7" customWidth="1"/>
     <col min="4" max="4" width="29.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="31.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.375" style="83" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.75" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1">
+    <row r="1" spans="1:7" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>919</v>
       </c>
@@ -28945,11 +27479,14 @@
       <c r="E1" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="85" t="s">
+        <v>1876</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="10" t="s">
         <v>925</v>
       </c>
@@ -28965,11 +27502,14 @@
       <c r="E2" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="86">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="10" t="s">
         <v>931</v>
       </c>
@@ -28985,11 +27525,14 @@
       <c r="E3" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="86">
+        <v>2</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="10" t="s">
         <v>935</v>
       </c>
@@ -29005,11 +27548,14 @@
       <c r="E4" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="86">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="10" t="s">
         <v>939</v>
       </c>
@@ -29025,11 +27571,14 @@
       <c r="E5" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="86">
+        <v>4</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="10" t="s">
         <v>942</v>
       </c>
@@ -29045,11 +27594,14 @@
       <c r="E6" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="86">
+        <v>5</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" s="10" t="s">
         <v>946</v>
       </c>
@@ -29065,11 +27617,14 @@
       <c r="E7" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="86">
+        <v>6</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="10" t="s">
         <v>951</v>
       </c>
@@ -29085,11 +27640,14 @@
       <c r="E8" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="86">
+        <v>7</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="10" t="s">
         <v>956</v>
       </c>
@@ -29105,11 +27663,14 @@
       <c r="E9" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="86">
+        <v>8</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="10" t="s">
         <v>960</v>
       </c>
@@ -29125,11 +27686,14 @@
       <c r="E10" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="86">
+        <v>9</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="10" t="s">
         <v>964</v>
       </c>
@@ -29145,11 +27709,14 @@
       <c r="E11" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="86">
+        <v>10</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" s="10" t="s">
         <v>968</v>
       </c>
@@ -29165,11 +27732,14 @@
       <c r="E12" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="86">
+        <v>11</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="10" t="s">
         <v>972</v>
       </c>
@@ -29185,11 +27755,14 @@
       <c r="E13" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="86">
+        <v>12</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="10" t="s">
         <v>976</v>
       </c>
@@ -29205,11 +27778,14 @@
       <c r="E14" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="86">
+        <v>13</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="10" t="s">
         <v>981</v>
       </c>
@@ -29225,11 +27801,14 @@
       <c r="E15" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="86">
+        <v>14</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" s="10" t="s">
         <v>985</v>
       </c>
@@ -29245,11 +27824,14 @@
       <c r="E16" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="86">
+        <v>15</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" s="10" t="s">
         <v>990</v>
       </c>
@@ -29265,11 +27847,14 @@
       <c r="E17" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="86">
+        <v>16</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" s="10" t="s">
         <v>995</v>
       </c>
@@ -29285,11 +27870,14 @@
       <c r="E18" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="86">
+        <v>17</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" s="10" t="s">
         <v>999</v>
       </c>
@@ -29305,11 +27893,14 @@
       <c r="E19" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="86">
+        <v>18</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>1003</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="10" t="s">
         <v>1004</v>
       </c>
@@ -29325,11 +27916,14 @@
       <c r="E20" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="86">
+        <v>19</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="10" t="s">
         <v>1008</v>
       </c>
@@ -29345,11 +27939,14 @@
       <c r="E21" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="86">
+        <v>20</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" s="10" t="s">
         <v>1013</v>
       </c>
@@ -29365,11 +27962,14 @@
       <c r="E22" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="86">
+        <v>21</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" s="10" t="s">
         <v>1016</v>
       </c>
@@ -29385,11 +27985,14 @@
       <c r="E23" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="86">
+        <v>22</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" s="10" t="s">
         <v>1021</v>
       </c>
@@ -29405,11 +28008,14 @@
       <c r="E24" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="86">
+        <v>23</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="10" t="s">
         <v>1026</v>
       </c>
@@ -29425,11 +28031,14 @@
       <c r="E25" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="86">
+        <v>24</v>
+      </c>
+      <c r="G25" s="10" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" s="10" t="s">
         <v>1031</v>
       </c>
@@ -29445,11 +28054,14 @@
       <c r="E26" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="86">
+        <v>25</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" s="10" t="s">
         <v>1036</v>
       </c>
@@ -29465,11 +28077,14 @@
       <c r="E27" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="86">
+        <v>26</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" s="44" t="s">
         <v>1040</v>
       </c>
@@ -29485,11 +28100,14 @@
       <c r="E28" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="86">
+        <v>27</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" s="10" t="s">
         <v>1045</v>
       </c>
@@ -29505,11 +28123,14 @@
       <c r="E29" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="86">
+        <v>28</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" s="10" t="s">
         <v>1049</v>
       </c>
@@ -29525,11 +28146,14 @@
       <c r="E30" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="86">
+        <v>29</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" s="10" t="s">
         <v>1052</v>
       </c>
@@ -29545,11 +28169,14 @@
       <c r="E31" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="86">
+        <v>30</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>1054</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" s="10" t="s">
         <v>1055</v>
       </c>
@@ -29565,11 +28192,14 @@
       <c r="E32" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="86">
+        <v>31</v>
+      </c>
+      <c r="G32" s="10" t="s">
         <v>1058</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" s="10" t="s">
         <v>1059</v>
       </c>
@@ -29585,11 +28215,14 @@
       <c r="E33" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="86">
+        <v>32</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>1063</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34" s="10" t="s">
         <v>1064</v>
       </c>
@@ -29605,11 +28238,14 @@
       <c r="E34" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="86">
+        <v>33</v>
+      </c>
+      <c r="G34" s="10" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:7">
       <c r="A35" s="10" t="s">
         <v>1069</v>
       </c>
@@ -29625,11 +28261,14 @@
       <c r="E35" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="86">
+        <v>34</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:7">
       <c r="A36" s="10" t="s">
         <v>1074</v>
       </c>
@@ -29645,11 +28284,14 @@
       <c r="E36" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="86">
+        <v>35</v>
+      </c>
+      <c r="G36" s="10" t="s">
         <v>1077</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:7">
       <c r="A37" s="44" t="s">
         <v>1078</v>
       </c>
@@ -29665,11 +28307,14 @@
       <c r="E37" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="86">
+        <v>36</v>
+      </c>
+      <c r="G37" s="10" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:7">
       <c r="A38" s="10" t="s">
         <v>1083</v>
       </c>
@@ -29685,11 +28330,14 @@
       <c r="E38" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="86">
+        <v>37</v>
+      </c>
+      <c r="G38" s="10" t="s">
         <v>1086</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:7">
       <c r="A39" s="10" t="s">
         <v>1087</v>
       </c>
@@ -29705,11 +28353,14 @@
       <c r="E39" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="86">
+        <v>38</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>1089</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:7">
       <c r="A40" s="10" t="s">
         <v>1090</v>
       </c>
@@ -29725,11 +28376,14 @@
       <c r="E40" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="86">
+        <v>39</v>
+      </c>
+      <c r="G40" s="10" t="s">
         <v>1094</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:7">
       <c r="A41" s="10" t="s">
         <v>1095</v>
       </c>
@@ -29745,11 +28399,14 @@
       <c r="E41" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="86">
+        <v>40</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:7">
       <c r="A42" s="10" t="s">
         <v>1100</v>
       </c>
@@ -29765,11 +28422,14 @@
       <c r="E42" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="86">
+        <v>41</v>
+      </c>
+      <c r="G42" s="10" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:7">
       <c r="A43" s="10" t="s">
         <v>1105</v>
       </c>
@@ -29785,11 +28445,14 @@
       <c r="E43" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="86">
+        <v>42</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:7">
       <c r="A44" s="10" t="s">
         <v>1110</v>
       </c>
@@ -29805,11 +28468,14 @@
       <c r="E44" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="86">
+        <v>43</v>
+      </c>
+      <c r="G44" s="10" t="s">
         <v>1114</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:7">
       <c r="A45" s="10" t="s">
         <v>1115</v>
       </c>
@@ -29825,11 +28491,14 @@
       <c r="E45" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="86">
+        <v>44</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>1117</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:7">
       <c r="A46" s="10" t="s">
         <v>1118</v>
       </c>
@@ -29845,11 +28514,14 @@
       <c r="E46" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="86">
+        <v>45</v>
+      </c>
+      <c r="G46" s="10" t="s">
         <v>1120</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:7">
       <c r="A47" s="44" t="s">
         <v>1121</v>
       </c>
@@ -29865,11 +28537,14 @@
       <c r="E47" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="86">
+        <v>46</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:7">
       <c r="A48" s="10" t="s">
         <v>1125</v>
       </c>
@@ -29885,11 +28560,14 @@
       <c r="E48" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="86">
+        <v>47</v>
+      </c>
+      <c r="G48" s="10" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:7">
       <c r="A49" s="10" t="s">
         <v>1130</v>
       </c>
@@ -29905,50 +28583,53 @@
       <c r="E49" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="86">
+        <v>48</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1">
+    <row r="50" spans="1:7" ht="15" customHeight="1">
       <c r="C50" s="25"/>
     </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1">
+    <row r="51" spans="1:7" ht="15" customHeight="1">
       <c r="C51" s="25"/>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1">
+    <row r="53" spans="1:7" ht="15" customHeight="1">
       <c r="C53" s="25"/>
     </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1">
+    <row r="54" spans="1:7" ht="15" customHeight="1">
       <c r="C54" s="25"/>
     </row>
-    <row r="55" spans="1:6" ht="15" customHeight="1">
+    <row r="55" spans="1:7" ht="15" customHeight="1">
       <c r="C55" s="25"/>
     </row>
-    <row r="56" spans="1:6" ht="15" customHeight="1">
+    <row r="56" spans="1:7" ht="15" customHeight="1">
       <c r="C56" s="25"/>
     </row>
-    <row r="57" spans="1:6" ht="15" customHeight="1">
+    <row r="57" spans="1:7" ht="15" customHeight="1">
       <c r="C57" s="25"/>
     </row>
-    <row r="58" spans="1:6" ht="15" customHeight="1">
+    <row r="58" spans="1:7" ht="15" customHeight="1">
       <c r="C58" s="25"/>
     </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1">
+    <row r="59" spans="1:7" ht="15" customHeight="1">
       <c r="C59" s="25"/>
     </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1">
+    <row r="60" spans="1:7" ht="15" customHeight="1">
       <c r="C60" s="25"/>
     </row>
-    <row r="61" spans="1:6" ht="15" customHeight="1">
+    <row r="61" spans="1:7" ht="15" customHeight="1">
       <c r="C61" s="25"/>
     </row>
-    <row r="62" spans="1:6" ht="15" customHeight="1">
+    <row r="62" spans="1:7" ht="15" customHeight="1">
       <c r="C62" s="25"/>
     </row>
-    <row r="63" spans="1:6" ht="15" customHeight="1">
+    <row r="63" spans="1:7" ht="15" customHeight="1">
       <c r="C63" s="25"/>
     </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1">
+    <row r="64" spans="1:7" ht="15" customHeight="1">
       <c r="C64" s="25"/>
     </row>
     <row r="65" spans="3:3" ht="15" customHeight="1">
@@ -30093,7 +28774,7 @@
       <c r="C114" s="24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -30126,8 +28807,8 @@
     <col min="27" max="27" width="5.125" style="35" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" customWidth="1"/>
-    <col min="30" max="130" width="9" style="9" customWidth="1"/>
-    <col min="131" max="16384" width="9" style="9"/>
+    <col min="30" max="131" width="9" style="9" customWidth="1"/>
+    <col min="132" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -30772,24 +29453,25 @@
       <c r="A50" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="25.5" style="3" customWidth="1"/>
     <col min="2" max="2" width="15.125" style="3" customWidth="1"/>
     <col min="3" max="3" width="21.375" style="3" customWidth="1"/>
     <col min="4" max="4" width="49.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.375" style="83" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1">
+    <row r="1" spans="1:6" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>1163</v>
       </c>
@@ -30802,11 +29484,14 @@
       <c r="D1" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="85" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1">
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>1166</v>
       </c>
@@ -30819,11 +29504,14 @@
       <c r="D2" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="86">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1">
+    <row r="3" spans="1:6" ht="18" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>1169</v>
       </c>
@@ -30836,11 +29524,14 @@
       <c r="D3" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="86">
+        <v>2</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1">
+    <row r="4" spans="1:6" ht="18" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>1171</v>
       </c>
@@ -30853,11 +29544,14 @@
       <c r="D4" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="86">
+        <v>3</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1">
+    <row r="5" spans="1:6" ht="18" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>1174</v>
       </c>
@@ -30870,11 +29564,14 @@
       <c r="D5" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="86">
+        <v>4</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>1175</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1">
+    <row r="6" spans="1:6" ht="18" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>1176</v>
       </c>
@@ -30887,11 +29584,14 @@
       <c r="D6" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="86">
+        <v>5</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>1177</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1">
+    <row r="7" spans="1:6" ht="18" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>1178</v>
       </c>
@@ -30904,11 +29604,14 @@
       <c r="D7" s="7" t="s">
         <v>1179</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="86">
+        <v>6</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>1180</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1">
+    <row r="8" spans="1:6" ht="18" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>1181</v>
       </c>
@@ -30921,11 +29624,14 @@
       <c r="D8" s="7" t="s">
         <v>1182</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="86">
+        <v>7</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1">
+    <row r="9" spans="1:6" ht="18" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>1184</v>
       </c>
@@ -30938,11 +29644,14 @@
       <c r="D9" s="7" t="s">
         <v>1182</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="86">
+        <v>8</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>1185</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1">
+    <row r="10" spans="1:6" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>1186</v>
       </c>
@@ -30955,11 +29664,14 @@
       <c r="D10" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="86">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>1188</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1">
+    <row r="11" spans="1:6" ht="18" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>1189</v>
       </c>
@@ -30972,11 +29684,14 @@
       <c r="D11" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="86">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>1191</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1">
+    <row r="12" spans="1:6" ht="18" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>1192</v>
       </c>
@@ -30989,11 +29704,14 @@
       <c r="D12" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="86">
+        <v>11</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>1193</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1">
+    <row r="13" spans="1:6" ht="18" customHeight="1">
       <c r="A13" s="7" t="s">
         <v>1194</v>
       </c>
@@ -31006,11 +29724,14 @@
       <c r="D13" s="7" t="s">
         <v>1195</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="86">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>1196</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1">
+    <row r="14" spans="1:6" ht="18" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>1197</v>
       </c>
@@ -31023,11 +29744,14 @@
       <c r="D14" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="86">
+        <v>13</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>1198</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1">
+    <row r="15" spans="1:6" ht="18" customHeight="1">
       <c r="A15" s="7" t="s">
         <v>1199</v>
       </c>
@@ -31040,11 +29764,14 @@
       <c r="D15" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="86">
+        <v>14</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>1200</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1">
+    <row r="16" spans="1:6" ht="18" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>1201</v>
       </c>
@@ -31057,11 +29784,14 @@
       <c r="D16" s="7" t="s">
         <v>1202</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="86">
+        <v>15</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1">
+    <row r="17" spans="1:6" ht="18" customHeight="1">
       <c r="A17" s="7" t="s">
         <v>1204</v>
       </c>
@@ -31074,11 +29804,14 @@
       <c r="D17" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="86">
+        <v>16</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>1205</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1">
+    <row r="18" spans="1:6" ht="18" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>1206</v>
       </c>
@@ -31091,11 +29824,14 @@
       <c r="D18" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="86">
+        <v>17</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>1207</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1">
+    <row r="19" spans="1:6" ht="18" customHeight="1">
       <c r="A19" s="7" t="s">
         <v>1208</v>
       </c>
@@ -31108,11 +29844,14 @@
       <c r="D19" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="86">
+        <v>18</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>1209</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1">
+    <row r="20" spans="1:6" ht="18" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>1210</v>
       </c>
@@ -31125,11 +29864,14 @@
       <c r="D20" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="86">
+        <v>19</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>1211</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1">
+    <row r="21" spans="1:6" ht="18" customHeight="1">
       <c r="A21" s="7" t="s">
         <v>1212</v>
       </c>
@@ -31142,11 +29884,14 @@
       <c r="D21" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="86">
+        <v>20</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>1213</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1">
+    <row r="22" spans="1:6" ht="18" customHeight="1">
       <c r="A22" s="7" t="s">
         <v>1214</v>
       </c>
@@ -31159,11 +29904,14 @@
       <c r="D22" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="86">
+        <v>21</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>1215</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="18" customHeight="1">
+    <row r="23" spans="1:6" ht="18" customHeight="1">
       <c r="A23" s="7" t="s">
         <v>1216</v>
       </c>
@@ -31176,11 +29924,14 @@
       <c r="D23" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="86">
+        <v>22</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>1217</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="18" customHeight="1">
+    <row r="24" spans="1:6" ht="18" customHeight="1">
       <c r="A24" s="7" t="s">
         <v>1218</v>
       </c>
@@ -31193,11 +29944,14 @@
       <c r="D24" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="86">
+        <v>23</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18" customHeight="1">
+    <row r="25" spans="1:6" ht="18" customHeight="1">
       <c r="A25" s="7" t="s">
         <v>1220</v>
       </c>
@@ -31210,11 +29964,14 @@
       <c r="D25" s="7" t="s">
         <v>1221</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="86">
+        <v>24</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>1222</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="18" customHeight="1">
+    <row r="26" spans="1:6" ht="18" customHeight="1">
       <c r="A26" s="7" t="s">
         <v>1223</v>
       </c>
@@ -31227,11 +29984,14 @@
       <c r="D26" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="86">
+        <v>25</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>1224</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18" customHeight="1">
+    <row r="27" spans="1:6" ht="18" customHeight="1">
       <c r="A27" s="7" t="s">
         <v>1225</v>
       </c>
@@ -31244,11 +30004,14 @@
       <c r="D27" s="7" t="s">
         <v>1226</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="86">
+        <v>26</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>1227</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="18" customHeight="1">
+    <row r="28" spans="1:6" ht="18" customHeight="1">
       <c r="A28" s="11" t="s">
         <v>1228</v>
       </c>
@@ -31261,11 +30024,14 @@
       <c r="D28" s="11" t="s">
         <v>1229</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="86">
+        <v>27</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>1230</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="18" customHeight="1">
+    <row r="29" spans="1:6" ht="18" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>1231</v>
       </c>
@@ -31278,11 +30044,14 @@
       <c r="D29" s="7" t="s">
         <v>1182</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="86">
+        <v>28</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>1232</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="18" customHeight="1">
+    <row r="30" spans="1:6" ht="18" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>1233</v>
       </c>
@@ -31295,11 +30064,14 @@
       <c r="D30" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="86">
+        <v>29</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>1234</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="18" customHeight="1">
+    <row r="31" spans="1:6" ht="18" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>1235</v>
       </c>
@@ -31312,11 +30084,14 @@
       <c r="D31" s="7" t="s">
         <v>1195</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="86">
+        <v>30</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>1236</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="18" customHeight="1">
+    <row r="32" spans="1:6" ht="18" customHeight="1">
       <c r="A32" s="7" t="s">
         <v>1237</v>
       </c>
@@ -31329,11 +30104,14 @@
       <c r="D32" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="86">
+        <v>31</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="18" customHeight="1">
+    <row r="33" spans="1:6" ht="18" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>1240</v>
       </c>
@@ -31346,11 +30124,14 @@
       <c r="D33" s="7" t="s">
         <v>1241</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="86">
+        <v>32</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="18" customHeight="1">
+    <row r="34" spans="1:6" ht="18" customHeight="1">
       <c r="A34" s="7" t="s">
         <v>1243</v>
       </c>
@@ -31363,11 +30144,14 @@
       <c r="D34" s="7" t="s">
         <v>1244</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="86">
+        <v>33</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="18" customHeight="1">
+    <row r="35" spans="1:6" ht="18" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>1246</v>
       </c>
@@ -31380,11 +30164,14 @@
       <c r="D35" s="7" t="s">
         <v>1244</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="86">
+        <v>34</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>1247</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="18" customHeight="1">
+    <row r="36" spans="1:6" ht="18" customHeight="1">
       <c r="A36" s="7" t="s">
         <v>1248</v>
       </c>
@@ -31397,11 +30184,14 @@
       <c r="D36" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="86">
+        <v>35</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>1249</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="18" customHeight="1">
+    <row r="37" spans="1:6" ht="18" customHeight="1">
       <c r="A37" s="11" t="s">
         <v>1250</v>
       </c>
@@ -31414,11 +30204,14 @@
       <c r="D37" s="11" t="s">
         <v>1229</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="86">
+        <v>36</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>1251</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="18" customHeight="1">
+    <row r="38" spans="1:6" ht="18" customHeight="1">
       <c r="A38" s="7" t="s">
         <v>1252</v>
       </c>
@@ -31431,11 +30224,14 @@
       <c r="D38" s="7" t="s">
         <v>1253</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="86">
+        <v>37</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>1254</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="18" customHeight="1">
+    <row r="39" spans="1:6" ht="18" customHeight="1">
       <c r="A39" s="7" t="s">
         <v>1255</v>
       </c>
@@ -31448,11 +30244,14 @@
       <c r="D39" s="7" t="s">
         <v>1256</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="86">
+        <v>38</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>1257</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="18" customHeight="1">
+    <row r="40" spans="1:6" ht="18" customHeight="1">
       <c r="A40" s="7" t="s">
         <v>1258</v>
       </c>
@@ -31465,11 +30264,14 @@
       <c r="D40" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="86">
+        <v>39</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>1259</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="18" customHeight="1">
+    <row r="41" spans="1:6" ht="18" customHeight="1">
       <c r="A41" s="7" t="s">
         <v>1260</v>
       </c>
@@ -31482,11 +30284,14 @@
       <c r="D41" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="86">
+        <v>40</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>1262</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="18" customHeight="1">
+    <row r="42" spans="1:6" ht="18" customHeight="1">
       <c r="A42" s="7" t="s">
         <v>1263</v>
       </c>
@@ -31499,11 +30304,14 @@
       <c r="D42" s="7" t="s">
         <v>1221</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="86">
+        <v>41</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>1264</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="18" customHeight="1">
+    <row r="43" spans="1:6" ht="18" customHeight="1">
       <c r="A43" s="7" t="s">
         <v>1265</v>
       </c>
@@ -31516,11 +30324,14 @@
       <c r="D43" s="7" t="s">
         <v>1182</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="86">
+        <v>42</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>1266</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="18" customHeight="1">
+    <row r="44" spans="1:6" ht="18" customHeight="1">
       <c r="A44" s="7" t="s">
         <v>1267</v>
       </c>
@@ -31533,11 +30344,14 @@
       <c r="D44" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="86">
+        <v>43</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>1268</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="18" customHeight="1">
+    <row r="45" spans="1:6" ht="18" customHeight="1">
       <c r="A45" s="7" t="s">
         <v>1269</v>
       </c>
@@ -31550,11 +30364,14 @@
       <c r="D45" s="7" t="s">
         <v>1244</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="86">
+        <v>44</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>1270</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="18" customHeight="1">
+    <row r="46" spans="1:6" ht="18" customHeight="1">
       <c r="A46" s="7" t="s">
         <v>1271</v>
       </c>
@@ -31567,11 +30384,14 @@
       <c r="D46" s="7" t="s">
         <v>1272</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="86">
+        <v>45</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>1273</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="18" customHeight="1">
+    <row r="47" spans="1:6" ht="18" customHeight="1">
       <c r="A47" s="11" t="s">
         <v>1274</v>
       </c>
@@ -31584,11 +30404,14 @@
       <c r="D47" s="11" t="s">
         <v>1244</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="86">
+        <v>46</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="18" customHeight="1">
+    <row r="48" spans="1:6" ht="18" customHeight="1">
       <c r="A48" s="7" t="s">
         <v>1276</v>
       </c>
@@ -31601,11 +30424,14 @@
       <c r="D48" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="86">
+        <v>47</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="18" customHeight="1">
+    <row r="49" spans="1:6" ht="18" customHeight="1">
       <c r="A49" s="7" t="s">
         <v>1278</v>
       </c>
@@ -31618,32 +30444,35 @@
       <c r="D49" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="86">
+        <v>48</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>1279</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="18" customHeight="1">
+    <row r="50" spans="1:6" ht="18" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-    </row>
-    <row r="51" spans="1:5" ht="18" customHeight="1">
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="1:6" ht="18" customHeight="1">
       <c r="C51" s="7"/>
     </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1"/>
-    <row r="54" spans="1:5" ht="15" customHeight="1"/>
-    <row r="55" spans="1:5" ht="15" customHeight="1"/>
-    <row r="56" spans="1:5" ht="15" customHeight="1"/>
-    <row r="57" spans="1:5" ht="15" customHeight="1"/>
-    <row r="58" spans="1:5" ht="15" customHeight="1"/>
-    <row r="59" spans="1:5" ht="15" customHeight="1"/>
-    <row r="60" spans="1:5" ht="15" customHeight="1"/>
-    <row r="61" spans="1:5" ht="15" customHeight="1"/>
-    <row r="62" spans="1:5" ht="15" customHeight="1"/>
-    <row r="63" spans="1:5" ht="15" customHeight="1"/>
-    <row r="64" spans="1:5" ht="15" customHeight="1"/>
+    <row r="53" spans="1:6" ht="15" customHeight="1"/>
+    <row r="54" spans="1:6" ht="15" customHeight="1"/>
+    <row r="55" spans="1:6" ht="15" customHeight="1"/>
+    <row r="56" spans="1:6" ht="15" customHeight="1"/>
+    <row r="57" spans="1:6" ht="15" customHeight="1"/>
+    <row r="58" spans="1:6" ht="15" customHeight="1"/>
+    <row r="59" spans="1:6" ht="15" customHeight="1"/>
+    <row r="60" spans="1:6" ht="15" customHeight="1"/>
+    <row r="61" spans="1:6" ht="15" customHeight="1"/>
+    <row r="62" spans="1:6" ht="15" customHeight="1"/>
+    <row r="63" spans="1:6" ht="15" customHeight="1"/>
+    <row r="64" spans="1:6" ht="15" customHeight="1"/>
     <row r="65" ht="15" customHeight="1"/>
     <row r="66" ht="15" customHeight="1"/>
     <row r="67" ht="15" customHeight="1"/>
@@ -31692,7 +30521,7 @@
     <row r="112" ht="15" customHeight="1"/>
     <row r="114" ht="15" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -39904,14 +38733,14 @@
       <c r="F357" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="16.25" style="7" customWidth="1"/>
@@ -39922,13 +38751,14 @@
     <col min="6" max="6" width="10.5" style="7" customWidth="1"/>
     <col min="7" max="7" width="11.125" style="7" customWidth="1"/>
     <col min="8" max="8" width="24.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="41.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="7" customWidth="1"/>
-    <col min="11" max="11" width="14.25" style="7" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="83" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.75" style="7" customWidth="1"/>
+    <col min="12" max="12" width="14.25" style="7" customWidth="1"/>
+    <col min="13" max="13" width="8.875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>1281</v>
       </c>
@@ -39953,17 +38783,20 @@
       <c r="H1" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="85" t="s">
+        <v>1876</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="L1" s="39" t="s">
         <v>1521</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="M1" s="39" t="s">
         <v>1522</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="7" t="s">
         <v>1287</v>
       </c>
@@ -39988,20 +38821,23 @@
       <c r="H2" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="86">
+        <v>1</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>1528</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>1529</v>
       </c>
-      <c r="K2" s="7">
+      <c r="L2" s="7">
         <v>4</v>
       </c>
-      <c r="L2" s="7">
+      <c r="M2" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="7" t="s">
         <v>1291</v>
       </c>
@@ -40026,20 +38862,23 @@
       <c r="H3" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="86">
+        <v>2</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>1532</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="K3" s="7">
+      <c r="L3" s="7">
         <v>4</v>
       </c>
-      <c r="L3" s="7">
+      <c r="M3" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="7" t="s">
         <v>1294</v>
       </c>
@@ -40064,20 +38903,23 @@
       <c r="H4" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="86">
+        <v>3</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>1537</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>1538</v>
       </c>
-      <c r="K4" s="7">
+      <c r="L4" s="7">
         <v>4</v>
       </c>
-      <c r="L4" s="7">
+      <c r="M4" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="7" t="s">
         <v>1297</v>
       </c>
@@ -40102,20 +38944,23 @@
       <c r="H5" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="86">
+        <v>4</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>1542</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K5" s="7">
+      <c r="L5" s="7">
         <v>2</v>
       </c>
-      <c r="L5" s="7">
+      <c r="M5" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
         <v>1300</v>
       </c>
@@ -40140,20 +38985,23 @@
       <c r="H6" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="86">
+        <v>5</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>1546</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K6" s="7">
+      <c r="L6" s="7">
         <v>5</v>
       </c>
-      <c r="L6" s="7">
+      <c r="M6" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
         <v>1302</v>
       </c>
@@ -40178,20 +39026,23 @@
       <c r="H7" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="86">
+        <v>6</v>
+      </c>
+      <c r="J7" s="25" t="s">
         <v>1549</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>1550</v>
       </c>
-      <c r="K7" s="7">
-        <v>1</v>
-      </c>
       <c r="L7" s="7">
+        <v>1</v>
+      </c>
+      <c r="M7" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="7" t="s">
         <v>1304</v>
       </c>
@@ -40216,20 +39067,23 @@
       <c r="H8" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="86">
+        <v>7</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>1552</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="K8" s="7" t="s">
         <v>1538</v>
       </c>
-      <c r="K8" s="7">
+      <c r="L8" s="7">
         <v>2</v>
       </c>
-      <c r="L8" s="7">
+      <c r="M8" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="7" t="s">
         <v>1306</v>
       </c>
@@ -40254,20 +39108,23 @@
       <c r="H9" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="86">
+        <v>8</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>1553</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="K9" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K9" s="7">
+      <c r="L9" s="7">
         <v>8</v>
       </c>
-      <c r="L9" s="7">
+      <c r="M9" s="7">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
         <v>1309</v>
       </c>
@@ -40292,20 +39149,23 @@
       <c r="H10" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="86">
+        <v>9</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>1555</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="K10" s="7" t="s">
         <v>1556</v>
       </c>
-      <c r="K10" s="7">
+      <c r="L10" s="7">
         <v>7</v>
       </c>
-      <c r="L10" s="7">
+      <c r="M10" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="7" t="s">
         <v>1311</v>
       </c>
@@ -40330,20 +39190,23 @@
       <c r="H11" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="86">
+        <v>10</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>1557</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>1529</v>
       </c>
-      <c r="K11" s="7">
+      <c r="L11" s="7">
         <v>4</v>
       </c>
-      <c r="L11" s="7">
+      <c r="M11" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="7" t="s">
         <v>1313</v>
       </c>
@@ -40368,20 +39231,23 @@
       <c r="H12" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="86">
+        <v>11</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>1559</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="K12" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K12" s="7">
+      <c r="L12" s="7">
         <v>3</v>
       </c>
-      <c r="L12" s="7">
+      <c r="M12" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
         <v>1315</v>
       </c>
@@ -40406,20 +39272,23 @@
       <c r="H13" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="86">
+        <v>12</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>1561</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="K13" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K13" s="7">
+      <c r="L13" s="7">
         <v>3</v>
       </c>
-      <c r="L13" s="7">
+      <c r="M13" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="A14" s="7" t="s">
         <v>1317</v>
       </c>
@@ -40444,20 +39313,23 @@
       <c r="H14" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="86">
+        <v>13</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>1563</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="K14" s="7" t="s">
         <v>1564</v>
       </c>
-      <c r="K14" s="7">
+      <c r="L14" s="7">
         <v>2</v>
       </c>
-      <c r="L14" s="7">
+      <c r="M14" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
         <v>1319</v>
       </c>
@@ -40482,20 +39354,23 @@
       <c r="H15" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="86">
+        <v>14</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>1566</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="K15" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K15" s="7">
+      <c r="L15" s="7">
         <v>4</v>
       </c>
-      <c r="L15" s="7">
+      <c r="M15" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
         <v>1321</v>
       </c>
@@ -40520,20 +39395,23 @@
       <c r="H16" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="86">
+        <v>15</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>1567</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="K16" s="7" t="s">
         <v>1529</v>
       </c>
-      <c r="K16" s="7">
+      <c r="L16" s="7">
         <v>2</v>
       </c>
-      <c r="L16" s="7">
+      <c r="M16" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
         <v>1323</v>
       </c>
@@ -40558,20 +39436,23 @@
       <c r="H17" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="86">
+        <v>16</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>1569</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="K17" s="7" t="s">
         <v>1570</v>
       </c>
-      <c r="K17" s="7">
+      <c r="L17" s="7">
         <v>2</v>
       </c>
-      <c r="L17" s="7">
+      <c r="M17" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
         <v>1325</v>
       </c>
@@ -40596,20 +39477,23 @@
       <c r="H18" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="86">
+        <v>17</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>1572</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="K18" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K18" s="7">
+      <c r="L18" s="7">
         <v>3</v>
       </c>
-      <c r="L18" s="7">
+      <c r="M18" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
         <v>1327</v>
       </c>
@@ -40634,20 +39518,23 @@
       <c r="H19" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="86">
+        <v>18</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>1574</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="K19" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K19" s="7">
+      <c r="L19" s="7">
         <v>6</v>
       </c>
-      <c r="L19" s="7">
+      <c r="M19" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:13">
       <c r="A20" s="7" t="s">
         <v>1329</v>
       </c>
@@ -40672,20 +39559,23 @@
       <c r="H20" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="86">
+        <v>19</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>1576</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="K20" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K20" s="7">
+      <c r="L20" s="7">
         <v>12</v>
       </c>
-      <c r="L20" s="7">
+      <c r="M20" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
         <v>1331</v>
       </c>
@@ -40710,20 +39600,23 @@
       <c r="H21" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="86">
+        <v>20</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>1578</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="K21" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K21" s="7">
+      <c r="L21" s="7">
         <v>4</v>
       </c>
-      <c r="L21" s="7">
+      <c r="M21" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
         <v>1333</v>
       </c>
@@ -40748,20 +39641,23 @@
       <c r="H22" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="86">
+        <v>21</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>1580</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="K22" s="7" t="s">
         <v>1581</v>
       </c>
-      <c r="K22" s="7">
-        <v>1</v>
-      </c>
       <c r="L22" s="7">
+        <v>1</v>
+      </c>
+      <c r="M22" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
         <v>1335</v>
       </c>
@@ -40786,20 +39682,23 @@
       <c r="H23" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="86">
+        <v>22</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>1582</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="K23" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K23" s="7">
+      <c r="L23" s="7">
         <v>3</v>
       </c>
-      <c r="L23" s="7">
+      <c r="M23" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
         <v>26</v>
       </c>
@@ -40824,20 +39723,23 @@
       <c r="H24" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="86">
+        <v>23</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>1584</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="K24" s="7" t="s">
         <v>1585</v>
       </c>
-      <c r="K24" s="7">
+      <c r="L24" s="7">
         <v>5</v>
       </c>
-      <c r="L24" s="7">
+      <c r="M24" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
         <v>1337</v>
       </c>
@@ -40862,20 +39764,23 @@
       <c r="H25" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="86">
+        <v>24</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>1586</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="K25" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K25" s="7">
+      <c r="L25" s="7">
         <v>5</v>
       </c>
-      <c r="L25" s="7">
+      <c r="M25" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
         <v>24</v>
       </c>
@@ -40900,20 +39805,23 @@
       <c r="H26" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="86">
+        <v>25</v>
+      </c>
+      <c r="J26" s="7" t="s">
         <v>1587</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="K26" s="7" t="s">
         <v>1581</v>
       </c>
-      <c r="K26" s="7">
+      <c r="L26" s="7">
         <v>3</v>
       </c>
-      <c r="L26" s="7">
+      <c r="M26" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
         <v>1339</v>
       </c>
@@ -40938,20 +39846,23 @@
       <c r="H27" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="86">
+        <v>26</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>1589</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="K27" s="7" t="s">
         <v>1590</v>
       </c>
-      <c r="K27" s="7">
+      <c r="L27" s="7">
         <v>5</v>
       </c>
-      <c r="L27" s="7">
+      <c r="M27" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
         <v>1341</v>
       </c>
@@ -40976,20 +39887,23 @@
       <c r="H28" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="86">
+        <v>27</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>1592</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="K28" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K28" s="7">
+      <c r="L28" s="7">
         <v>4</v>
       </c>
-      <c r="L28" s="7">
+      <c r="M28" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
         <v>1343</v>
       </c>
@@ -41014,20 +39928,23 @@
       <c r="H29" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="86">
+        <v>28</v>
+      </c>
+      <c r="J29" s="7" t="s">
         <v>1593</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="K29" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K29" s="7">
+      <c r="L29" s="7">
         <v>7</v>
       </c>
-      <c r="L29" s="7">
+      <c r="M29" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:13">
       <c r="A30" s="10" t="s">
         <v>1345</v>
       </c>
@@ -41052,20 +39969,23 @@
       <c r="H30" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="86">
+        <v>29</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>1596</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="K30" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K30" s="7">
+      <c r="L30" s="7">
         <v>6</v>
       </c>
-      <c r="L30" s="7">
+      <c r="M30" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:13">
       <c r="A31" s="7" t="s">
         <v>1347</v>
       </c>
@@ -41090,20 +40010,23 @@
       <c r="H31" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="86">
+        <v>30</v>
+      </c>
+      <c r="J31" s="7" t="s">
         <v>1598</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="K31" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K31" s="7">
+      <c r="L31" s="7">
         <v>5</v>
       </c>
-      <c r="L31" s="7">
+      <c r="M31" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:13">
       <c r="A32" s="7" t="s">
         <v>1349</v>
       </c>
@@ -41128,20 +40051,23 @@
       <c r="H32" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="86">
+        <v>31</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>1602</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="K32" s="7" t="s">
         <v>1585</v>
       </c>
-      <c r="K32" s="7">
+      <c r="L32" s="7">
         <v>7</v>
       </c>
-      <c r="L32" s="7">
+      <c r="M32" s="7">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:13">
       <c r="A33" s="7" t="s">
         <v>1351</v>
       </c>
@@ -41166,20 +40092,23 @@
       <c r="H33" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="86">
+        <v>32</v>
+      </c>
+      <c r="J33" s="7" t="s">
         <v>1603</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="K33" s="7" t="s">
         <v>1604</v>
       </c>
-      <c r="K33" s="7">
+      <c r="L33" s="7">
         <v>3</v>
       </c>
-      <c r="L33" s="7">
+      <c r="M33" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:13">
       <c r="A34" s="10" t="s">
         <v>1354</v>
       </c>
@@ -41204,20 +40133,23 @@
       <c r="H34" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I34" s="86">
+        <v>33</v>
+      </c>
+      <c r="J34" s="7" t="s">
         <v>1606</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="K34" s="7" t="s">
         <v>1607</v>
       </c>
-      <c r="K34" s="7">
-        <v>1</v>
-      </c>
       <c r="L34" s="7">
+        <v>1</v>
+      </c>
+      <c r="M34" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:13">
       <c r="A35" s="10" t="s">
         <v>1356</v>
       </c>
@@ -41242,20 +40174,23 @@
       <c r="H35" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I35" s="86">
+        <v>34</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>1609</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="K35" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K35" s="7">
+      <c r="L35" s="7">
         <v>5</v>
       </c>
-      <c r="L35" s="7">
+      <c r="M35" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:13">
       <c r="A36" s="10" t="s">
         <v>1358</v>
       </c>
@@ -41280,20 +40215,23 @@
       <c r="H36" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I36" s="86">
+        <v>35</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>1610</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="K36" s="7" t="s">
         <v>1611</v>
       </c>
-      <c r="K36" s="7">
-        <v>1</v>
-      </c>
       <c r="L36" s="7">
+        <v>1</v>
+      </c>
+      <c r="M36" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:13">
       <c r="A37" s="7" t="s">
         <v>1360</v>
       </c>
@@ -41318,20 +40256,23 @@
       <c r="H37" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I37" s="86">
+        <v>36</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>1612</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="K37" s="7" t="s">
         <v>1613</v>
       </c>
-      <c r="K37" s="7">
+      <c r="L37" s="7">
         <v>2</v>
       </c>
-      <c r="L37" s="7">
+      <c r="M37" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:13">
       <c r="A38" s="7" t="s">
         <v>1362</v>
       </c>
@@ -41356,20 +40297,23 @@
       <c r="H38" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I38" s="86">
+        <v>37</v>
+      </c>
+      <c r="J38" s="7" t="s">
         <v>1615</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="K38" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K38" s="7">
+      <c r="L38" s="7">
         <v>7</v>
       </c>
-      <c r="L38" s="7">
+      <c r="M38" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:13">
       <c r="A39" s="7" t="s">
         <v>1364</v>
       </c>
@@ -41394,20 +40338,23 @@
       <c r="H39" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="I39" s="86">
+        <v>38</v>
+      </c>
+      <c r="J39" s="7" t="s">
         <v>1616</v>
       </c>
-      <c r="J39" s="7" t="s">
+      <c r="K39" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K39" s="7">
+      <c r="L39" s="7">
         <v>7</v>
       </c>
-      <c r="L39" s="7">
+      <c r="M39" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:13">
       <c r="A40" s="7" t="s">
         <v>1366</v>
       </c>
@@ -41432,20 +40379,23 @@
       <c r="H40" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I40" s="86">
+        <v>39</v>
+      </c>
+      <c r="J40" s="7" t="s">
         <v>1618</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="K40" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K40" s="7">
+      <c r="L40" s="7">
         <v>8</v>
       </c>
-      <c r="L40" s="7">
+      <c r="M40" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:13">
       <c r="A41" s="7" t="s">
         <v>1368</v>
       </c>
@@ -41470,20 +40420,23 @@
       <c r="H41" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="I41" s="86">
+        <v>40</v>
+      </c>
+      <c r="J41" s="7" t="s">
         <v>1620</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="K41" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K41" s="7">
+      <c r="L41" s="7">
         <v>7</v>
       </c>
-      <c r="L41" s="7">
+      <c r="M41" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:13">
       <c r="A42" s="7" t="s">
         <v>1370</v>
       </c>
@@ -41508,20 +40461,23 @@
       <c r="H42" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="I42" s="86">
+        <v>41</v>
+      </c>
+      <c r="J42" s="7" t="s">
         <v>1621</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="K42" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K42" s="7">
+      <c r="L42" s="7">
         <v>8</v>
       </c>
-      <c r="L42" s="7">
+      <c r="M42" s="7">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:13">
       <c r="A43" s="7" t="s">
         <v>1372</v>
       </c>
@@ -41546,20 +40502,23 @@
       <c r="H43" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I43" s="86">
+        <v>42</v>
+      </c>
+      <c r="J43" s="7" t="s">
         <v>1622</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="K43" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K43" s="7">
+      <c r="L43" s="7">
         <v>4</v>
       </c>
-      <c r="L43" s="7">
+      <c r="M43" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:13">
       <c r="A44" s="10" t="s">
         <v>1373</v>
       </c>
@@ -41584,20 +40543,23 @@
       <c r="H44" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="I44" s="86">
+        <v>43</v>
+      </c>
+      <c r="J44" s="7" t="s">
         <v>1623</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="K44" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K44" s="7">
+      <c r="L44" s="7">
         <v>60</v>
       </c>
-      <c r="L44" s="7">
+      <c r="M44" s="7">
         <v>91</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:13">
       <c r="A45" s="10" t="s">
         <v>1375</v>
       </c>
@@ -41622,20 +40584,23 @@
       <c r="H45" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="I45" s="86">
+        <v>44</v>
+      </c>
+      <c r="J45" s="7" t="s">
         <v>1625</v>
       </c>
-      <c r="J45" s="7" t="s">
+      <c r="K45" s="7" t="s">
         <v>1556</v>
       </c>
-      <c r="K45" s="7">
+      <c r="L45" s="7">
         <v>10</v>
       </c>
-      <c r="L45" s="7">
+      <c r="M45" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:13">
       <c r="A46" s="10" t="s">
         <v>1377</v>
       </c>
@@ -41660,20 +40625,23 @@
       <c r="H46" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I46" s="7" t="s">
+      <c r="I46" s="86">
+        <v>45</v>
+      </c>
+      <c r="J46" s="7" t="s">
         <v>1627</v>
       </c>
-      <c r="J46" s="7" t="s">
+      <c r="K46" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K46" s="7">
+      <c r="L46" s="7">
         <v>8</v>
       </c>
-      <c r="L46" s="7">
+      <c r="M46" s="7">
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:13">
       <c r="A47" s="10" t="s">
         <v>1379</v>
       </c>
@@ -41698,20 +40666,23 @@
       <c r="H47" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I47" s="7" t="s">
+      <c r="I47" s="86">
+        <v>46</v>
+      </c>
+      <c r="J47" s="7" t="s">
         <v>1628</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="K47" s="7" t="s">
         <v>1556</v>
       </c>
-      <c r="K47" s="7">
+      <c r="L47" s="7">
         <v>6</v>
       </c>
-      <c r="L47" s="7">
+      <c r="M47" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:13">
       <c r="A48" s="10" t="s">
         <v>1381</v>
       </c>
@@ -41736,20 +40707,23 @@
       <c r="H48" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="I48" s="86">
+        <v>47</v>
+      </c>
+      <c r="J48" s="7" t="s">
         <v>1629</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="K48" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K48" s="7">
+      <c r="L48" s="7">
         <v>5</v>
       </c>
-      <c r="L48" s="7">
+      <c r="M48" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:13">
       <c r="A49" s="10" t="s">
         <v>1383</v>
       </c>
@@ -41774,20 +40748,23 @@
       <c r="H49" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="I49" s="86">
+        <v>48</v>
+      </c>
+      <c r="J49" s="7" t="s">
         <v>1630</v>
       </c>
-      <c r="J49" s="7" t="s">
+      <c r="K49" s="7" t="s">
         <v>1556</v>
       </c>
-      <c r="K49" s="7">
+      <c r="L49" s="7">
         <v>9</v>
       </c>
-      <c r="L49" s="7">
+      <c r="M49" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:13">
       <c r="A50" s="10" t="s">
         <v>1385</v>
       </c>
@@ -41812,20 +40789,23 @@
       <c r="H50" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="I50" s="86">
+        <v>49</v>
+      </c>
+      <c r="J50" s="7" t="s">
         <v>1631</v>
       </c>
-      <c r="J50" s="7" t="s">
+      <c r="K50" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K50" s="7">
+      <c r="L50" s="7">
         <v>7</v>
       </c>
-      <c r="L50" s="7">
+      <c r="M50" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:13">
       <c r="A51" s="10" t="s">
         <v>1387</v>
       </c>
@@ -41850,20 +40830,23 @@
       <c r="H51" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I51" s="86">
+        <v>50</v>
+      </c>
+      <c r="J51" s="7" t="s">
         <v>1632</v>
       </c>
-      <c r="J51" s="7" t="s">
+      <c r="K51" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K51" s="7">
+      <c r="L51" s="7">
         <v>7</v>
       </c>
-      <c r="L51" s="7">
+      <c r="M51" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:13">
       <c r="A52" s="10" t="s">
         <v>1389</v>
       </c>
@@ -41888,20 +40871,23 @@
       <c r="H52" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="I52" s="86">
+        <v>51</v>
+      </c>
+      <c r="J52" s="7" t="s">
         <v>1633</v>
       </c>
-      <c r="J52" s="7" t="s">
+      <c r="K52" s="7" t="s">
         <v>1634</v>
       </c>
-      <c r="K52" s="7">
+      <c r="L52" s="7">
         <v>2</v>
       </c>
-      <c r="L52" s="7">
+      <c r="M52" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:13">
       <c r="A53" s="10" t="s">
         <v>1391</v>
       </c>
@@ -41926,20 +40912,23 @@
       <c r="H53" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="I53" s="86">
+        <v>52</v>
+      </c>
+      <c r="J53" s="7" t="s">
         <v>1635</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="K53" s="7" t="s">
         <v>1585</v>
       </c>
-      <c r="K53" s="7">
+      <c r="L53" s="7">
         <v>8</v>
       </c>
-      <c r="L53" s="7">
+      <c r="M53" s="7">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:13">
       <c r="A54" s="10" t="s">
         <v>1393</v>
       </c>
@@ -41964,20 +40953,23 @@
       <c r="H54" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I54" s="7" t="s">
+      <c r="I54" s="86">
+        <v>53</v>
+      </c>
+      <c r="J54" s="7" t="s">
         <v>1636</v>
       </c>
-      <c r="J54" s="7" t="s">
+      <c r="K54" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K54" s="7">
+      <c r="L54" s="7">
         <v>7</v>
       </c>
-      <c r="L54" s="7">
+      <c r="M54" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:13">
       <c r="A55" s="10" t="s">
         <v>1395</v>
       </c>
@@ -42002,20 +40994,23 @@
       <c r="H55" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="I55" s="86">
+        <v>54</v>
+      </c>
+      <c r="J55" s="7" t="s">
         <v>1638</v>
       </c>
-      <c r="J55" s="7" t="s">
+      <c r="K55" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K55" s="7">
+      <c r="L55" s="7">
         <v>6</v>
       </c>
-      <c r="L55" s="7">
+      <c r="M55" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:13">
       <c r="A56" s="10" t="s">
         <v>1397</v>
       </c>
@@ -42040,20 +41035,23 @@
       <c r="H56" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="I56" s="86">
+        <v>55</v>
+      </c>
+      <c r="J56" s="7" t="s">
         <v>1639</v>
       </c>
-      <c r="J56" s="7" t="s">
+      <c r="K56" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K56" s="7">
+      <c r="L56" s="7">
         <v>5</v>
       </c>
-      <c r="L56" s="7">
+      <c r="M56" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:13">
       <c r="A57" s="10" t="s">
         <v>1399</v>
       </c>
@@ -42078,20 +41076,23 @@
       <c r="H57" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I57" s="7" t="s">
+      <c r="I57" s="86">
+        <v>56</v>
+      </c>
+      <c r="J57" s="7" t="s">
         <v>1640</v>
       </c>
-      <c r="J57" s="7" t="s">
+      <c r="K57" s="7" t="s">
         <v>1550</v>
       </c>
-      <c r="K57" s="7">
+      <c r="L57" s="7">
         <v>3</v>
       </c>
-      <c r="L57" s="7">
+      <c r="M57" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:13">
       <c r="A58" s="10" t="s">
         <v>1401</v>
       </c>
@@ -42116,20 +41117,23 @@
       <c r="H58" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I58" s="7" t="s">
+      <c r="I58" s="86">
+        <v>57</v>
+      </c>
+      <c r="J58" s="7" t="s">
         <v>1641</v>
       </c>
-      <c r="J58" s="7" t="s">
+      <c r="K58" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K58" s="7">
+      <c r="L58" s="7">
         <v>8</v>
       </c>
-      <c r="L58" s="7">
+      <c r="M58" s="7">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:13">
       <c r="A59" s="10" t="s">
         <v>1403</v>
       </c>
@@ -42154,20 +41158,23 @@
       <c r="H59" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="I59" s="86">
+        <v>58</v>
+      </c>
+      <c r="J59" s="7" t="s">
         <v>1642</v>
       </c>
-      <c r="J59" s="7" t="s">
+      <c r="K59" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K59" s="7">
+      <c r="L59" s="7">
         <v>5</v>
       </c>
-      <c r="L59" s="7">
+      <c r="M59" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:13">
       <c r="A60" s="10" t="s">
         <v>1405</v>
       </c>
@@ -42192,20 +41199,23 @@
       <c r="H60" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="I60" s="86">
+        <v>59</v>
+      </c>
+      <c r="J60" s="7" t="s">
         <v>1643</v>
       </c>
-      <c r="J60" s="7" t="s">
+      <c r="K60" s="7" t="s">
         <v>1644</v>
       </c>
-      <c r="K60" s="7">
+      <c r="L60" s="7">
         <v>7</v>
       </c>
-      <c r="L60" s="7">
+      <c r="M60" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:13">
       <c r="A61" s="10" t="s">
         <v>1407</v>
       </c>
@@ -42230,20 +41240,23 @@
       <c r="H61" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I61" s="7" t="s">
+      <c r="I61" s="86">
+        <v>60</v>
+      </c>
+      <c r="J61" s="7" t="s">
         <v>1645</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="K61" s="11" t="s">
         <v>1646</v>
       </c>
-      <c r="K61" s="7">
+      <c r="L61" s="7">
         <v>4</v>
       </c>
-      <c r="L61" s="7">
+      <c r="M61" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:13">
       <c r="A62" s="10" t="s">
         <v>1409</v>
       </c>
@@ -42268,20 +41281,23 @@
       <c r="H62" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I62" s="7" t="s">
+      <c r="I62" s="86">
+        <v>61</v>
+      </c>
+      <c r="J62" s="7" t="s">
         <v>1648</v>
       </c>
-      <c r="J62" s="7" t="s">
+      <c r="K62" s="7" t="s">
         <v>1649</v>
       </c>
-      <c r="K62" s="7">
+      <c r="L62" s="7">
         <v>5</v>
       </c>
-      <c r="L62" s="7">
+      <c r="M62" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:13">
       <c r="A63" s="10" t="s">
         <v>1411</v>
       </c>
@@ -42306,20 +41322,23 @@
       <c r="H63" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I63" s="7" t="s">
+      <c r="I63" s="86">
+        <v>62</v>
+      </c>
+      <c r="J63" s="7" t="s">
         <v>1651</v>
       </c>
-      <c r="J63" s="7" t="s">
+      <c r="K63" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K63" s="7">
+      <c r="L63" s="7">
         <v>10</v>
       </c>
-      <c r="L63" s="7">
+      <c r="M63" s="7">
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:13">
       <c r="A64" s="10" t="s">
         <v>1413</v>
       </c>
@@ -42344,20 +41363,23 @@
       <c r="H64" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I64" s="7" t="s">
+      <c r="I64" s="86">
+        <v>63</v>
+      </c>
+      <c r="J64" s="7" t="s">
         <v>1652</v>
       </c>
-      <c r="J64" s="7" t="s">
+      <c r="K64" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K64" s="7">
+      <c r="L64" s="7">
         <v>5</v>
       </c>
-      <c r="L64" s="7">
+      <c r="M64" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:13">
       <c r="A65" s="10" t="s">
         <v>1415</v>
       </c>
@@ -42382,20 +41404,23 @@
       <c r="H65" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I65" s="7" t="s">
+      <c r="I65" s="86">
+        <v>64</v>
+      </c>
+      <c r="J65" s="7" t="s">
         <v>1653</v>
       </c>
-      <c r="J65" s="7" t="s">
+      <c r="K65" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K65" s="7">
+      <c r="L65" s="7">
         <v>5</v>
       </c>
-      <c r="L65" s="7">
+      <c r="M65" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:13">
       <c r="A66" s="10" t="s">
         <v>1417</v>
       </c>
@@ -42420,20 +41445,23 @@
       <c r="H66" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I66" s="7" t="s">
+      <c r="I66" s="86">
+        <v>65</v>
+      </c>
+      <c r="J66" s="7" t="s">
         <v>1654</v>
       </c>
-      <c r="J66" s="7" t="s">
+      <c r="K66" s="7" t="s">
         <v>1655</v>
       </c>
-      <c r="K66" s="7">
+      <c r="L66" s="7">
         <v>3</v>
       </c>
-      <c r="L66" s="7">
+      <c r="M66" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:13">
       <c r="A67" s="10" t="s">
         <v>1419</v>
       </c>
@@ -42458,20 +41486,23 @@
       <c r="H67" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I67" s="7" t="s">
+      <c r="I67" s="86">
+        <v>66</v>
+      </c>
+      <c r="J67" s="7" t="s">
         <v>1656</v>
       </c>
-      <c r="J67" s="7" t="s">
+      <c r="K67" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K67" s="7">
+      <c r="L67" s="7">
         <v>6</v>
       </c>
-      <c r="L67" s="7">
+      <c r="M67" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:13">
       <c r="A68" s="10" t="s">
         <v>1421</v>
       </c>
@@ -42496,20 +41527,23 @@
       <c r="H68" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I68" s="7" t="s">
+      <c r="I68" s="86">
+        <v>67</v>
+      </c>
+      <c r="J68" s="7" t="s">
         <v>1658</v>
       </c>
-      <c r="J68" s="7" t="s">
+      <c r="K68" s="7" t="s">
         <v>1556</v>
       </c>
-      <c r="K68" s="7">
+      <c r="L68" s="7">
         <v>8</v>
       </c>
-      <c r="L68" s="7">
+      <c r="M68" s="7">
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:13">
       <c r="A69" s="10" t="s">
         <v>1423</v>
       </c>
@@ -42534,20 +41568,23 @@
       <c r="H69" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I69" s="7" t="s">
+      <c r="I69" s="86">
+        <v>68</v>
+      </c>
+      <c r="J69" s="7" t="s">
         <v>1660</v>
       </c>
-      <c r="J69" s="7" t="s">
+      <c r="K69" s="7" t="s">
         <v>1570</v>
       </c>
-      <c r="K69" s="7">
+      <c r="L69" s="7">
         <v>4</v>
       </c>
-      <c r="L69" s="7">
+      <c r="M69" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:13">
       <c r="A70" s="10" t="s">
         <v>1425</v>
       </c>
@@ -42572,20 +41609,23 @@
       <c r="H70" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I70" s="7" t="s">
+      <c r="I70" s="86">
+        <v>69</v>
+      </c>
+      <c r="J70" s="7" t="s">
         <v>1661</v>
       </c>
-      <c r="J70" s="7" t="s">
+      <c r="K70" s="7" t="s">
         <v>1662</v>
       </c>
-      <c r="K70" s="7">
+      <c r="L70" s="7">
         <v>9</v>
       </c>
-      <c r="L70" s="7">
+      <c r="M70" s="7">
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:13">
       <c r="A71" s="10" t="s">
         <v>1427</v>
       </c>
@@ -42610,20 +41650,23 @@
       <c r="H71" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I71" s="7" t="s">
+      <c r="I71" s="86">
+        <v>70</v>
+      </c>
+      <c r="J71" s="7" t="s">
         <v>1663</v>
       </c>
-      <c r="J71" s="7" t="s">
+      <c r="K71" s="7" t="s">
         <v>1590</v>
       </c>
-      <c r="K71" s="7">
+      <c r="L71" s="7">
         <v>8</v>
       </c>
-      <c r="L71" s="7">
+      <c r="M71" s="7">
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:13">
       <c r="A72" s="10" t="s">
         <v>1429</v>
       </c>
@@ -42648,20 +41691,23 @@
       <c r="H72" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I72" s="7" t="s">
+      <c r="I72" s="86">
+        <v>71</v>
+      </c>
+      <c r="J72" s="7" t="s">
         <v>1666</v>
       </c>
-      <c r="J72" s="7" t="s">
+      <c r="K72" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K72" s="7">
+      <c r="L72" s="7">
         <v>14</v>
       </c>
-      <c r="L72" s="7">
+      <c r="M72" s="7">
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:13">
       <c r="A73" s="10" t="s">
         <v>1431</v>
       </c>
@@ -42686,20 +41732,23 @@
       <c r="H73" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I73" s="7" t="s">
+      <c r="I73" s="86">
+        <v>72</v>
+      </c>
+      <c r="J73" s="7" t="s">
         <v>1667</v>
       </c>
-      <c r="J73" s="7" t="s">
+      <c r="K73" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="K73" s="7">
+      <c r="L73" s="7">
         <v>13</v>
       </c>
-      <c r="L73" s="7">
+      <c r="M73" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:13">
       <c r="A74" s="10" t="s">
         <v>1433</v>
       </c>
@@ -42724,20 +41773,23 @@
       <c r="H74" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I74" s="7" t="s">
+      <c r="I74" s="86">
+        <v>73</v>
+      </c>
+      <c r="J74" s="7" t="s">
         <v>1668</v>
       </c>
-      <c r="J74" s="7" t="s">
+      <c r="K74" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K74" s="7">
+      <c r="L74" s="7">
         <v>9</v>
       </c>
-      <c r="L74" s="7">
+      <c r="M74" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:13">
       <c r="A75" s="10" t="s">
         <v>1435</v>
       </c>
@@ -42762,20 +41814,23 @@
       <c r="H75" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I75" s="7" t="s">
+      <c r="I75" s="86">
+        <v>74</v>
+      </c>
+      <c r="J75" s="7" t="s">
         <v>1669</v>
       </c>
-      <c r="J75" s="7" t="s">
+      <c r="K75" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="K75" s="7">
+      <c r="L75" s="7">
         <v>12</v>
       </c>
-      <c r="L75" s="7">
+      <c r="M75" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:13">
       <c r="A76" s="10" t="s">
         <v>1437</v>
       </c>
@@ -42800,20 +41855,23 @@
       <c r="H76" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I76" s="7" t="s">
+      <c r="I76" s="86">
+        <v>75</v>
+      </c>
+      <c r="J76" s="7" t="s">
         <v>1670</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="K76" s="11" t="s">
         <v>1538</v>
       </c>
-      <c r="K76" s="7">
+      <c r="L76" s="7">
         <v>6</v>
       </c>
-      <c r="L76" s="7">
+      <c r="M76" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:13">
       <c r="A77" s="10" t="s">
         <v>1439</v>
       </c>
@@ -42838,20 +41896,23 @@
       <c r="H77" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I77" s="7" t="s">
+      <c r="I77" s="86">
+        <v>76</v>
+      </c>
+      <c r="J77" s="7" t="s">
         <v>1671</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="K77" s="11" t="s">
         <v>1529</v>
       </c>
-      <c r="K77" s="7">
+      <c r="L77" s="7">
         <v>7</v>
       </c>
-      <c r="L77" s="7">
+      <c r="M77" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:13">
       <c r="A78" s="7" t="s">
         <v>1441</v>
       </c>
@@ -42876,20 +41937,23 @@
       <c r="H78" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I78" s="7" t="s">
+      <c r="I78" s="86">
+        <v>77</v>
+      </c>
+      <c r="J78" s="7" t="s">
         <v>1672</v>
       </c>
-      <c r="J78" s="7" t="s">
+      <c r="K78" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K78" s="7">
+      <c r="L78" s="7">
         <v>6</v>
       </c>
-      <c r="L78" s="7">
+      <c r="M78" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:13">
       <c r="A79" s="10" t="s">
         <v>1443</v>
       </c>
@@ -42914,20 +41978,23 @@
       <c r="H79" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I79" s="7" t="s">
+      <c r="I79" s="86">
+        <v>78</v>
+      </c>
+      <c r="J79" s="7" t="s">
         <v>1674</v>
       </c>
-      <c r="J79" s="7" t="s">
+      <c r="K79" s="7" t="s">
         <v>1556</v>
       </c>
-      <c r="K79" s="7">
+      <c r="L79" s="7">
         <v>7</v>
       </c>
-      <c r="L79" s="7">
+      <c r="M79" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:13">
       <c r="A80" s="10" t="s">
         <v>1445</v>
       </c>
@@ -42952,20 +42019,23 @@
       <c r="H80" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I80" s="7" t="s">
+      <c r="I80" s="86">
+        <v>79</v>
+      </c>
+      <c r="J80" s="7" t="s">
         <v>1675</v>
       </c>
-      <c r="J80" s="7" t="s">
+      <c r="K80" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K80" s="7">
+      <c r="L80" s="7">
         <v>6</v>
       </c>
-      <c r="L80" s="7">
+      <c r="M80" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:13">
       <c r="A81" s="10" t="s">
         <v>1447</v>
       </c>
@@ -42990,20 +42060,23 @@
       <c r="H81" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I81" s="7" t="s">
+      <c r="I81" s="86">
+        <v>80</v>
+      </c>
+      <c r="J81" s="7" t="s">
         <v>1676</v>
       </c>
-      <c r="J81" s="7" t="s">
+      <c r="K81" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K81" s="7">
+      <c r="L81" s="7">
         <v>10</v>
       </c>
-      <c r="L81" s="7">
+      <c r="M81" s="7">
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:13">
       <c r="A82" s="10" t="s">
         <v>1449</v>
       </c>
@@ -43028,20 +42101,23 @@
       <c r="H82" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I82" s="7" t="s">
+      <c r="I82" s="86">
+        <v>81</v>
+      </c>
+      <c r="J82" s="7" t="s">
         <v>1678</v>
       </c>
-      <c r="J82" s="7" t="s">
+      <c r="K82" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K82" s="7">
+      <c r="L82" s="7">
         <v>8</v>
       </c>
-      <c r="L82" s="7">
+      <c r="M82" s="7">
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:13">
       <c r="A83" s="10" t="s">
         <v>1451</v>
       </c>
@@ -43066,20 +42142,23 @@
       <c r="H83" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I83" s="7" t="s">
+      <c r="I83" s="86">
+        <v>82</v>
+      </c>
+      <c r="J83" s="7" t="s">
         <v>1679</v>
       </c>
-      <c r="J83" s="7" t="s">
+      <c r="K83" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="K83" s="7">
+      <c r="L83" s="7">
         <v>8</v>
       </c>
-      <c r="L83" s="7">
+      <c r="M83" s="7">
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:13">
       <c r="A84" s="10" t="s">
         <v>1453</v>
       </c>
@@ -43104,20 +42183,23 @@
       <c r="H84" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I84" s="7" t="s">
+      <c r="I84" s="86">
+        <v>83</v>
+      </c>
+      <c r="J84" s="7" t="s">
         <v>1680</v>
       </c>
-      <c r="J84" s="7" t="s">
+      <c r="K84" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K84" s="7">
+      <c r="L84" s="7">
         <v>12</v>
       </c>
-      <c r="L84" s="7">
+      <c r="M84" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:13">
       <c r="A85" s="10" t="s">
         <v>1455</v>
       </c>
@@ -43142,20 +42224,23 @@
       <c r="H85" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I85" s="7" t="s">
+      <c r="I85" s="86">
+        <v>84</v>
+      </c>
+      <c r="J85" s="7" t="s">
         <v>1681</v>
       </c>
-      <c r="J85" s="7" t="s">
+      <c r="K85" s="7" t="s">
         <v>1655</v>
       </c>
-      <c r="K85" s="7">
+      <c r="L85" s="7">
         <v>5</v>
       </c>
-      <c r="L85" s="7">
+      <c r="M85" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:13">
       <c r="A86" s="10" t="s">
         <v>1457</v>
       </c>
@@ -43180,20 +42265,23 @@
       <c r="H86" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I86" s="7" t="s">
+      <c r="I86" s="86">
+        <v>85</v>
+      </c>
+      <c r="J86" s="7" t="s">
         <v>1682</v>
       </c>
-      <c r="J86" s="7" t="s">
+      <c r="K86" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K86" s="7">
+      <c r="L86" s="7">
         <v>10</v>
       </c>
-      <c r="L86" s="7">
+      <c r="M86" s="7">
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:13">
       <c r="A87" s="10" t="s">
         <v>1459</v>
       </c>
@@ -43218,20 +42306,23 @@
       <c r="H87" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I87" s="7" t="s">
+      <c r="I87" s="86">
+        <v>86</v>
+      </c>
+      <c r="J87" s="7" t="s">
         <v>1683</v>
       </c>
-      <c r="J87" s="7" t="s">
+      <c r="K87" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K87" s="7">
+      <c r="L87" s="7">
         <v>8</v>
       </c>
-      <c r="L87" s="7">
+      <c r="M87" s="7">
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:13">
       <c r="A88" s="10" t="s">
         <v>1461</v>
       </c>
@@ -43256,20 +42347,23 @@
       <c r="H88" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I88" s="7" t="s">
+      <c r="I88" s="86">
+        <v>87</v>
+      </c>
+      <c r="J88" s="7" t="s">
         <v>1684</v>
       </c>
-      <c r="J88" s="7" t="s">
+      <c r="K88" s="7" t="s">
         <v>1662</v>
       </c>
-      <c r="K88" s="7">
+      <c r="L88" s="7">
         <v>5</v>
       </c>
-      <c r="L88" s="7">
+      <c r="M88" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:13">
       <c r="A89" s="10" t="s">
         <v>1463</v>
       </c>
@@ -43294,20 +42388,23 @@
       <c r="H89" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I89" s="7" t="s">
+      <c r="I89" s="86">
+        <v>88</v>
+      </c>
+      <c r="J89" s="7" t="s">
         <v>1686</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="K89" s="11" t="s">
         <v>1556</v>
       </c>
-      <c r="K89" s="7">
+      <c r="L89" s="7">
         <v>5</v>
       </c>
-      <c r="L89" s="7">
+      <c r="M89" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:13">
       <c r="A90" s="10" t="s">
         <v>1465</v>
       </c>
@@ -43332,20 +42429,23 @@
       <c r="H90" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I90" s="7" t="s">
+      <c r="I90" s="86">
+        <v>89</v>
+      </c>
+      <c r="J90" s="7" t="s">
         <v>1687</v>
       </c>
-      <c r="J90" s="7" t="s">
+      <c r="K90" s="7" t="s">
         <v>1646</v>
       </c>
-      <c r="K90" s="7">
+      <c r="L90" s="7">
         <v>2</v>
       </c>
-      <c r="L90" s="7">
+      <c r="M90" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:13">
       <c r="A91" s="10" t="s">
         <v>1467</v>
       </c>
@@ -43370,20 +42470,23 @@
       <c r="H91" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I91" s="7" t="s">
+      <c r="I91" s="86">
+        <v>90</v>
+      </c>
+      <c r="J91" s="7" t="s">
         <v>1688</v>
       </c>
-      <c r="J91" s="7" t="s">
+      <c r="K91" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K91" s="7">
+      <c r="L91" s="7">
         <v>8</v>
       </c>
-      <c r="L91" s="7">
+      <c r="M91" s="7">
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:13">
       <c r="A92" s="10" t="s">
         <v>1469</v>
       </c>
@@ -43408,20 +42511,23 @@
       <c r="H92" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I92" s="7" t="s">
+      <c r="I92" s="86">
+        <v>91</v>
+      </c>
+      <c r="J92" s="7" t="s">
         <v>1689</v>
       </c>
-      <c r="J92" s="7" t="s">
+      <c r="K92" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="K92" s="7">
+      <c r="L92" s="7">
         <v>8</v>
       </c>
-      <c r="L92" s="7">
+      <c r="M92" s="7">
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:13">
       <c r="A93" s="10" t="s">
         <v>1471</v>
       </c>
@@ -43446,20 +42552,23 @@
       <c r="H93" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I93" s="7" t="s">
+      <c r="I93" s="86">
+        <v>92</v>
+      </c>
+      <c r="J93" s="7" t="s">
         <v>1690</v>
       </c>
-      <c r="J93" s="7" t="s">
+      <c r="K93" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="K93" s="7">
+      <c r="L93" s="7">
         <v>75</v>
       </c>
-      <c r="L93" s="7">
+      <c r="M93" s="7">
         <v>106</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:13">
       <c r="A94" s="10" t="s">
         <v>1473</v>
       </c>
@@ -43484,20 +42593,23 @@
       <c r="H94" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I94" s="7" t="s">
+      <c r="I94" s="86">
+        <v>93</v>
+      </c>
+      <c r="J94" s="7" t="s">
         <v>1692</v>
       </c>
-      <c r="J94" s="7" t="s">
+      <c r="K94" s="7" t="s">
         <v>1662</v>
       </c>
-      <c r="K94" s="7">
+      <c r="L94" s="7">
         <v>6</v>
       </c>
-      <c r="L94" s="7">
+      <c r="M94" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:13">
       <c r="A95" s="10" t="s">
         <v>1475</v>
       </c>
@@ -43522,20 +42634,23 @@
       <c r="H95" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I95" s="7" t="s">
+      <c r="I95" s="86">
+        <v>94</v>
+      </c>
+      <c r="J95" s="7" t="s">
         <v>1693</v>
       </c>
-      <c r="J95" s="11" t="s">
+      <c r="K95" s="11" t="s">
         <v>1694</v>
       </c>
-      <c r="K95" s="7">
+      <c r="L95" s="7">
         <v>9</v>
       </c>
-      <c r="L95" s="7">
+      <c r="M95" s="7">
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:13">
       <c r="A96" s="10" t="s">
         <v>1477</v>
       </c>
@@ -43560,20 +42675,23 @@
       <c r="H96" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I96" s="7" t="s">
+      <c r="I96" s="86">
+        <v>95</v>
+      </c>
+      <c r="J96" s="7" t="s">
         <v>1695</v>
       </c>
-      <c r="J96" s="7" t="s">
+      <c r="K96" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K96" s="7">
+      <c r="L96" s="7">
         <v>7</v>
       </c>
-      <c r="L96" s="7">
+      <c r="M96" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:13">
       <c r="A97" s="10" t="s">
         <v>1479</v>
       </c>
@@ -43598,20 +42716,23 @@
       <c r="H97" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I97" s="7" t="s">
+      <c r="I97" s="86">
+        <v>96</v>
+      </c>
+      <c r="J97" s="7" t="s">
         <v>1696</v>
       </c>
-      <c r="J97" s="7" t="s">
+      <c r="K97" s="7" t="s">
         <v>1577</v>
       </c>
-      <c r="K97" s="7">
+      <c r="L97" s="7">
         <v>11</v>
       </c>
-      <c r="L97" s="7">
+      <c r="M97" s="7">
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:13">
       <c r="A98" s="10" t="s">
         <v>1481</v>
       </c>
@@ -43636,20 +42757,23 @@
       <c r="H98" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I98" s="7" t="s">
+      <c r="I98" s="86">
+        <v>97</v>
+      </c>
+      <c r="J98" s="7" t="s">
         <v>1697</v>
       </c>
-      <c r="J98" s="7" t="s">
+      <c r="K98" s="7" t="s">
         <v>1644</v>
       </c>
-      <c r="K98" s="7">
+      <c r="L98" s="7">
         <v>7</v>
       </c>
-      <c r="L98" s="7">
+      <c r="M98" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:13">
       <c r="A99" s="10" t="s">
         <v>1483</v>
       </c>
@@ -43674,20 +42798,23 @@
       <c r="H99" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I99" s="7" t="s">
+      <c r="I99" s="86">
+        <v>98</v>
+      </c>
+      <c r="J99" s="7" t="s">
         <v>1698</v>
       </c>
-      <c r="J99" s="7" t="s">
+      <c r="K99" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K99" s="7">
+      <c r="L99" s="7">
         <v>11</v>
       </c>
-      <c r="L99" s="7">
+      <c r="M99" s="7">
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:13">
       <c r="A100" s="7" t="s">
         <v>1485</v>
       </c>
@@ -43712,20 +42839,23 @@
       <c r="H100" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I100" s="7" t="s">
+      <c r="I100" s="86">
+        <v>99</v>
+      </c>
+      <c r="J100" s="7" t="s">
         <v>1699</v>
       </c>
-      <c r="J100" s="7" t="s">
+      <c r="K100" s="7" t="s">
         <v>1529</v>
       </c>
-      <c r="K100" s="7">
+      <c r="L100" s="7">
         <v>5</v>
       </c>
-      <c r="L100" s="7">
+      <c r="M100" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:13">
       <c r="A101" s="10" t="s">
         <v>1487</v>
       </c>
@@ -43750,20 +42880,23 @@
       <c r="H101" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I101" s="7" t="s">
+      <c r="I101" s="86">
+        <v>100</v>
+      </c>
+      <c r="J101" s="7" t="s">
         <v>1701</v>
       </c>
-      <c r="J101" s="43" t="s">
+      <c r="K101" s="43" t="s">
         <v>1702</v>
       </c>
-      <c r="K101" s="7">
+      <c r="L101" s="7">
         <v>28</v>
       </c>
-      <c r="L101" s="7">
+      <c r="M101" s="7">
         <v>43</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:13">
       <c r="A102" s="10" t="s">
         <v>1489</v>
       </c>
@@ -43788,20 +42921,23 @@
       <c r="H102" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I102" s="7" t="s">
+      <c r="I102" s="86">
+        <v>101</v>
+      </c>
+      <c r="J102" s="7" t="s">
         <v>1704</v>
       </c>
-      <c r="J102" s="7" t="s">
+      <c r="K102" s="7" t="s">
         <v>1573</v>
       </c>
-      <c r="K102" s="7">
+      <c r="L102" s="7">
         <v>10</v>
       </c>
-      <c r="L102" s="7">
+      <c r="M102" s="7">
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:13">
       <c r="A103" s="10" t="s">
         <v>1491</v>
       </c>
@@ -43826,20 +42962,23 @@
       <c r="H103" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I103" s="7" t="s">
+      <c r="I103" s="86">
+        <v>102</v>
+      </c>
+      <c r="J103" s="7" t="s">
         <v>1705</v>
       </c>
-      <c r="J103" s="7" t="s">
+      <c r="K103" s="7" t="s">
         <v>1585</v>
       </c>
-      <c r="K103" s="7">
+      <c r="L103" s="7">
         <v>16</v>
       </c>
-      <c r="L103" s="7">
+      <c r="M103" s="7">
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:13">
       <c r="A104" s="10" t="s">
         <v>1493</v>
       </c>
@@ -43864,20 +43003,23 @@
       <c r="H104" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I104" s="7" t="s">
+      <c r="I104" s="86">
+        <v>103</v>
+      </c>
+      <c r="J104" s="7" t="s">
         <v>1707</v>
       </c>
-      <c r="J104" s="7" t="s">
+      <c r="K104" s="7" t="s">
         <v>1708</v>
       </c>
-      <c r="K104" s="7">
+      <c r="L104" s="7">
         <v>50</v>
       </c>
-      <c r="L104" s="7">
+      <c r="M104" s="7">
         <v>75</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:13">
       <c r="A105" s="10" t="s">
         <v>1495</v>
       </c>
@@ -43902,20 +43044,23 @@
       <c r="H105" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I105" s="7" t="s">
+      <c r="I105" s="86">
+        <v>104</v>
+      </c>
+      <c r="J105" s="7" t="s">
         <v>1709</v>
       </c>
-      <c r="J105" s="7" t="s">
+      <c r="K105" s="7" t="s">
         <v>1710</v>
       </c>
-      <c r="K105" s="7">
+      <c r="L105" s="7">
         <v>55</v>
       </c>
-      <c r="L105" s="7">
+      <c r="M105" s="7">
         <v>82</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:13">
       <c r="A106" s="10" t="s">
         <v>1497</v>
       </c>
@@ -43940,20 +43085,23 @@
       <c r="H106" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I106" s="7" t="s">
+      <c r="I106" s="86">
+        <v>105</v>
+      </c>
+      <c r="J106" s="7" t="s">
         <v>1711</v>
       </c>
-      <c r="J106" s="7" t="s">
+      <c r="K106" s="7" t="s">
         <v>1554</v>
       </c>
-      <c r="K106" s="7">
+      <c r="L106" s="7">
         <v>12</v>
       </c>
-      <c r="L106" s="7">
+      <c r="M106" s="7">
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:13">
       <c r="A107" s="10" t="s">
         <v>1499</v>
       </c>
@@ -43978,20 +43126,23 @@
       <c r="H107" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I107" s="7" t="s">
+      <c r="I107" s="86">
+        <v>106</v>
+      </c>
+      <c r="J107" s="7" t="s">
         <v>1712</v>
       </c>
-      <c r="J107" s="7" t="s">
+      <c r="K107" s="7" t="s">
         <v>1556</v>
       </c>
-      <c r="K107" s="7">
+      <c r="L107" s="7">
         <v>11</v>
       </c>
-      <c r="L107" s="7">
+      <c r="M107" s="7">
         <v>19</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:13">
       <c r="A108" s="10" t="s">
         <v>1501</v>
       </c>
@@ -44016,20 +43167,23 @@
       <c r="H108" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I108" s="7" t="s">
+      <c r="I108" s="86">
+        <v>107</v>
+      </c>
+      <c r="J108" s="7" t="s">
         <v>1713</v>
       </c>
-      <c r="J108" s="7" t="s">
+      <c r="K108" s="7" t="s">
         <v>1649</v>
       </c>
-      <c r="K108" s="7">
+      <c r="L108" s="7">
         <v>5</v>
       </c>
-      <c r="L108" s="7">
+      <c r="M108" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:13">
       <c r="A109" s="10" t="s">
         <v>1503</v>
       </c>
@@ -44054,20 +43208,23 @@
       <c r="H109" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I109" s="7" t="s">
+      <c r="I109" s="86">
+        <v>108</v>
+      </c>
+      <c r="J109" s="7" t="s">
         <v>1714</v>
       </c>
-      <c r="J109" s="43" t="s">
+      <c r="K109" s="43" t="s">
         <v>1702</v>
       </c>
-      <c r="K109" s="7">
+      <c r="L109" s="7">
         <v>8</v>
       </c>
-      <c r="L109" s="7">
+      <c r="M109" s="7">
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:13">
       <c r="A110" s="10" t="s">
         <v>1505</v>
       </c>
@@ -44092,20 +43249,23 @@
       <c r="H110" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I110" s="7" t="s">
+      <c r="I110" s="86">
+        <v>109</v>
+      </c>
+      <c r="J110" s="7" t="s">
         <v>1715</v>
       </c>
-      <c r="J110" s="7" t="s">
+      <c r="K110" s="7" t="s">
         <v>1716</v>
       </c>
-      <c r="K110" s="7">
+      <c r="L110" s="7">
         <v>4</v>
       </c>
-      <c r="L110" s="7">
+      <c r="M110" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:13">
       <c r="A111" s="10" t="s">
         <v>1507</v>
       </c>
@@ -44130,20 +43290,23 @@
       <c r="H111" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I111" s="7" t="s">
+      <c r="I111" s="86">
+        <v>110</v>
+      </c>
+      <c r="J111" s="7" t="s">
         <v>1718</v>
       </c>
-      <c r="J111" s="7" t="s">
+      <c r="K111" s="7" t="s">
         <v>1649</v>
       </c>
-      <c r="K111" s="7">
+      <c r="L111" s="7">
         <v>7</v>
       </c>
-      <c r="L111" s="7">
+      <c r="M111" s="7">
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:13">
       <c r="A112" s="10" t="s">
         <v>1509</v>
       </c>
@@ -44168,20 +43331,23 @@
       <c r="H112" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I112" s="7" t="s">
+      <c r="I112" s="86">
+        <v>111</v>
+      </c>
+      <c r="J112" s="7" t="s">
         <v>1719</v>
       </c>
-      <c r="J112" s="11" t="s">
+      <c r="K112" s="11" t="s">
         <v>1529</v>
       </c>
-      <c r="K112" s="7">
+      <c r="L112" s="7">
         <v>10</v>
       </c>
-      <c r="L112" s="7">
+      <c r="M112" s="7">
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:13">
       <c r="A113" s="10" t="s">
         <v>1512</v>
       </c>
@@ -44206,20 +43372,23 @@
       <c r="H113" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I113" s="7" t="s">
+      <c r="I113" s="86">
+        <v>112</v>
+      </c>
+      <c r="J113" s="7" t="s">
         <v>1720</v>
       </c>
-      <c r="J113" s="11" t="s">
+      <c r="K113" s="11" t="s">
         <v>1611</v>
       </c>
-      <c r="K113" s="7">
+      <c r="L113" s="7">
         <v>2</v>
       </c>
-      <c r="L113" s="7">
+      <c r="M113" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:13">
       <c r="A114" s="10" t="s">
         <v>1514</v>
       </c>
@@ -44244,20 +43413,23 @@
       <c r="H114" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I114" s="7" t="s">
+      <c r="I114" s="86">
+        <v>113</v>
+      </c>
+      <c r="J114" s="7" t="s">
         <v>1722</v>
       </c>
-      <c r="J114" s="7" t="s">
+      <c r="K114" s="7" t="s">
         <v>1723</v>
       </c>
-      <c r="K114" s="7">
+      <c r="L114" s="7">
         <v>45</v>
       </c>
-      <c r="L114" s="7">
+      <c r="M114" s="7">
         <v>67</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:13">
       <c r="A115" s="10" t="s">
         <v>1515</v>
       </c>
@@ -44282,60 +43454,63 @@
       <c r="H115" s="7" t="s">
         <v>1527</v>
       </c>
-      <c r="I115" s="7" t="s">
+      <c r="I115" s="86">
+        <v>114</v>
+      </c>
+      <c r="J115" s="7" t="s">
         <v>1724</v>
       </c>
-      <c r="J115" s="7" t="s">
+      <c r="K115" s="7" t="s">
         <v>1694</v>
       </c>
-      <c r="K115" s="7">
-        <v>1</v>
-      </c>
       <c r="L115" s="7">
+        <v>1</v>
+      </c>
+      <c r="M115" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:13">
       <c r="A117" s="10"/>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:13">
       <c r="A118" s="10"/>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:13">
       <c r="A119" s="10"/>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:13">
       <c r="A120" s="10"/>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:13">
       <c r="A121" s="10"/>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:13">
       <c r="A122" s="10"/>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:13">
       <c r="A123" s="10"/>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:13">
       <c r="A124" s="10"/>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:13">
       <c r="A125" s="10"/>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:13">
       <c r="A126" s="10"/>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:13">
       <c r="A127" s="10"/>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:13">
       <c r="A128" s="10"/>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="A1:A8 A27 A30 A34 A40 A44 A57:A58 A67 A103 A116:A1048576">
     <cfRule type="duplicateValues" dxfId="161" priority="2013"/>
   </conditionalFormatting>
@@ -45112,7 +44287,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20"/>
+  <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0361124-5054-487D-A3D5-3B0F1D4928ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53BC306-7260-4A92-BEE0-DD3DC9EC5B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7238" uniqueCount="1879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7222" uniqueCount="1867">
   <si>
     <t>NpcID</t>
   </si>
@@ -7620,13 +7620,18 @@
     <t>TheoryName</t>
   </si>
   <si>
-    <t>ba_mai</t>
-  </si>
-  <si>
-    <t>把脉</t>
-  </si>
-  <si>
-    <t>游戏中人体被划分为表、心、肝、脾、肺、肾六个区域；每个区域由气、血、寒热、湿燥四种属性构成；医者通过把脉确定病位和病性。
+    <t>si_zhen</t>
+  </si>
+  <si>
+    <t>四诊</t>
+  </si>
+  <si>
+    <t>【四诊】
+四诊是中医收集患者病情资料的四种基本诊察方法，包括望诊、闻诊、问诊和切诊。医者通过观察、听闻、询问和触按患者所表现出的各种信息，了解疾病的病因、病位、性质以及正邪盛衰，为辨证和治疗提供依据。
+望诊是观察患者的神、色、形、态以及舌象和局部变化；
+闻诊包括听声音和嗅气味，如辨别说话、呼吸、咳嗽等声音及异常气味；
+问诊是询问疾病经过、主要症状、生活习惯及既往情况；
+切诊包括脉诊和按诊，通过切脉与触按身体了解脉象及局部变化。
 【寸关尺】
 寸、关、尺是脉诊中的三个把脉位置，在手腕桡骨动脉上。医者通过按压这三个位置，感受脉象的强弱、快慢、沉浮、流畅程度，从而推测人体不同区域和脏腑的健康状况。
 【对应脏腑区域】
@@ -7636,61 +7641,7 @@
 左尺：肾阴
 右寸：肺
 右关：脾
-右尺：肾阳
-【脉象】
-游戏中脉象由波形图表示。
-波峰的高低反映气的强弱；
-波峰越高气滞程度越高，波峰越低气虚程度越高。
-波线的粗细反映血的状态；
-波线越粗血瘀程度越高，波线越细血虚程度越高。
-波宽的宽窄反映湿燥程度；
-波宽越宽越湿，波宽越窄越燥。
-波速的快慢反映寒热程度；
-波速越快越热，波速越慢越寒。</t>
-  </si>
-  <si>
-    <t>kai_fang</t>
-  </si>
-  <si>
-    <t>断病开方</t>
-  </si>
-  <si>
-    <t>【断病】
-可以在搜索栏输入疾病名或拼音、拼音首字母快速查找药材。
-【开方】
-点击选中君臣佐使区域，药材栏选取添加药材和药量，左键点击增加，右键减少。可以在搜索栏输入药材名或拼音、拼音首字母快速查找药材。
-【君臣佐使】
-方剂配伍的基本原则，指一个药方里不同药材扮演的不同角色，就像一只分工明确的团队。
-君药：针对主要病症的核心药材，力量最强，用量最大。
-臣药：辅助君药增强疗效，治疗兼带症状。
-佐药：制约君臣药的毒性或烈性，治疗次要症状。
-使药：调和诸药，引导药物直达病位，解毒缓解副作用。</t>
-  </si>
-  <si>
-    <t>李东璧在行医过程中记录的心得笔记，白天行医时可翻阅笔记查找药材、方剂、疾病。
-在搜索栏输入药材、方剂、疾病的中文名或拼音、拼音首字母可快速查找。</t>
-  </si>
-  <si>
-    <t>yu_zhi_fang_ji</t>
-  </si>
-  <si>
-    <t>预制方剂</t>
-  </si>
-  <si>
-    <t>现在你可以预制方剂，开方时搜索并选取方剂名，可自动填入该方剂包含的的所有药材及剂量。</t>
-  </si>
-  <si>
-    <t>si_zhen</t>
-  </si>
-  <si>
-    <t>四诊</t>
-  </si>
-  <si>
-    <t>【四诊】
-四诊是中医收集患者病情资料的四种基本诊察方法，包括望诊、闻诊、问诊和切诊。医者通过观察、听闻、询问和触按患者所表现出的各种信息，了解疾病的病因、病位、性质以及正邪盛衰，为辨证和治疗提供依据。
-望诊是观察患者的神、色、形、态以及舌象和局部变化；闻诊包括听声音和嗅气味，如辨别说话、呼吸、咳嗽等声音及异常气味；问诊是询问疾病经过、主要症状、生活习惯及既往情况；切诊包括脉诊和按诊，通过切脉与触按身体了解脉象及局部变化。
-四诊各有侧重，也会相互补充。同一种疾病可能表现出不同征象，不同疾病也可能出现相似症状，因此不能仅凭舌象、脉象或某一个症状作出判断。医者需要将四诊所得资料结合起来分析，称为“四诊合参”。
-通过四诊合参，医者可进一步运用八纲、脏腑、气血津液等辨证方法，对病情作出综合判断。四诊是中医辨证论治的基础，其结果也会受到患者体质、年龄、环境和病程等因素影响。</t>
+右尺：肾阳</t>
   </si>
   <si>
     <t>ba_gang_bian_zheng</t>
@@ -8068,26 +8019,6 @@
 惊是七情之一，是人在突然遇到意外、声响或危险时产生的急剧情绪反应。惊与恐有所不同：惊通常由突发刺激引起，事先没有心理准备；恐则多是对已知或预期危险产生的害怕。
 中医认为惊主要影响心神，可使气机紊乱，称为“惊则气乱”。受到突然惊吓后，心神失去安定，气血运行也可能暂时失常，并可进一步影响肾的封藏功能。
 惊伤心神时，常见心悸、失眠、神志不宁、精神恍惚、容易受惊或注意力难以集中等表现；情况严重时，还可能出现昏厥或神志异常。判断时需要结合刺激强度、持续影响及患者原有的身心状态综合分析。</t>
-  </si>
-  <si>
-    <r>
-      <t>初学医</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>术</t>
-    </r>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
-    <t>第一次行医</t>
-    <phoneticPr fontId="19"/>
   </si>
 </sst>
 </file>
@@ -10412,8 +10343,8 @@
     <col min="7" max="7" width="25.5" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.75" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="84" width="9.125" style="23" customWidth="1"/>
-    <col min="85" max="16384" width="9.125" style="23"/>
+    <col min="10" max="85" width="9.125" style="23" customWidth="1"/>
+    <col min="86" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -12511,7 +12442,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
@@ -12543,10 +12474,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="48" t="s">
         <v>1776</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="48" t="s">
         <v>1777</v>
       </c>
       <c r="C2" s="7">
@@ -12558,19 +12489,19 @@
       <c r="E2" s="85">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="48" t="s">
         <v>1778</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="74" t="s">
         <v>1779</v>
       </c>
       <c r="B3" s="74" t="s">
         <v>1780</v>
       </c>
       <c r="C3" s="7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>1732</v>
@@ -12583,14 +12514,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>1729</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>1730</v>
+      <c r="A4" s="74" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B4" s="74" t="s">
+        <v>1783</v>
       </c>
       <c r="C4" s="7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>1732</v>
@@ -12598,19 +12529,19 @@
       <c r="E4" s="85">
         <v>3</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>1782</v>
+      <c r="F4" s="74" t="s">
+        <v>1784</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>1783</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>1784</v>
+        <v>1785</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>1786</v>
       </c>
       <c r="C5" s="7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>1732</v>
@@ -12619,35 +12550,35 @@
         <v>4</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1">
-      <c r="A6" s="48" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>1787</v>
+      <c r="A6" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1789</v>
       </c>
       <c r="C6" s="7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E6" s="85">
-        <v>1</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>1788</v>
+        <v>5</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>1790</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1">
-      <c r="A7" s="74" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>1790</v>
+      <c r="A7" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>1792</v>
       </c>
       <c r="C7" s="7">
         <v>10</v>
@@ -12656,107 +12587,107 @@
         <v>1732</v>
       </c>
       <c r="E7" s="85">
-        <v>2</v>
-      </c>
-      <c r="F7" s="74" t="s">
-        <v>1791</v>
+        <v>6</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>1793</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1">
       <c r="A8" s="74" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="C8" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E8" s="85">
-        <v>3</v>
-      </c>
-      <c r="F8" s="74" t="s">
-        <v>1794</v>
+        <v>7</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1796</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>1795</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>1796</v>
+        <v>1797</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1798</v>
       </c>
       <c r="C9" s="7">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E9" s="85">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1799</v>
+        <v>1620</v>
       </c>
       <c r="C10" s="7">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E10" s="85">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="C11" s="7">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E11" s="85">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1">
-      <c r="A12" s="74" t="s">
-        <v>1804</v>
-      </c>
-      <c r="B12" s="74" t="s">
+      <c r="A12" s="7" t="s">
         <v>1805</v>
       </c>
+      <c r="B12" s="7" t="s">
+        <v>1596</v>
+      </c>
       <c r="C12" s="7">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E12" s="85">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>1806</v>
@@ -12767,7 +12698,7 @@
         <v>1807</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1808</v>
+        <v>1566</v>
       </c>
       <c r="C13" s="7">
         <v>40</v>
@@ -12776,18 +12707,18 @@
         <v>1732</v>
       </c>
       <c r="E13" s="85">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="C14" s="7">
         <v>40</v>
@@ -12796,18 +12727,18 @@
         <v>1732</v>
       </c>
       <c r="E14" s="85">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1">
+      <c r="A15" s="48" t="s">
         <v>1811</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="48" t="s">
         <v>1812</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>1813</v>
       </c>
       <c r="C15" s="7">
         <v>40</v>
@@ -12816,18 +12747,18 @@
         <v>1732</v>
       </c>
       <c r="E15" s="85">
-        <v>10</v>
-      </c>
-      <c r="F15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18" customHeight="1">
+      <c r="A16" s="48" t="s">
         <v>1814</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1">
-      <c r="A16" s="7" t="s">
+      <c r="B16" s="48" t="s">
         <v>1815</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>1596</v>
       </c>
       <c r="C16" s="7">
         <v>40</v>
@@ -12836,18 +12767,18 @@
         <v>1732</v>
       </c>
       <c r="E16" s="85">
-        <v>11</v>
-      </c>
-      <c r="F16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="48" t="s">
         <v>1816</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="48" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B17" s="48" t="s">
         <v>1817</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>1566</v>
       </c>
       <c r="C17" s="7">
         <v>40</v>
@@ -12856,18 +12787,18 @@
         <v>1732</v>
       </c>
       <c r="E17" s="85">
-        <v>12</v>
-      </c>
-      <c r="F17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="48" t="s">
         <v>1818</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="48" t="s">
         <v>1819</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>1615</v>
+      <c r="B18" s="48" t="s">
+        <v>1820</v>
       </c>
       <c r="C18" s="7">
         <v>40</v>
@@ -12876,98 +12807,98 @@
         <v>1732</v>
       </c>
       <c r="E18" s="85">
-        <v>13</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>1820</v>
+        <v>17</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>1821</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1">
-      <c r="A19" s="48" t="s">
-        <v>1821</v>
-      </c>
-      <c r="B19" s="48" t="s">
+      <c r="A19" s="7" t="s">
         <v>1822</v>
       </c>
+      <c r="B19" s="7" t="s">
+        <v>1823</v>
+      </c>
       <c r="C19" s="7">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E19" s="85">
-        <v>14</v>
-      </c>
-      <c r="F19" s="48" t="s">
-        <v>1823</v>
+        <v>18</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>1824</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1">
-      <c r="A20" s="48" t="s">
-        <v>1824</v>
-      </c>
-      <c r="B20" s="48" t="s">
+      <c r="A20" s="7" t="s">
         <v>1825</v>
       </c>
+      <c r="B20" s="7" t="s">
+        <v>1826</v>
+      </c>
       <c r="C20" s="7">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E20" s="85">
-        <v>15</v>
-      </c>
-      <c r="F20" s="48" t="s">
-        <v>1826</v>
+        <v>19</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>1827</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1">
-      <c r="A21" s="48" t="s">
-        <v>1353</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>1827</v>
+      <c r="A21" s="7" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1829</v>
       </c>
       <c r="C21" s="7">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E21" s="85">
-        <v>16</v>
-      </c>
-      <c r="F21" s="48" t="s">
-        <v>1828</v>
+        <v>20</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>1830</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1">
-      <c r="A22" s="48" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B22" s="48" t="s">
-        <v>1830</v>
+      <c r="A22" s="7" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>1832</v>
       </c>
       <c r="C22" s="7">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E22" s="85">
-        <v>17</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>1831</v>
+        <v>21</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>1833</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="C23" s="7">
         <v>60</v>
@@ -12976,18 +12907,18 @@
         <v>1732</v>
       </c>
       <c r="E23" s="85">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="C24" s="7">
         <v>60</v>
@@ -12996,18 +12927,18 @@
         <v>1732</v>
       </c>
       <c r="E24" s="85">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="C25" s="7">
         <v>60</v>
@@ -13016,98 +12947,98 @@
         <v>1732</v>
       </c>
       <c r="E25" s="85">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="C26" s="7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E26" s="85">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="C27" s="7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E27" s="85">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="C28" s="7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E28" s="85">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="C29" s="7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>1732</v>
       </c>
       <c r="E29" s="85">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="C30" s="7">
         <v>80</v>
@@ -13116,18 +13047,18 @@
         <v>1732</v>
       </c>
       <c r="E30" s="85">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="C31" s="7">
         <v>80</v>
@@ -13136,18 +13067,18 @@
         <v>1732</v>
       </c>
       <c r="E31" s="85">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="C32" s="7">
         <v>80</v>
@@ -13156,18 +13087,18 @@
         <v>1732</v>
       </c>
       <c r="E32" s="85">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="18" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="C33" s="7">
         <v>80</v>
@@ -13176,91 +13107,43 @@
         <v>1732</v>
       </c>
       <c r="E33" s="85">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18" customHeight="1">
-      <c r="A34" s="7" t="s">
-        <v>1865</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>1866</v>
-      </c>
-      <c r="C34" s="7">
-        <v>80</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>1732</v>
-      </c>
-      <c r="E34" s="85">
-        <v>29</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>1867</v>
-      </c>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1">
-      <c r="A35" s="7" t="s">
-        <v>1868</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>1869</v>
-      </c>
-      <c r="C35" s="7">
-        <v>80</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>1732</v>
-      </c>
-      <c r="E35" s="85">
-        <v>30</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>1870</v>
-      </c>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="7"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1">
-      <c r="A36" s="7" t="s">
-        <v>1871</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>1872</v>
-      </c>
-      <c r="C36" s="7">
-        <v>80</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>1732</v>
-      </c>
-      <c r="E36" s="85">
-        <v>31</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>1873</v>
-      </c>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="85"/>
+      <c r="F36" s="7"/>
     </row>
     <row r="37" spans="1:6" ht="18" customHeight="1">
-      <c r="A37" s="7" t="s">
-        <v>1874</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>1875</v>
-      </c>
-      <c r="C37" s="7">
-        <v>80</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>1732</v>
-      </c>
-      <c r="E37" s="85">
-        <v>32</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>1876</v>
-      </c>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="7"/>
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1">
       <c r="A38" s="7"/>
@@ -13331,7 +13214,6 @@
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="85"/>
       <c r="F46" s="7"/>
     </row>
     <row r="47" spans="1:6" ht="18" customHeight="1">
@@ -13339,38 +13221,7 @@
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="85"/>
       <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" ht="18" customHeight="1">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="85"/>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="1:6" ht="18" customHeight="1">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="85"/>
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="1:6" ht="18" customHeight="1">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="F50" s="7"/>
-    </row>
-    <row r="51" spans="1:6" ht="18" customHeight="1">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="F51" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19"/>
@@ -13397,8 +13248,8 @@
     <col min="16" max="18" width="8.375" style="46" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.75" style="46" customWidth="1"/>
     <col min="20" max="20" width="10" style="46" bestFit="1" customWidth="1"/>
-    <col min="21" max="34" width="9" style="47" customWidth="1"/>
-    <col min="35" max="16384" width="9" style="47"/>
+    <col min="21" max="35" width="9" style="47" customWidth="1"/>
+    <col min="36" max="16384" width="9" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="46" customFormat="1" ht="36" customHeight="1">
@@ -13792,7 +13643,7 @@
         <v>328</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>1877</v>
+        <v>329</v>
       </c>
       <c r="C11" s="48" t="s">
         <v>305</v>
@@ -13826,7 +13677,7 @@
         <v>330</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>1878</v>
+        <v>331</v>
       </c>
       <c r="C12" s="48" t="s">
         <v>310</v>
@@ -15700,8 +15551,8 @@
     <col min="9" max="9" width="48" style="10" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="64" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="66" customWidth="1"/>
-    <col min="12" max="58" width="8.875" style="36" customWidth="1"/>
-    <col min="59" max="16384" width="8.875" style="36"/>
+    <col min="12" max="59" width="8.875" style="36" customWidth="1"/>
+    <col min="60" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -28826,8 +28677,8 @@
     <col min="27" max="27" width="5.125" style="35" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" customWidth="1"/>
-    <col min="30" max="132" width="9" style="9" customWidth="1"/>
-    <col min="133" max="16384" width="9" style="9"/>
+    <col min="30" max="133" width="9" style="9" customWidth="1"/>
+    <col min="134" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -43570,8 +43421,8 @@
     <cfRule type="duplicateValues" dxfId="149" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
-    <cfRule type="duplicateValues" dxfId="148" priority="2332"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="2331"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="2331"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="2332"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" dxfId="146" priority="162"/>
@@ -43598,32 +43449,32 @@
     <cfRule type="duplicateValues" dxfId="137" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="136" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" dxfId="134" priority="121"/>
     <cfRule type="duplicateValues" dxfId="133" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="132" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="130" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
-    <cfRule type="duplicateValues" dxfId="128" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" dxfId="126" priority="112"/>
     <cfRule type="duplicateValues" dxfId="125" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
-    <cfRule type="duplicateValues" dxfId="124" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" dxfId="122" priority="140"/>
@@ -43662,20 +43513,20 @@
     <cfRule type="duplicateValues" dxfId="105" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
-    <cfRule type="duplicateValues" dxfId="104" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" dxfId="102" priority="78"/>
     <cfRule type="duplicateValues" dxfId="101" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="100" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="98" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" dxfId="96" priority="90"/>
@@ -43686,8 +43537,8 @@
     <cfRule type="duplicateValues" dxfId="93" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
-    <cfRule type="duplicateValues" dxfId="92" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" dxfId="90" priority="106"/>
@@ -43698,32 +43549,32 @@
     <cfRule type="duplicateValues" dxfId="87" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="86" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="82" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="80" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" dxfId="78" priority="152"/>
     <cfRule type="duplicateValues" dxfId="77" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="76" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="74" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="72" priority="86"/>
@@ -43734,8 +43585,8 @@
     <cfRule type="duplicateValues" dxfId="69" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" dxfId="66" priority="60"/>
@@ -43746,8 +43597,8 @@
     <cfRule type="duplicateValues" dxfId="63" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="62" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" dxfId="60" priority="150"/>
@@ -43758,8 +43609,8 @@
     <cfRule type="duplicateValues" dxfId="57" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="56" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" dxfId="54" priority="42"/>
@@ -43770,36 +43621,36 @@
     <cfRule type="duplicateValues" dxfId="51" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
-    <cfRule type="duplicateValues" dxfId="50" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" dxfId="48" priority="95"/>
     <cfRule type="duplicateValues" dxfId="47" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
-    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
-    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" dxfId="42" priority="1727"/>
     <cfRule type="duplicateValues" dxfId="41" priority="1728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
-    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" dxfId="38" priority="982"/>
     <cfRule type="duplicateValues" dxfId="37" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
-    <cfRule type="duplicateValues" dxfId="36" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" dxfId="34" priority="13"/>
@@ -43830,12 +43681,12 @@
     <cfRule type="duplicateValues" dxfId="21" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
-    <cfRule type="duplicateValues" dxfId="20" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" dxfId="16" priority="26"/>
@@ -43850,12 +43701,12 @@
     <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
-    <cfRule type="duplicateValues" dxfId="10" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
-    <cfRule type="duplicateValues" dxfId="8" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" dxfId="6" priority="1709"/>
@@ -43866,8 +43717,8 @@
     <cfRule type="duplicateValues" dxfId="3" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
-    <cfRule type="duplicateValues" dxfId="2" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="395"/>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53BC306-7260-4A92-BEE0-DD3DC9EC5B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1785237C-C37B-4757-993E-2F67A3D56C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -10343,8 +10343,8 @@
     <col min="7" max="7" width="25.5" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.75" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="85" width="9.125" style="23" customWidth="1"/>
-    <col min="86" max="16384" width="9.125" style="23"/>
+    <col min="10" max="86" width="9.125" style="23" customWidth="1"/>
+    <col min="87" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -13248,8 +13248,8 @@
     <col min="16" max="18" width="8.375" style="46" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.75" style="46" customWidth="1"/>
     <col min="20" max="20" width="10" style="46" bestFit="1" customWidth="1"/>
-    <col min="21" max="35" width="9" style="47" customWidth="1"/>
-    <col min="36" max="16384" width="9" style="47"/>
+    <col min="21" max="36" width="9" style="47" customWidth="1"/>
+    <col min="37" max="16384" width="9" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="46" customFormat="1" ht="36" customHeight="1">
@@ -15551,8 +15551,8 @@
     <col min="9" max="9" width="48" style="10" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="64" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="66" customWidth="1"/>
-    <col min="12" max="59" width="8.875" style="36" customWidth="1"/>
-    <col min="60" max="16384" width="8.875" style="36"/>
+    <col min="12" max="60" width="8.875" style="36" customWidth="1"/>
+    <col min="61" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -28677,8 +28677,8 @@
     <col min="27" max="27" width="5.125" style="35" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" customWidth="1"/>
-    <col min="30" max="133" width="9" style="9" customWidth="1"/>
-    <col min="134" max="16384" width="9" style="9"/>
+    <col min="30" max="134" width="9" style="9" customWidth="1"/>
+    <col min="135" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -43421,8 +43421,8 @@
     <cfRule type="duplicateValues" dxfId="149" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
-    <cfRule type="duplicateValues" dxfId="148" priority="2331"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="2332"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="2332"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="2331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" dxfId="146" priority="162"/>
@@ -43449,32 +43449,32 @@
     <cfRule type="duplicateValues" dxfId="137" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="136" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" dxfId="134" priority="121"/>
     <cfRule type="duplicateValues" dxfId="133" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="132" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="130" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
-    <cfRule type="duplicateValues" dxfId="128" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" dxfId="126" priority="112"/>
     <cfRule type="duplicateValues" dxfId="125" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
-    <cfRule type="duplicateValues" dxfId="124" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" dxfId="122" priority="140"/>
@@ -43513,20 +43513,20 @@
     <cfRule type="duplicateValues" dxfId="105" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
-    <cfRule type="duplicateValues" dxfId="104" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" dxfId="102" priority="78"/>
     <cfRule type="duplicateValues" dxfId="101" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="100" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="98" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" dxfId="96" priority="90"/>
@@ -43537,8 +43537,8 @@
     <cfRule type="duplicateValues" dxfId="93" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
-    <cfRule type="duplicateValues" dxfId="92" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" dxfId="90" priority="106"/>
@@ -43549,32 +43549,32 @@
     <cfRule type="duplicateValues" dxfId="87" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="84" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="82" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="80" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" dxfId="78" priority="152"/>
     <cfRule type="duplicateValues" dxfId="77" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="76" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="74" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="72" priority="86"/>
@@ -43585,8 +43585,8 @@
     <cfRule type="duplicateValues" dxfId="69" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="68" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" dxfId="66" priority="60"/>
@@ -43597,8 +43597,8 @@
     <cfRule type="duplicateValues" dxfId="63" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="62" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" dxfId="60" priority="150"/>
@@ -43609,8 +43609,8 @@
     <cfRule type="duplicateValues" dxfId="57" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="56" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" dxfId="54" priority="42"/>
@@ -43621,36 +43621,36 @@
     <cfRule type="duplicateValues" dxfId="51" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
-    <cfRule type="duplicateValues" dxfId="50" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" dxfId="48" priority="95"/>
     <cfRule type="duplicateValues" dxfId="47" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
-    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
-    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" dxfId="42" priority="1727"/>
     <cfRule type="duplicateValues" dxfId="41" priority="1728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
-    <cfRule type="duplicateValues" dxfId="40" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" dxfId="38" priority="982"/>
     <cfRule type="duplicateValues" dxfId="37" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
-    <cfRule type="duplicateValues" dxfId="36" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" dxfId="34" priority="13"/>
@@ -43681,12 +43681,12 @@
     <cfRule type="duplicateValues" dxfId="21" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
-    <cfRule type="duplicateValues" dxfId="20" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" dxfId="16" priority="26"/>
@@ -43701,12 +43701,12 @@
     <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
-    <cfRule type="duplicateValues" dxfId="10" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
-    <cfRule type="duplicateValues" dxfId="8" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" dxfId="6" priority="1709"/>
@@ -43717,8 +43717,8 @@
     <cfRule type="duplicateValues" dxfId="3" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
-    <cfRule type="duplicateValues" dxfId="2" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="395"/>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -6807,7 +6807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T62"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="7.5" bestFit="1" customWidth="1" style="46" min="1" max="1"/>
@@ -9964,6 +9964,62 @@
       </c>
       <c r="T62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>028_03</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>028治疗失败</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>028_01</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>zeng_ti_ming</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>痰迷心窍</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/StoryNpc/zeng_ti_ming/zeng_ti_ming.png</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AA60"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9976,7 +10032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K441"/>
+  <dimension ref="A1:K442"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -27522,6 +27578,49 @@
         </is>
       </c>
       <c r="K441" s="55" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="50" t="inlineStr">
+        <is>
+          <t>028_03</t>
+        </is>
+      </c>
+      <c r="B442" s="50" t="inlineStr">
+        <is>
+          <t>028治疗失败</t>
+        </is>
+      </c>
+      <c r="C442" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D442" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E442" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F442" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G442" s="51" t="inlineStr"/>
+      <c r="H442" s="54" t="inlineStr"/>
+      <c r="I442" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J442" s="53" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
+        </is>
+      </c>
+      <c r="K442" s="50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -301,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -508,6 +508,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -10032,7 +10035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K442"/>
+  <dimension ref="A1:K448"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -27076,7 +27079,7 @@
       </c>
       <c r="K428" s="55" t="inlineStr"/>
     </row>
-    <row r="429">
+    <row r="429" ht="30" customHeight="1">
       <c r="A429" s="50" t="inlineStr">
         <is>
           <t>028_01</t>
@@ -27114,7 +27117,7 @@
       </c>
       <c r="J429" s="53" t="inlineStr">
         <is>
-          <t>大夫啊，您快帮忙看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语考中了考中了的…</t>
+          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
         </is>
       </c>
       <c r="K429" s="50" t="inlineStr"/>
@@ -27262,7 +27265,7 @@
       </c>
       <c r="J433" s="53" t="inlineStr">
         <is>
-          <t>贵公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
+          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
         </is>
       </c>
       <c r="K433" s="50" t="inlineStr"/>
@@ -27533,9 +27536,9 @@
       <c r="G440" s="55" t="inlineStr"/>
       <c r="H440" s="55" t="inlineStr"/>
       <c r="I440" s="55" t="inlineStr"/>
-      <c r="J440" s="56" t="inlineStr">
-        <is>
-          <t>很多人表面看着正常，其实病得都不轻呢。</t>
+      <c r="J440" s="53" t="inlineStr">
+        <is>
+          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
         </is>
       </c>
       <c r="K440" s="55" t="inlineStr"/>
@@ -27572,9 +27575,9 @@
       <c r="G441" s="55" t="inlineStr"/>
       <c r="H441" s="55" t="inlineStr"/>
       <c r="I441" s="55" t="inlineStr"/>
-      <c r="J441" s="56" t="inlineStr">
-        <is>
-          <t>胡扯，我看你就是没病说成有病，</t>
+      <c r="J441" s="53" t="inlineStr">
+        <is>
+          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
         </is>
       </c>
       <c r="K441" s="55" t="inlineStr"/>
@@ -27582,45 +27585,279 @@
     <row r="442">
       <c r="A442" s="50" t="inlineStr">
         <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B442" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C442" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D442" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E442" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F442" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G442" s="55" t="inlineStr"/>
+      <c r="H442" s="55" t="inlineStr"/>
+      <c r="I442" s="55" t="inlineStr"/>
+      <c r="J442" s="53" t="inlineStr">
+        <is>
+          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
+        </is>
+      </c>
+      <c r="K442" s="55" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B443" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C443" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D443" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E443" s="53" t="inlineStr">
+        <is>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F443" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G443" s="55" t="inlineStr"/>
+      <c r="H443" s="55" t="inlineStr"/>
+      <c r="I443" s="55" t="inlineStr"/>
+      <c r="J443" s="53" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K443" s="55" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B444" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C444" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D444" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E444" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F444" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G444" s="55" t="inlineStr"/>
+      <c r="H444" s="55" t="inlineStr"/>
+      <c r="I444" s="55" t="inlineStr"/>
+      <c r="J444" s="88" t="inlineStr">
+        <is>
+          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
+        </is>
+      </c>
+      <c r="K444" s="55" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B445" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C445" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="D445" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E445" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F445" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G445" s="55" t="inlineStr"/>
+      <c r="H445" s="55" t="inlineStr"/>
+      <c r="I445" s="55" t="inlineStr"/>
+      <c r="J445" s="88" t="inlineStr">
+        <is>
+          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+        </is>
+      </c>
+      <c r="K445" s="55" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B446" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C446" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D446" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E446" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F446" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G446" s="55" t="inlineStr"/>
+      <c r="H446" s="55" t="inlineStr"/>
+      <c r="I446" s="55" t="inlineStr"/>
+      <c r="J446" s="88" t="inlineStr">
+        <is>
+          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+        </is>
+      </c>
+      <c r="K446" s="55" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B447" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C447" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D447" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E447" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F447" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G447" s="55" t="inlineStr"/>
+      <c r="H447" s="55" t="inlineStr"/>
+      <c r="I447" s="55" t="inlineStr"/>
+      <c r="J447" s="88" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K447" s="55" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="50" t="inlineStr">
+        <is>
           <t>028_03</t>
         </is>
       </c>
-      <c r="B442" s="50" t="inlineStr">
+      <c r="B448" s="50" t="inlineStr">
         <is>
           <t>028治疗失败</t>
         </is>
       </c>
-      <c r="C442" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D442" s="50" t="inlineStr">
+      <c r="C448" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D448" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E442" s="53" t="inlineStr">
+      <c r="E448" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F442" s="52" t="inlineStr">
+      <c r="F448" s="52" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G442" s="51" t="inlineStr"/>
-      <c r="H442" s="54" t="inlineStr"/>
-      <c r="I442" s="51" t="inlineStr">
+      <c r="G448" s="51" t="inlineStr"/>
+      <c r="H448" s="54" t="inlineStr"/>
+      <c r="I448" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J442" s="53" t="inlineStr">
+      <c r="J448" s="53" t="inlineStr">
         <is>
           <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
-      <c r="K442" s="50" t="inlineStr"/>
+      <c r="K448" s="50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="H8" s="48" t="n">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I8" s="48" t="inlineStr"/>
       <c r="J8" s="48" t="inlineStr"/>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -32023,7 +32023,7 @@
 【主治】痰迷心窍
 【组成】
 君：半夏 二钱五分，胆南星 二钱五分
-臣：枳实 二钱，陈皮 一分五钱
+臣：枳实 二钱，陈皮 一钱五分
 佐：竹茹 一钱，茯苓 二钱，石菖蒲 一钱，人参 一钱
 使：生姜 一钱，甘草 一钱
 【配伍】

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -6954,15 +6954,13 @@
       </c>
       <c r="E2" s="48" t="inlineStr"/>
       <c r="F2" s="48" t="inlineStr"/>
-      <c r="G2" s="48" t="inlineStr">
-        <is>
-          <t>gte</t>
-        </is>
-      </c>
-      <c r="H2" s="48" t="n">
-        <v>107</v>
-      </c>
-      <c r="I2" s="48" t="inlineStr"/>
+      <c r="G2" s="48" t="inlineStr"/>
+      <c r="H2" s="48" t="inlineStr"/>
+      <c r="I2" s="48" t="inlineStr">
+        <is>
+          <t>气分热盛</t>
+        </is>
+      </c>
       <c r="J2" s="48" t="inlineStr">
         <is>
           <t>021</t>
@@ -7048,7 +7046,7 @@
         </is>
       </c>
       <c r="D4" s="48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="48" t="inlineStr"/>
       <c r="F4" s="48" t="inlineStr"/>
@@ -7093,7 +7091,9 @@
           <t>night</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr"/>
+      <c r="D5" s="48" t="n">
+        <v>1</v>
+      </c>
       <c r="E5" s="48" t="inlineStr"/>
       <c r="F5" s="48" t="inlineStr"/>
       <c r="G5" s="48" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
       <c r="H27" s="48" t="inlineStr"/>
       <c r="I27" s="48" t="inlineStr">
         <is>
-          <t>鸡子黄</t>
+          <t>气分热盛</t>
         </is>
       </c>
       <c r="J27" s="48" t="inlineStr">
@@ -10110,7 +10110,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="50" t="inlineStr">
         <is>
           <t>000_01</t>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="K32" s="50" t="inlineStr"/>
     </row>
-    <row r="33" ht="33" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="50" t="inlineStr">
         <is>
           <t>000_04</t>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="K163" s="50" t="inlineStr"/>
     </row>
-    <row r="164">
+    <row r="164" ht="33" customHeight="1">
       <c r="A164" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -32615,7 +32615,7 @@
 君：钩藤 三钱，菊花 三钱
 臣：防风 三钱，石膏 三钱
 佐：茯苓 三钱，半夏 三钱，陈皮 三钱，人参 三钱
-使：甘草 三钱
+使：甘草 三钱，生姜 二钱
 【配伍】
 钩藤、菊花：平肝息风、清利头目
 石膏：清热泻火、除烦止晕

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -32661,7 +32661,7 @@
 君：柴胡 三钱
 臣：当归 三钱，白芍 三钱
 佐：白术 三钱，茯苓 三钱，生姜 一钱，薄荷 一钱
-使：甘草 一钱五分
+使：甘草 一钱
 【配伍】
 柴胡：疏肝解郁、条达肝气，疏散郁滞。
 当归、白芍：养血柔肝，补肝体、缓肝急；防肝郁化火伤阴。

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story'!$A$1:$AA$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StoryLine'!$A$1:$BI$450</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="游ゴシック"/>
       <color theme="1"/>
@@ -163,17 +164,24 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="BIZ UDGothic"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -301,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -506,14 +514,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -2420,8 +2434,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="87"/>
-    <col width="9.125" customWidth="1" style="23" min="88" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="88"/>
+    <col width="9.125" customWidth="1" style="23" min="89" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5623,7 +5637,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="21.75" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -6827,8 +6841,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="37"/>
-    <col width="9" customWidth="1" style="47" min="38" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="38"/>
+    <col width="9" customWidth="1" style="47" min="39" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
@@ -9231,7 +9245,9 @@
       <c r="M48" s="48" t="inlineStr"/>
       <c r="N48" s="48" t="inlineStr"/>
       <c r="O48" s="48" t="inlineStr"/>
-      <c r="P48" s="48" t="inlineStr"/>
+      <c r="P48" s="48" t="n">
+        <v>1000</v>
+      </c>
       <c r="Q48" s="48" t="inlineStr"/>
       <c r="R48" s="48" t="inlineStr"/>
       <c r="S48" s="48" t="b">
@@ -9393,7 +9409,9 @@
       <c r="M51" s="48" t="inlineStr"/>
       <c r="N51" s="48" t="inlineStr"/>
       <c r="O51" s="48" t="inlineStr"/>
-      <c r="P51" s="48" t="inlineStr"/>
+      <c r="P51" s="48" t="n">
+        <v>2000</v>
+      </c>
       <c r="Q51" s="48" t="inlineStr"/>
       <c r="R51" s="48" t="inlineStr"/>
       <c r="S51" s="48" t="b">
@@ -9867,7 +9885,7 @@
       </c>
       <c r="T60" s="83" t="inlineStr"/>
     </row>
-    <row r="61">
+    <row r="61" ht="17.65" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>028_01</t>
@@ -9923,7 +9941,7 @@
       </c>
       <c r="T61" t="inlineStr"/>
     </row>
-    <row r="62">
+    <row r="62" ht="17.65" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -9967,7 +9985,7 @@
       </c>
       <c r="T62" t="inlineStr"/>
     </row>
-    <row r="63">
+    <row r="63" ht="17.65" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>028_03</t>
@@ -10031,11 +10049,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K448"/>
+  <dimension ref="A1:K450"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -10049,8 +10067,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="61"/>
-    <col width="8.875" customWidth="1" style="36" min="62" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="62"/>
+    <col width="8.875" customWidth="1" style="36" min="63" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10145,7 +10163,7 @@
       </c>
       <c r="K2" s="50" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" hidden="1">
       <c r="A3" s="50" t="inlineStr">
         <is>
           <t>000_01</t>
@@ -10188,7 +10206,7 @@
       </c>
       <c r="K3" s="50" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="4" hidden="1">
       <c r="A4" s="50" t="inlineStr">
         <is>
           <t>000_01</t>
@@ -10231,7 +10249,7 @@
       </c>
       <c r="K4" s="50" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="5" hidden="1">
       <c r="A5" s="50" t="inlineStr">
         <is>
           <t>000_01</t>
@@ -10270,7 +10288,7 @@
       </c>
       <c r="K5" s="50" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" hidden="1">
       <c r="A6" s="50" t="inlineStr">
         <is>
           <t>000_01</t>
@@ -10352,7 +10370,7 @@
       </c>
       <c r="K7" s="50" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" hidden="1">
       <c r="A8" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10395,7 +10413,7 @@
       </c>
       <c r="K8" s="50" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="9" hidden="1">
       <c r="A9" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10426,7 +10444,7 @@
       </c>
       <c r="K9" s="50" t="inlineStr"/>
     </row>
-    <row r="10">
+    <row r="10" hidden="1">
       <c r="A10" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10465,7 +10483,7 @@
       </c>
       <c r="K10" s="50" t="inlineStr"/>
     </row>
-    <row r="11">
+    <row r="11" hidden="1">
       <c r="A11" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10508,7 +10526,7 @@
       </c>
       <c r="K11" s="50" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" hidden="1">
       <c r="A12" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10547,7 +10565,7 @@
       </c>
       <c r="K12" s="55" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" hidden="1">
       <c r="A13" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10586,7 +10604,7 @@
       </c>
       <c r="K13" s="55" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" hidden="1">
       <c r="A14" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10625,7 +10643,7 @@
       </c>
       <c r="K14" s="55" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" hidden="1">
       <c r="A15" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10664,7 +10682,7 @@
       </c>
       <c r="K15" s="55" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" hidden="1">
       <c r="A16" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10703,7 +10721,7 @@
       </c>
       <c r="K16" s="55" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" hidden="1">
       <c r="A17" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10742,7 +10760,7 @@
       </c>
       <c r="K17" s="55" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" hidden="1">
       <c r="A18" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10785,7 +10803,7 @@
       </c>
       <c r="K18" s="55" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="19" hidden="1">
       <c r="A19" s="50" t="inlineStr">
         <is>
           <t>000_02</t>
@@ -10867,7 +10885,7 @@
       </c>
       <c r="K20" s="50" t="inlineStr"/>
     </row>
-    <row r="21">
+    <row r="21" hidden="1">
       <c r="A21" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -10910,7 +10928,7 @@
       </c>
       <c r="K21" s="50" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="22" hidden="1">
       <c r="A22" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -10949,7 +10967,7 @@
       </c>
       <c r="K22" s="50" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="23" hidden="1">
       <c r="A23" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -10992,7 +11010,7 @@
       </c>
       <c r="K23" s="50" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="24" hidden="1">
       <c r="A24" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -11031,7 +11049,7 @@
       </c>
       <c r="K24" s="50" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" hidden="1">
       <c r="A25" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -11074,7 +11092,7 @@
       </c>
       <c r="K25" s="55" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="26" hidden="1">
       <c r="A26" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -11117,7 +11135,7 @@
       </c>
       <c r="K26" s="55" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" hidden="1">
       <c r="A27" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -11160,7 +11178,7 @@
       </c>
       <c r="K27" s="55" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="28" hidden="1">
       <c r="A28" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -11203,7 +11221,7 @@
       </c>
       <c r="K28" s="55" t="inlineStr"/>
     </row>
-    <row r="29">
+    <row r="29" hidden="1">
       <c r="A29" s="50" t="inlineStr">
         <is>
           <t>000_03</t>
@@ -11285,7 +11303,7 @@
       </c>
       <c r="K30" s="50" t="inlineStr"/>
     </row>
-    <row r="31">
+    <row r="31" hidden="1">
       <c r="A31" s="50" t="inlineStr">
         <is>
           <t>000_04</t>
@@ -11316,7 +11334,7 @@
       </c>
       <c r="K31" s="50" t="inlineStr"/>
     </row>
-    <row r="32">
+    <row r="32" hidden="1">
       <c r="A32" s="50" t="inlineStr">
         <is>
           <t>000_04</t>
@@ -11359,7 +11377,7 @@
       </c>
       <c r="K32" s="50" t="inlineStr"/>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" hidden="1" ht="30" customHeight="1">
       <c r="A33" s="50" t="inlineStr">
         <is>
           <t>000_04</t>
@@ -11398,7 +11416,7 @@
       </c>
       <c r="K33" s="50" t="inlineStr"/>
     </row>
-    <row r="34">
+    <row r="34" hidden="1">
       <c r="A34" s="50" t="inlineStr">
         <is>
           <t>000_04</t>
@@ -11466,7 +11484,7 @@
       <c r="H35" s="55" t="inlineStr"/>
       <c r="I35" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/000/000_00.png</t>
+          <t>res://Assets/Background/black.png</t>
         </is>
       </c>
       <c r="J35" s="68" t="inlineStr">
@@ -11480,7 +11498,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="1">
       <c r="A36" s="50" t="inlineStr">
         <is>
           <t>000_05</t>
@@ -11511,7 +11529,7 @@
       </c>
       <c r="K36" s="50" t="inlineStr"/>
     </row>
-    <row r="37" ht="54" customHeight="1">
+    <row r="37" hidden="1" ht="54" customHeight="1">
       <c r="A37" s="50" t="inlineStr">
         <is>
           <t>000_05</t>
@@ -11610,7 +11628,7 @@
       <c r="H39" s="54" t="inlineStr"/>
       <c r="I39" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/000/001.png</t>
+          <t>res://Assets/Background/000/000_01.png</t>
         </is>
       </c>
       <c r="J39" s="53" t="inlineStr">
@@ -11663,7 +11681,7 @@
       </c>
       <c r="K40" s="50" t="inlineStr"/>
     </row>
-    <row r="41">
+    <row r="41" hidden="1">
       <c r="A41" s="50" t="inlineStr">
         <is>
           <t>000_07</t>
@@ -11702,7 +11720,7 @@
       </c>
       <c r="K41" s="50" t="inlineStr"/>
     </row>
-    <row r="42">
+    <row r="42" hidden="1">
       <c r="A42" s="50" t="inlineStr">
         <is>
           <t>000_07</t>
@@ -11801,7 +11819,7 @@
       <c r="H44" s="54" t="inlineStr"/>
       <c r="I44" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/000/000_00.png</t>
+          <t>res://Assets/Background/black.png</t>
         </is>
       </c>
       <c r="J44" s="50" t="inlineStr">
@@ -11811,7 +11829,7 @@
       </c>
       <c r="K44" s="50" t="inlineStr"/>
     </row>
-    <row r="45">
+    <row r="45" hidden="1">
       <c r="A45" s="50" t="inlineStr">
         <is>
           <t>000_08</t>
@@ -11877,7 +11895,7 @@
       </c>
       <c r="K46" s="50" t="inlineStr"/>
     </row>
-    <row r="47">
+    <row r="47" hidden="1">
       <c r="A47" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -11916,7 +11934,7 @@
       </c>
       <c r="K47" s="50" t="inlineStr"/>
     </row>
-    <row r="48">
+    <row r="48" hidden="1">
       <c r="A48" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -11955,7 +11973,7 @@
       </c>
       <c r="K48" s="50" t="inlineStr"/>
     </row>
-    <row r="49">
+    <row r="49" hidden="1">
       <c r="A49" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -11994,7 +12012,7 @@
       </c>
       <c r="K49" s="50" t="inlineStr"/>
     </row>
-    <row r="50">
+    <row r="50" hidden="1">
       <c r="A50" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -12033,7 +12051,7 @@
       </c>
       <c r="K50" s="50" t="inlineStr"/>
     </row>
-    <row r="51">
+    <row r="51" hidden="1">
       <c r="A51" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -12072,7 +12090,7 @@
       </c>
       <c r="K51" s="55" t="inlineStr"/>
     </row>
-    <row r="52" ht="36" customHeight="1">
+    <row r="52" hidden="1" ht="36" customHeight="1">
       <c r="A52" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -12111,7 +12129,7 @@
       </c>
       <c r="K52" s="55" t="inlineStr"/>
     </row>
-    <row r="53">
+    <row r="53" hidden="1">
       <c r="A53" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -12150,7 +12168,7 @@
       </c>
       <c r="K53" s="55" t="inlineStr"/>
     </row>
-    <row r="54">
+    <row r="54" hidden="1">
       <c r="A54" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -12189,7 +12207,7 @@
       </c>
       <c r="K54" s="55" t="inlineStr"/>
     </row>
-    <row r="55">
+    <row r="55" hidden="1">
       <c r="A55" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -12228,7 +12246,7 @@
       </c>
       <c r="K55" s="55" t="inlineStr"/>
     </row>
-    <row r="56" ht="36" customHeight="1">
+    <row r="56" hidden="1" ht="36" customHeight="1">
       <c r="A56" s="50" t="inlineStr">
         <is>
           <t>001</t>
@@ -12267,7 +12285,7 @@
       </c>
       <c r="K56" s="55" t="inlineStr"/>
     </row>
-    <row r="57">
+    <row r="57" hidden="1">
       <c r="A57" s="55" t="inlineStr">
         <is>
           <t>001</t>
@@ -12321,7 +12339,7 @@
       <c r="F58" s="52" t="inlineStr"/>
       <c r="G58" s="51" t="inlineStr"/>
       <c r="H58" s="52" t="inlineStr"/>
-      <c r="I58" s="87" t="inlineStr">
+      <c r="I58" s="90" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring_night.png</t>
         </is>
@@ -12333,7 +12351,7 @@
       </c>
       <c r="K58" s="50" t="inlineStr"/>
     </row>
-    <row r="59" ht="18.75" customHeight="1">
+    <row r="59" hidden="1" ht="18.75" customHeight="1">
       <c r="A59" s="50" t="inlineStr">
         <is>
           <t>002</t>
@@ -12364,7 +12382,7 @@
       </c>
       <c r="G59" s="51" t="inlineStr"/>
       <c r="H59" s="52" t="inlineStr"/>
-      <c r="I59" s="87" t="inlineStr"/>
+      <c r="I59" s="90" t="inlineStr"/>
       <c r="J59" s="57" t="inlineStr">
         <is>
           <t>麻桂相须，增强发汗散寒之力，专治表实无汗。麻杏相使，宣降相配，专治寒邪闭肺之喘逆…</t>
@@ -12372,7 +12390,7 @@
       </c>
       <c r="K59" s="50" t="inlineStr"/>
     </row>
-    <row r="60">
+    <row r="60" hidden="1">
       <c r="A60" s="50" t="inlineStr">
         <is>
           <t>002</t>
@@ -12411,7 +12429,7 @@
       </c>
       <c r="K60" s="50" t="inlineStr"/>
     </row>
-    <row r="61">
+    <row r="61" hidden="1">
       <c r="A61" s="50" t="inlineStr">
         <is>
           <t>002</t>
@@ -12481,7 +12499,7 @@
       </c>
       <c r="G62" s="51" t="inlineStr"/>
       <c r="H62" s="52" t="inlineStr"/>
-      <c r="I62" s="87" t="inlineStr">
+      <c r="I62" s="90" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -12493,7 +12511,7 @@
       </c>
       <c r="K62" s="50" t="inlineStr"/>
     </row>
-    <row r="63">
+    <row r="63" hidden="1">
       <c r="A63" s="50" t="inlineStr">
         <is>
           <t>002</t>
@@ -12532,7 +12550,7 @@
       </c>
       <c r="K63" s="50" t="inlineStr"/>
     </row>
-    <row r="64">
+    <row r="64" hidden="1">
       <c r="A64" s="50" t="inlineStr">
         <is>
           <t>002</t>
@@ -12571,7 +12589,7 @@
       </c>
       <c r="K64" s="50" t="inlineStr"/>
     </row>
-    <row r="65">
+    <row r="65" hidden="1">
       <c r="A65" s="50" t="inlineStr">
         <is>
           <t>002</t>
@@ -12653,7 +12671,7 @@
       </c>
       <c r="K66" s="50" t="inlineStr"/>
     </row>
-    <row r="67">
+    <row r="67" hidden="1">
       <c r="A67" s="50" t="inlineStr">
         <is>
           <t>003</t>
@@ -12735,7 +12753,7 @@
       </c>
       <c r="K68" s="50" t="inlineStr"/>
     </row>
-    <row r="69">
+    <row r="69" hidden="1">
       <c r="A69" s="50" t="inlineStr">
         <is>
           <t>004_01</t>
@@ -12774,7 +12792,7 @@
       </c>
       <c r="K69" s="50" t="inlineStr"/>
     </row>
-    <row r="70">
+    <row r="70" hidden="1">
       <c r="A70" s="50" t="inlineStr">
         <is>
           <t>004_01</t>
@@ -12813,7 +12831,7 @@
       </c>
       <c r="K70" s="50" t="inlineStr"/>
     </row>
-    <row r="71" ht="34.5" customHeight="1">
+    <row r="71" hidden="1" ht="34.5" customHeight="1">
       <c r="A71" s="50" t="inlineStr">
         <is>
           <t>004_01</t>
@@ -12852,7 +12870,7 @@
       </c>
       <c r="K71" s="50" t="inlineStr"/>
     </row>
-    <row r="72">
+    <row r="72" hidden="1">
       <c r="A72" s="50" t="inlineStr">
         <is>
           <t>004_01</t>
@@ -12891,7 +12909,7 @@
       </c>
       <c r="K72" s="50" t="inlineStr"/>
     </row>
-    <row r="73">
+    <row r="73" hidden="1">
       <c r="A73" s="55" t="inlineStr">
         <is>
           <t>004_01</t>
@@ -12973,7 +12991,7 @@
       </c>
       <c r="K74" s="50" t="inlineStr"/>
     </row>
-    <row r="75">
+    <row r="75" hidden="1">
       <c r="A75" s="50" t="inlineStr">
         <is>
           <t>004_02</t>
@@ -13012,7 +13030,7 @@
       </c>
       <c r="K75" s="50" t="inlineStr"/>
     </row>
-    <row r="76">
+    <row r="76" hidden="1">
       <c r="A76" s="50" t="inlineStr">
         <is>
           <t>004_02</t>
@@ -13051,7 +13069,7 @@
       </c>
       <c r="K76" s="50" t="inlineStr"/>
     </row>
-    <row r="77">
+    <row r="77" hidden="1">
       <c r="A77" s="50" t="inlineStr">
         <is>
           <t>004_02</t>
@@ -13090,7 +13108,7 @@
       </c>
       <c r="K77" s="50" t="inlineStr"/>
     </row>
-    <row r="78">
+    <row r="78" hidden="1">
       <c r="A78" s="50" t="inlineStr">
         <is>
           <t>004_02</t>
@@ -13129,7 +13147,7 @@
       </c>
       <c r="K78" s="50" t="inlineStr"/>
     </row>
-    <row r="79">
+    <row r="79" hidden="1">
       <c r="A79" s="55" t="inlineStr">
         <is>
           <t>004_02</t>
@@ -13254,7 +13272,7 @@
       </c>
       <c r="K81" s="50" t="inlineStr"/>
     </row>
-    <row r="82">
+    <row r="82" hidden="1">
       <c r="A82" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13293,7 +13311,7 @@
       </c>
       <c r="K82" s="50" t="inlineStr"/>
     </row>
-    <row r="83">
+    <row r="83" hidden="1">
       <c r="A83" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13332,7 +13350,7 @@
       </c>
       <c r="K83" s="50" t="inlineStr"/>
     </row>
-    <row r="84">
+    <row r="84" hidden="1">
       <c r="A84" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13371,7 +13389,7 @@
       </c>
       <c r="K84" s="50" t="inlineStr"/>
     </row>
-    <row r="85" ht="33" customHeight="1">
+    <row r="85" hidden="1" ht="33" customHeight="1">
       <c r="A85" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13410,7 +13428,7 @@
       </c>
       <c r="K85" s="50" t="inlineStr"/>
     </row>
-    <row r="86">
+    <row r="86" hidden="1">
       <c r="A86" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13449,7 +13467,7 @@
       </c>
       <c r="K86" s="55" t="inlineStr"/>
     </row>
-    <row r="87">
+    <row r="87" hidden="1">
       <c r="A87" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13488,7 +13506,7 @@
       </c>
       <c r="K87" s="55" t="inlineStr"/>
     </row>
-    <row r="88">
+    <row r="88" hidden="1">
       <c r="A88" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13527,7 +13545,7 @@
       </c>
       <c r="K88" s="55" t="inlineStr"/>
     </row>
-    <row r="89">
+    <row r="89" hidden="1">
       <c r="A89" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13566,7 +13584,7 @@
       </c>
       <c r="K89" s="55" t="inlineStr"/>
     </row>
-    <row r="90">
+    <row r="90" hidden="1">
       <c r="A90" s="50" t="inlineStr">
         <is>
           <t>004_04</t>
@@ -13640,7 +13658,7 @@
       </c>
       <c r="K91" s="50" t="inlineStr"/>
     </row>
-    <row r="92">
+    <row r="92" hidden="1">
       <c r="A92" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -13722,7 +13740,7 @@
       </c>
       <c r="K93" s="50" t="inlineStr"/>
     </row>
-    <row r="94">
+    <row r="94" hidden="1">
       <c r="A94" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -13761,7 +13779,7 @@
       </c>
       <c r="K94" s="50" t="inlineStr"/>
     </row>
-    <row r="95">
+    <row r="95" hidden="1">
       <c r="A95" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -13800,7 +13818,7 @@
       </c>
       <c r="K95" s="50" t="inlineStr"/>
     </row>
-    <row r="96">
+    <row r="96" hidden="1">
       <c r="A96" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -13839,7 +13857,7 @@
       </c>
       <c r="K96" s="55" t="inlineStr"/>
     </row>
-    <row r="97">
+    <row r="97" hidden="1">
       <c r="A97" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -13878,7 +13896,7 @@
       </c>
       <c r="K97" s="55" t="inlineStr"/>
     </row>
-    <row r="98">
+    <row r="98" hidden="1">
       <c r="A98" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -13952,7 +13970,7 @@
       </c>
       <c r="K99" s="55" t="inlineStr"/>
     </row>
-    <row r="100">
+    <row r="100" hidden="1">
       <c r="A100" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -13991,7 +14009,7 @@
       </c>
       <c r="K100" s="55" t="inlineStr"/>
     </row>
-    <row r="101">
+    <row r="101" hidden="1">
       <c r="A101" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -14073,7 +14091,7 @@
       </c>
       <c r="K102" s="55" t="inlineStr"/>
     </row>
-    <row r="103">
+    <row r="103" hidden="1">
       <c r="A103" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -14112,7 +14130,7 @@
       </c>
       <c r="K103" s="55" t="inlineStr"/>
     </row>
-    <row r="104">
+    <row r="104" hidden="1">
       <c r="A104" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -14147,7 +14165,7 @@
         </is>
       </c>
       <c r="H104" s="52" t="inlineStr"/>
-      <c r="I104" s="87" t="inlineStr"/>
+      <c r="I104" s="90" t="inlineStr"/>
       <c r="J104" s="56" t="inlineStr">
         <is>
           <t>咳咳咳，父王…</t>
@@ -14155,7 +14173,7 @@
       </c>
       <c r="K104" s="55" t="inlineStr"/>
     </row>
-    <row r="105">
+    <row r="105" hidden="1">
       <c r="A105" s="50" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -14241,7 +14259,7 @@
       </c>
       <c r="K106" s="50" t="inlineStr"/>
     </row>
-    <row r="107">
+    <row r="107" hidden="1">
       <c r="A107" s="50" t="inlineStr">
         <is>
           <t>005_02</t>
@@ -14280,7 +14298,7 @@
       </c>
       <c r="K107" s="50" t="inlineStr"/>
     </row>
-    <row r="108">
+    <row r="108" hidden="1">
       <c r="A108" s="50" t="inlineStr">
         <is>
           <t>005_02</t>
@@ -14319,7 +14337,7 @@
       </c>
       <c r="K108" s="50" t="inlineStr"/>
     </row>
-    <row r="109">
+    <row r="109" hidden="1">
       <c r="A109" s="50" t="inlineStr">
         <is>
           <t>005_02</t>
@@ -14358,7 +14376,7 @@
       </c>
       <c r="K109" s="50" t="inlineStr"/>
     </row>
-    <row r="110">
+    <row r="110" hidden="1">
       <c r="A110" s="50" t="inlineStr">
         <is>
           <t>005_02</t>
@@ -14397,7 +14415,7 @@
       </c>
       <c r="K110" s="50" t="inlineStr"/>
     </row>
-    <row r="111">
+    <row r="111" hidden="1">
       <c r="A111" s="50" t="inlineStr">
         <is>
           <t>005_02</t>
@@ -14436,7 +14454,7 @@
       </c>
       <c r="K111" s="55" t="inlineStr"/>
     </row>
-    <row r="112">
+    <row r="112" hidden="1">
       <c r="A112" s="50" t="inlineStr">
         <is>
           <t>005_02</t>
@@ -14475,7 +14493,7 @@
       </c>
       <c r="K112" s="55" t="inlineStr"/>
     </row>
-    <row r="113">
+    <row r="113" hidden="1">
       <c r="A113" s="50" t="inlineStr">
         <is>
           <t>005_02</t>
@@ -14514,7 +14532,7 @@
       </c>
       <c r="K113" s="55" t="inlineStr"/>
     </row>
-    <row r="114">
+    <row r="114" hidden="1">
       <c r="A114" s="50" t="inlineStr">
         <is>
           <t>005_02</t>
@@ -14592,7 +14610,7 @@
       </c>
       <c r="K115" s="50" t="inlineStr"/>
     </row>
-    <row r="116">
+    <row r="116" hidden="1">
       <c r="A116" s="50" t="inlineStr">
         <is>
           <t>005_03</t>
@@ -14631,7 +14649,7 @@
       </c>
       <c r="K116" s="50" t="inlineStr"/>
     </row>
-    <row r="117">
+    <row r="117" hidden="1">
       <c r="A117" s="50" t="inlineStr">
         <is>
           <t>005_03</t>
@@ -14670,7 +14688,7 @@
       </c>
       <c r="K117" s="50" t="inlineStr"/>
     </row>
-    <row r="118">
+    <row r="118" hidden="1">
       <c r="A118" s="50" t="inlineStr">
         <is>
           <t>005_03</t>
@@ -14709,7 +14727,7 @@
       </c>
       <c r="K118" s="50" t="inlineStr"/>
     </row>
-    <row r="119">
+    <row r="119" hidden="1">
       <c r="A119" s="50" t="inlineStr">
         <is>
           <t>005_03</t>
@@ -14791,7 +14809,7 @@
       </c>
       <c r="K120" s="50" t="inlineStr"/>
     </row>
-    <row r="121">
+    <row r="121" hidden="1">
       <c r="A121" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -14830,7 +14848,7 @@
       </c>
       <c r="K121" s="50" t="inlineStr"/>
     </row>
-    <row r="122">
+    <row r="122" hidden="1">
       <c r="A122" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -14869,7 +14887,7 @@
       </c>
       <c r="K122" s="50" t="inlineStr"/>
     </row>
-    <row r="123">
+    <row r="123" hidden="1">
       <c r="A123" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -14908,7 +14926,7 @@
       </c>
       <c r="K123" s="50" t="inlineStr"/>
     </row>
-    <row r="124">
+    <row r="124" hidden="1">
       <c r="A124" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -14947,7 +14965,7 @@
       </c>
       <c r="K124" s="50" t="inlineStr"/>
     </row>
-    <row r="125">
+    <row r="125" hidden="1">
       <c r="A125" s="55" t="inlineStr">
         <is>
           <t>006</t>
@@ -14986,7 +15004,7 @@
       </c>
       <c r="K125" s="55" t="inlineStr"/>
     </row>
-    <row r="126">
+    <row r="126" hidden="1">
       <c r="A126" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -15025,7 +15043,7 @@
       </c>
       <c r="K126" s="55" t="inlineStr"/>
     </row>
-    <row r="127">
+    <row r="127" hidden="1">
       <c r="A127" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -15064,7 +15082,7 @@
       </c>
       <c r="K127" s="55" t="inlineStr"/>
     </row>
-    <row r="128">
+    <row r="128" hidden="1">
       <c r="A128" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -15103,7 +15121,7 @@
       </c>
       <c r="K128" s="55" t="inlineStr"/>
     </row>
-    <row r="129">
+    <row r="129" hidden="1">
       <c r="A129" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -15142,7 +15160,7 @@
       </c>
       <c r="K129" s="55" t="inlineStr"/>
     </row>
-    <row r="130">
+    <row r="130" hidden="1">
       <c r="A130" s="50" t="inlineStr">
         <is>
           <t>006</t>
@@ -15181,7 +15199,7 @@
       </c>
       <c r="K130" s="55" t="inlineStr"/>
     </row>
-    <row r="131">
+    <row r="131" hidden="1">
       <c r="A131" s="55" t="inlineStr">
         <is>
           <t>006</t>
@@ -15220,7 +15238,7 @@
       </c>
       <c r="K131" s="55" t="inlineStr"/>
     </row>
-    <row r="132">
+    <row r="132" hidden="1">
       <c r="A132" s="55" t="inlineStr">
         <is>
           <t>006</t>
@@ -15259,7 +15277,7 @@
       </c>
       <c r="K132" s="55" t="inlineStr"/>
     </row>
-    <row r="133">
+    <row r="133" hidden="1">
       <c r="A133" s="55" t="inlineStr">
         <is>
           <t>006</t>
@@ -15341,7 +15359,7 @@
       </c>
       <c r="K134" s="50" t="inlineStr"/>
     </row>
-    <row r="135">
+    <row r="135" hidden="1">
       <c r="A135" s="50" t="inlineStr">
         <is>
           <t>007_01</t>
@@ -15380,7 +15398,7 @@
       </c>
       <c r="K135" s="50" t="inlineStr"/>
     </row>
-    <row r="136">
+    <row r="136" hidden="1">
       <c r="A136" s="50" t="inlineStr">
         <is>
           <t>007_01</t>
@@ -15419,7 +15437,7 @@
       </c>
       <c r="K136" s="50" t="inlineStr"/>
     </row>
-    <row r="137">
+    <row r="137" hidden="1">
       <c r="A137" s="50" t="inlineStr">
         <is>
           <t>007_01</t>
@@ -15501,7 +15519,7 @@
       </c>
       <c r="K138" s="50" t="inlineStr"/>
     </row>
-    <row r="139">
+    <row r="139" hidden="1">
       <c r="A139" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15540,7 +15558,7 @@
       </c>
       <c r="K139" s="50" t="inlineStr"/>
     </row>
-    <row r="140">
+    <row r="140" hidden="1">
       <c r="A140" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15579,7 +15597,7 @@
       </c>
       <c r="K140" s="50" t="inlineStr"/>
     </row>
-    <row r="141">
+    <row r="141" hidden="1">
       <c r="A141" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15618,7 +15636,7 @@
       </c>
       <c r="K141" s="50" t="inlineStr"/>
     </row>
-    <row r="142" ht="18.75" customHeight="1">
+    <row r="142" hidden="1" ht="18.75" customHeight="1">
       <c r="A142" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15657,7 +15675,7 @@
       </c>
       <c r="K142" s="50" t="inlineStr"/>
     </row>
-    <row r="143">
+    <row r="143" hidden="1">
       <c r="A143" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15696,7 +15714,7 @@
       </c>
       <c r="K143" s="55" t="inlineStr"/>
     </row>
-    <row r="144">
+    <row r="144" hidden="1">
       <c r="A144" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15735,7 +15753,7 @@
       </c>
       <c r="K144" s="55" t="inlineStr"/>
     </row>
-    <row r="145">
+    <row r="145" hidden="1">
       <c r="A145" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15774,7 +15792,7 @@
       </c>
       <c r="K145" s="55" t="inlineStr"/>
     </row>
-    <row r="146">
+    <row r="146" hidden="1">
       <c r="A146" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15813,7 +15831,7 @@
       </c>
       <c r="K146" s="55" t="inlineStr"/>
     </row>
-    <row r="147">
+    <row r="147" hidden="1">
       <c r="A147" s="50" t="inlineStr">
         <is>
           <t>007_02</t>
@@ -15938,7 +15956,7 @@
       </c>
       <c r="K149" s="50" t="inlineStr"/>
     </row>
-    <row r="150">
+    <row r="150" hidden="1">
       <c r="A150" s="50" t="inlineStr">
         <is>
           <t>008_01</t>
@@ -15977,7 +15995,7 @@
       </c>
       <c r="K150" s="50" t="inlineStr"/>
     </row>
-    <row r="151">
+    <row r="151" hidden="1">
       <c r="A151" s="50" t="inlineStr">
         <is>
           <t>008_01</t>
@@ -16016,7 +16034,7 @@
       </c>
       <c r="K151" s="50" t="inlineStr"/>
     </row>
-    <row r="152">
+    <row r="152" hidden="1">
       <c r="A152" s="50" t="inlineStr">
         <is>
           <t>008_01</t>
@@ -16059,7 +16077,7 @@
       </c>
       <c r="K152" s="50" t="inlineStr"/>
     </row>
-    <row r="153">
+    <row r="153" hidden="1">
       <c r="A153" s="50" t="inlineStr">
         <is>
           <t>008_01</t>
@@ -16098,7 +16116,7 @@
       </c>
       <c r="K153" s="50" t="inlineStr"/>
     </row>
-    <row r="154">
+    <row r="154" hidden="1">
       <c r="A154" s="50" t="inlineStr">
         <is>
           <t>008_01</t>
@@ -16184,7 +16202,7 @@
       </c>
       <c r="K155" s="50" t="inlineStr"/>
     </row>
-    <row r="156">
+    <row r="156" hidden="1">
       <c r="A156" s="50" t="inlineStr">
         <is>
           <t>008_02</t>
@@ -16223,7 +16241,7 @@
       </c>
       <c r="K156" s="50" t="inlineStr"/>
     </row>
-    <row r="157">
+    <row r="157" hidden="1">
       <c r="A157" s="50" t="inlineStr">
         <is>
           <t>008_02</t>
@@ -16266,7 +16284,7 @@
       </c>
       <c r="K157" s="50" t="inlineStr"/>
     </row>
-    <row r="158">
+    <row r="158" hidden="1">
       <c r="A158" s="50" t="inlineStr">
         <is>
           <t>008_02</t>
@@ -16305,7 +16323,7 @@
       </c>
       <c r="K158" s="50" t="inlineStr"/>
     </row>
-    <row r="159">
+    <row r="159" hidden="1">
       <c r="A159" s="50" t="inlineStr">
         <is>
           <t>008_02</t>
@@ -16430,7 +16448,7 @@
       </c>
       <c r="K161" s="50" t="inlineStr"/>
     </row>
-    <row r="162">
+    <row r="162" hidden="1">
       <c r="A162" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16512,7 +16530,7 @@
       </c>
       <c r="K163" s="50" t="inlineStr"/>
     </row>
-    <row r="164" ht="33" customHeight="1">
+    <row r="164" hidden="1" ht="33" customHeight="1">
       <c r="A164" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16551,7 +16569,7 @@
       </c>
       <c r="K164" s="50" t="inlineStr"/>
     </row>
-    <row r="165">
+    <row r="165" hidden="1">
       <c r="A165" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16590,7 +16608,7 @@
       </c>
       <c r="K165" s="50" t="inlineStr"/>
     </row>
-    <row r="166">
+    <row r="166" hidden="1">
       <c r="A166" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16672,7 +16690,7 @@
       </c>
       <c r="K167" s="55" t="inlineStr"/>
     </row>
-    <row r="168">
+    <row r="168" hidden="1">
       <c r="A168" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16711,7 +16729,7 @@
       </c>
       <c r="K168" s="55" t="inlineStr"/>
     </row>
-    <row r="169">
+    <row r="169" hidden="1">
       <c r="A169" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16793,7 +16811,7 @@
       </c>
       <c r="K170" s="55" t="inlineStr"/>
     </row>
-    <row r="171">
+    <row r="171" hidden="1">
       <c r="A171" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16832,7 +16850,7 @@
       </c>
       <c r="K171" s="55" t="inlineStr"/>
     </row>
-    <row r="172">
+    <row r="172" hidden="1">
       <c r="A172" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16871,7 +16889,7 @@
       </c>
       <c r="K172" s="55" t="inlineStr"/>
     </row>
-    <row r="173">
+    <row r="173" hidden="1">
       <c r="A173" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16910,7 +16928,7 @@
       </c>
       <c r="K173" s="55" t="inlineStr"/>
     </row>
-    <row r="174">
+    <row r="174" hidden="1">
       <c r="A174" s="50" t="inlineStr">
         <is>
           <t>009</t>
@@ -16992,7 +17010,7 @@
       </c>
       <c r="K175" s="50" t="inlineStr"/>
     </row>
-    <row r="176">
+    <row r="176" hidden="1">
       <c r="A176" s="50" t="inlineStr">
         <is>
           <t>010</t>
@@ -17035,7 +17053,7 @@
       </c>
       <c r="K176" s="50" t="inlineStr"/>
     </row>
-    <row r="177">
+    <row r="177" hidden="1">
       <c r="A177" s="50" t="inlineStr">
         <is>
           <t>010</t>
@@ -17074,7 +17092,7 @@
       </c>
       <c r="K177" s="50" t="inlineStr"/>
     </row>
-    <row r="178">
+    <row r="178" hidden="1">
       <c r="A178" s="50" t="inlineStr">
         <is>
           <t>010</t>
@@ -17113,7 +17131,7 @@
       </c>
       <c r="K178" s="50" t="inlineStr"/>
     </row>
-    <row r="179">
+    <row r="179" hidden="1">
       <c r="A179" s="50" t="inlineStr">
         <is>
           <t>010</t>
@@ -17152,7 +17170,7 @@
       </c>
       <c r="K179" s="50" t="inlineStr"/>
     </row>
-    <row r="180">
+    <row r="180" hidden="1">
       <c r="A180" s="50" t="inlineStr">
         <is>
           <t>010</t>
@@ -17234,7 +17252,7 @@
       </c>
       <c r="K181" s="50" t="inlineStr"/>
     </row>
-    <row r="182">
+    <row r="182" hidden="1">
       <c r="A182" s="50" t="inlineStr">
         <is>
           <t>011</t>
@@ -17273,7 +17291,7 @@
       </c>
       <c r="K182" s="50" t="inlineStr"/>
     </row>
-    <row r="183">
+    <row r="183" hidden="1">
       <c r="A183" s="50" t="inlineStr">
         <is>
           <t>011</t>
@@ -17312,7 +17330,7 @@
       </c>
       <c r="K183" s="50" t="inlineStr"/>
     </row>
-    <row r="184">
+    <row r="184" hidden="1">
       <c r="A184" s="50" t="inlineStr">
         <is>
           <t>011</t>
@@ -17351,7 +17369,7 @@
       </c>
       <c r="K184" s="50" t="inlineStr"/>
     </row>
-    <row r="185">
+    <row r="185" hidden="1">
       <c r="A185" s="50" t="inlineStr">
         <is>
           <t>011</t>
@@ -17390,7 +17408,7 @@
       </c>
       <c r="K185" s="50" t="inlineStr"/>
     </row>
-    <row r="186">
+    <row r="186" hidden="1">
       <c r="A186" s="50" t="inlineStr">
         <is>
           <t>011</t>
@@ -17429,7 +17447,7 @@
       </c>
       <c r="K186" s="55" t="inlineStr"/>
     </row>
-    <row r="187">
+    <row r="187" hidden="1">
       <c r="A187" s="50" t="inlineStr">
         <is>
           <t>011</t>
@@ -17468,7 +17486,7 @@
       </c>
       <c r="K187" s="55" t="inlineStr"/>
     </row>
-    <row r="188">
+    <row r="188" hidden="1">
       <c r="A188" s="50" t="inlineStr">
         <is>
           <t>011</t>
@@ -17550,7 +17568,7 @@
       </c>
       <c r="K189" s="50" t="inlineStr"/>
     </row>
-    <row r="190">
+    <row r="190" hidden="1">
       <c r="A190" s="50" t="inlineStr">
         <is>
           <t>012</t>
@@ -17589,7 +17607,7 @@
       </c>
       <c r="K190" s="50" t="inlineStr"/>
     </row>
-    <row r="191" ht="33" customHeight="1">
+    <row r="191" hidden="1" ht="33" customHeight="1">
       <c r="A191" s="50" t="inlineStr">
         <is>
           <t>012</t>
@@ -17628,7 +17646,7 @@
       </c>
       <c r="K191" s="50" t="inlineStr"/>
     </row>
-    <row r="192">
+    <row r="192" hidden="1">
       <c r="A192" s="50" t="inlineStr">
         <is>
           <t>012</t>
@@ -17667,7 +17685,7 @@
       </c>
       <c r="K192" s="50" t="inlineStr"/>
     </row>
-    <row r="193">
+    <row r="193" hidden="1">
       <c r="A193" s="50" t="inlineStr">
         <is>
           <t>012</t>
@@ -17706,7 +17724,7 @@
       </c>
       <c r="K193" s="50" t="inlineStr"/>
     </row>
-    <row r="194">
+    <row r="194" hidden="1">
       <c r="A194" s="50" t="inlineStr">
         <is>
           <t>012</t>
@@ -17745,7 +17763,7 @@
       </c>
       <c r="K194" s="55" t="inlineStr"/>
     </row>
-    <row r="195">
+    <row r="195" hidden="1">
       <c r="A195" s="50" t="inlineStr">
         <is>
           <t>012</t>
@@ -17827,7 +17845,7 @@
       </c>
       <c r="K196" s="50" t="inlineStr"/>
     </row>
-    <row r="197">
+    <row r="197" hidden="1">
       <c r="A197" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -17866,7 +17884,7 @@
       </c>
       <c r="K197" s="50" t="inlineStr"/>
     </row>
-    <row r="198">
+    <row r="198" hidden="1">
       <c r="A198" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -17905,7 +17923,7 @@
       </c>
       <c r="K198" s="50" t="inlineStr"/>
     </row>
-    <row r="199">
+    <row r="199" hidden="1">
       <c r="A199" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -17944,7 +17962,7 @@
       </c>
       <c r="K199" s="50" t="inlineStr"/>
     </row>
-    <row r="200">
+    <row r="200" hidden="1">
       <c r="A200" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -17983,7 +18001,7 @@
       </c>
       <c r="K200" s="50" t="inlineStr"/>
     </row>
-    <row r="201">
+    <row r="201" hidden="1">
       <c r="A201" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -18022,7 +18040,7 @@
       </c>
       <c r="K201" s="55" t="inlineStr"/>
     </row>
-    <row r="202">
+    <row r="202" hidden="1">
       <c r="A202" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -18061,7 +18079,7 @@
       </c>
       <c r="K202" s="55" t="inlineStr"/>
     </row>
-    <row r="203">
+    <row r="203" hidden="1">
       <c r="A203" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -18100,7 +18118,7 @@
       </c>
       <c r="K203" s="55" t="inlineStr"/>
     </row>
-    <row r="204">
+    <row r="204" hidden="1">
       <c r="A204" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -18139,7 +18157,7 @@
       </c>
       <c r="K204" s="55" t="inlineStr"/>
     </row>
-    <row r="205">
+    <row r="205" hidden="1">
       <c r="A205" s="50" t="inlineStr">
         <is>
           <t>013</t>
@@ -18221,7 +18239,7 @@
       </c>
       <c r="K206" s="50" t="inlineStr"/>
     </row>
-    <row r="207">
+    <row r="207" hidden="1">
       <c r="A207" s="50" t="inlineStr">
         <is>
           <t>014_01</t>
@@ -18260,7 +18278,7 @@
       </c>
       <c r="K207" s="50" t="inlineStr"/>
     </row>
-    <row r="208">
+    <row r="208" hidden="1">
       <c r="A208" s="50" t="inlineStr">
         <is>
           <t>014_01</t>
@@ -18342,7 +18360,7 @@
       </c>
       <c r="K209" s="50" t="inlineStr"/>
     </row>
-    <row r="210">
+    <row r="210" hidden="1">
       <c r="A210" s="50" t="inlineStr">
         <is>
           <t>014_02</t>
@@ -18381,7 +18399,7 @@
       </c>
       <c r="K210" s="50" t="inlineStr"/>
     </row>
-    <row r="211">
+    <row r="211" hidden="1">
       <c r="A211" s="50" t="inlineStr">
         <is>
           <t>014_02</t>
@@ -18420,7 +18438,7 @@
       </c>
       <c r="K211" s="50" t="inlineStr"/>
     </row>
-    <row r="212">
+    <row r="212" hidden="1">
       <c r="A212" s="50" t="inlineStr">
         <is>
           <t>014_02</t>
@@ -18459,7 +18477,7 @@
       </c>
       <c r="K212" s="50" t="inlineStr"/>
     </row>
-    <row r="213">
+    <row r="213" hidden="1">
       <c r="A213" s="50" t="inlineStr">
         <is>
           <t>014_02</t>
@@ -18498,7 +18516,7 @@
       </c>
       <c r="K213" s="50" t="inlineStr"/>
     </row>
-    <row r="214">
+    <row r="214" hidden="1">
       <c r="A214" s="50" t="inlineStr">
         <is>
           <t>014_02</t>
@@ -18537,7 +18555,7 @@
       </c>
       <c r="K214" s="55" t="inlineStr"/>
     </row>
-    <row r="215">
+    <row r="215" hidden="1">
       <c r="A215" s="50" t="inlineStr">
         <is>
           <t>014_02</t>
@@ -18576,7 +18594,7 @@
       </c>
       <c r="K215" s="55" t="inlineStr"/>
     </row>
-    <row r="216">
+    <row r="216" hidden="1">
       <c r="A216" s="50" t="inlineStr">
         <is>
           <t>014_02</t>
@@ -18615,7 +18633,7 @@
       </c>
       <c r="K216" s="55" t="inlineStr"/>
     </row>
-    <row r="217">
+    <row r="217" hidden="1">
       <c r="A217" s="50" t="inlineStr">
         <is>
           <t>014_02</t>
@@ -18732,7 +18750,7 @@
       </c>
       <c r="K219" s="50" t="inlineStr"/>
     </row>
-    <row r="220">
+    <row r="220" hidden="1">
       <c r="A220" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -18771,7 +18789,7 @@
       </c>
       <c r="K220" s="50" t="inlineStr"/>
     </row>
-    <row r="221">
+    <row r="221" hidden="1">
       <c r="A221" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -18810,7 +18828,7 @@
       </c>
       <c r="K221" s="50" t="inlineStr"/>
     </row>
-    <row r="222">
+    <row r="222" hidden="1">
       <c r="A222" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -18849,7 +18867,7 @@
       </c>
       <c r="K222" s="50" t="inlineStr"/>
     </row>
-    <row r="223">
+    <row r="223" hidden="1">
       <c r="A223" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -18888,7 +18906,7 @@
       </c>
       <c r="K223" s="50" t="inlineStr"/>
     </row>
-    <row r="224">
+    <row r="224" hidden="1">
       <c r="A224" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -18927,7 +18945,7 @@
       </c>
       <c r="K224" s="55" t="inlineStr"/>
     </row>
-    <row r="225">
+    <row r="225" hidden="1">
       <c r="A225" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -18966,7 +18984,7 @@
       </c>
       <c r="K225" s="55" t="inlineStr"/>
     </row>
-    <row r="226">
+    <row r="226" hidden="1">
       <c r="A226" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19005,7 +19023,7 @@
       </c>
       <c r="K226" s="55" t="inlineStr"/>
     </row>
-    <row r="227">
+    <row r="227" hidden="1">
       <c r="A227" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19044,7 +19062,7 @@
       </c>
       <c r="K227" s="55" t="inlineStr"/>
     </row>
-    <row r="228">
+    <row r="228" hidden="1">
       <c r="A228" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19083,7 +19101,7 @@
       </c>
       <c r="K228" s="55" t="inlineStr"/>
     </row>
-    <row r="229">
+    <row r="229" hidden="1">
       <c r="A229" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19122,7 +19140,7 @@
       </c>
       <c r="K229" s="55" t="inlineStr"/>
     </row>
-    <row r="230">
+    <row r="230" hidden="1">
       <c r="A230" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19161,7 +19179,7 @@
       </c>
       <c r="K230" s="55" t="inlineStr"/>
     </row>
-    <row r="231">
+    <row r="231" hidden="1">
       <c r="A231" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19278,7 +19296,7 @@
       </c>
       <c r="K233" s="55" t="inlineStr"/>
     </row>
-    <row r="234">
+    <row r="234" hidden="1">
       <c r="A234" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19317,7 +19335,7 @@
       </c>
       <c r="K234" s="55" t="inlineStr"/>
     </row>
-    <row r="235">
+    <row r="235" hidden="1">
       <c r="A235" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19356,7 +19374,7 @@
       </c>
       <c r="K235" s="55" t="inlineStr"/>
     </row>
-    <row r="236">
+    <row r="236" hidden="1">
       <c r="A236" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19387,7 +19405,7 @@
       </c>
       <c r="K236" s="55" t="inlineStr"/>
     </row>
-    <row r="237">
+    <row r="237" hidden="1">
       <c r="A237" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19426,7 +19444,7 @@
       </c>
       <c r="K237" s="55" t="inlineStr"/>
     </row>
-    <row r="238">
+    <row r="238" hidden="1">
       <c r="A238" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19465,7 +19483,7 @@
       </c>
       <c r="K238" s="55" t="inlineStr"/>
     </row>
-    <row r="239">
+    <row r="239" hidden="1">
       <c r="A239" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19504,7 +19522,7 @@
       </c>
       <c r="K239" s="55" t="inlineStr"/>
     </row>
-    <row r="240">
+    <row r="240" hidden="1">
       <c r="A240" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19543,7 +19561,7 @@
       </c>
       <c r="K240" s="55" t="inlineStr"/>
     </row>
-    <row r="241">
+    <row r="241" hidden="1">
       <c r="A241" s="50" t="inlineStr">
         <is>
           <t>015</t>
@@ -19625,7 +19643,7 @@
       </c>
       <c r="K242" s="50" t="inlineStr"/>
     </row>
-    <row r="243">
+    <row r="243" hidden="1">
       <c r="A243" s="50" t="inlineStr">
         <is>
           <t>016</t>
@@ -19664,7 +19682,7 @@
       </c>
       <c r="K243" s="50" t="inlineStr"/>
     </row>
-    <row r="244">
+    <row r="244" hidden="1">
       <c r="A244" s="50" t="inlineStr">
         <is>
           <t>016</t>
@@ -19703,7 +19721,7 @@
       </c>
       <c r="K244" s="50" t="inlineStr"/>
     </row>
-    <row r="245">
+    <row r="245" hidden="1">
       <c r="A245" s="50" t="inlineStr">
         <is>
           <t>016</t>
@@ -19742,7 +19760,7 @@
       </c>
       <c r="K245" s="50" t="inlineStr"/>
     </row>
-    <row r="246">
+    <row r="246" hidden="1">
       <c r="A246" s="50" t="inlineStr">
         <is>
           <t>016</t>
@@ -19781,7 +19799,7 @@
       </c>
       <c r="K246" s="50" t="inlineStr"/>
     </row>
-    <row r="247">
+    <row r="247" hidden="1">
       <c r="A247" s="50" t="inlineStr">
         <is>
           <t>016</t>
@@ -19820,7 +19838,7 @@
       </c>
       <c r="K247" s="50" t="inlineStr"/>
     </row>
-    <row r="248">
+    <row r="248" hidden="1">
       <c r="A248" s="50" t="inlineStr">
         <is>
           <t>016</t>
@@ -19859,7 +19877,7 @@
       </c>
       <c r="K248" s="50" t="inlineStr"/>
     </row>
-    <row r="249">
+    <row r="249" hidden="1">
       <c r="A249" s="50" t="inlineStr">
         <is>
           <t>016</t>
@@ -19898,7 +19916,7 @@
       </c>
       <c r="K249" s="50" t="inlineStr"/>
     </row>
-    <row r="250">
+    <row r="250" hidden="1">
       <c r="A250" s="50" t="inlineStr">
         <is>
           <t>016</t>
@@ -19984,7 +20002,7 @@
       </c>
       <c r="K251" s="50" t="inlineStr"/>
     </row>
-    <row r="252">
+    <row r="252" hidden="1">
       <c r="A252" s="50" t="inlineStr">
         <is>
           <t>017_01</t>
@@ -20066,7 +20084,7 @@
       </c>
       <c r="K253" s="50" t="inlineStr"/>
     </row>
-    <row r="254">
+    <row r="254" hidden="1">
       <c r="A254" s="50" t="inlineStr">
         <is>
           <t>017_02</t>
@@ -20109,7 +20127,7 @@
       </c>
       <c r="K254" s="50" t="inlineStr"/>
     </row>
-    <row r="255">
+    <row r="255" hidden="1">
       <c r="A255" s="50" t="inlineStr">
         <is>
           <t>017_02</t>
@@ -20148,7 +20166,7 @@
       </c>
       <c r="K255" s="50" t="inlineStr"/>
     </row>
-    <row r="256">
+    <row r="256" hidden="1">
       <c r="A256" s="50" t="inlineStr">
         <is>
           <t>017_02</t>
@@ -20191,7 +20209,7 @@
       </c>
       <c r="K256" s="50" t="inlineStr"/>
     </row>
-    <row r="257">
+    <row r="257" hidden="1">
       <c r="A257" s="50" t="inlineStr">
         <is>
           <t>017_02</t>
@@ -20230,7 +20248,7 @@
       </c>
       <c r="K257" s="50" t="inlineStr"/>
     </row>
-    <row r="258">
+    <row r="258" hidden="1">
       <c r="A258" s="50" t="inlineStr">
         <is>
           <t>017_02</t>
@@ -20273,7 +20291,7 @@
       </c>
       <c r="K258" s="55" t="inlineStr"/>
     </row>
-    <row r="259">
+    <row r="259" hidden="1">
       <c r="A259" s="50" t="inlineStr">
         <is>
           <t>017_02</t>
@@ -20316,7 +20334,7 @@
       </c>
       <c r="K259" s="55" t="inlineStr"/>
     </row>
-    <row r="260">
+    <row r="260" hidden="1">
       <c r="A260" s="50" t="inlineStr">
         <is>
           <t>017_02</t>
@@ -20433,7 +20451,7 @@
       </c>
       <c r="K262" s="50" t="inlineStr"/>
     </row>
-    <row r="263">
+    <row r="263" hidden="1">
       <c r="A263" s="50" t="inlineStr">
         <is>
           <t>018</t>
@@ -20472,7 +20490,7 @@
       </c>
       <c r="K263" s="50" t="inlineStr"/>
     </row>
-    <row r="264">
+    <row r="264" hidden="1">
       <c r="A264" s="50" t="inlineStr">
         <is>
           <t>018</t>
@@ -20554,7 +20572,7 @@
       </c>
       <c r="K265" s="50" t="inlineStr"/>
     </row>
-    <row r="266">
+    <row r="266" hidden="1">
       <c r="A266" s="50" t="inlineStr">
         <is>
           <t>018</t>
@@ -20593,7 +20611,7 @@
       </c>
       <c r="K266" s="50" t="inlineStr"/>
     </row>
-    <row r="267">
+    <row r="267" hidden="1">
       <c r="A267" s="50" t="inlineStr">
         <is>
           <t>018</t>
@@ -20675,7 +20693,7 @@
       </c>
       <c r="K268" s="50" t="inlineStr"/>
     </row>
-    <row r="269">
+    <row r="269" hidden="1">
       <c r="A269" s="50" t="inlineStr">
         <is>
           <t>019</t>
@@ -20714,7 +20732,7 @@
       </c>
       <c r="K269" s="50" t="inlineStr"/>
     </row>
-    <row r="270">
+    <row r="270" hidden="1">
       <c r="A270" s="50" t="inlineStr">
         <is>
           <t>019</t>
@@ -20753,7 +20771,7 @@
       </c>
       <c r="K270" s="50" t="inlineStr"/>
     </row>
-    <row r="271">
+    <row r="271" hidden="1">
       <c r="A271" s="50" t="inlineStr">
         <is>
           <t>019</t>
@@ -20792,7 +20810,7 @@
       </c>
       <c r="K271" s="50" t="inlineStr"/>
     </row>
-    <row r="272">
+    <row r="272" hidden="1">
       <c r="A272" s="50" t="inlineStr">
         <is>
           <t>019</t>
@@ -20870,7 +20888,7 @@
         </is>
       </c>
     </row>
-    <row r="274">
+    <row r="274" hidden="1">
       <c r="A274" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21030,7 +21048,7 @@
       </c>
       <c r="K277" s="50" t="inlineStr"/>
     </row>
-    <row r="278">
+    <row r="278" hidden="1">
       <c r="A278" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21069,7 +21087,7 @@
       </c>
       <c r="K278" s="55" t="inlineStr"/>
     </row>
-    <row r="279">
+    <row r="279" hidden="1">
       <c r="A279" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21159,7 +21177,7 @@
       </c>
       <c r="K280" s="55" t="inlineStr"/>
     </row>
-    <row r="281">
+    <row r="281" hidden="1">
       <c r="A281" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21198,7 +21216,7 @@
       </c>
       <c r="K281" s="55" t="inlineStr"/>
     </row>
-    <row r="282">
+    <row r="282" hidden="1">
       <c r="A282" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21280,7 +21298,7 @@
       </c>
       <c r="K283" s="55" t="inlineStr"/>
     </row>
-    <row r="284">
+    <row r="284" hidden="1">
       <c r="A284" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21319,7 +21337,7 @@
       </c>
       <c r="K284" s="55" t="inlineStr"/>
     </row>
-    <row r="285">
+    <row r="285" hidden="1">
       <c r="A285" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21358,7 +21376,7 @@
       </c>
       <c r="K285" s="55" t="inlineStr"/>
     </row>
-    <row r="286">
+    <row r="286" hidden="1">
       <c r="A286" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21397,7 +21415,7 @@
       </c>
       <c r="K286" s="55" t="inlineStr"/>
     </row>
-    <row r="287">
+    <row r="287" hidden="1">
       <c r="A287" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21436,7 +21454,7 @@
       </c>
       <c r="K287" s="55" t="inlineStr"/>
     </row>
-    <row r="288">
+    <row r="288" hidden="1">
       <c r="A288" s="50" t="inlineStr">
         <is>
           <t>020</t>
@@ -21506,7 +21524,7 @@
         </is>
       </c>
     </row>
-    <row r="290">
+    <row r="290" hidden="1">
       <c r="A290" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21537,7 +21555,7 @@
       </c>
       <c r="K290" s="50" t="inlineStr"/>
     </row>
-    <row r="291">
+    <row r="291" hidden="1">
       <c r="A291" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21568,7 +21586,7 @@
       </c>
       <c r="K291" s="50" t="inlineStr"/>
     </row>
-    <row r="292">
+    <row r="292" hidden="1">
       <c r="A292" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21607,7 +21625,7 @@
       </c>
       <c r="K292" s="50" t="inlineStr"/>
     </row>
-    <row r="293">
+    <row r="293" hidden="1">
       <c r="A293" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21646,7 +21664,7 @@
       </c>
       <c r="K293" s="50" t="inlineStr"/>
     </row>
-    <row r="294">
+    <row r="294" hidden="1">
       <c r="A294" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21685,7 +21703,7 @@
       </c>
       <c r="K294" s="50" t="inlineStr"/>
     </row>
-    <row r="295">
+    <row r="295" hidden="1">
       <c r="A295" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21724,7 +21742,7 @@
       </c>
       <c r="K295" s="50" t="inlineStr"/>
     </row>
-    <row r="296">
+    <row r="296" hidden="1">
       <c r="A296" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21763,7 +21781,7 @@
       </c>
       <c r="K296" s="50" t="inlineStr"/>
     </row>
-    <row r="297">
+    <row r="297" hidden="1">
       <c r="A297" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21802,7 +21820,7 @@
       </c>
       <c r="K297" s="50" t="inlineStr"/>
     </row>
-    <row r="298">
+    <row r="298" hidden="1">
       <c r="A298" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -21884,7 +21902,7 @@
       </c>
       <c r="K299" s="50" t="inlineStr"/>
     </row>
-    <row r="300">
+    <row r="300" hidden="1">
       <c r="A300" s="50" t="inlineStr">
         <is>
           <t>022_01</t>
@@ -21966,7 +21984,7 @@
       </c>
       <c r="K301" s="50" t="inlineStr"/>
     </row>
-    <row r="302">
+    <row r="302" hidden="1">
       <c r="A302" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22005,7 +22023,7 @@
       </c>
       <c r="K302" s="50" t="inlineStr"/>
     </row>
-    <row r="303">
+    <row r="303" hidden="1">
       <c r="A303" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22044,7 +22062,7 @@
       </c>
       <c r="K303" s="50" t="inlineStr"/>
     </row>
-    <row r="304">
+    <row r="304" hidden="1">
       <c r="A304" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22083,7 +22101,7 @@
       </c>
       <c r="K304" s="50" t="inlineStr"/>
     </row>
-    <row r="305">
+    <row r="305" hidden="1">
       <c r="A305" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22122,7 +22140,7 @@
       </c>
       <c r="K305" s="50" t="inlineStr"/>
     </row>
-    <row r="306">
+    <row r="306" hidden="1">
       <c r="A306" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22161,7 +22179,7 @@
       </c>
       <c r="K306" s="55" t="inlineStr"/>
     </row>
-    <row r="307">
+    <row r="307" hidden="1">
       <c r="A307" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22200,7 +22218,7 @@
       </c>
       <c r="K307" s="55" t="inlineStr"/>
     </row>
-    <row r="308">
+    <row r="308" hidden="1">
       <c r="A308" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22239,7 +22257,7 @@
       </c>
       <c r="K308" s="55" t="inlineStr"/>
     </row>
-    <row r="309">
+    <row r="309" hidden="1">
       <c r="A309" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22278,7 +22296,7 @@
       </c>
       <c r="K309" s="55" t="inlineStr"/>
     </row>
-    <row r="310">
+    <row r="310" hidden="1">
       <c r="A310" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22317,7 +22335,7 @@
       </c>
       <c r="K310" s="55" t="inlineStr"/>
     </row>
-    <row r="311">
+    <row r="311" hidden="1">
       <c r="A311" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22356,7 +22374,7 @@
       </c>
       <c r="K311" s="55" t="inlineStr"/>
     </row>
-    <row r="312">
+    <row r="312" hidden="1">
       <c r="A312" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22395,7 +22413,7 @@
       </c>
       <c r="K312" s="55" t="inlineStr"/>
     </row>
-    <row r="313">
+    <row r="313" hidden="1">
       <c r="A313" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22434,7 +22452,7 @@
       </c>
       <c r="K313" s="55" t="inlineStr"/>
     </row>
-    <row r="314">
+    <row r="314" hidden="1">
       <c r="A314" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22473,7 +22491,7 @@
       </c>
       <c r="K314" s="55" t="inlineStr"/>
     </row>
-    <row r="315">
+    <row r="315" hidden="1">
       <c r="A315" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22512,7 +22530,7 @@
       </c>
       <c r="K315" s="55" t="inlineStr"/>
     </row>
-    <row r="316">
+    <row r="316" hidden="1">
       <c r="A316" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22551,7 +22569,7 @@
       </c>
       <c r="K316" s="55" t="inlineStr"/>
     </row>
-    <row r="317">
+    <row r="317" hidden="1">
       <c r="A317" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22590,7 +22608,7 @@
       </c>
       <c r="K317" s="55" t="inlineStr"/>
     </row>
-    <row r="318">
+    <row r="318" hidden="1">
       <c r="A318" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22629,7 +22647,7 @@
       </c>
       <c r="K318" s="55" t="inlineStr"/>
     </row>
-    <row r="319">
+    <row r="319" hidden="1">
       <c r="A319" s="55" t="inlineStr">
         <is>
           <t>022_02</t>
@@ -22754,7 +22772,7 @@
       </c>
       <c r="K321" s="50" t="inlineStr"/>
     </row>
-    <row r="322">
+    <row r="322" hidden="1">
       <c r="A322" s="50" t="inlineStr">
         <is>
           <t>023_01</t>
@@ -22797,7 +22815,7 @@
       </c>
       <c r="K322" s="50" t="inlineStr"/>
     </row>
-    <row r="323">
+    <row r="323" hidden="1">
       <c r="A323" s="50" t="inlineStr">
         <is>
           <t>023_01</t>
@@ -22836,7 +22854,7 @@
       </c>
       <c r="K323" s="50" t="inlineStr"/>
     </row>
-    <row r="324">
+    <row r="324" hidden="1">
       <c r="A324" s="50" t="inlineStr">
         <is>
           <t>023_01</t>
@@ -22875,7 +22893,7 @@
       </c>
       <c r="K324" s="50" t="inlineStr"/>
     </row>
-    <row r="325">
+    <row r="325" hidden="1">
       <c r="A325" s="50" t="inlineStr">
         <is>
           <t>023_01</t>
@@ -22914,7 +22932,7 @@
       </c>
       <c r="K325" s="50" t="inlineStr"/>
     </row>
-    <row r="326">
+    <row r="326" hidden="1">
       <c r="A326" s="55" t="inlineStr">
         <is>
           <t>023_01</t>
@@ -22953,7 +22971,7 @@
       </c>
       <c r="K326" s="50" t="inlineStr"/>
     </row>
-    <row r="327">
+    <row r="327" hidden="1">
       <c r="A327" s="55" t="inlineStr">
         <is>
           <t>023_01</t>
@@ -22992,7 +23010,7 @@
       </c>
       <c r="K327" s="50" t="inlineStr"/>
     </row>
-    <row r="328">
+    <row r="328" hidden="1">
       <c r="A328" s="55" t="inlineStr">
         <is>
           <t>023_01</t>
@@ -23031,7 +23049,7 @@
       </c>
       <c r="K328" s="50" t="inlineStr"/>
     </row>
-    <row r="329">
+    <row r="329" ht="33" customHeight="1">
       <c r="A329" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23074,7 +23092,7 @@
       </c>
       <c r="K329" s="50" t="inlineStr"/>
     </row>
-    <row r="330">
+    <row r="330" hidden="1">
       <c r="A330" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23117,7 +23135,7 @@
       </c>
       <c r="K330" s="50" t="inlineStr"/>
     </row>
-    <row r="331">
+    <row r="331" hidden="1">
       <c r="A331" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23156,7 +23174,7 @@
       </c>
       <c r="K331" s="50" t="inlineStr"/>
     </row>
-    <row r="332">
+    <row r="332" hidden="1">
       <c r="A332" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23195,7 +23213,7 @@
       </c>
       <c r="K332" s="50" t="inlineStr"/>
     </row>
-    <row r="333">
+    <row r="333" hidden="1">
       <c r="A333" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23225,11 +23243,7 @@
         </is>
       </c>
       <c r="G333" s="51" t="inlineStr"/>
-      <c r="H333" s="51" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H333" s="51" t="inlineStr"/>
       <c r="I333" s="51" t="inlineStr"/>
       <c r="J333" s="50" t="inlineStr">
         <is>
@@ -23238,7 +23252,7 @@
       </c>
       <c r="K333" s="50" t="inlineStr"/>
     </row>
-    <row r="334">
+    <row r="334" hidden="1">
       <c r="A334" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23272,11 +23286,7 @@
           <t>sick</t>
         </is>
       </c>
-      <c r="H334" s="55" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H334" s="55" t="inlineStr"/>
       <c r="I334" s="55" t="inlineStr"/>
       <c r="J334" s="50" t="inlineStr">
         <is>
@@ -23301,29 +23311,21 @@
       </c>
       <c r="D335" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E335" s="55" t="inlineStr">
-        <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F335" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E335" s="55" t="inlineStr"/>
+      <c r="F335" s="51" t="inlineStr"/>
       <c r="G335" s="55" t="inlineStr"/>
       <c r="H335" s="55" t="inlineStr"/>
       <c r="I335" s="51" t="inlineStr">
         <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J335" s="55" t="inlineStr">
-        <is>
-          <t>先生，刚才那姑娘是得了什么病啊？</t>
+          <t>res://Assets/Background/black.png</t>
+        </is>
+      </c>
+      <c r="J335" s="88" t="inlineStr">
+        <is>
+          <t>收入一两白银</t>
         </is>
       </c>
       <c r="K335" s="50" t="inlineStr"/>
@@ -23347,27 +23349,31 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E336" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E336" s="55" t="inlineStr">
+        <is>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F336" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G336" s="55" t="inlineStr"/>
       <c r="H336" s="55" t="inlineStr"/>
-      <c r="I336" s="55" t="inlineStr"/>
-      <c r="J336" s="55" t="inlineStr">
-        <is>
-          <t>您是？</t>
+      <c r="I336" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J336" s="68" t="inlineStr">
+        <is>
+          <t>大夫，刚才那姑娘是得了什么病啊？</t>
         </is>
       </c>
       <c r="K336" s="50" t="inlineStr"/>
     </row>
-    <row r="337">
+    <row r="337" hidden="1">
       <c r="A337" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23386,14 +23392,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E337" s="55" t="inlineStr">
-        <is>
-          <t>王百堂</t>
+      <c r="E337" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F337" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G337" s="55" t="inlineStr"/>
@@ -23401,12 +23407,12 @@
       <c r="I337" s="55" t="inlineStr"/>
       <c r="J337" s="55" t="inlineStr">
         <is>
-          <t>小生是姑娘的一位相识，担心姑娘身体，来问问大夫。</t>
+          <t>您是？</t>
         </is>
       </c>
       <c r="K337" s="50" t="inlineStr"/>
     </row>
-    <row r="338">
+    <row r="338" hidden="1">
       <c r="A338" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23425,14 +23431,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E338" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E338" s="55" t="inlineStr">
+        <is>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F338" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G338" s="55" t="inlineStr"/>
@@ -23440,12 +23446,12 @@
       <c r="I338" s="55" t="inlineStr"/>
       <c r="J338" s="55" t="inlineStr">
         <is>
-          <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
+          <t>小生是姑娘的一位相识，担心姑娘身体，来问问大夫。</t>
         </is>
       </c>
       <c r="K338" s="50" t="inlineStr"/>
     </row>
-    <row r="339">
+    <row r="339" hidden="1">
       <c r="A339" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23464,14 +23470,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E339" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E339" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F339" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G339" s="55" t="inlineStr"/>
@@ -23479,12 +23485,12 @@
       <c r="I339" s="55" t="inlineStr"/>
       <c r="J339" s="55" t="inlineStr">
         <is>
-          <t>哎哟？这里面有事儿，快说来听听。</t>
+          <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
         </is>
       </c>
       <c r="K339" s="50" t="inlineStr"/>
     </row>
-    <row r="340">
+    <row r="340" hidden="1">
       <c r="A340" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23505,25 +23511,25 @@
       </c>
       <c r="E340" s="55" t="inlineStr">
         <is>
-          <t>王百堂</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F340" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G340" s="55" t="inlineStr"/>
       <c r="H340" s="55" t="inlineStr"/>
       <c r="I340" s="55" t="inlineStr"/>
-      <c r="J340" s="68" t="inlineStr">
-        <is>
-          <t>实不相瞒，小生在柳月坊与飞燕相识，一见倾心，私底下定了终身。</t>
+      <c r="J340" s="55" t="inlineStr">
+        <is>
+          <t>哎哟？这里面有事儿，快说来听听。</t>
         </is>
       </c>
       <c r="K340" s="50" t="inlineStr"/>
     </row>
-    <row r="341">
+    <row r="341" hidden="1">
       <c r="A341" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23555,14 +23561,14 @@
       <c r="G341" s="55" t="inlineStr"/>
       <c r="H341" s="55" t="inlineStr"/>
       <c r="I341" s="55" t="inlineStr"/>
-      <c r="J341" s="55" t="inlineStr">
-        <is>
-          <t>原想着凑够五百两银子，给她赎身。可那老鸨坐地起价，张口就要一千两，这让我们上哪去凑这么多银子啊…</t>
+      <c r="J341" s="68" t="inlineStr">
+        <is>
+          <t>实不相瞒，小生在柳月坊与飞燕相识，一见倾心，私底下定了终身。</t>
         </is>
       </c>
       <c r="K341" s="50" t="inlineStr"/>
     </row>
-    <row r="342">
+    <row r="342" hidden="1">
       <c r="A342" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23581,14 +23587,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E342" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E342" s="55" t="inlineStr">
+        <is>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F342" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G342" s="55" t="inlineStr"/>
@@ -23596,12 +23602,12 @@
       <c r="I342" s="55" t="inlineStr"/>
       <c r="J342" s="55" t="inlineStr">
         <is>
-          <t>想必姑娘是因为这事急坏了身子。</t>
+          <t>原想着凑够五百两银子，给她赎身。可那老鸨坐地起价，张口就要一千两，这让我们上哪去凑这么多银子啊…</t>
         </is>
       </c>
       <c r="K342" s="50" t="inlineStr"/>
     </row>
-    <row r="343">
+    <row r="343" hidden="1">
       <c r="A343" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23620,14 +23626,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E343" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E343" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F343" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G343" s="55" t="inlineStr"/>
@@ -23635,12 +23641,12 @@
       <c r="I343" s="55" t="inlineStr"/>
       <c r="J343" s="55" t="inlineStr">
         <is>
-          <t>唉，又是一对儿苦命的鸳鸯。</t>
+          <t>想必姑娘是因为这事急坏了身子。</t>
         </is>
       </c>
       <c r="K343" s="50" t="inlineStr"/>
     </row>
-    <row r="344">
+    <row r="344" hidden="1">
       <c r="A344" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23659,27 +23665,27 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E344" s="56" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E344" s="55" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F344" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G344" s="55" t="inlineStr"/>
       <c r="H344" s="55" t="inlineStr"/>
       <c r="I344" s="55" t="inlineStr"/>
-      <c r="J344" s="56" t="inlineStr">
-        <is>
-          <t>相公咱想办法帮帮他们吧。</t>
+      <c r="J344" s="55" t="inlineStr">
+        <is>
+          <t>唉，又是一对儿苦命的鸳鸯。</t>
         </is>
       </c>
       <c r="K344" s="50" t="inlineStr"/>
     </row>
-    <row r="345">
+    <row r="345" hidden="1">
       <c r="A345" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
@@ -23698,65 +23704,61 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E345" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E345" s="56" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F345" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G345" s="55" t="inlineStr"/>
       <c r="H345" s="55" t="inlineStr"/>
       <c r="I345" s="55" t="inlineStr"/>
-      <c r="J345" s="55" t="inlineStr">
+      <c r="J345" s="56" t="inlineStr">
+        <is>
+          <t>相公咱想办法帮帮他们吧。</t>
+        </is>
+      </c>
+      <c r="K345" s="50" t="inlineStr"/>
+    </row>
+    <row r="346" hidden="1">
+      <c r="A346" s="50" t="inlineStr">
+        <is>
+          <t>023_02</t>
+        </is>
+      </c>
+      <c r="B346" s="50" t="inlineStr">
+        <is>
+          <t>023治疗成功</t>
+        </is>
+      </c>
+      <c r="C346" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="D346" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E346" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F346" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G346" s="55" t="inlineStr"/>
+      <c r="H346" s="55" t="inlineStr"/>
+      <c r="I346" s="55" t="inlineStr"/>
+      <c r="J346" s="55" t="inlineStr">
         <is>
           <t>我也想帮他们，可怎么帮呢？</t>
-        </is>
-      </c>
-      <c r="K345" s="50" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="50" t="inlineStr">
-        <is>
-          <t>023_03</t>
-        </is>
-      </c>
-      <c r="B346" s="50" t="inlineStr">
-        <is>
-          <t>023治疗失败</t>
-        </is>
-      </c>
-      <c r="C346" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D346" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E346" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F346" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G346" s="51" t="inlineStr"/>
-      <c r="H346" s="52" t="inlineStr"/>
-      <c r="I346" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J346" s="53" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K346" s="50" t="inlineStr"/>
@@ -23764,12 +23766,12 @@
     <row r="347">
       <c r="A347" s="50" t="inlineStr">
         <is>
-          <t>024_01</t>
+          <t>023_03</t>
         </is>
       </c>
       <c r="B347" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕肺阴虚</t>
+          <t>023治疗失败</t>
         </is>
       </c>
       <c r="C347" s="50" t="n">
@@ -23785,9 +23787,9 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F347" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="F347" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G347" s="51" t="inlineStr"/>
@@ -23799,7 +23801,7 @@
       </c>
       <c r="J347" s="53" t="inlineStr">
         <is>
-          <t>姑娘你来啦，病好点了吗？</t>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K347" s="50" t="inlineStr"/>
@@ -23816,89 +23818,93 @@
         </is>
       </c>
       <c r="C348" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D348" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E348" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F348" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G348" s="51" t="inlineStr"/>
+      <c r="H348" s="52" t="inlineStr"/>
+      <c r="I348" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J348" s="53" t="inlineStr">
+        <is>
+          <t>姑娘你来啦，病好点了吗？</t>
+        </is>
+      </c>
+      <c r="K348" s="50" t="inlineStr"/>
+    </row>
+    <row r="349" hidden="1">
+      <c r="A349" s="50" t="inlineStr">
+        <is>
+          <t>024_01</t>
+        </is>
+      </c>
+      <c r="B349" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺阴虚</t>
+        </is>
+      </c>
+      <c r="C349" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="D348" s="50" t="inlineStr">
+      <c r="D349" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E348" s="53" t="inlineStr">
+      <c r="E349" s="53" t="inlineStr">
         <is>
           <t>谢飞燕</t>
         </is>
       </c>
-      <c r="F348" s="52" t="inlineStr">
+      <c r="F349" s="52" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="G348" s="52" t="inlineStr">
+      <c r="G349" s="52" t="inlineStr">
         <is>
           <t>sick</t>
         </is>
       </c>
-      <c r="H348" s="52" t="inlineStr"/>
-      <c r="I348" s="51" t="inlineStr"/>
-      <c r="J348" s="53" t="inlineStr">
-        <is>
-          <t>唉，这些日子一直不太好，前天还咳出血丝来了…</t>
-        </is>
-      </c>
-      <c r="K348" s="50" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="50" t="inlineStr">
-        <is>
-          <t>024_01</t>
-        </is>
-      </c>
-      <c r="B349" s="50" t="inlineStr">
-        <is>
-          <t>谢飞燕肺阴虚</t>
-        </is>
-      </c>
-      <c r="C349" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D349" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E349" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F349" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G349" s="51" t="inlineStr"/>
       <c r="H349" s="52" t="inlineStr"/>
       <c r="I349" s="51" t="inlineStr"/>
       <c r="J349" s="53" t="inlineStr">
         <is>
-          <t>请坐，我再给你看看。</t>
+          <t>唉，这些日子一直不太好，前天还咳出血丝来了…</t>
         </is>
       </c>
       <c r="K349" s="50" t="inlineStr"/>
     </row>
-    <row r="350">
+    <row r="350" hidden="1">
       <c r="A350" s="50" t="inlineStr">
         <is>
-          <t>024_02</t>
+          <t>024_01</t>
         </is>
       </c>
       <c r="B350" s="50" t="inlineStr">
         <is>
-          <t>024治疗成功</t>
+          <t>谢飞燕肺阴虚</t>
         </is>
       </c>
       <c r="C350" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D350" s="50" t="inlineStr">
         <is>
@@ -23917,14 +23923,10 @@
       </c>
       <c r="G350" s="51" t="inlineStr"/>
       <c r="H350" s="52" t="inlineStr"/>
-      <c r="I350" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I350" s="51" t="inlineStr"/>
       <c r="J350" s="53" t="inlineStr">
         <is>
-          <t>姑娘你这病，因气虚日久，气不化津，已经恶化为肺阴虚了。给你开些沙参麦冬汤补津养肺。</t>
+          <t>请坐，我再给你看看。</t>
         </is>
       </c>
       <c r="K350" s="50" t="inlineStr"/>
@@ -23941,77 +23943,81 @@
         </is>
       </c>
       <c r="C351" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D351" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E351" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F351" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G351" s="51" t="inlineStr"/>
+      <c r="H351" s="52" t="inlineStr"/>
+      <c r="I351" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J351" s="53" t="inlineStr">
+        <is>
+          <t>姑娘你这病，因气虚日久，气不化津，已经恶化为肺阴虚了。给你开些沙参麦冬汤补津养肺。</t>
+        </is>
+      </c>
+      <c r="K351" s="50" t="inlineStr"/>
+    </row>
+    <row r="352" hidden="1">
+      <c r="A352" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B352" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C352" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="D351" s="50" t="inlineStr">
+      <c r="D352" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E351" s="53" t="inlineStr">
+      <c r="E352" s="53" t="inlineStr">
         <is>
           <t>谢飞燕</t>
         </is>
       </c>
-      <c r="F351" s="52" t="inlineStr">
+      <c r="F352" s="52" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="G351" s="52" t="inlineStr">
+      <c r="G352" s="52" t="inlineStr">
         <is>
           <t>sick</t>
         </is>
       </c>
-      <c r="H351" s="52" t="inlineStr"/>
-      <c r="I351" s="51" t="inlineStr"/>
-      <c r="J351" s="53" t="inlineStr">
-        <is>
-          <t>多谢先生…</t>
-        </is>
-      </c>
-      <c r="K351" s="50" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="50" t="inlineStr">
-        <is>
-          <t>024_02</t>
-        </is>
-      </c>
-      <c r="B352" s="50" t="inlineStr">
-        <is>
-          <t>024治疗成功</t>
-        </is>
-      </c>
-      <c r="C352" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D352" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E352" s="53" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F352" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G352" s="51" t="inlineStr"/>
       <c r="H352" s="52" t="inlineStr"/>
       <c r="I352" s="51" t="inlineStr"/>
       <c r="J352" s="53" t="inlineStr">
         <is>
-          <t>可这药只能医肺病，不能医心病，心病还须心药医。</t>
+          <t>多谢先生…</t>
         </is>
       </c>
       <c r="K352" s="50" t="inlineStr"/>
     </row>
-    <row r="353">
+    <row r="353" hidden="1">
       <c r="A353" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24023,7 +24029,7 @@
         </is>
       </c>
       <c r="C353" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D353" s="50" t="inlineStr">
         <is>
@@ -24032,29 +24038,25 @@
       </c>
       <c r="E353" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F353" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G353" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H353" s="51" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G353" s="51" t="inlineStr"/>
+      <c r="H353" s="52" t="inlineStr"/>
       <c r="I353" s="51" t="inlineStr"/>
       <c r="J353" s="53" t="inlineStr">
         <is>
-          <t>夫人这是何意味？</t>
+          <t>可这药只能医肺病，不能医心病，心病还须心药医。</t>
         </is>
       </c>
       <c r="K353" s="50" t="inlineStr"/>
     </row>
-    <row r="354">
+    <row r="354" hidden="1">
       <c r="A354" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24066,7 +24068,7 @@
         </is>
       </c>
       <c r="C354" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D354" s="50" t="inlineStr">
         <is>
@@ -24075,80 +24077,80 @@
       </c>
       <c r="E354" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F354" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G354" s="51" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G354" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H354" s="51" t="inlineStr"/>
       <c r="I354" s="51" t="inlineStr"/>
       <c r="J354" s="53" t="inlineStr">
         <is>
+          <t>夫人这是何意味？</t>
+        </is>
+      </c>
+      <c r="K354" s="50" t="inlineStr"/>
+    </row>
+    <row r="355" hidden="1">
+      <c r="A355" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B355" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C355" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D355" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E355" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F355" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G355" s="51" t="inlineStr"/>
+      <c r="H355" s="51" t="inlineStr"/>
+      <c r="I355" s="51" t="inlineStr"/>
+      <c r="J355" s="53" t="inlineStr">
+        <is>
           <t>前些天你来看病，你前脚刚走，王公子就来这问你的病情，很是担心你。</t>
         </is>
       </c>
-      <c r="K354" s="50" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" s="50" t="inlineStr">
+      <c r="K355" s="50" t="inlineStr"/>
+    </row>
+    <row r="356" hidden="1">
+      <c r="A356" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
         </is>
       </c>
-      <c r="B355" s="50" t="inlineStr">
+      <c r="B356" s="50" t="inlineStr">
         <is>
           <t>024治疗成功</t>
         </is>
       </c>
-      <c r="C355" s="50" t="n">
+      <c r="C356" s="50" t="n">
         <v>6</v>
-      </c>
-      <c r="D355" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E355" s="53" t="inlineStr">
-        <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F355" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G355" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H355" s="55" t="inlineStr"/>
-      <c r="I355" s="55" t="inlineStr"/>
-      <c r="J355" s="56" t="inlineStr">
-        <is>
-          <t>唉，我们这行当是做不长久的，只盼着有个如意的郎君，趁着年轻嫁入好人家。</t>
-        </is>
-      </c>
-      <c r="K355" s="50" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" s="50" t="inlineStr">
-        <is>
-          <t>024_02</t>
-        </is>
-      </c>
-      <c r="B356" s="50" t="inlineStr">
-        <is>
-          <t>024治疗成功</t>
-        </is>
-      </c>
-      <c r="C356" s="50" t="n">
-        <v>7</v>
       </c>
       <c r="D356" s="50" t="inlineStr">
         <is>
@@ -24174,12 +24176,12 @@
       <c r="I356" s="55" t="inlineStr"/>
       <c r="J356" s="56" t="inlineStr">
         <is>
-          <t>王郎待我真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
+          <t>唉，我们这行当是做不长久的，只盼着有个如意的郎君，趁着年轻嫁入好人家。</t>
         </is>
       </c>
       <c r="K356" s="50" t="inlineStr"/>
     </row>
-    <row r="357">
+    <row r="357" hidden="1">
       <c r="A357" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24191,7 +24193,7 @@
         </is>
       </c>
       <c r="C357" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D357" s="50" t="inlineStr">
         <is>
@@ -24200,25 +24202,29 @@
       </c>
       <c r="E357" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F357" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G357" s="55" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G357" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H357" s="55" t="inlineStr"/>
       <c r="I357" s="55" t="inlineStr"/>
       <c r="J357" s="56" t="inlineStr">
         <is>
-          <t>我有一计，可使你二人有情人终成眷属。</t>
+          <t>王郎待我真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
         </is>
       </c>
       <c r="K357" s="50" t="inlineStr"/>
     </row>
-    <row r="358">
+    <row r="358" hidden="1">
       <c r="A358" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24230,38 +24236,34 @@
         </is>
       </c>
       <c r="C358" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D358" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E358" s="56" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E358" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F358" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G358" s="55" t="inlineStr"/>
-      <c r="H358" s="55" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H358" s="55" t="inlineStr"/>
       <c r="I358" s="55" t="inlineStr"/>
       <c r="J358" s="56" t="inlineStr">
         <is>
-          <t>少夫人你有什么主意呀？快说快说！</t>
+          <t>我有一计，可使你二人有情人终成眷属。</t>
         </is>
       </c>
       <c r="K358" s="50" t="inlineStr"/>
     </row>
-    <row r="359">
+    <row r="359" hidden="1">
       <c r="A359" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24273,21 +24275,21 @@
         </is>
       </c>
       <c r="C359" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D359" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E359" s="53" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E359" s="56" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F359" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G359" s="55" t="inlineStr"/>
@@ -24299,12 +24301,12 @@
       <c r="I359" s="55" t="inlineStr"/>
       <c r="J359" s="56" t="inlineStr">
         <is>
-          <t>明日你让金姨妈来一趟，如此这般….</t>
+          <t>少夫人你有什么主意呀？快说快说！</t>
         </is>
       </c>
       <c r="K359" s="50" t="inlineStr"/>
     </row>
-    <row r="360">
+    <row r="360" hidden="1">
       <c r="A360" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24316,26 +24318,38 @@
         </is>
       </c>
       <c r="C360" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D360" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E360" s="53" t="inlineStr"/>
-      <c r="F360" s="52" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E360" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F360" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="G360" s="55" t="inlineStr"/>
-      <c r="H360" s="55" t="inlineStr"/>
+      <c r="H360" s="55" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I360" s="55" t="inlineStr"/>
       <c r="J360" s="56" t="inlineStr">
         <is>
-          <t>吴芷兰和众人说出了自己的主意</t>
+          <t>明日你让金姨妈来一趟，如此这般….</t>
         </is>
       </c>
       <c r="K360" s="50" t="inlineStr"/>
     </row>
-    <row r="361">
+    <row r="361" hidden="1">
       <c r="A361" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24347,34 +24361,26 @@
         </is>
       </c>
       <c r="C361" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D361" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E361" s="53" t="inlineStr">
-        <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F361" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E361" s="53" t="inlineStr"/>
+      <c r="F361" s="52" t="inlineStr"/>
       <c r="G361" s="55" t="inlineStr"/>
       <c r="H361" s="55" t="inlineStr"/>
       <c r="I361" s="55" t="inlineStr"/>
       <c r="J361" s="56" t="inlineStr">
         <is>
-          <t>先生若是能帮我们渡此难关，便是再造父母。</t>
+          <t>吴芷兰和众人说出了自己的主意</t>
         </is>
       </c>
       <c r="K361" s="50" t="inlineStr"/>
     </row>
-    <row r="362">
+    <row r="362" hidden="1">
       <c r="A362" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24386,25 +24392,29 @@
         </is>
       </c>
       <c r="C362" s="50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D362" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E362" s="55" t="inlineStr"/>
-      <c r="F362" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E362" s="53" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F362" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="G362" s="55" t="inlineStr"/>
       <c r="H362" s="55" t="inlineStr"/>
-      <c r="I362" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I362" s="55" t="inlineStr"/>
       <c r="J362" s="56" t="inlineStr">
         <is>
-          <t>次日</t>
+          <t>先生若是能帮我们渡此难关，便是再造父母。</t>
         </is>
       </c>
       <c r="K362" s="50" t="inlineStr"/>
@@ -24421,29 +24431,25 @@
         </is>
       </c>
       <c r="C363" s="50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D363" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E363" s="56" t="inlineStr">
-        <is>
-          <t>金姨妈</t>
-        </is>
-      </c>
-      <c r="F363" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E363" s="53" t="inlineStr"/>
+      <c r="F363" s="52" t="inlineStr"/>
       <c r="G363" s="55" t="inlineStr"/>
       <c r="H363" s="55" t="inlineStr"/>
-      <c r="I363" s="55" t="inlineStr"/>
+      <c r="I363" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/black.png</t>
+        </is>
+      </c>
       <c r="J363" s="56" t="inlineStr">
         <is>
-          <t>李大夫，你叫我来是什么事儿啊？</t>
+          <t>收入二两白银</t>
         </is>
       </c>
       <c r="K363" s="50" t="inlineStr"/>
@@ -24460,34 +24466,30 @@
         </is>
       </c>
       <c r="C364" s="50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D364" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E364" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F364" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E364" s="55" t="inlineStr"/>
+      <c r="F364" s="51" t="inlineStr"/>
       <c r="G364" s="55" t="inlineStr"/>
       <c r="H364" s="55" t="inlineStr"/>
-      <c r="I364" s="55" t="inlineStr"/>
+      <c r="I364" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J364" s="56" t="inlineStr">
         <is>
-          <t>昨日经我仔细检查，谢姑娘的病乃是肺痨，此病只能缓解，不能根治，而且身边之人都有可能沾染。</t>
+          <t>次日</t>
         </is>
       </c>
       <c r="K364" s="50" t="inlineStr"/>
     </row>
-    <row r="365">
+    <row r="365" hidden="1">
       <c r="A365" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24499,7 +24501,7 @@
         </is>
       </c>
       <c r="C365" s="50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D365" s="50" t="inlineStr">
         <is>
@@ -24521,12 +24523,12 @@
       <c r="I365" s="55" t="inlineStr"/>
       <c r="J365" s="56" t="inlineStr">
         <is>
-          <t>啊？这可如何是好？</t>
+          <t>李大夫，你叫我来是什么事儿啊？</t>
         </is>
       </c>
       <c r="K365" s="50" t="inlineStr"/>
     </row>
-    <row r="366">
+    <row r="366" hidden="1">
       <c r="A366" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24538,7 +24540,7 @@
         </is>
       </c>
       <c r="C366" s="50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D366" s="50" t="inlineStr">
         <is>
@@ -24560,12 +24562,12 @@
       <c r="I366" s="55" t="inlineStr"/>
       <c r="J366" s="56" t="inlineStr">
         <is>
-          <t>您还是早做打算，给女儿寻觅个好归宿吧。</t>
+          <t>昨日经我仔细检查，谢姑娘的病乃是肺痨，此病只能缓解，不能根治，而且身边之人都有可能沾染。</t>
         </is>
       </c>
       <c r="K366" s="50" t="inlineStr"/>
     </row>
-    <row r="367">
+    <row r="367" hidden="1">
       <c r="A367" s="50" t="inlineStr">
         <is>
           <t>024_02</t>
@@ -24577,7 +24579,7 @@
         </is>
       </c>
       <c r="C367" s="50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D367" s="50" t="inlineStr">
         <is>
@@ -24599,93 +24601,85 @@
       <c r="I367" s="55" t="inlineStr"/>
       <c r="J367" s="56" t="inlineStr">
         <is>
+          <t>啊？这可如何是好？</t>
+        </is>
+      </c>
+      <c r="K367" s="50" t="inlineStr"/>
+    </row>
+    <row r="368" hidden="1">
+      <c r="A368" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B368" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C368" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="D368" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E368" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F368" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G368" s="55" t="inlineStr"/>
+      <c r="H368" s="55" t="inlineStr"/>
+      <c r="I368" s="55" t="inlineStr"/>
+      <c r="J368" s="56" t="inlineStr">
+        <is>
+          <t>您还是早做打算，给女儿寻觅个好归宿吧。</t>
+        </is>
+      </c>
+      <c r="K368" s="50" t="inlineStr"/>
+    </row>
+    <row r="369" hidden="1">
+      <c r="A369" s="50" t="inlineStr">
+        <is>
+          <t>024_02</t>
+        </is>
+      </c>
+      <c r="B369" s="50" t="inlineStr">
+        <is>
+          <t>024治疗成功</t>
+        </is>
+      </c>
+      <c r="C369" s="50" t="n">
+        <v>19</v>
+      </c>
+      <c r="D369" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E369" s="56" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F369" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G369" s="55" t="inlineStr"/>
+      <c r="H369" s="55" t="inlineStr"/>
+      <c r="I369" s="55" t="inlineStr"/>
+      <c r="J369" s="56" t="inlineStr">
+        <is>
           <t>(若是这样，不如趁那小子不知情，便宜与了他去….)</t>
-        </is>
-      </c>
-      <c r="K367" s="50" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="50" t="inlineStr">
-        <is>
-          <t>024_03</t>
-        </is>
-      </c>
-      <c r="B368" s="50" t="inlineStr">
-        <is>
-          <t>024治疗失败</t>
-        </is>
-      </c>
-      <c r="C368" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D368" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E368" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F368" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G368" s="51" t="inlineStr"/>
-      <c r="H368" s="52" t="inlineStr"/>
-      <c r="I368" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J368" s="50" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
-        </is>
-      </c>
-      <c r="K368" s="50" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" s="50" t="inlineStr">
-        <is>
-          <t>024_04</t>
-        </is>
-      </c>
-      <c r="B369" s="50" t="inlineStr">
-        <is>
-          <t>王百堂来访</t>
-        </is>
-      </c>
-      <c r="C369" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D369" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E369" s="50" t="inlineStr">
-        <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F369" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G369" s="51" t="inlineStr"/>
-      <c r="H369" s="54" t="inlineStr"/>
-      <c r="I369" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J369" s="50" t="inlineStr">
-        <is>
-          <t>恩公！小生拜见恩公。</t>
         </is>
       </c>
       <c r="K369" s="50" t="inlineStr"/>
@@ -24693,38 +24687,42 @@
     <row r="370">
       <c r="A370" s="50" t="inlineStr">
         <is>
-          <t>024_04</t>
+          <t>024_03</t>
         </is>
       </c>
       <c r="B370" s="50" t="inlineStr">
         <is>
-          <t>王百堂来访</t>
+          <t>024治疗失败</t>
         </is>
       </c>
       <c r="C370" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D370" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E370" s="50" t="inlineStr">
+      <c r="E370" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F370" s="54" t="inlineStr">
+      <c r="F370" s="52" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
       <c r="G370" s="51" t="inlineStr"/>
-      <c r="H370" s="54" t="inlineStr"/>
-      <c r="I370" s="51" t="inlineStr"/>
+      <c r="H370" s="52" t="inlineStr"/>
+      <c r="I370" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J370" s="50" t="inlineStr">
         <is>
-          <t>是你啊，快请起。你和谢姑娘怎么样了？</t>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K370" s="50" t="inlineStr"/>
@@ -24741,7 +24739,7 @@
         </is>
       </c>
       <c r="C371" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D371" s="50" t="inlineStr">
         <is>
@@ -24760,15 +24758,19 @@
       </c>
       <c r="G371" s="51" t="inlineStr"/>
       <c r="H371" s="54" t="inlineStr"/>
-      <c r="I371" s="51" t="inlineStr"/>
+      <c r="I371" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J371" s="50" t="inlineStr">
         <is>
-          <t>承蒙恩公出手相助，我二人已结为夫妻，在城外安顿下来，今日特来拜谢。</t>
+          <t>恩公！小生拜见恩公。</t>
         </is>
       </c>
       <c r="K371" s="50" t="inlineStr"/>
     </row>
-    <row r="372">
+    <row r="372" hidden="1">
       <c r="A372" s="50" t="inlineStr">
         <is>
           <t>024_04</t>
@@ -24780,7 +24782,7 @@
         </is>
       </c>
       <c r="C372" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D372" s="50" t="inlineStr">
         <is>
@@ -24789,25 +24791,25 @@
       </c>
       <c r="E372" s="50" t="inlineStr">
         <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F372" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F372" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G372" s="51" t="inlineStr"/>
-      <c r="H372" s="51" t="inlineStr"/>
+      <c r="H372" s="54" t="inlineStr"/>
       <c r="I372" s="51" t="inlineStr"/>
       <c r="J372" s="50" t="inlineStr">
         <is>
-          <t>听闻恩公酷好青囊之书，先父也是一生行医，家中有不少先父留下的笔记心得，今日便赠予恩公。</t>
+          <t>是你啊，快请起。你和谢姑娘怎么样了？</t>
         </is>
       </c>
       <c r="K372" s="50" t="inlineStr"/>
     </row>
-    <row r="373">
+    <row r="373" hidden="1">
       <c r="A373" s="50" t="inlineStr">
         <is>
           <t>024_04</t>
@@ -24819,7 +24821,7 @@
         </is>
       </c>
       <c r="C373" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D373" s="50" t="inlineStr">
         <is>
@@ -24828,166 +24830,162 @@
       </c>
       <c r="E373" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F373" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F373" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G373" s="51" t="inlineStr"/>
-      <c r="H373" s="51" t="inlineStr"/>
+      <c r="H373" s="54" t="inlineStr"/>
       <c r="I373" s="51" t="inlineStr"/>
       <c r="J373" s="50" t="inlineStr">
         <is>
+          <t>承蒙恩公出手相助，我二人已结为夫妻，在城外安顿下来，今日特来拜谢。</t>
+        </is>
+      </c>
+      <c r="K373" s="50" t="inlineStr"/>
+    </row>
+    <row r="374" hidden="1">
+      <c r="A374" s="50" t="inlineStr">
+        <is>
+          <t>024_04</t>
+        </is>
+      </c>
+      <c r="B374" s="50" t="inlineStr">
+        <is>
+          <t>王百堂来访</t>
+        </is>
+      </c>
+      <c r="C374" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D374" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E374" s="50" t="inlineStr">
+        <is>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F374" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G374" s="51" t="inlineStr"/>
+      <c r="H374" s="51" t="inlineStr"/>
+      <c r="I374" s="51" t="inlineStr"/>
+      <c r="J374" s="50" t="inlineStr">
+        <is>
+          <t>听闻恩公酷好青囊之书，先父也是一生行医，家中有不少先父留下的笔记心得，今日便赠予恩公。</t>
+        </is>
+      </c>
+      <c r="K374" s="50" t="inlineStr"/>
+    </row>
+    <row r="375" hidden="1">
+      <c r="A375" s="50" t="inlineStr">
+        <is>
+          <t>024_04</t>
+        </is>
+      </c>
+      <c r="B375" s="50" t="inlineStr">
+        <is>
+          <t>王百堂来访</t>
+        </is>
+      </c>
+      <c r="C375" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D375" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E375" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F375" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G375" s="51" t="inlineStr"/>
+      <c r="H375" s="51" t="inlineStr"/>
+      <c r="I375" s="51" t="inlineStr"/>
+      <c r="J375" s="50" t="inlineStr">
+        <is>
           <t>哎呀，这可太好了，真是求之不得啊。</t>
         </is>
       </c>
-      <c r="K373" s="50" t="inlineStr"/>
-    </row>
-    <row r="374" ht="34.5" customHeight="1">
-      <c r="A374" s="50" t="inlineStr">
+      <c r="K375" s="50" t="inlineStr"/>
+    </row>
+    <row r="376" ht="34.5" customHeight="1">
+      <c r="A376" s="50" t="inlineStr">
         <is>
           <t>025_01</t>
         </is>
       </c>
-      <c r="B374" s="50" t="inlineStr">
+      <c r="B376" s="50" t="inlineStr">
         <is>
           <t>和尚肾精不足</t>
         </is>
       </c>
-      <c r="C374" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D374" s="50" t="inlineStr">
+      <c r="C376" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D376" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E374" s="50" t="inlineStr">
+      <c r="E376" s="50" t="inlineStr">
         <is>
           <t>性空</t>
         </is>
       </c>
-      <c r="F374" s="51" t="inlineStr">
+      <c r="F376" s="51" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="G374" s="51" t="inlineStr">
+      <c r="G376" s="51" t="inlineStr">
         <is>
           <t>sick</t>
         </is>
       </c>
-      <c r="H374" s="52" t="inlineStr"/>
-      <c r="I374" s="51" t="inlineStr">
+      <c r="H376" s="52" t="inlineStr"/>
+      <c r="I376" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J374" s="67" t="inlineStr">
+      <c r="J376" s="67" t="inlineStr">
         <is>
           <t>阿弥陀佛，贫僧法号性空，《中论》曰："众因缘生法，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
         </is>
       </c>
-      <c r="K374" s="50" t="inlineStr"/>
-    </row>
-    <row r="375">
-      <c r="A375" s="50" t="inlineStr">
+      <c r="K376" s="50" t="inlineStr"/>
+    </row>
+    <row r="377" hidden="1">
+      <c r="A377" s="50" t="inlineStr">
         <is>
           <t>025_01</t>
         </is>
       </c>
-      <c r="B375" s="50" t="inlineStr">
+      <c r="B377" s="50" t="inlineStr">
         <is>
           <t>和尚肾精不足</t>
         </is>
       </c>
-      <c r="C375" s="50" t="n">
+      <c r="C377" s="50" t="n">
         <v>2</v>
-      </c>
-      <c r="D375" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E375" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F375" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G375" s="51" t="inlineStr"/>
-      <c r="H375" s="52" t="inlineStr"/>
-      <c r="I375" s="51" t="inlineStr"/>
-      <c r="J375" s="67" t="inlineStr">
-        <is>
-          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
-        </is>
-      </c>
-      <c r="K375" s="50" t="inlineStr"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="50" t="inlineStr">
-        <is>
-          <t>025_01</t>
-        </is>
-      </c>
-      <c r="B376" s="50" t="inlineStr">
-        <is>
-          <t>和尚肾精不足</t>
-        </is>
-      </c>
-      <c r="C376" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D376" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E376" s="50" t="inlineStr">
-        <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F376" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G376" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H376" s="52" t="inlineStr"/>
-      <c r="I376" s="51" t="inlineStr"/>
-      <c r="J376" s="50" t="inlineStr">
-        <is>
-          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
-        </is>
-      </c>
-      <c r="K376" s="50" t="inlineStr"/>
-    </row>
-    <row r="377">
-      <c r="A377" s="50" t="inlineStr">
-        <is>
-          <t>025_02</t>
-        </is>
-      </c>
-      <c r="B377" s="50" t="inlineStr">
-        <is>
-          <t>025治疗成功</t>
-        </is>
-      </c>
-      <c r="C377" s="50" t="n">
-        <v>1</v>
       </c>
       <c r="D377" s="50" t="inlineStr">
         <is>
@@ -25006,31 +25004,27 @@
       </c>
       <c r="G377" s="51" t="inlineStr"/>
       <c r="H377" s="52" t="inlineStr"/>
-      <c r="I377" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I377" s="51" t="inlineStr"/>
       <c r="J377" s="67" t="inlineStr">
         <is>
-          <t>师父所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
+          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
         </is>
       </c>
       <c r="K377" s="50" t="inlineStr"/>
     </row>
-    <row r="378">
+    <row r="378" hidden="1">
       <c r="A378" s="50" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>025_01</t>
         </is>
       </c>
       <c r="B378" s="50" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>和尚肾精不足</t>
         </is>
       </c>
       <c r="C378" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D378" s="50" t="inlineStr">
         <is>
@@ -25049,14 +25043,14 @@
       </c>
       <c r="G378" s="51" t="inlineStr">
         <is>
-          <t>after</t>
+          <t>sick</t>
         </is>
       </c>
       <c r="H378" s="52" t="inlineStr"/>
       <c r="I378" s="51" t="inlineStr"/>
       <c r="J378" s="50" t="inlineStr">
         <is>
-          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
+          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
         </is>
       </c>
       <c r="K378" s="50" t="inlineStr"/>
@@ -25073,7 +25067,7 @@
         </is>
       </c>
       <c r="C379" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D379" s="50" t="inlineStr">
         <is>
@@ -25092,15 +25086,19 @@
       </c>
       <c r="G379" s="51" t="inlineStr"/>
       <c r="H379" s="52" t="inlineStr"/>
-      <c r="I379" s="51" t="inlineStr"/>
-      <c r="J379" s="50" t="inlineStr">
-        <is>
-          <t>…</t>
+      <c r="I379" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J379" s="67" t="inlineStr">
+        <is>
+          <t>师父所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
         </is>
       </c>
       <c r="K379" s="50" t="inlineStr"/>
     </row>
-    <row r="380">
+    <row r="380" hidden="1">
       <c r="A380" s="50" t="inlineStr">
         <is>
           <t>025_02</t>
@@ -25112,7 +25110,7 @@
         </is>
       </c>
       <c r="C380" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D380" s="50" t="inlineStr">
         <is>
@@ -25134,16 +25132,16 @@
           <t>after</t>
         </is>
       </c>
-      <c r="H380" s="51" t="inlineStr"/>
+      <c r="H380" s="52" t="inlineStr"/>
       <c r="I380" s="51" t="inlineStr"/>
       <c r="J380" s="50" t="inlineStr">
         <is>
-          <t>一定是我晚上念经太过用功，着凉了。</t>
+          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
         </is>
       </c>
       <c r="K380" s="50" t="inlineStr"/>
     </row>
-    <row r="381">
+    <row r="381" hidden="1">
       <c r="A381" s="50" t="inlineStr">
         <is>
           <t>025_02</t>
@@ -25155,7 +25153,7 @@
         </is>
       </c>
       <c r="C381" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D381" s="50" t="inlineStr">
         <is>
@@ -25173,172 +25171,176 @@
         </is>
       </c>
       <c r="G381" s="51" t="inlineStr"/>
-      <c r="H381" s="51" t="inlineStr"/>
+      <c r="H381" s="52" t="inlineStr"/>
       <c r="I381" s="51" t="inlineStr"/>
       <c r="J381" s="50" t="inlineStr">
         <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K381" s="50" t="inlineStr"/>
+    </row>
+    <row r="382" hidden="1">
+      <c r="A382" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B382" s="50" t="inlineStr">
+        <is>
+          <t>025治疗成功</t>
+        </is>
+      </c>
+      <c r="C382" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D382" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E382" s="50" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F382" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G382" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H382" s="51" t="inlineStr"/>
+      <c r="I382" s="51" t="inlineStr"/>
+      <c r="J382" s="50" t="inlineStr">
+        <is>
+          <t>一定是我晚上念经太过用功，着凉了。</t>
+        </is>
+      </c>
+      <c r="K382" s="50" t="inlineStr"/>
+    </row>
+    <row r="383" hidden="1">
+      <c r="A383" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B383" s="50" t="inlineStr">
+        <is>
+          <t>025治疗成功</t>
+        </is>
+      </c>
+      <c r="C383" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D383" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E383" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F383" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G383" s="51" t="inlineStr"/>
+      <c r="H383" s="51" t="inlineStr"/>
+      <c r="I383" s="51" t="inlineStr"/>
+      <c r="J383" s="50" t="inlineStr">
+        <is>
           <t>是是是，师父说得对，也不是没有这个可能。</t>
         </is>
       </c>
-      <c r="K381" s="50" t="inlineStr"/>
-    </row>
-    <row r="382">
-      <c r="A382" s="50" t="inlineStr">
+      <c r="K383" s="50" t="inlineStr"/>
+    </row>
+    <row r="384" hidden="1">
+      <c r="A384" s="50" t="inlineStr">
         <is>
           <t>025_02</t>
         </is>
       </c>
-      <c r="B382" s="50" t="inlineStr">
+      <c r="B384" s="50" t="inlineStr">
         <is>
           <t>025治疗成功</t>
         </is>
       </c>
-      <c r="C382" s="50" t="n">
+      <c r="C384" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="D382" s="50" t="inlineStr">
+      <c r="D384" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E382" s="50" t="inlineStr">
+      <c r="E384" s="50" t="inlineStr">
         <is>
           <t>性空</t>
         </is>
       </c>
-      <c r="F382" s="51" t="inlineStr">
+      <c r="F384" s="51" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="G382" s="51" t="inlineStr">
+      <c r="G384" s="51" t="inlineStr">
         <is>
           <t>after</t>
         </is>
       </c>
-      <c r="H382" s="55" t="inlineStr">
+      <c r="H384" s="55" t="inlineStr">
         <is>
           <t>hide</t>
         </is>
       </c>
-      <c r="I382" s="55" t="inlineStr"/>
-      <c r="J382" s="73" t="inlineStr">
+      <c r="I384" s="55" t="inlineStr"/>
+      <c r="J384" s="73" t="inlineStr">
         <is>
           <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
         </is>
       </c>
-      <c r="K382" s="50" t="inlineStr"/>
-    </row>
-    <row r="383">
-      <c r="A383" s="50" t="inlineStr">
+      <c r="K384" s="50" t="inlineStr"/>
+    </row>
+    <row r="385" hidden="1">
+      <c r="A385" s="50" t="inlineStr">
         <is>
           <t>025_02</t>
         </is>
       </c>
-      <c r="B383" s="50" t="inlineStr">
+      <c r="B385" s="50" t="inlineStr">
         <is>
           <t>025治疗成功</t>
         </is>
       </c>
-      <c r="C383" s="50" t="n">
+      <c r="C385" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="D383" s="50" t="inlineStr">
+      <c r="D385" s="50" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="E383" s="50" t="inlineStr"/>
-      <c r="F383" s="51" t="inlineStr"/>
-      <c r="G383" s="51" t="inlineStr"/>
-      <c r="H383" s="55" t="inlineStr"/>
-      <c r="I383" s="55" t="inlineStr"/>
-      <c r="J383" s="56" t="inlineStr">
-        <is>
-          <t>金钱+2两</t>
-        </is>
-      </c>
-      <c r="K383" s="50" t="inlineStr"/>
-    </row>
-    <row r="384">
-      <c r="A384" s="50" t="inlineStr">
-        <is>
-          <t>025_02</t>
-        </is>
-      </c>
-      <c r="B384" s="50" t="inlineStr">
-        <is>
-          <t>025治疗成功</t>
-        </is>
-      </c>
-      <c r="C384" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="D384" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E384" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F384" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G384" s="55" t="inlineStr"/>
-      <c r="H384" s="55" t="inlineStr"/>
-      <c r="I384" s="55" t="inlineStr"/>
-      <c r="J384" s="55" t="inlineStr">
-        <is>
-          <t>哇，这就是传说中的花和尚吗？</t>
-        </is>
-      </c>
-      <c r="K384" s="50" t="inlineStr"/>
-    </row>
-    <row r="385">
-      <c r="A385" s="50" t="inlineStr">
-        <is>
-          <t>025_02</t>
-        </is>
-      </c>
-      <c r="B385" s="50" t="inlineStr">
-        <is>
-          <t>025治疗成功</t>
-        </is>
-      </c>
-      <c r="C385" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="D385" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E385" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F385" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G385" s="55" t="inlineStr"/>
+      <c r="E385" s="50" t="inlineStr"/>
+      <c r="F385" s="51" t="inlineStr"/>
+      <c r="G385" s="51" t="inlineStr"/>
       <c r="H385" s="55" t="inlineStr"/>
       <c r="I385" s="55" t="inlineStr"/>
-      <c r="J385" s="55" t="inlineStr">
-        <is>
-          <t>…</t>
+      <c r="J385" s="56" t="inlineStr">
+        <is>
+          <t>金钱+2两</t>
         </is>
       </c>
       <c r="K385" s="50" t="inlineStr"/>
     </row>
-    <row r="386">
+    <row r="386" hidden="1">
       <c r="A386" s="50" t="inlineStr">
         <is>
           <t>025_02</t>
@@ -25350,7 +25352,7 @@
         </is>
       </c>
       <c r="C386" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D386" s="50" t="inlineStr">
         <is>
@@ -25359,12 +25361,12 @@
       </c>
       <c r="E386" s="55" t="inlineStr">
         <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F386" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F386" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G386" s="55" t="inlineStr"/>
@@ -25372,12 +25374,12 @@
       <c r="I386" s="55" t="inlineStr"/>
       <c r="J386" s="55" t="inlineStr">
         <is>
-          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+          <t>哇，这就是传说中的花和尚吗？</t>
         </is>
       </c>
       <c r="K386" s="50" t="inlineStr"/>
     </row>
-    <row r="387">
+    <row r="387" hidden="1">
       <c r="A387" s="50" t="inlineStr">
         <is>
           <t>025_02</t>
@@ -25389,21 +25391,21 @@
         </is>
       </c>
       <c r="C387" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D387" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E387" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E387" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F387" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G387" s="55" t="inlineStr"/>
@@ -25411,12 +25413,12 @@
       <c r="I387" s="55" t="inlineStr"/>
       <c r="J387" s="55" t="inlineStr">
         <is>
-          <t>找打！</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K387" s="50" t="inlineStr"/>
     </row>
-    <row r="388">
+    <row r="388" hidden="1">
       <c r="A388" s="50" t="inlineStr">
         <is>
           <t>025_02</t>
@@ -25428,7 +25430,7 @@
         </is>
       </c>
       <c r="C388" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D388" s="50" t="inlineStr">
         <is>
@@ -25450,93 +25452,85 @@
       <c r="I388" s="55" t="inlineStr"/>
       <c r="J388" s="55" t="inlineStr">
         <is>
+          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+        </is>
+      </c>
+      <c r="K388" s="50" t="inlineStr"/>
+    </row>
+    <row r="389" hidden="1">
+      <c r="A389" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B389" s="50" t="inlineStr">
+        <is>
+          <t>025治疗成功</t>
+        </is>
+      </c>
+      <c r="C389" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D389" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E389" s="55" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F389" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G389" s="55" t="inlineStr"/>
+      <c r="H389" s="55" t="inlineStr"/>
+      <c r="I389" s="55" t="inlineStr"/>
+      <c r="J389" s="55" t="inlineStr">
+        <is>
+          <t>找打！</t>
+        </is>
+      </c>
+      <c r="K389" s="50" t="inlineStr"/>
+    </row>
+    <row r="390" hidden="1">
+      <c r="A390" s="50" t="inlineStr">
+        <is>
+          <t>025_02</t>
+        </is>
+      </c>
+      <c r="B390" s="50" t="inlineStr">
+        <is>
+          <t>025治疗成功</t>
+        </is>
+      </c>
+      <c r="C390" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D390" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E390" s="55" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F390" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G390" s="55" t="inlineStr"/>
+      <c r="H390" s="55" t="inlineStr"/>
+      <c r="I390" s="55" t="inlineStr"/>
+      <c r="J390" s="55" t="inlineStr">
+        <is>
           <t>哎哟！</t>
-        </is>
-      </c>
-      <c r="K388" s="50" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" s="50" t="inlineStr">
-        <is>
-          <t>025_03</t>
-        </is>
-      </c>
-      <c r="B389" s="50" t="inlineStr">
-        <is>
-          <t>025治疗失败</t>
-        </is>
-      </c>
-      <c r="C389" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D389" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E389" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F389" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G389" s="51" t="inlineStr"/>
-      <c r="H389" s="52" t="inlineStr"/>
-      <c r="I389" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J389" s="50" t="inlineStr">
-        <is>
-          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
-        </is>
-      </c>
-      <c r="K389" s="50" t="inlineStr"/>
-    </row>
-    <row r="390">
-      <c r="A390" s="50" t="inlineStr">
-        <is>
-          <t>026_01</t>
-        </is>
-      </c>
-      <c r="B390" s="50" t="inlineStr">
-        <is>
-          <t>吴芷兰妊娠</t>
-        </is>
-      </c>
-      <c r="C390" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D390" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E390" s="53" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F390" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G390" s="51" t="inlineStr"/>
-      <c r="H390" s="52" t="inlineStr"/>
-      <c r="I390" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J390" s="53" t="inlineStr">
-        <is>
-          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
         </is>
       </c>
       <c r="K390" s="50" t="inlineStr"/>
@@ -25544,23 +25538,23 @@
     <row r="391">
       <c r="A391" s="50" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_03</t>
         </is>
       </c>
       <c r="B391" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗失败</t>
         </is>
       </c>
       <c r="C391" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D391" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E391" s="53" t="inlineStr">
+      <c r="E391" s="50" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
@@ -25572,10 +25566,14 @@
       </c>
       <c r="G391" s="51" t="inlineStr"/>
       <c r="H391" s="52" t="inlineStr"/>
-      <c r="I391" s="51" t="inlineStr"/>
-      <c r="J391" s="53" t="inlineStr">
-        <is>
-          <t>芷兰！！！</t>
+      <c r="I391" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J391" s="50" t="inlineStr">
+        <is>
+          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
         </is>
       </c>
       <c r="K391" s="50" t="inlineStr"/>
@@ -25592,7 +25590,7 @@
         </is>
       </c>
       <c r="C392" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D392" s="50" t="inlineStr">
         <is>
@@ -25601,7 +25599,7 @@
       </c>
       <c r="E392" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F392" s="52" t="inlineStr">
@@ -25609,25 +25607,21 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G392" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+      <c r="G392" s="51" t="inlineStr"/>
       <c r="H392" s="52" t="inlineStr"/>
       <c r="I392" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/026/026.png</t>
+          <t>current_scene</t>
         </is>
       </c>
       <c r="J392" s="53" t="inlineStr">
         <is>
-          <t>…...</t>
+          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
         </is>
       </c>
       <c r="K392" s="50" t="inlineStr"/>
     </row>
-    <row r="393">
+    <row r="393" hidden="1">
       <c r="A393" s="50" t="inlineStr">
         <is>
           <t>026_01</t>
@@ -25639,7 +25633,7 @@
         </is>
       </c>
       <c r="C393" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D393" s="50" t="inlineStr">
         <is>
@@ -25648,24 +25642,20 @@
       </c>
       <c r="E393" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F393" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G393" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G393" s="51" t="inlineStr"/>
       <c r="H393" s="52" t="inlineStr"/>
       <c r="I393" s="51" t="inlineStr"/>
       <c r="J393" s="53" t="inlineStr">
         <is>
-          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+          <t>芷兰！！！</t>
         </is>
       </c>
       <c r="K393" s="50" t="inlineStr"/>
@@ -25682,111 +25672,119 @@
         </is>
       </c>
       <c r="C394" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D394" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E394" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F394" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G394" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H394" s="52" t="inlineStr"/>
+      <c r="I394" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J394" s="53" t="inlineStr">
+        <is>
+          <t>…...</t>
+        </is>
+      </c>
+      <c r="K394" s="50" t="inlineStr"/>
+    </row>
+    <row r="395" hidden="1">
+      <c r="A395" s="50" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="B395" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C395" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D395" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E395" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F395" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G395" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H395" s="52" t="inlineStr"/>
+      <c r="I395" s="51" t="inlineStr"/>
+      <c r="J395" s="53" t="inlineStr">
+        <is>
+          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+        </is>
+      </c>
+      <c r="K395" s="50" t="inlineStr"/>
+    </row>
+    <row r="396" hidden="1">
+      <c r="A396" s="50" t="inlineStr">
+        <is>
+          <t>026_01</t>
+        </is>
+      </c>
+      <c r="B396" s="50" t="inlineStr">
+        <is>
+          <t>吴芷兰妊娠</t>
+        </is>
+      </c>
+      <c r="C396" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="D394" s="50" t="inlineStr">
+      <c r="D396" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E394" s="53" t="inlineStr">
+      <c r="E396" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F394" s="52" t="inlineStr">
+      <c r="F396" s="52" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="G394" s="51" t="inlineStr"/>
-      <c r="H394" s="51" t="inlineStr"/>
-      <c r="I394" s="51" t="inlineStr"/>
-      <c r="J394" s="53" t="inlineStr">
+      <c r="G396" s="51" t="inlineStr"/>
+      <c r="H396" s="51" t="inlineStr"/>
+      <c r="I396" s="51" t="inlineStr"/>
+      <c r="J396" s="53" t="inlineStr">
         <is>
           <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
-        </is>
-      </c>
-      <c r="K394" s="50" t="inlineStr"/>
-    </row>
-    <row r="395">
-      <c r="A395" s="50" t="inlineStr">
-        <is>
-          <t>026_02</t>
-        </is>
-      </c>
-      <c r="B395" s="50" t="inlineStr">
-        <is>
-          <t>026治疗成功</t>
-        </is>
-      </c>
-      <c r="C395" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D395" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E395" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F395" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G395" s="51" t="inlineStr"/>
-      <c r="H395" s="52" t="inlineStr"/>
-      <c r="I395" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J395" s="67" t="inlineStr">
-        <is>
-          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
-        </is>
-      </c>
-      <c r="K395" s="50" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" s="50" t="inlineStr">
-        <is>
-          <t>026_02</t>
-        </is>
-      </c>
-      <c r="B396" s="50" t="inlineStr">
-        <is>
-          <t>026治疗成功</t>
-        </is>
-      </c>
-      <c r="C396" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D396" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E396" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F396" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G396" s="51" t="inlineStr"/>
-      <c r="H396" s="52" t="inlineStr"/>
-      <c r="I396" s="51" t="inlineStr"/>
-      <c r="J396" s="50" t="inlineStr">
-        <is>
-          <t>芷兰…我们有孩子了…</t>
         </is>
       </c>
       <c r="K396" s="50" t="inlineStr"/>
@@ -25803,7 +25801,7 @@
         </is>
       </c>
       <c r="C397" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D397" s="50" t="inlineStr">
         <is>
@@ -25812,25 +25810,29 @@
       </c>
       <c r="E397" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F397" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G397" s="51" t="inlineStr"/>
       <c r="H397" s="52" t="inlineStr"/>
-      <c r="I397" s="51" t="inlineStr"/>
-      <c r="J397" s="50" t="inlineStr">
-        <is>
-          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+      <c r="I397" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J397" s="67" t="inlineStr">
+        <is>
+          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
         </is>
       </c>
       <c r="K397" s="50" t="inlineStr"/>
     </row>
-    <row r="398">
+    <row r="398" hidden="1">
       <c r="A398" s="50" t="inlineStr">
         <is>
           <t>026_02</t>
@@ -25842,7 +25844,7 @@
         </is>
       </c>
       <c r="C398" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D398" s="50" t="inlineStr">
         <is>
@@ -25860,16 +25862,16 @@
         </is>
       </c>
       <c r="G398" s="51" t="inlineStr"/>
-      <c r="H398" s="51" t="inlineStr"/>
+      <c r="H398" s="52" t="inlineStr"/>
       <c r="I398" s="51" t="inlineStr"/>
-      <c r="J398" s="67" t="inlineStr">
-        <is>
-          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+      <c r="J398" s="50" t="inlineStr">
+        <is>
+          <t>芷兰…我们有孩子了…</t>
         </is>
       </c>
       <c r="K398" s="50" t="inlineStr"/>
     </row>
-    <row r="399">
+    <row r="399" hidden="1">
       <c r="A399" s="50" t="inlineStr">
         <is>
           <t>026_02</t>
@@ -25881,7 +25883,7 @@
         </is>
       </c>
       <c r="C399" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D399" s="50" t="inlineStr">
         <is>
@@ -25890,149 +25892,141 @@
       </c>
       <c r="E399" s="50" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F399" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G399" s="51" t="inlineStr"/>
-      <c r="H399" s="51" t="inlineStr"/>
+      <c r="H399" s="52" t="inlineStr"/>
       <c r="I399" s="51" t="inlineStr"/>
       <c r="J399" s="50" t="inlineStr">
         <is>
+          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+        </is>
+      </c>
+      <c r="K399" s="50" t="inlineStr"/>
+    </row>
+    <row r="400" hidden="1">
+      <c r="A400" s="50" t="inlineStr">
+        <is>
+          <t>026_02</t>
+        </is>
+      </c>
+      <c r="B400" s="50" t="inlineStr">
+        <is>
+          <t>026治疗成功</t>
+        </is>
+      </c>
+      <c r="C400" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D400" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E400" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F400" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G400" s="51" t="inlineStr"/>
+      <c r="H400" s="51" t="inlineStr"/>
+      <c r="I400" s="51" t="inlineStr"/>
+      <c r="J400" s="67" t="inlineStr">
+        <is>
+          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+        </is>
+      </c>
+      <c r="K400" s="50" t="inlineStr"/>
+    </row>
+    <row r="401" hidden="1">
+      <c r="A401" s="50" t="inlineStr">
+        <is>
+          <t>026_02</t>
+        </is>
+      </c>
+      <c r="B401" s="50" t="inlineStr">
+        <is>
+          <t>026治疗成功</t>
+        </is>
+      </c>
+      <c r="C401" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D401" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E401" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F401" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G401" s="51" t="inlineStr"/>
+      <c r="H401" s="51" t="inlineStr"/>
+      <c r="I401" s="51" t="inlineStr"/>
+      <c r="J401" s="50" t="inlineStr">
+        <is>
           <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
         </is>
       </c>
-      <c r="K399" s="50" t="inlineStr"/>
-    </row>
-    <row r="400">
-      <c r="A400" s="50" t="inlineStr">
-        <is>
-          <t>026_03</t>
-        </is>
-      </c>
-      <c r="B400" s="50" t="inlineStr">
-        <is>
-          <t>026治疗失败</t>
-        </is>
-      </c>
-      <c r="C400" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D400" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E400" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F400" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G400" s="51" t="inlineStr"/>
-      <c r="H400" s="52" t="inlineStr"/>
-      <c r="I400" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J400" s="50" t="inlineStr">
-        <is>
-          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
-        </is>
-      </c>
-      <c r="K400" s="50" t="inlineStr"/>
-    </row>
-    <row r="401">
-      <c r="A401" s="50" t="inlineStr">
-        <is>
-          <t>027</t>
-        </is>
-      </c>
-      <c r="B401" s="50" t="inlineStr">
-        <is>
-          <t>上元灯节</t>
-        </is>
-      </c>
-      <c r="C401" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D401" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E401" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F401" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G401" s="51" t="inlineStr"/>
-      <c r="H401" s="54" t="inlineStr"/>
-      <c r="I401" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/004/004.png</t>
-        </is>
-      </c>
-      <c r="J401" s="53" t="inlineStr">
-        <is>
-          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
-        </is>
-      </c>
-      <c r="K401" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
-        </is>
-      </c>
+      <c r="K401" s="50" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="50" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_03</t>
         </is>
       </c>
       <c r="B402" s="50" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗失败</t>
         </is>
       </c>
       <c r="C402" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D402" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E402" s="53" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F402" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
+      <c r="E402" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F402" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G402" s="51" t="inlineStr"/>
-      <c r="H402" s="54" t="inlineStr"/>
-      <c r="I402" s="51" t="inlineStr"/>
-      <c r="J402" s="53" t="inlineStr">
-        <is>
-          <t>太好了，咱们快出发吧。</t>
+      <c r="H402" s="52" t="inlineStr"/>
+      <c r="I402" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J402" s="50" t="inlineStr">
+        <is>
+          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
         </is>
       </c>
       <c r="K402" s="50" t="inlineStr"/>
@@ -26049,7 +26043,7 @@
         </is>
       </c>
       <c r="C403" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D403" s="50" t="inlineStr">
         <is>
@@ -26058,25 +26052,33 @@
       </c>
       <c r="E403" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F403" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F403" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G403" s="51" t="inlineStr"/>
       <c r="H403" s="54" t="inlineStr"/>
-      <c r="I403" s="51" t="inlineStr"/>
+      <c r="I403" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/004/004.png</t>
+        </is>
+      </c>
       <c r="J403" s="53" t="inlineStr">
         <is>
-          <t>走。</t>
-        </is>
-      </c>
-      <c r="K403" s="50" t="inlineStr"/>
-    </row>
-    <row r="404">
+          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
+        </is>
+      </c>
+      <c r="K403" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" hidden="1">
       <c r="A404" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26088,38 +26090,34 @@
         </is>
       </c>
       <c r="C404" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D404" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E404" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F404" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E404" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F404" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G404" s="51" t="inlineStr"/>
-      <c r="H404" s="52" t="inlineStr"/>
-      <c r="I404" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_01.png</t>
-        </is>
-      </c>
+      <c r="H404" s="54" t="inlineStr"/>
+      <c r="I404" s="51" t="inlineStr"/>
       <c r="J404" s="53" t="inlineStr">
         <is>
-          <t>哇，好多人啊！好热闹啊！</t>
+          <t>太好了，咱们快出发吧。</t>
         </is>
       </c>
       <c r="K404" s="50" t="inlineStr"/>
     </row>
-    <row r="405">
+    <row r="405" hidden="1">
       <c r="A405" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26131,7 +26129,7 @@
         </is>
       </c>
       <c r="C405" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D405" s="50" t="inlineStr">
         <is>
@@ -26140,7 +26138,7 @@
       </c>
       <c r="E405" s="53" t="inlineStr">
         <is>
-          <t>陈皮</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F405" s="54" t="inlineStr">
@@ -26149,15 +26147,11 @@
         </is>
       </c>
       <c r="G405" s="51" t="inlineStr"/>
-      <c r="H405" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H405" s="54" t="inlineStr"/>
       <c r="I405" s="51" t="inlineStr"/>
       <c r="J405" s="53" t="inlineStr">
         <is>
-          <t>看你那没见过世面的样子。</t>
+          <t>走。</t>
         </is>
       </c>
       <c r="K405" s="50" t="inlineStr"/>
@@ -26174,103 +26168,107 @@
         </is>
       </c>
       <c r="C406" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D406" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E406" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F406" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G406" s="51" t="inlineStr"/>
+      <c r="H406" s="52" t="inlineStr"/>
+      <c r="I406" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_01.png</t>
+        </is>
+      </c>
+      <c r="J406" s="53" t="inlineStr">
+        <is>
+          <t>哇，好多人啊！好热闹啊！</t>
+        </is>
+      </c>
+      <c r="K406" s="50" t="inlineStr"/>
+    </row>
+    <row r="407" hidden="1">
+      <c r="A407" s="50" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B407" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C407" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D407" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E407" s="53" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F407" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G407" s="51" t="inlineStr"/>
+      <c r="H407" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I407" s="51" t="inlineStr"/>
+      <c r="J407" s="53" t="inlineStr">
+        <is>
+          <t>看你那没见过世面的样子。</t>
+        </is>
+      </c>
+      <c r="K407" s="50" t="inlineStr"/>
+    </row>
+    <row r="408" hidden="1">
+      <c r="A408" s="50" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B408" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C408" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="D406" s="50" t="inlineStr">
+      <c r="D408" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E406" s="50" t="inlineStr">
+      <c r="E408" s="50" t="inlineStr">
         <is>
           <t>半夏</t>
         </is>
       </c>
-      <c r="F406" s="52" t="inlineStr">
+      <c r="F408" s="52" t="inlineStr">
         <is>
           <t>mid</t>
-        </is>
-      </c>
-      <c r="G406" s="55" t="inlineStr"/>
-      <c r="H406" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I406" s="55" t="inlineStr"/>
-      <c r="J406" s="56" t="inlineStr">
-        <is>
-          <t>找打，你别跑！</t>
-        </is>
-      </c>
-      <c r="K406" s="55" t="inlineStr"/>
-    </row>
-    <row r="407">
-      <c r="A407" s="50" t="inlineStr">
-        <is>
-          <t>027</t>
-        </is>
-      </c>
-      <c r="B407" s="50" t="inlineStr">
-        <is>
-          <t>上元灯节</t>
-        </is>
-      </c>
-      <c r="C407" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="D407" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E407" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F407" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G407" s="55" t="inlineStr"/>
-      <c r="H407" s="55" t="inlineStr"/>
-      <c r="I407" s="55" t="inlineStr"/>
-      <c r="J407" s="56" t="inlineStr">
-        <is>
-          <t>那边好像有唱戏的，咱们去那边看看。</t>
-        </is>
-      </c>
-      <c r="K407" s="55" t="inlineStr"/>
-    </row>
-    <row r="408">
-      <c r="A408" s="50" t="inlineStr">
-        <is>
-          <t>027</t>
-        </is>
-      </c>
-      <c r="B408" s="50" t="inlineStr">
-        <is>
-          <t>上元灯节</t>
-        </is>
-      </c>
-      <c r="C408" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="D408" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E408" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F408" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
         </is>
       </c>
       <c r="G408" s="55" t="inlineStr"/>
@@ -26279,19 +26277,15 @@
           <t>hide</t>
         </is>
       </c>
-      <c r="I408" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_02.png</t>
-        </is>
-      </c>
+      <c r="I408" s="55" t="inlineStr"/>
       <c r="J408" s="56" t="inlineStr">
         <is>
-          <t>夫人，那边有座桥，咱们去走百病！</t>
+          <t>找打，你别跑！</t>
         </is>
       </c>
       <c r="K408" s="55" t="inlineStr"/>
     </row>
-    <row r="409">
+    <row r="409" hidden="1">
       <c r="A409" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26303,7 +26297,7 @@
         </is>
       </c>
       <c r="C409" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D409" s="50" t="inlineStr">
         <is>
@@ -26312,7 +26306,7 @@
       </c>
       <c r="E409" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F409" s="52" t="inlineStr">
@@ -26321,15 +26315,11 @@
         </is>
       </c>
       <c r="G409" s="55" t="inlineStr"/>
-      <c r="H409" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H409" s="55" t="inlineStr"/>
       <c r="I409" s="55" t="inlineStr"/>
       <c r="J409" s="56" t="inlineStr">
         <is>
-          <t>走，今夜走三桥，一年无灾病。</t>
+          <t>那边好像有唱戏的，咱们去那边看看。</t>
         </is>
       </c>
       <c r="K409" s="55" t="inlineStr"/>
@@ -26346,73 +26336,85 @@
         </is>
       </c>
       <c r="C410" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D410" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E410" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E410" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F410" s="52" t="inlineStr">
         <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G410" s="55" t="inlineStr"/>
+      <c r="H410" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I410" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_02.png</t>
+        </is>
+      </c>
+      <c r="J410" s="56" t="inlineStr">
+        <is>
+          <t>夫人，那边有座桥，咱们去走百病！</t>
+        </is>
+      </c>
+      <c r="K410" s="55" t="inlineStr"/>
+    </row>
+    <row r="411" hidden="1">
+      <c r="A411" s="50" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B411" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C411" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D411" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E411" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F411" s="52" t="inlineStr">
+        <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="G410" s="55" t="inlineStr"/>
-      <c r="H410" s="55" t="inlineStr"/>
-      <c r="I410" s="55" t="inlineStr"/>
-      <c r="J410" s="56" t="inlineStr">
-        <is>
-          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
-        </is>
-      </c>
-      <c r="K410" s="55" t="inlineStr"/>
-    </row>
-    <row r="411">
-      <c r="A411" s="50" t="inlineStr">
-        <is>
-          <t>027</t>
-        </is>
-      </c>
-      <c r="B411" s="50" t="inlineStr">
-        <is>
-          <t>上元灯节</t>
-        </is>
-      </c>
-      <c r="C411" s="50" t="n">
-        <v>11</v>
-      </c>
-      <c r="D411" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E411" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F411" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
       <c r="G411" s="55" t="inlineStr"/>
-      <c r="H411" s="55" t="inlineStr"/>
+      <c r="H411" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I411" s="55" t="inlineStr"/>
       <c r="J411" s="56" t="inlineStr">
         <is>
-          <t>哎哟，爹，您就别操心了。</t>
+          <t>走，今夜走三桥，一年无灾病。</t>
         </is>
       </c>
       <c r="K411" s="55" t="inlineStr"/>
     </row>
-    <row r="412">
+    <row r="412" hidden="1">
       <c r="A412" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26424,7 +26426,7 @@
         </is>
       </c>
       <c r="C412" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D412" s="50" t="inlineStr">
         <is>
@@ -26446,12 +26448,12 @@
       <c r="I412" s="55" t="inlineStr"/>
       <c r="J412" s="56" t="inlineStr">
         <is>
-          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
+          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
         </is>
       </c>
       <c r="K412" s="55" t="inlineStr"/>
     </row>
-    <row r="413">
+    <row r="413" hidden="1">
       <c r="A413" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26463,7 +26465,7 @@
         </is>
       </c>
       <c r="C413" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D413" s="50" t="inlineStr">
         <is>
@@ -26485,12 +26487,12 @@
       <c r="I413" s="55" t="inlineStr"/>
       <c r="J413" s="56" t="inlineStr">
         <is>
-          <t>别说了爹，咱们看戏去吧。</t>
+          <t>哎哟，爹，您就别操心了。</t>
         </is>
       </c>
       <c r="K413" s="55" t="inlineStr"/>
     </row>
-    <row r="414">
+    <row r="414" hidden="1">
       <c r="A414" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26502,7 +26504,7 @@
         </is>
       </c>
       <c r="C414" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D414" s="50" t="inlineStr">
         <is>
@@ -26511,25 +26513,25 @@
       </c>
       <c r="E414" s="53" t="inlineStr">
         <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F414" s="54" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F414" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G414" s="55" t="inlineStr"/>
       <c r="H414" s="55" t="inlineStr"/>
-      <c r="I414" s="51" t="inlineStr"/>
+      <c r="I414" s="55" t="inlineStr"/>
       <c r="J414" s="56" t="inlineStr">
         <is>
-          <t>老爷，那边儿在唱紫钗记呢。</t>
+          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
         </is>
       </c>
       <c r="K414" s="55" t="inlineStr"/>
     </row>
-    <row r="415">
+    <row r="415" hidden="1">
       <c r="A415" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26541,30 +26543,34 @@
         </is>
       </c>
       <c r="C415" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D415" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E415" s="55" t="inlineStr"/>
-      <c r="F415" s="50" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E415" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F415" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="G415" s="55" t="inlineStr"/>
       <c r="H415" s="55" t="inlineStr"/>
-      <c r="I415" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_03.png</t>
-        </is>
-      </c>
+      <c r="I415" s="55" t="inlineStr"/>
       <c r="J415" s="56" t="inlineStr">
         <is>
-          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
+          <t>别说了爹，咱们看戏去吧。</t>
         </is>
       </c>
       <c r="K415" s="55" t="inlineStr"/>
     </row>
-    <row r="416">
+    <row r="416" hidden="1">
       <c r="A416" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26576,7 +26582,7 @@
         </is>
       </c>
       <c r="C416" s="50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D416" s="50" t="inlineStr">
         <is>
@@ -26585,20 +26591,20 @@
       </c>
       <c r="E416" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F416" s="52" t="inlineStr">
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F416" s="54" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
       <c r="G416" s="55" t="inlineStr"/>
       <c r="H416" s="55" t="inlineStr"/>
-      <c r="I416" s="55" t="inlineStr"/>
-      <c r="J416" s="55" t="inlineStr">
-        <is>
-          <t>相公，咱们去猜灯谜吧！</t>
+      <c r="I416" s="51" t="inlineStr"/>
+      <c r="J416" s="56" t="inlineStr">
+        <is>
+          <t>老爷，那边儿在唱紫钗记呢。</t>
         </is>
       </c>
       <c r="K416" s="55" t="inlineStr"/>
@@ -26615,34 +26621,30 @@
         </is>
       </c>
       <c r="C417" s="50" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D417" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E417" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F417" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E417" s="55" t="inlineStr"/>
+      <c r="F417" s="50" t="inlineStr"/>
       <c r="G417" s="55" t="inlineStr"/>
       <c r="H417" s="55" t="inlineStr"/>
-      <c r="I417" s="55" t="inlineStr"/>
-      <c r="J417" s="55" t="inlineStr">
-        <is>
-          <t>走！</t>
+      <c r="I417" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_03.png</t>
+        </is>
+      </c>
+      <c r="J417" s="56" t="inlineStr">
+        <is>
+          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
         </is>
       </c>
       <c r="K417" s="55" t="inlineStr"/>
     </row>
-    <row r="418">
+    <row r="418" hidden="1">
       <c r="A418" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26654,7 +26656,7 @@
         </is>
       </c>
       <c r="C418" s="50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D418" s="50" t="inlineStr">
         <is>
@@ -26663,29 +26665,25 @@
       </c>
       <c r="E418" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F418" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F418" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G418" s="55" t="inlineStr"/>
       <c r="H418" s="55" t="inlineStr"/>
-      <c r="I418" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_04.png</t>
-        </is>
-      </c>
-      <c r="J418" s="68" t="inlineStr">
-        <is>
-          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
+      <c r="I418" s="55" t="inlineStr"/>
+      <c r="J418" s="55" t="inlineStr">
+        <is>
+          <t>相公，咱们去猜灯谜吧！</t>
         </is>
       </c>
       <c r="K418" s="55" t="inlineStr"/>
     </row>
-    <row r="419">
+    <row r="419" hidden="1">
       <c r="A419" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26697,7 +26695,7 @@
         </is>
       </c>
       <c r="C419" s="50" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D419" s="50" t="inlineStr">
         <is>
@@ -26706,12 +26704,12 @@
       </c>
       <c r="E419" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F419" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F419" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G419" s="55" t="inlineStr"/>
@@ -26719,7 +26717,7 @@
       <c r="I419" s="55" t="inlineStr"/>
       <c r="J419" s="55" t="inlineStr">
         <is>
-          <t>我知道，这是个"府"字。</t>
+          <t>走！</t>
         </is>
       </c>
       <c r="K419" s="55" t="inlineStr"/>
@@ -26736,7 +26734,7 @@
         </is>
       </c>
       <c r="C420" s="50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D420" s="50" t="inlineStr">
         <is>
@@ -26755,15 +26753,19 @@
       </c>
       <c r="G420" s="55" t="inlineStr"/>
       <c r="H420" s="55" t="inlineStr"/>
-      <c r="I420" s="55" t="inlineStr"/>
-      <c r="J420" s="55" t="inlineStr">
-        <is>
-          <t>还是娘子聪慧啊，哈哈。</t>
+      <c r="I420" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_04.png</t>
+        </is>
+      </c>
+      <c r="J420" s="68" t="inlineStr">
+        <is>
+          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
         </is>
       </c>
       <c r="K420" s="55" t="inlineStr"/>
     </row>
-    <row r="421">
+    <row r="421" hidden="1">
       <c r="A421" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26775,7 +26777,7 @@
         </is>
       </c>
       <c r="C421" s="50" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D421" s="50" t="inlineStr">
         <is>
@@ -26797,12 +26799,12 @@
       <c r="I421" s="55" t="inlineStr"/>
       <c r="J421" s="55" t="inlineStr">
         <is>
-          <t>你看这个，"大雪压青松"，打一味药材。</t>
+          <t>我知道，这是个"府"字。</t>
         </is>
       </c>
       <c r="K421" s="55" t="inlineStr"/>
     </row>
-    <row r="422">
+    <row r="422" hidden="1">
       <c r="A422" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26814,7 +26816,7 @@
         </is>
       </c>
       <c r="C422" s="50" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D422" s="50" t="inlineStr">
         <is>
@@ -26834,14 +26836,14 @@
       <c r="G422" s="55" t="inlineStr"/>
       <c r="H422" s="55" t="inlineStr"/>
       <c r="I422" s="55" t="inlineStr"/>
-      <c r="J422" s="68" t="inlineStr">
-        <is>
-          <t>这个我会，是"忍冬"。</t>
+      <c r="J422" s="55" t="inlineStr">
+        <is>
+          <t>还是娘子聪慧啊，哈哈。</t>
         </is>
       </c>
       <c r="K422" s="55" t="inlineStr"/>
     </row>
-    <row r="423">
+    <row r="423" hidden="1">
       <c r="A423" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26853,7 +26855,7 @@
         </is>
       </c>
       <c r="C423" s="50" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D423" s="50" t="inlineStr">
         <is>
@@ -26862,25 +26864,25 @@
       </c>
       <c r="E423" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F423" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G423" s="55" t="inlineStr"/>
       <c r="H423" s="55" t="inlineStr"/>
       <c r="I423" s="55" t="inlineStr"/>
-      <c r="J423" s="68" t="inlineStr">
-        <is>
-          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
+      <c r="J423" s="55" t="inlineStr">
+        <is>
+          <t>你看这个，"大雪压青松"，打一味药材。</t>
         </is>
       </c>
       <c r="K423" s="55" t="inlineStr"/>
     </row>
-    <row r="424">
+    <row r="424" hidden="1">
       <c r="A424" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26892,7 +26894,7 @@
         </is>
       </c>
       <c r="C424" s="50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D424" s="50" t="inlineStr">
         <is>
@@ -26901,29 +26903,25 @@
       </c>
       <c r="E424" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F424" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F424" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G424" s="55" t="inlineStr"/>
       <c r="H424" s="55" t="inlineStr"/>
-      <c r="I424" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_05.png</t>
-        </is>
-      </c>
-      <c r="J424" s="55" t="inlineStr">
-        <is>
-          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
+      <c r="I424" s="55" t="inlineStr"/>
+      <c r="J424" s="68" t="inlineStr">
+        <is>
+          <t>这个我会，是"忍冬"。</t>
         </is>
       </c>
       <c r="K424" s="55" t="inlineStr"/>
     </row>
-    <row r="425">
+    <row r="425" hidden="1">
       <c r="A425" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -26935,7 +26933,7 @@
         </is>
       </c>
       <c r="C425" s="50" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D425" s="50" t="inlineStr">
         <is>
@@ -26944,20 +26942,20 @@
       </c>
       <c r="E425" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F425" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F425" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G425" s="55" t="inlineStr"/>
       <c r="H425" s="55" t="inlineStr"/>
       <c r="I425" s="55" t="inlineStr"/>
-      <c r="J425" s="55" t="inlineStr">
-        <is>
-          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
+      <c r="J425" s="68" t="inlineStr">
+        <is>
+          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
         </is>
       </c>
       <c r="K425" s="55" t="inlineStr"/>
@@ -26974,7 +26972,7 @@
         </is>
       </c>
       <c r="C426" s="50" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D426" s="50" t="inlineStr">
         <is>
@@ -26983,25 +26981,29 @@
       </c>
       <c r="E426" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F426" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G426" s="55" t="inlineStr"/>
       <c r="H426" s="55" t="inlineStr"/>
-      <c r="I426" s="55" t="inlineStr"/>
+      <c r="I426" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_05.png</t>
+        </is>
+      </c>
       <c r="J426" s="55" t="inlineStr">
         <is>
-          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
         </is>
       </c>
       <c r="K426" s="55" t="inlineStr"/>
     </row>
-    <row r="427">
+    <row r="427" hidden="1">
       <c r="A427" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -27013,7 +27015,7 @@
         </is>
       </c>
       <c r="C427" s="50" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D427" s="50" t="inlineStr">
         <is>
@@ -27022,12 +27024,12 @@
       </c>
       <c r="E427" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F427" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F427" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G427" s="55" t="inlineStr"/>
@@ -27035,12 +27037,12 @@
       <c r="I427" s="55" t="inlineStr"/>
       <c r="J427" s="55" t="inlineStr">
         <is>
-          <t>是啊，一家人平平安安就好啊。</t>
+          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
         </is>
       </c>
       <c r="K427" s="55" t="inlineStr"/>
     </row>
-    <row r="428">
+    <row r="428" hidden="1">
       <c r="A428" s="50" t="inlineStr">
         <is>
           <t>027</t>
@@ -27052,7 +27054,7 @@
         </is>
       </c>
       <c r="C428" s="50" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D428" s="50" t="inlineStr">
         <is>
@@ -27061,12 +27063,12 @@
       </c>
       <c r="E428" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F428" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G428" s="55" t="inlineStr"/>
@@ -27074,133 +27076,133 @@
       <c r="I428" s="55" t="inlineStr"/>
       <c r="J428" s="55" t="inlineStr">
         <is>
+          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+        </is>
+      </c>
+      <c r="K428" s="55" t="inlineStr"/>
+    </row>
+    <row r="429" hidden="1">
+      <c r="A429" s="50" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B429" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C429" s="50" t="n">
+        <v>27</v>
+      </c>
+      <c r="D429" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E429" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F429" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G429" s="55" t="inlineStr"/>
+      <c r="H429" s="55" t="inlineStr"/>
+      <c r="I429" s="55" t="inlineStr"/>
+      <c r="J429" s="55" t="inlineStr">
+        <is>
+          <t>是啊，一家人平平安安就好啊。</t>
+        </is>
+      </c>
+      <c r="K429" s="55" t="inlineStr"/>
+    </row>
+    <row r="430" hidden="1">
+      <c r="A430" s="50" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B430" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C430" s="50" t="n">
+        <v>28</v>
+      </c>
+      <c r="D430" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E430" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F430" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G430" s="55" t="inlineStr"/>
+      <c r="H430" s="55" t="inlineStr"/>
+      <c r="I430" s="55" t="inlineStr"/>
+      <c r="J430" s="55" t="inlineStr">
+        <is>
           <t>好了，不早了，咱们该回家了。</t>
         </is>
       </c>
-      <c r="K428" s="55" t="inlineStr"/>
-    </row>
-    <row r="429" ht="30" customHeight="1">
-      <c r="A429" s="50" t="inlineStr">
+      <c r="K430" s="55" t="inlineStr"/>
+    </row>
+    <row r="431" ht="30" customHeight="1">
+      <c r="A431" s="50" t="inlineStr">
         <is>
           <t>028_01</t>
         </is>
       </c>
-      <c r="B429" s="50" t="inlineStr">
+      <c r="B431" s="50" t="inlineStr">
         <is>
           <t>曾题名痰火扰心</t>
         </is>
       </c>
-      <c r="C429" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D429" s="50" t="inlineStr">
+      <c r="C431" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D431" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E429" s="53" t="inlineStr">
+      <c r="E431" s="53" t="inlineStr">
         <is>
           <t>曾和</t>
         </is>
       </c>
-      <c r="F429" s="51" t="inlineStr">
+      <c r="F431" s="51" t="inlineStr">
         <is>
           <t>left</t>
-        </is>
-      </c>
-      <c r="G429" s="51" t="inlineStr"/>
-      <c r="H429" s="54" t="inlineStr"/>
-      <c r="I429" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J429" s="53" t="inlineStr">
-        <is>
-          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
-        </is>
-      </c>
-      <c r="K429" s="50" t="inlineStr"/>
-    </row>
-    <row r="430">
-      <c r="A430" s="50" t="inlineStr">
-        <is>
-          <t>028_01</t>
-        </is>
-      </c>
-      <c r="B430" s="50" t="inlineStr">
-        <is>
-          <t>曾题名痰火扰心</t>
-        </is>
-      </c>
-      <c r="C430" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D430" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E430" s="53" t="inlineStr">
-        <is>
-          <t>曾题名</t>
-        </is>
-      </c>
-      <c r="F430" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G430" s="51" t="inlineStr"/>
-      <c r="H430" s="54" t="inlineStr"/>
-      <c r="I430" s="51" t="inlineStr"/>
-      <c r="J430" s="53" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K430" s="50" t="inlineStr"/>
-    </row>
-    <row r="431">
-      <c r="A431" s="50" t="inlineStr">
-        <is>
-          <t>028_01</t>
-        </is>
-      </c>
-      <c r="B431" s="50" t="inlineStr">
-        <is>
-          <t>曾题名痰火扰心</t>
-        </is>
-      </c>
-      <c r="C431" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D431" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E431" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F431" s="54" t="inlineStr">
-        <is>
-          <t>right</t>
         </is>
       </c>
       <c r="G431" s="51" t="inlineStr"/>
       <c r="H431" s="54" t="inlineStr"/>
-      <c r="I431" s="51" t="inlineStr"/>
+      <c r="I431" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J431" s="53" t="inlineStr">
         <is>
-          <t>别急，坐下来让我看看。</t>
+          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
         </is>
       </c>
       <c r="K431" s="50" t="inlineStr"/>
     </row>
-    <row r="432">
+    <row r="432" hidden="1">
       <c r="A432" s="50" t="inlineStr">
         <is>
           <t>028_01</t>
@@ -27212,34 +27214,46 @@
         </is>
       </c>
       <c r="C432" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D432" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E432" s="50" t="inlineStr"/>
-      <c r="F432" s="51" t="inlineStr"/>
+      <c r="E432" s="53" t="inlineStr">
+        <is>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F432" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G432" s="51" t="inlineStr"/>
-      <c r="H432" s="51" t="inlineStr"/>
+      <c r="H432" s="54" t="inlineStr"/>
       <c r="I432" s="51" t="inlineStr"/>
-      <c r="J432" s="50" t="inlineStr"/>
+      <c r="J432" s="53" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
       <c r="K432" s="50" t="inlineStr"/>
     </row>
-    <row r="433">
+    <row r="433" hidden="1">
       <c r="A433" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B433" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C433" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D433" s="50" t="inlineStr">
         <is>
@@ -27251,62 +27265,46 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F433" s="52" t="inlineStr">
+      <c r="F433" s="54" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
       <c r="G433" s="51" t="inlineStr"/>
       <c r="H433" s="54" t="inlineStr"/>
-      <c r="I433" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I433" s="51" t="inlineStr"/>
       <c r="J433" s="53" t="inlineStr">
         <is>
-          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
+          <t>别急，坐下来让我看看。</t>
         </is>
       </c>
       <c r="K433" s="50" t="inlineStr"/>
     </row>
-    <row r="434">
+    <row r="434" hidden="1">
       <c r="A434" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B434" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C434" s="50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D434" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E434" s="53" t="inlineStr">
-        <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F434" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="E434" s="50" t="inlineStr"/>
+      <c r="F434" s="51" t="inlineStr"/>
       <c r="G434" s="51" t="inlineStr"/>
-      <c r="H434" s="54" t="inlineStr"/>
+      <c r="H434" s="51" t="inlineStr"/>
       <c r="I434" s="51" t="inlineStr"/>
-      <c r="J434" s="53" t="inlineStr">
-        <is>
-          <t>好好的怎么就得了这怪病呢？</t>
-        </is>
-      </c>
+      <c r="J434" s="50" t="inlineStr"/>
       <c r="K434" s="50" t="inlineStr"/>
     </row>
     <row r="435">
@@ -27321,7 +27319,7 @@
         </is>
       </c>
       <c r="C435" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D435" s="50" t="inlineStr">
         <is>
@@ -27339,16 +27337,20 @@
         </is>
       </c>
       <c r="G435" s="51" t="inlineStr"/>
-      <c r="H435" s="51" t="inlineStr"/>
-      <c r="I435" s="51" t="inlineStr"/>
+      <c r="H435" s="54" t="inlineStr"/>
+      <c r="I435" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J435" s="53" t="inlineStr">
         <is>
-          <t>是不是读书压力太大了呀？</t>
+          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
         </is>
       </c>
       <c r="K435" s="50" t="inlineStr"/>
     </row>
-    <row r="436">
+    <row r="436" hidden="1">
       <c r="A436" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27360,7 +27362,7 @@
         </is>
       </c>
       <c r="C436" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D436" s="50" t="inlineStr">
         <is>
@@ -27369,25 +27371,25 @@
       </c>
       <c r="E436" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F436" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G436" s="51" t="inlineStr"/>
-      <c r="H436" s="51" t="inlineStr"/>
+      <c r="H436" s="54" t="inlineStr"/>
       <c r="I436" s="51" t="inlineStr"/>
       <c r="J436" s="53" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>好好的怎么就得了这怪病呢？</t>
         </is>
       </c>
       <c r="K436" s="50" t="inlineStr"/>
     </row>
-    <row r="437">
+    <row r="437" hidden="1">
       <c r="A437" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27399,7 +27401,7 @@
         </is>
       </c>
       <c r="C437" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D437" s="50" t="inlineStr">
         <is>
@@ -27408,12 +27410,12 @@
       </c>
       <c r="E437" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F437" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F437" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G437" s="51" t="inlineStr"/>
@@ -27421,12 +27423,12 @@
       <c r="I437" s="51" t="inlineStr"/>
       <c r="J437" s="53" t="inlineStr">
         <is>
-          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+          <t>是不是读书压力太大了呀？</t>
         </is>
       </c>
       <c r="K437" s="50" t="inlineStr"/>
     </row>
-    <row r="438">
+    <row r="438" hidden="1">
       <c r="A438" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27438,7 +27440,7 @@
         </is>
       </c>
       <c r="C438" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D438" s="50" t="inlineStr">
         <is>
@@ -27447,51 +27449,51 @@
       </c>
       <c r="E438" s="53" t="inlineStr">
         <is>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F438" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G438" s="51" t="inlineStr"/>
+      <c r="H438" s="51" t="inlineStr"/>
+      <c r="I438" s="51" t="inlineStr"/>
+      <c r="J438" s="53" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K438" s="50" t="inlineStr"/>
+    </row>
+    <row r="439" hidden="1">
+      <c r="A439" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B439" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C439" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D439" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E439" s="53" t="inlineStr">
+        <is>
           <t>曾和</t>
         </is>
       </c>
-      <c r="F438" s="54" t="inlineStr">
+      <c r="F439" s="54" t="inlineStr">
         <is>
           <t>left</t>
-        </is>
-      </c>
-      <c r="G438" s="55" t="inlineStr"/>
-      <c r="H438" s="55" t="inlineStr"/>
-      <c r="I438" s="55" t="inlineStr"/>
-      <c r="J438" s="56" t="inlineStr">
-        <is>
-          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
-        </is>
-      </c>
-      <c r="K438" s="55" t="inlineStr"/>
-    </row>
-    <row r="439">
-      <c r="A439" s="50" t="inlineStr">
-        <is>
-          <t>028_02</t>
-        </is>
-      </c>
-      <c r="B439" s="50" t="inlineStr">
-        <is>
-          <t>028治疗成功</t>
-        </is>
-      </c>
-      <c r="C439" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="D439" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E439" s="53" t="inlineStr">
-        <is>
-          <t>曾题名</t>
-        </is>
-      </c>
-      <c r="F439" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
         </is>
       </c>
       <c r="G439" s="51" t="inlineStr"/>
@@ -27499,12 +27501,12 @@
       <c r="I439" s="51" t="inlineStr"/>
       <c r="J439" s="53" t="inlineStr">
         <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K439" s="55" t="inlineStr"/>
-    </row>
-    <row r="440">
+          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+        </is>
+      </c>
+      <c r="K439" s="50" t="inlineStr"/>
+    </row>
+    <row r="440" hidden="1">
       <c r="A440" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27516,7 +27518,7 @@
         </is>
       </c>
       <c r="C440" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D440" s="50" t="inlineStr">
         <is>
@@ -27525,25 +27527,25 @@
       </c>
       <c r="E440" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F440" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F440" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G440" s="55" t="inlineStr"/>
       <c r="H440" s="55" t="inlineStr"/>
       <c r="I440" s="55" t="inlineStr"/>
-      <c r="J440" s="53" t="inlineStr">
-        <is>
-          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
+      <c r="J440" s="56" t="inlineStr">
+        <is>
+          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
         </is>
       </c>
       <c r="K440" s="55" t="inlineStr"/>
     </row>
-    <row r="441">
+    <row r="441" hidden="1">
       <c r="A441" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27555,7 +27557,7 @@
         </is>
       </c>
       <c r="C441" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D441" s="50" t="inlineStr">
         <is>
@@ -27564,25 +27566,25 @@
       </c>
       <c r="E441" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F441" s="54" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G441" s="55" t="inlineStr"/>
-      <c r="H441" s="55" t="inlineStr"/>
-      <c r="I441" s="55" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G441" s="51" t="inlineStr"/>
+      <c r="H441" s="51" t="inlineStr"/>
+      <c r="I441" s="51" t="inlineStr"/>
       <c r="J441" s="53" t="inlineStr">
         <is>
-          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K441" s="55" t="inlineStr"/>
     </row>
-    <row r="442">
+    <row r="442" hidden="1">
       <c r="A442" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27594,7 +27596,7 @@
         </is>
       </c>
       <c r="C442" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D442" s="50" t="inlineStr">
         <is>
@@ -27603,12 +27605,12 @@
       </c>
       <c r="E442" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F442" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F442" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G442" s="55" t="inlineStr"/>
@@ -27616,12 +27618,12 @@
       <c r="I442" s="55" t="inlineStr"/>
       <c r="J442" s="53" t="inlineStr">
         <is>
-          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
+          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
         </is>
       </c>
       <c r="K442" s="55" t="inlineStr"/>
     </row>
-    <row r="443">
+    <row r="443" hidden="1">
       <c r="A443" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27633,7 +27635,7 @@
         </is>
       </c>
       <c r="C443" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D443" s="50" t="inlineStr">
         <is>
@@ -27642,12 +27644,12 @@
       </c>
       <c r="E443" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F443" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G443" s="55" t="inlineStr"/>
@@ -27655,12 +27657,12 @@
       <c r="I443" s="55" t="inlineStr"/>
       <c r="J443" s="53" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
         </is>
       </c>
       <c r="K443" s="55" t="inlineStr"/>
     </row>
-    <row r="444">
+    <row r="444" hidden="1">
       <c r="A444" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27672,7 +27674,7 @@
         </is>
       </c>
       <c r="C444" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D444" s="50" t="inlineStr">
         <is>
@@ -27681,25 +27683,25 @@
       </c>
       <c r="E444" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F444" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F444" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G444" s="55" t="inlineStr"/>
       <c r="H444" s="55" t="inlineStr"/>
       <c r="I444" s="55" t="inlineStr"/>
-      <c r="J444" s="88" t="inlineStr">
-        <is>
-          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
+      <c r="J444" s="53" t="inlineStr">
+        <is>
+          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
         </is>
       </c>
       <c r="K444" s="55" t="inlineStr"/>
     </row>
-    <row r="445">
+    <row r="445" hidden="1">
       <c r="A445" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27711,7 +27713,7 @@
         </is>
       </c>
       <c r="C445" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D445" s="50" t="inlineStr">
         <is>
@@ -27720,25 +27722,25 @@
       </c>
       <c r="E445" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F445" s="54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G445" s="55" t="inlineStr"/>
       <c r="H445" s="55" t="inlineStr"/>
       <c r="I445" s="55" t="inlineStr"/>
-      <c r="J445" s="88" t="inlineStr">
-        <is>
-          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+      <c r="J445" s="53" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
       <c r="K445" s="55" t="inlineStr"/>
     </row>
-    <row r="446">
+    <row r="446" hidden="1">
       <c r="A446" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27750,7 +27752,7 @@
         </is>
       </c>
       <c r="C446" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D446" s="50" t="inlineStr">
         <is>
@@ -27759,25 +27761,25 @@
       </c>
       <c r="E446" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F446" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F446" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G446" s="55" t="inlineStr"/>
       <c r="H446" s="55" t="inlineStr"/>
       <c r="I446" s="55" t="inlineStr"/>
-      <c r="J446" s="88" t="inlineStr">
-        <is>
-          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+      <c r="J446" s="87" t="inlineStr">
+        <is>
+          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
         </is>
       </c>
       <c r="K446" s="55" t="inlineStr"/>
     </row>
-    <row r="447">
+    <row r="447" hidden="1">
       <c r="A447" s="50" t="inlineStr">
         <is>
           <t>028_02</t>
@@ -27789,7 +27791,7 @@
         </is>
       </c>
       <c r="C447" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D447" s="50" t="inlineStr">
         <is>
@@ -27798,69 +27800,155 @@
       </c>
       <c r="E447" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F447" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F447" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G447" s="55" t="inlineStr"/>
       <c r="H447" s="55" t="inlineStr"/>
       <c r="I447" s="55" t="inlineStr"/>
-      <c r="J447" s="88" t="inlineStr">
+      <c r="J447" s="87" t="inlineStr">
+        <is>
+          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+        </is>
+      </c>
+      <c r="K447" s="55" t="inlineStr"/>
+    </row>
+    <row r="448" hidden="1">
+      <c r="A448" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B448" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C448" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D448" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E448" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F448" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G448" s="55" t="inlineStr"/>
+      <c r="H448" s="55" t="inlineStr"/>
+      <c r="I448" s="55" t="inlineStr"/>
+      <c r="J448" s="87" t="inlineStr">
+        <is>
+          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+        </is>
+      </c>
+      <c r="K448" s="55" t="inlineStr"/>
+    </row>
+    <row r="449" hidden="1">
+      <c r="A449" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B449" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C449" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D449" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E449" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F449" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G449" s="55" t="inlineStr"/>
+      <c r="H449" s="55" t="inlineStr"/>
+      <c r="I449" s="55" t="inlineStr"/>
+      <c r="J449" s="87" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="K447" s="55" t="inlineStr"/>
-    </row>
-    <row r="448">
-      <c r="A448" s="50" t="inlineStr">
+      <c r="K449" s="55" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="50" t="inlineStr">
         <is>
           <t>028_03</t>
         </is>
       </c>
-      <c r="B448" s="50" t="inlineStr">
+      <c r="B450" s="50" t="inlineStr">
         <is>
           <t>028治疗失败</t>
         </is>
       </c>
-      <c r="C448" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D448" s="50" t="inlineStr">
+      <c r="C450" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D450" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E448" s="53" t="inlineStr">
+      <c r="E450" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F448" s="52" t="inlineStr">
+      <c r="F450" s="52" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G448" s="51" t="inlineStr"/>
-      <c r="H448" s="54" t="inlineStr"/>
-      <c r="I448" s="51" t="inlineStr">
+      <c r="G450" s="51" t="inlineStr"/>
+      <c r="H450" s="54" t="inlineStr"/>
+      <c r="I450" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J448" s="53" t="inlineStr">
+      <c r="J450" s="53" t="inlineStr">
         <is>
           <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
-      <c r="K448" s="50" t="inlineStr"/>
+      <c r="K450" s="50" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BI450">
+    <filterColumn colId="8" hiddenButton="0" showButton="1">
+      <customFilters>
+        <customFilter val=" " operator="notEqual"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -27871,7 +27959,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" customWidth="1" style="3" min="1" max="1"/>
     <col width="19.25" customWidth="1" style="3" min="2" max="2"/>
@@ -30059,7 +30147,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="1" max="1"/>
     <col width="4.5" customWidth="1" style="32" min="2" max="2"/>
@@ -30084,8 +30172,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="135"/>
-    <col width="9" customWidth="1" style="9" min="136" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="136"/>
+    <col width="9" customWidth="1" style="9" min="137" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -30895,7 +30983,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="25.5" customWidth="1" style="3" min="1" max="1"/>
     <col width="15.125" customWidth="1" style="3" min="2" max="2"/>
@@ -31623,7 +31711,7 @@
           <t>大青龙汤
 【出处】《伤寒论》
 【功效】发汗解表，兼清里热
-【主治】外寒里热
+【主治】表寒里热
 【组成】
 君：麻黄 六钱
 臣：桂枝 二钱，石膏 一两
@@ -33149,7 +33237,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G357"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="14.375" customWidth="1" style="4" min="1" max="1"/>
     <col width="11.875" customWidth="1" style="4" min="2" max="2"/>
@@ -44928,7 +45016,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="16.25" customWidth="1" style="7" min="1" max="1"/>
     <col width="11.625" customWidth="1" style="7" min="2" max="2"/>
@@ -53107,8 +53195,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -53135,32 +53223,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
     <cfRule type="duplicateValues" priority="123" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
     <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
     <cfRule type="duplicateValues" priority="117" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
     <cfRule type="duplicateValues" priority="115" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
     <cfRule type="duplicateValues" priority="110" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -53199,20 +53287,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
     <cfRule type="duplicateValues" priority="154" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
     <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
     <cfRule type="duplicateValues" priority="146" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -53223,8 +53311,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
     <cfRule type="duplicateValues" priority="54" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -53235,32 +53323,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
     <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
     <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
     <cfRule type="duplicateValues" priority="49" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
     <cfRule type="duplicateValues" priority="148" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
     <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
     <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -53271,8 +53359,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
     <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -53283,8 +53371,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
     <cfRule type="duplicateValues" priority="56" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -53295,8 +53383,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
     <cfRule type="duplicateValues" priority="52" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -53307,36 +53395,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
     <cfRule type="duplicateValues" priority="99" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
     <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
     <cfRule type="duplicateValues" priority="62" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
     <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -53367,12 +53455,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
     <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
     <cfRule type="duplicateValues" priority="16" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -53387,12 +53475,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
     <cfRule type="duplicateValues" priority="88" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
     <cfRule type="duplicateValues" priority="142" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -53403,8 +53491,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
     <cfRule type="duplicateValues" priority="131" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>
@@ -53420,7 +53508,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.65"/>
   <cols>
     <col width="45.625" customWidth="1" min="1" max="1"/>
     <col width="23.5" customWidth="1" min="2" max="2"/>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -7745,7 +7745,9 @@
       <c r="M18" s="48" t="inlineStr"/>
       <c r="N18" s="48" t="inlineStr"/>
       <c r="O18" s="48" t="inlineStr"/>
-      <c r="P18" s="48" t="inlineStr"/>
+      <c r="P18" s="48" t="n">
+        <v>1000</v>
+      </c>
       <c r="Q18" s="48" t="n">
         <v>1000</v>
       </c>
@@ -8491,7 +8493,9 @@
       <c r="M33" s="48" t="inlineStr"/>
       <c r="N33" s="48" t="inlineStr"/>
       <c r="O33" s="48" t="inlineStr"/>
-      <c r="P33" s="48" t="inlineStr"/>
+      <c r="P33" s="48" t="n">
+        <v>1000</v>
+      </c>
       <c r="Q33" s="48" t="inlineStr"/>
       <c r="R33" s="48" t="inlineStr"/>
       <c r="S33" s="48" t="b">
@@ -8745,7 +8749,9 @@
       <c r="M38" s="48" t="inlineStr"/>
       <c r="N38" s="48" t="inlineStr"/>
       <c r="O38" s="48" t="inlineStr"/>
-      <c r="P38" s="48" t="inlineStr"/>
+      <c r="P38" s="48" t="n">
+        <v>1000</v>
+      </c>
       <c r="Q38" s="48" t="inlineStr"/>
       <c r="R38" s="48" t="inlineStr"/>
       <c r="S38" s="48" t="b">
@@ -9410,7 +9416,7 @@
       <c r="N51" s="48" t="inlineStr"/>
       <c r="O51" s="48" t="inlineStr"/>
       <c r="P51" s="48" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="Q51" s="48" t="inlineStr"/>
       <c r="R51" s="48" t="inlineStr"/>
@@ -10053,7 +10059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K450"/>
+  <dimension ref="A1:K452"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -14449,7 +14455,7 @@
       <c r="I111" s="51" t="inlineStr"/>
       <c r="J111" s="52" t="inlineStr">
         <is>
-          <t>世子乃人中龙凤，可草民眼里看到的只有一位需要医治的病人，王爷只需付200文诊费即可。</t>
+          <t>世子乃人中龙凤，可草民眼里看到的只有一位需要医治的病人，王爷只需付一两白银诊费即可。</t>
         </is>
       </c>
       <c r="K111" s="55" t="inlineStr"/>
@@ -14558,7 +14564,7 @@
       <c r="I114" s="51" t="inlineStr"/>
       <c r="J114" s="52" t="inlineStr">
         <is>
-          <t>名望+1000</t>
+          <t>名望+1000，收入一两白银</t>
         </is>
       </c>
       <c r="K114" s="55" t="inlineStr"/>
@@ -18675,55 +18681,43 @@
     <row r="218">
       <c r="A218" s="50" t="inlineStr">
         <is>
-          <t>014_03</t>
+          <t>014_02</t>
         </is>
       </c>
       <c r="B218" s="50" t="inlineStr">
         <is>
-          <t>014治疗失败</t>
+          <t>014治疗成功</t>
         </is>
       </c>
       <c r="C218" s="50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D218" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E218" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F218" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G218" s="51" t="inlineStr"/>
-      <c r="H218" s="52" t="inlineStr"/>
-      <c r="I218" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J218" s="50" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
-        </is>
-      </c>
-      <c r="K218" s="50" t="inlineStr"/>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E218" s="53" t="inlineStr"/>
+      <c r="F218" s="52" t="inlineStr"/>
+      <c r="G218" s="55" t="inlineStr"/>
+      <c r="H218" s="55" t="inlineStr"/>
+      <c r="I218" s="51" t="inlineStr"/>
+      <c r="J218" s="56" t="inlineStr">
+        <is>
+          <t>收入一两白银</t>
+        </is>
+      </c>
+      <c r="K218" s="55" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="50" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>014_03</t>
         </is>
       </c>
       <c r="B219" s="50" t="inlineStr">
         <is>
-          <t>雷万钧归来</t>
+          <t>014治疗失败</t>
         </is>
       </c>
       <c r="C219" s="50" t="n">
@@ -18731,11 +18725,19 @@
       </c>
       <c r="D219" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E219" s="50" t="inlineStr"/>
-      <c r="F219" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E219" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F219" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G219" s="51" t="inlineStr"/>
       <c r="H219" s="52" t="inlineStr"/>
       <c r="I219" s="51" t="inlineStr">
@@ -18743,9 +18745,9 @@
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J219" s="53" t="inlineStr">
-        <is>
-          <t>咚咚咚…</t>
+      <c r="J219" s="50" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K219" s="50" t="inlineStr"/>
@@ -18762,29 +18764,25 @@
         </is>
       </c>
       <c r="C220" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D220" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E220" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F220" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E220" s="50" t="inlineStr"/>
+      <c r="F220" s="51" t="inlineStr"/>
       <c r="G220" s="51" t="inlineStr"/>
       <c r="H220" s="52" t="inlineStr"/>
-      <c r="I220" s="51" t="inlineStr"/>
+      <c r="I220" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J220" s="53" t="inlineStr">
         <is>
-          <t>谁？</t>
+          <t>咚咚咚…</t>
         </is>
       </c>
       <c r="K220" s="50" t="inlineStr"/>
@@ -18801,7 +18799,7 @@
         </is>
       </c>
       <c r="C221" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D221" s="50" t="inlineStr">
         <is>
@@ -18810,20 +18808,20 @@
       </c>
       <c r="E221" s="53" t="inlineStr">
         <is>
-          <t>雷万钧</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F221" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G221" s="51" t="inlineStr"/>
       <c r="H221" s="52" t="inlineStr"/>
       <c r="I221" s="51" t="inlineStr"/>
-      <c r="J221" s="72" t="inlineStr">
-        <is>
-          <t>贤弟，是我。</t>
+      <c r="J221" s="53" t="inlineStr">
+        <is>
+          <t>谁？</t>
         </is>
       </c>
       <c r="K221" s="50" t="inlineStr"/>
@@ -18840,7 +18838,7 @@
         </is>
       </c>
       <c r="C222" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D222" s="50" t="inlineStr">
         <is>
@@ -18849,20 +18847,20 @@
       </c>
       <c r="E222" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>雷万钧</t>
         </is>
       </c>
       <c r="F222" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G222" s="51" t="inlineStr"/>
-      <c r="H222" s="51" t="inlineStr"/>
+      <c r="H222" s="52" t="inlineStr"/>
       <c r="I222" s="51" t="inlineStr"/>
-      <c r="J222" s="53" t="inlineStr">
-        <is>
-          <t>雷兄，怎么样，事情有眉目了吗？</t>
+      <c r="J222" s="72" t="inlineStr">
+        <is>
+          <t>贤弟，是我。</t>
         </is>
       </c>
       <c r="K222" s="50" t="inlineStr"/>
@@ -18879,7 +18877,7 @@
         </is>
       </c>
       <c r="C223" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D223" s="50" t="inlineStr">
         <is>
@@ -18888,20 +18886,20 @@
       </c>
       <c r="E223" s="53" t="inlineStr">
         <is>
-          <t>雷万钧</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F223" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G223" s="51" t="inlineStr"/>
       <c r="H223" s="51" t="inlineStr"/>
       <c r="I223" s="51" t="inlineStr"/>
-      <c r="J223" s="51" t="inlineStr">
-        <is>
-          <t>唉…按察司、布政司都不受理，去所部都指挥使司面见老宪台，他老人家说这里面水太深，让我别多管闲事…</t>
+      <c r="J223" s="53" t="inlineStr">
+        <is>
+          <t>雷兄，怎么样，事情有眉目了吗？</t>
         </is>
       </c>
       <c r="K223" s="50" t="inlineStr"/>
@@ -18918,7 +18916,7 @@
         </is>
       </c>
       <c r="C224" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D224" s="50" t="inlineStr">
         <is>
@@ -18927,23 +18925,23 @@
       </c>
       <c r="E224" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>雷万钧</t>
         </is>
       </c>
       <c r="F224" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G224" s="55" t="inlineStr"/>
-      <c r="H224" s="55" t="inlineStr"/>
-      <c r="I224" s="55" t="inlineStr"/>
-      <c r="J224" s="56" t="inlineStr">
-        <is>
-          <t>看来这事远比我们想的复杂…</t>
-        </is>
-      </c>
-      <c r="K224" s="55" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G224" s="51" t="inlineStr"/>
+      <c r="H224" s="51" t="inlineStr"/>
+      <c r="I224" s="51" t="inlineStr"/>
+      <c r="J224" s="51" t="inlineStr">
+        <is>
+          <t>唉…按察司、布政司都不受理，去所部都指挥使司面见老宪台，他老人家说这里面水太深，让我别多管闲事…</t>
+        </is>
+      </c>
+      <c r="K224" s="50" t="inlineStr"/>
     </row>
     <row r="225" hidden="1">
       <c r="A225" s="50" t="inlineStr">
@@ -18957,7 +18955,7 @@
         </is>
       </c>
       <c r="C225" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D225" s="50" t="inlineStr">
         <is>
@@ -18966,20 +18964,20 @@
       </c>
       <c r="E225" s="53" t="inlineStr">
         <is>
-          <t>雷万钧</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F225" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G225" s="55" t="inlineStr"/>
       <c r="H225" s="55" t="inlineStr"/>
       <c r="I225" s="55" t="inlineStr"/>
-      <c r="J225" s="55" t="inlineStr">
-        <is>
-          <t>放任不管的话，是要出大事的...</t>
+      <c r="J225" s="56" t="inlineStr">
+        <is>
+          <t>看来这事远比我们想的复杂…</t>
         </is>
       </c>
       <c r="K225" s="55" t="inlineStr"/>
@@ -18996,7 +18994,7 @@
         </is>
       </c>
       <c r="C226" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D226" s="50" t="inlineStr">
         <is>
@@ -19005,12 +19003,12 @@
       </c>
       <c r="E226" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>雷万钧</t>
         </is>
       </c>
       <c r="F226" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G226" s="55" t="inlineStr"/>
@@ -19018,7 +19016,7 @@
       <c r="I226" s="55" t="inlineStr"/>
       <c r="J226" s="55" t="inlineStr">
         <is>
-          <t>我想到了一个能帮上忙的人。</t>
+          <t>放任不管的话，是要出大事的...</t>
         </is>
       </c>
       <c r="K226" s="55" t="inlineStr"/>
@@ -19035,7 +19033,7 @@
         </is>
       </c>
       <c r="C227" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D227" s="50" t="inlineStr">
         <is>
@@ -19044,12 +19042,12 @@
       </c>
       <c r="E227" s="53" t="inlineStr">
         <is>
-          <t>雷万钧</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F227" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G227" s="55" t="inlineStr"/>
@@ -19057,7 +19055,7 @@
       <c r="I227" s="55" t="inlineStr"/>
       <c r="J227" s="55" t="inlineStr">
         <is>
-          <t>哦？是谁？</t>
+          <t>我想到了一个能帮上忙的人。</t>
         </is>
       </c>
       <c r="K227" s="55" t="inlineStr"/>
@@ -19074,7 +19072,7 @@
         </is>
       </c>
       <c r="C228" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D228" s="50" t="inlineStr">
         <is>
@@ -19083,12 +19081,12 @@
       </c>
       <c r="E228" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>雷万钧</t>
         </is>
       </c>
       <c r="F228" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G228" s="55" t="inlineStr"/>
@@ -19096,7 +19094,7 @@
       <c r="I228" s="55" t="inlineStr"/>
       <c r="J228" s="55" t="inlineStr">
         <is>
-          <t>楚王。</t>
+          <t>哦？是谁？</t>
         </is>
       </c>
       <c r="K228" s="55" t="inlineStr"/>
@@ -19113,7 +19111,7 @@
         </is>
       </c>
       <c r="C229" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D229" s="50" t="inlineStr">
         <is>
@@ -19122,20 +19120,20 @@
       </c>
       <c r="E229" s="53" t="inlineStr">
         <is>
-          <t>雷万钧</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F229" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G229" s="55" t="inlineStr"/>
       <c r="H229" s="55" t="inlineStr"/>
       <c r="I229" s="55" t="inlineStr"/>
-      <c r="J229" s="68" t="inlineStr">
-        <is>
-          <t>贤弟认识这么大的人物？</t>
+      <c r="J229" s="55" t="inlineStr">
+        <is>
+          <t>楚王。</t>
         </is>
       </c>
       <c r="K229" s="55" t="inlineStr"/>
@@ -19152,7 +19150,7 @@
         </is>
       </c>
       <c r="C230" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D230" s="50" t="inlineStr">
         <is>
@@ -19161,20 +19159,20 @@
       </c>
       <c r="E230" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>雷万钧</t>
         </is>
       </c>
       <c r="F230" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G230" s="55" t="inlineStr"/>
       <c r="H230" s="55" t="inlineStr"/>
       <c r="I230" s="55" t="inlineStr"/>
-      <c r="J230" s="55" t="inlineStr">
-        <is>
-          <t>之前医治过世子，应该能说得上话。</t>
+      <c r="J230" s="68" t="inlineStr">
+        <is>
+          <t>贤弟认识这么大的人物？</t>
         </is>
       </c>
       <c r="K230" s="55" t="inlineStr"/>
@@ -19191,7 +19189,7 @@
         </is>
       </c>
       <c r="C231" s="50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D231" s="50" t="inlineStr">
         <is>
@@ -19200,12 +19198,12 @@
       </c>
       <c r="E231" s="53" t="inlineStr">
         <is>
-          <t>雷万钧</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F231" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G231" s="55" t="inlineStr"/>
@@ -19213,7 +19211,7 @@
       <c r="I231" s="55" t="inlineStr"/>
       <c r="J231" s="55" t="inlineStr">
         <is>
-          <t>那还等什么，我陪你现在就去！</t>
+          <t>之前医治过世子，应该能说得上话。</t>
         </is>
       </c>
       <c r="K231" s="55" t="inlineStr"/>
@@ -19230,25 +19228,29 @@
         </is>
       </c>
       <c r="C232" s="50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D232" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E232" s="55" t="inlineStr"/>
-      <c r="F232" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E232" s="53" t="inlineStr">
+        <is>
+          <t>雷万钧</t>
+        </is>
+      </c>
+      <c r="F232" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="G232" s="55" t="inlineStr"/>
       <c r="H232" s="55" t="inlineStr"/>
-      <c r="I232" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/015/015_01.png</t>
-        </is>
-      </c>
+      <c r="I232" s="55" t="inlineStr"/>
       <c r="J232" s="55" t="inlineStr">
         <is>
-          <t>一路无话，两人来到了楚王府</t>
+          <t>那还等什么，我陪你现在就去！</t>
         </is>
       </c>
       <c r="K232" s="55" t="inlineStr"/>
@@ -19265,33 +19267,25 @@
         </is>
       </c>
       <c r="C233" s="50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D233" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E233" s="55" t="inlineStr">
-        <is>
-          <t>楚王</t>
-        </is>
-      </c>
-      <c r="F233" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E233" s="55" t="inlineStr"/>
+      <c r="F233" s="51" t="inlineStr"/>
       <c r="G233" s="55" t="inlineStr"/>
       <c r="H233" s="55" t="inlineStr"/>
       <c r="I233" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/015/015_02.png</t>
+          <t>res://Assets/Background/015/015_01.png</t>
         </is>
       </c>
       <c r="J233" s="55" t="inlineStr">
         <is>
-          <t>前日一别，先生别来无恙啊。</t>
+          <t>一路无话，两人来到了楚王府</t>
         </is>
       </c>
       <c r="K233" s="55" t="inlineStr"/>
@@ -19308,29 +19302,33 @@
         </is>
       </c>
       <c r="C234" s="50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D234" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E234" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F234" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E234" s="55" t="inlineStr">
+        <is>
+          <t>楚王</t>
+        </is>
+      </c>
+      <c r="F234" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G234" s="55" t="inlineStr"/>
       <c r="H234" s="55" t="inlineStr"/>
-      <c r="I234" s="55" t="inlineStr"/>
+      <c r="I234" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/015/015_02.png</t>
+        </is>
+      </c>
       <c r="J234" s="55" t="inlineStr">
         <is>
-          <t>草民拜见王爷，今日来是有一事请王爷帮忙。</t>
+          <t>前日一别，先生别来无恙啊。</t>
         </is>
       </c>
       <c r="K234" s="55" t="inlineStr"/>
@@ -19347,21 +19345,21 @@
         </is>
       </c>
       <c r="C235" s="50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D235" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E235" s="55" t="inlineStr">
-        <is>
-          <t>楚王</t>
-        </is>
-      </c>
-      <c r="F235" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E235" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F235" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G235" s="55" t="inlineStr"/>
@@ -19369,7 +19367,7 @@
       <c r="I235" s="55" t="inlineStr"/>
       <c r="J235" s="55" t="inlineStr">
         <is>
-          <t>先生是犬子的救命恩人，若有本王能帮上忙的，一定尽力而为。</t>
+          <t>草民拜见王爷，今日来是有一事请王爷帮忙。</t>
         </is>
       </c>
       <c r="K235" s="55" t="inlineStr"/>
@@ -19386,21 +19384,29 @@
         </is>
       </c>
       <c r="C236" s="50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D236" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E236" s="53" t="inlineStr"/>
-      <c r="F236" s="52" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E236" s="55" t="inlineStr">
+        <is>
+          <t>楚王</t>
+        </is>
+      </c>
+      <c r="F236" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G236" s="55" t="inlineStr"/>
       <c r="H236" s="55" t="inlineStr"/>
       <c r="I236" s="55" t="inlineStr"/>
       <c r="J236" s="55" t="inlineStr">
         <is>
-          <t>李东璧将事情的前因后果如实告诉了楚王</t>
+          <t>先生是犬子的救命恩人，若有本王能帮上忙的，一定尽力而为。</t>
         </is>
       </c>
       <c r="K236" s="55" t="inlineStr"/>
@@ -19417,29 +19423,21 @@
         </is>
       </c>
       <c r="C237" s="50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D237" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E237" s="55" t="inlineStr">
-        <is>
-          <t>楚王</t>
-        </is>
-      </c>
-      <c r="F237" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E237" s="53" t="inlineStr"/>
+      <c r="F237" s="52" t="inlineStr"/>
       <c r="G237" s="55" t="inlineStr"/>
       <c r="H237" s="55" t="inlineStr"/>
       <c r="I237" s="55" t="inlineStr"/>
-      <c r="J237" s="56" t="inlineStr">
-        <is>
-          <t>嗯…这些地方官胆子也太大了。可自成祖文皇帝之后，藩王不临民，不治事，干预地方军政是谋逆的大罪，本王也爱莫能助。</t>
+      <c r="J237" s="55" t="inlineStr">
+        <is>
+          <t>李东璧将事情的前因后果如实告诉了楚王</t>
         </is>
       </c>
       <c r="K237" s="55" t="inlineStr"/>
@@ -19456,21 +19454,21 @@
         </is>
       </c>
       <c r="C238" s="50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D238" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E238" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F238" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E238" s="55" t="inlineStr">
+        <is>
+          <t>楚王</t>
+        </is>
+      </c>
+      <c r="F238" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G238" s="55" t="inlineStr"/>
@@ -19478,7 +19476,7 @@
       <c r="I238" s="55" t="inlineStr"/>
       <c r="J238" s="56" t="inlineStr">
         <is>
-          <t>这事儿要是您不管，就没人能管了…瘟病若起，湖广将民不聊生啊。</t>
+          <t>嗯…这些地方官胆子也太大了。可自成祖文皇帝之后，藩王不临民，不治事，干预地方军政是谋逆的大罪，本王也爱莫能助。</t>
         </is>
       </c>
       <c r="K238" s="55" t="inlineStr"/>
@@ -19495,21 +19493,21 @@
         </is>
       </c>
       <c r="C239" s="50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D239" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E239" s="55" t="inlineStr">
-        <is>
-          <t>楚王</t>
-        </is>
-      </c>
-      <c r="F239" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E239" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F239" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G239" s="55" t="inlineStr"/>
@@ -19517,7 +19515,7 @@
       <c r="I239" s="55" t="inlineStr"/>
       <c r="J239" s="56" t="inlineStr">
         <is>
-          <t>此事牵扯甚广，先生就不怕引火烧身吗？</t>
+          <t>这事儿要是您不管，就没人能管了…瘟病若起，湖广将民不聊生啊。</t>
         </is>
       </c>
       <c r="K239" s="55" t="inlineStr"/>
@@ -19534,29 +19532,29 @@
         </is>
       </c>
       <c r="C240" s="50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D240" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E240" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F240" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E240" s="55" t="inlineStr">
+        <is>
+          <t>楚王</t>
+        </is>
+      </c>
+      <c r="F240" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G240" s="55" t="inlineStr"/>
       <c r="H240" s="55" t="inlineStr"/>
       <c r="I240" s="55" t="inlineStr"/>
-      <c r="J240" s="55" t="inlineStr">
-        <is>
-          <t>草民自幼读四书五经，诸子百家，文章未成，功名未就，所学所求只有为生民立命，若以我一命换千万民生，吾往矣。</t>
+      <c r="J240" s="56" t="inlineStr">
+        <is>
+          <t>此事牵扯甚广，先生就不怕引火烧身吗？</t>
         </is>
       </c>
       <c r="K240" s="55" t="inlineStr"/>
@@ -19573,29 +19571,29 @@
         </is>
       </c>
       <c r="C241" s="50" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D241" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E241" s="55" t="inlineStr">
-        <is>
-          <t>楚王</t>
-        </is>
-      </c>
-      <c r="F241" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E241" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F241" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G241" s="55" t="inlineStr"/>
       <c r="H241" s="55" t="inlineStr"/>
       <c r="I241" s="55" t="inlineStr"/>
-      <c r="J241" s="56" t="inlineStr">
-        <is>
-          <t>先生所言让本王惭愧啊…待本王修一道密疏，向圣上禀明此事。先生也切莫再向他人提及。</t>
+      <c r="J241" s="55" t="inlineStr">
+        <is>
+          <t>草民自幼读四书五经，诸子百家，文章未成，功名未就，所学所求只有为生民立命，若以我一命换千万民生，吾往矣。</t>
         </is>
       </c>
       <c r="K241" s="55" t="inlineStr"/>
@@ -19603,45 +19601,41 @@
     <row r="242">
       <c r="A242" s="50" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B242" s="50" t="inlineStr">
         <is>
-          <t>沈修文来访</t>
+          <t>雷万钧归来</t>
         </is>
       </c>
       <c r="C242" s="50" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D242" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E242" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F242" s="52" t="inlineStr">
+      <c r="E242" s="55" t="inlineStr">
+        <is>
+          <t>楚王</t>
+        </is>
+      </c>
+      <c r="F242" s="51" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="G242" s="51" t="inlineStr"/>
-      <c r="H242" s="52" t="inlineStr"/>
-      <c r="I242" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J242" s="53" t="inlineStr">
-        <is>
-          <t>是沈先生啊，病好点了吗？</t>
-        </is>
-      </c>
-      <c r="K242" s="50" t="inlineStr"/>
+      <c r="G242" s="55" t="inlineStr"/>
+      <c r="H242" s="55" t="inlineStr"/>
+      <c r="I242" s="55" t="inlineStr"/>
+      <c r="J242" s="56" t="inlineStr">
+        <is>
+          <t>先生所言让本王惭愧啊…待本王修一道密疏，向圣上禀明此事。先生也切莫再向他人提及。</t>
+        </is>
+      </c>
+      <c r="K242" s="55" t="inlineStr"/>
     </row>
     <row r="243" hidden="1">
       <c r="A243" s="50" t="inlineStr">
@@ -19655,7 +19649,7 @@
         </is>
       </c>
       <c r="C243" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243" s="50" t="inlineStr">
         <is>
@@ -19664,20 +19658,24 @@
       </c>
       <c r="E243" s="53" t="inlineStr">
         <is>
-          <t>沈修文</t>
-        </is>
-      </c>
-      <c r="F243" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F243" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G243" s="51" t="inlineStr"/>
       <c r="H243" s="52" t="inlineStr"/>
-      <c r="I243" s="51" t="inlineStr"/>
+      <c r="I243" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J243" s="53" t="inlineStr">
         <is>
-          <t>小生时日不多了。</t>
+          <t>是沈先生啊，病好点了吗？</t>
         </is>
       </c>
       <c r="K243" s="50" t="inlineStr"/>
@@ -19694,7 +19692,7 @@
         </is>
       </c>
       <c r="C244" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D244" s="50" t="inlineStr">
         <is>
@@ -19703,12 +19701,12 @@
       </c>
       <c r="E244" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F244" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>沈修文</t>
+        </is>
+      </c>
+      <c r="F244" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G244" s="51" t="inlineStr"/>
@@ -19716,7 +19714,7 @@
       <c r="I244" s="51" t="inlineStr"/>
       <c r="J244" s="53" t="inlineStr">
         <is>
-          <t>啊？您的病没那么严重，只要按时吃药好好休息肯定会好起来的。</t>
+          <t>小生时日不多了。</t>
         </is>
       </c>
       <c r="K244" s="50" t="inlineStr"/>
@@ -19733,7 +19731,7 @@
         </is>
       </c>
       <c r="C245" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D245" s="50" t="inlineStr">
         <is>
@@ -19742,20 +19740,20 @@
       </c>
       <c r="E245" s="53" t="inlineStr">
         <is>
-          <t>沈修文</t>
-        </is>
-      </c>
-      <c r="F245" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F245" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G245" s="51" t="inlineStr"/>
-      <c r="H245" s="51" t="inlineStr"/>
+      <c r="H245" s="52" t="inlineStr"/>
       <c r="I245" s="51" t="inlineStr"/>
-      <c r="J245" s="50" t="inlineStr">
-        <is>
-          <t>治得了病，治不了命。今天来是有样东西要交给李大夫。</t>
+      <c r="J245" s="53" t="inlineStr">
+        <is>
+          <t>啊？您的病没那么严重，只要按时吃药好好休息肯定会好起来的。</t>
         </is>
       </c>
       <c r="K245" s="50" t="inlineStr"/>
@@ -19772,7 +19770,7 @@
         </is>
       </c>
       <c r="C246" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D246" s="50" t="inlineStr">
         <is>
@@ -19781,20 +19779,20 @@
       </c>
       <c r="E246" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F246" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>沈修文</t>
+        </is>
+      </c>
+      <c r="F246" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G246" s="51" t="inlineStr"/>
       <c r="H246" s="51" t="inlineStr"/>
       <c r="I246" s="51" t="inlineStr"/>
-      <c r="J246" s="56" t="inlineStr">
-        <is>
-          <t>这是？</t>
+      <c r="J246" s="50" t="inlineStr">
+        <is>
+          <t>治得了病，治不了命。今天来是有样东西要交给李大夫。</t>
         </is>
       </c>
       <c r="K246" s="50" t="inlineStr"/>
@@ -19811,7 +19809,7 @@
         </is>
       </c>
       <c r="C247" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D247" s="50" t="inlineStr">
         <is>
@@ -19820,20 +19818,20 @@
       </c>
       <c r="E247" s="53" t="inlineStr">
         <is>
-          <t>沈修文</t>
-        </is>
-      </c>
-      <c r="F247" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G247" s="55" t="inlineStr"/>
-      <c r="H247" s="55" t="inlineStr"/>
-      <c r="I247" s="55" t="inlineStr"/>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F247" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G247" s="51" t="inlineStr"/>
+      <c r="H247" s="51" t="inlineStr"/>
+      <c r="I247" s="51" t="inlineStr"/>
       <c r="J247" s="56" t="inlineStr">
         <is>
-          <t>这是吴世良让我写的账册抄本，交给您应该能派上用场。</t>
+          <t>这是？</t>
         </is>
       </c>
       <c r="K247" s="50" t="inlineStr"/>
@@ -19850,7 +19848,7 @@
         </is>
       </c>
       <c r="C248" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D248" s="50" t="inlineStr">
         <is>
@@ -19859,12 +19857,12 @@
       </c>
       <c r="E248" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F248" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>沈修文</t>
+        </is>
+      </c>
+      <c r="F248" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G248" s="55" t="inlineStr"/>
@@ -19872,7 +19870,7 @@
       <c r="I248" s="55" t="inlineStr"/>
       <c r="J248" s="56" t="inlineStr">
         <is>
-          <t>…....</t>
+          <t>这是吴世良让我写的账册抄本，交给您应该能派上用场。</t>
         </is>
       </c>
       <c r="K248" s="50" t="inlineStr"/>
@@ -19889,7 +19887,7 @@
         </is>
       </c>
       <c r="C249" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D249" s="50" t="inlineStr">
         <is>
@@ -19898,12 +19896,12 @@
       </c>
       <c r="E249" s="53" t="inlineStr">
         <is>
-          <t>沈修文</t>
-        </is>
-      </c>
-      <c r="F249" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F249" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G249" s="55" t="inlineStr"/>
@@ -19911,7 +19909,7 @@
       <c r="I249" s="55" t="inlineStr"/>
       <c r="J249" s="56" t="inlineStr">
         <is>
-          <t>说实话我很羡慕李大夫，所学的本事能有处施展，唉…小生就此别过。</t>
+          <t>…....</t>
         </is>
       </c>
       <c r="K249" s="50" t="inlineStr"/>
@@ -19928,7 +19926,7 @@
         </is>
       </c>
       <c r="C250" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D250" s="50" t="inlineStr">
         <is>
@@ -19937,12 +19935,12 @@
       </c>
       <c r="E250" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F250" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>沈修文</t>
+        </is>
+      </c>
+      <c r="F250" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G250" s="55" t="inlineStr"/>
@@ -19950,7 +19948,7 @@
       <c r="I250" s="55" t="inlineStr"/>
       <c r="J250" s="56" t="inlineStr">
         <is>
-          <t>沈先生…....</t>
+          <t>说实话我很羡慕李大夫，所学的本事能有处施展，唉…小生就此别过。</t>
         </is>
       </c>
       <c r="K250" s="50" t="inlineStr"/>
@@ -19958,46 +19956,38 @@
     <row r="251">
       <c r="A251" s="50" t="inlineStr">
         <is>
-          <t>017_01</t>
+          <t>016</t>
         </is>
       </c>
       <c r="B251" s="50" t="inlineStr">
         <is>
-          <t>杨善泉肾气不固</t>
+          <t>沈修文来访</t>
         </is>
       </c>
       <c r="C251" s="50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D251" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E251" s="50" t="inlineStr">
-        <is>
-          <t>杨善泉</t>
-        </is>
-      </c>
-      <c r="F251" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G251" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H251" s="52" t="inlineStr"/>
-      <c r="I251" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J251" s="50" t="inlineStr">
-        <is>
-          <t>李大夫，我这两天腰酸腿软，夜尿还多，给我开点药吧。</t>
+      <c r="E251" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F251" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G251" s="55" t="inlineStr"/>
+      <c r="H251" s="55" t="inlineStr"/>
+      <c r="I251" s="55" t="inlineStr"/>
+      <c r="J251" s="56" t="inlineStr">
+        <is>
+          <t>沈先生…....</t>
         </is>
       </c>
       <c r="K251" s="50" t="inlineStr"/>
@@ -20014,7 +20004,7 @@
         </is>
       </c>
       <c r="C252" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D252" s="50" t="inlineStr">
         <is>
@@ -20023,20 +20013,28 @@
       </c>
       <c r="E252" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F252" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G252" s="51" t="inlineStr"/>
+          <t>杨善泉</t>
+        </is>
+      </c>
+      <c r="F252" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G252" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H252" s="52" t="inlineStr"/>
-      <c r="I252" s="51" t="inlineStr"/>
-      <c r="J252" s="67" t="inlineStr">
-        <is>
-          <t>杨大使请坐。</t>
+      <c r="I252" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J252" s="50" t="inlineStr">
+        <is>
+          <t>李大夫，我这两天腰酸腿软，夜尿还多，给我开点药吧。</t>
         </is>
       </c>
       <c r="K252" s="50" t="inlineStr"/>
@@ -20044,16 +20042,16 @@
     <row r="253">
       <c r="A253" s="50" t="inlineStr">
         <is>
-          <t>017_02</t>
+          <t>017_01</t>
         </is>
       </c>
       <c r="B253" s="50" t="inlineStr">
         <is>
-          <t>017治疗成功</t>
+          <t>杨善泉肾气不固</t>
         </is>
       </c>
       <c r="C253" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253" s="50" t="inlineStr">
         <is>
@@ -20072,14 +20070,10 @@
       </c>
       <c r="G253" s="51" t="inlineStr"/>
       <c r="H253" s="52" t="inlineStr"/>
-      <c r="I253" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I253" s="51" t="inlineStr"/>
       <c r="J253" s="67" t="inlineStr">
         <is>
-          <t>杨大使所患的是肾气不固之症，要注意休养，最近是遇到什么事受了惊吗？</t>
+          <t>杨大使请坐。</t>
         </is>
       </c>
       <c r="K253" s="50" t="inlineStr"/>
@@ -20096,7 +20090,7 @@
         </is>
       </c>
       <c r="C254" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D254" s="50" t="inlineStr">
         <is>
@@ -20105,24 +20099,24 @@
       </c>
       <c r="E254" s="50" t="inlineStr">
         <is>
-          <t>杨善泉</t>
-        </is>
-      </c>
-      <c r="F254" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G254" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F254" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G254" s="51" t="inlineStr"/>
       <c r="H254" s="52" t="inlineStr"/>
-      <c r="I254" s="51" t="inlineStr"/>
-      <c r="J254" s="50" t="inlineStr">
-        <is>
-          <t>您听说沈师爷的事了吗？</t>
+      <c r="I254" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J254" s="67" t="inlineStr">
+        <is>
+          <t>杨大使所患的是肾气不固之症，要注意休养，最近是遇到什么事受了惊吗？</t>
         </is>
       </c>
       <c r="K254" s="50" t="inlineStr"/>
@@ -20139,7 +20133,7 @@
         </is>
       </c>
       <c r="C255" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D255" s="50" t="inlineStr">
         <is>
@@ -20148,20 +20142,24 @@
       </c>
       <c r="E255" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F255" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G255" s="51" t="inlineStr"/>
+          <t>杨善泉</t>
+        </is>
+      </c>
+      <c r="F255" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G255" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H255" s="52" t="inlineStr"/>
       <c r="I255" s="51" t="inlineStr"/>
       <c r="J255" s="50" t="inlineStr">
         <is>
-          <t>沈师爷怎么了？</t>
+          <t>您听说沈师爷的事了吗？</t>
         </is>
       </c>
       <c r="K255" s="50" t="inlineStr"/>
@@ -20178,7 +20176,7 @@
         </is>
       </c>
       <c r="C256" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D256" s="50" t="inlineStr">
         <is>
@@ -20187,24 +20185,20 @@
       </c>
       <c r="E256" s="50" t="inlineStr">
         <is>
-          <t>杨善泉</t>
-        </is>
-      </c>
-      <c r="F256" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G256" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H256" s="51" t="inlineStr"/>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F256" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G256" s="51" t="inlineStr"/>
+      <c r="H256" s="52" t="inlineStr"/>
       <c r="I256" s="51" t="inlineStr"/>
       <c r="J256" s="50" t="inlineStr">
         <is>
-          <t>昨天沈师爷在自己屋里死了…</t>
+          <t>沈师爷怎么了？</t>
         </is>
       </c>
       <c r="K256" s="50" t="inlineStr"/>
@@ -20221,7 +20215,7 @@
         </is>
       </c>
       <c r="C257" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D257" s="50" t="inlineStr">
         <is>
@@ -20230,20 +20224,24 @@
       </c>
       <c r="E257" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F257" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G257" s="51" t="inlineStr"/>
+          <t>杨善泉</t>
+        </is>
+      </c>
+      <c r="F257" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G257" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H257" s="51" t="inlineStr"/>
       <c r="I257" s="51" t="inlineStr"/>
       <c r="J257" s="50" t="inlineStr">
         <is>
-          <t>！！！</t>
+          <t>昨天沈师爷在自己屋里死了…</t>
         </is>
       </c>
       <c r="K257" s="50" t="inlineStr"/>
@@ -20260,7 +20258,7 @@
         </is>
       </c>
       <c r="C258" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D258" s="50" t="inlineStr">
         <is>
@@ -20269,27 +20267,23 @@
       </c>
       <c r="E258" s="50" t="inlineStr">
         <is>
-          <t>杨善泉</t>
-        </is>
-      </c>
-      <c r="F258" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G258" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H258" s="55" t="inlineStr"/>
-      <c r="I258" s="55" t="inlineStr"/>
-      <c r="J258" s="55" t="inlineStr">
-        <is>
-          <t>他们开始灭口了...下一个就该轮到我了...</t>
-        </is>
-      </c>
-      <c r="K258" s="55" t="inlineStr"/>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F258" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G258" s="51" t="inlineStr"/>
+      <c r="H258" s="51" t="inlineStr"/>
+      <c r="I258" s="51" t="inlineStr"/>
+      <c r="J258" s="50" t="inlineStr">
+        <is>
+          <t>！！！</t>
+        </is>
+      </c>
+      <c r="K258" s="50" t="inlineStr"/>
     </row>
     <row r="259" hidden="1">
       <c r="A259" s="50" t="inlineStr">
@@ -20303,7 +20297,7 @@
         </is>
       </c>
       <c r="C259" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D259" s="50" t="inlineStr">
         <is>
@@ -20327,9 +20321,9 @@
       </c>
       <c r="H259" s="55" t="inlineStr"/>
       <c r="I259" s="55" t="inlineStr"/>
-      <c r="J259" s="56" t="inlineStr">
-        <is>
-          <t>这一批药材入库验收、各地调拨都是我经的手，多少药、什么成色、送到哪里，账上都有我的画押。他们想把这笔账做干净，就不会留我这个活口。</t>
+      <c r="J259" s="55" t="inlineStr">
+        <is>
+          <t>他们开始灭口了...下一个就该轮到我了...</t>
         </is>
       </c>
       <c r="K259" s="55" t="inlineStr"/>
@@ -20346,7 +20340,7 @@
         </is>
       </c>
       <c r="C260" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D260" s="50" t="inlineStr">
         <is>
@@ -20355,20 +20349,24 @@
       </c>
       <c r="E260" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F260" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G260" s="55" t="inlineStr"/>
+          <t>杨善泉</t>
+        </is>
+      </c>
+      <c r="F260" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G260" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H260" s="55" t="inlineStr"/>
       <c r="I260" s="55" t="inlineStr"/>
-      <c r="J260" s="55" t="inlineStr">
-        <is>
-          <t>......</t>
+      <c r="J260" s="56" t="inlineStr">
+        <is>
+          <t>这一批药材入库验收、各地调拨都是我经的手，多少药、什么成色、送到哪里，账上都有我的画押。他们想把这笔账做干净，就不会留我这个活口。</t>
         </is>
       </c>
       <c r="K260" s="55" t="inlineStr"/>
@@ -20376,23 +20374,23 @@
     <row r="261">
       <c r="A261" s="50" t="inlineStr">
         <is>
-          <t>017_03</t>
+          <t>017_02</t>
         </is>
       </c>
       <c r="B261" s="50" t="inlineStr">
         <is>
-          <t>017治疗失败</t>
+          <t>017治疗成功</t>
         </is>
       </c>
       <c r="C261" s="50" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D261" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E261" s="59" t="inlineStr">
+      <c r="E261" s="50" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
@@ -20402,68 +20400,60 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G261" s="51" t="inlineStr"/>
-      <c r="H261" s="52" t="inlineStr"/>
-      <c r="I261" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J261" s="50" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
-        </is>
-      </c>
-      <c r="K261" s="50" t="inlineStr"/>
+      <c r="G261" s="55" t="inlineStr"/>
+      <c r="H261" s="55" t="inlineStr"/>
+      <c r="I261" s="55" t="inlineStr"/>
+      <c r="J261" s="55" t="inlineStr">
+        <is>
+          <t>......</t>
+        </is>
+      </c>
+      <c r="K261" s="55" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="50" t="inlineStr">
-        <is>
-          <t>018</t>
-        </is>
-      </c>
-      <c r="B262" s="50" t="inlineStr">
-        <is>
-          <t>库房失火</t>
-        </is>
-      </c>
-      <c r="C262" s="50" t="n">
-        <v>1</v>
+      <c r="A262" s="55" t="inlineStr">
+        <is>
+          <t>017_02</t>
+        </is>
+      </c>
+      <c r="B262" s="55" t="inlineStr">
+        <is>
+          <t>017治疗成功</t>
+        </is>
+      </c>
+      <c r="C262" s="55" t="n">
+        <v>9</v>
       </c>
       <c r="D262" s="50" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="E262" s="50" t="inlineStr"/>
-      <c r="F262" s="51" t="inlineStr"/>
-      <c r="G262" s="51" t="inlineStr"/>
-      <c r="H262" s="52" t="inlineStr"/>
-      <c r="I262" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J262" s="50" t="inlineStr">
-        <is>
-          <t>"库房失火啦！快来人救火啊！"</t>
-        </is>
-      </c>
-      <c r="K262" s="50" t="inlineStr"/>
+      <c r="E262" s="53" t="inlineStr"/>
+      <c r="F262" s="52" t="inlineStr"/>
+      <c r="G262" s="55" t="inlineStr"/>
+      <c r="H262" s="55" t="inlineStr"/>
+      <c r="I262" s="51" t="inlineStr"/>
+      <c r="J262" s="56" t="inlineStr">
+        <is>
+          <t>收入一两白银</t>
+        </is>
+      </c>
+      <c r="K262" s="55" t="inlineStr"/>
     </row>
     <row r="263" hidden="1">
       <c r="A263" s="50" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>017_03</t>
         </is>
       </c>
       <c r="B263" s="50" t="inlineStr">
         <is>
-          <t>库房失火</t>
+          <t>017治疗失败</t>
         </is>
       </c>
       <c r="C263" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D263" s="50" t="inlineStr">
         <is>
@@ -20472,20 +20462,24 @@
       </c>
       <c r="E263" s="59" t="inlineStr">
         <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F263" s="60" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F263" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G263" s="51" t="inlineStr"/>
       <c r="H263" s="52" t="inlineStr"/>
-      <c r="I263" s="51" t="inlineStr"/>
-      <c r="J263" s="59" t="inlineStr">
-        <is>
-          <t>少掌柜的，惠民药局的药料库起火啦！</t>
+      <c r="I263" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J263" s="50" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K263" s="50" t="inlineStr"/>
@@ -20502,29 +20496,25 @@
         </is>
       </c>
       <c r="C264" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D264" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E264" s="59" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F264" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E264" s="50" t="inlineStr"/>
+      <c r="F264" s="51" t="inlineStr"/>
       <c r="G264" s="51" t="inlineStr"/>
       <c r="H264" s="52" t="inlineStr"/>
-      <c r="I264" s="51" t="inlineStr"/>
-      <c r="J264" s="59" t="inlineStr">
-        <is>
-          <t>走，去帮忙。</t>
+      <c r="I264" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J264" s="50" t="inlineStr">
+        <is>
+          <t>"库房失火啦！快来人救火啊！"</t>
         </is>
       </c>
       <c r="K264" s="50" t="inlineStr"/>
@@ -20541,7 +20531,7 @@
         </is>
       </c>
       <c r="C265" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D265" s="50" t="inlineStr">
         <is>
@@ -20550,24 +20540,20 @@
       </c>
       <c r="E265" s="59" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F265" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F265" s="60" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G265" s="51" t="inlineStr"/>
-      <c r="H265" s="51" t="inlineStr"/>
-      <c r="I265" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/018/018.png</t>
-        </is>
-      </c>
+      <c r="H265" s="52" t="inlineStr"/>
+      <c r="I265" s="51" t="inlineStr"/>
       <c r="J265" s="59" t="inlineStr">
         <is>
-          <t>这火烧得蹊跷。</t>
+          <t>少掌柜的，惠民药局的药料库起火啦！</t>
         </is>
       </c>
       <c r="K265" s="50" t="inlineStr"/>
@@ -20584,7 +20570,7 @@
         </is>
       </c>
       <c r="C266" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D266" s="50" t="inlineStr">
         <is>
@@ -20593,20 +20579,20 @@
       </c>
       <c r="E266" s="59" t="inlineStr">
         <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F266" s="60" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F266" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G266" s="51" t="inlineStr"/>
-      <c r="H266" s="51" t="inlineStr"/>
+      <c r="H266" s="52" t="inlineStr"/>
       <c r="I266" s="51" t="inlineStr"/>
       <c r="J266" s="59" t="inlineStr">
         <is>
-          <t>那边抬出来一个人。</t>
+          <t>走，去帮忙。</t>
         </is>
       </c>
       <c r="K266" s="50" t="inlineStr"/>
@@ -20623,7 +20609,7 @@
         </is>
       </c>
       <c r="C267" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D267" s="50" t="inlineStr">
         <is>
@@ -20640,55 +20626,55 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G267" s="55" t="inlineStr"/>
-      <c r="H267" s="55" t="inlineStr"/>
-      <c r="I267" s="55" t="inlineStr"/>
-      <c r="J267" s="61" t="inlineStr">
-        <is>
-          <t>……是杨善泉。</t>
-        </is>
-      </c>
-      <c r="K267" s="55" t="inlineStr"/>
+      <c r="G267" s="51" t="inlineStr"/>
+      <c r="H267" s="51" t="inlineStr"/>
+      <c r="I267" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/018/018.png</t>
+        </is>
+      </c>
+      <c r="J267" s="59" t="inlineStr">
+        <is>
+          <t>这火烧得蹊跷。</t>
+        </is>
+      </c>
+      <c r="K267" s="50" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="50" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>018</t>
         </is>
       </c>
       <c r="B268" s="50" t="inlineStr">
         <is>
-          <t>赵顺来访</t>
+          <t>库房失火</t>
         </is>
       </c>
       <c r="C268" s="50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D268" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E268" s="53" t="inlineStr">
-        <is>
-          <t>赵顺</t>
-        </is>
-      </c>
-      <c r="F268" s="52" t="inlineStr">
+      <c r="E268" s="59" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F268" s="60" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
       <c r="G268" s="51" t="inlineStr"/>
-      <c r="H268" s="52" t="inlineStr"/>
-      <c r="I268" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J268" s="53" t="inlineStr">
-        <is>
-          <t>掌柜的生意兴隆啊(四处打量...)，那扇门是通后院的吧？</t>
+      <c r="H268" s="51" t="inlineStr"/>
+      <c r="I268" s="51" t="inlineStr"/>
+      <c r="J268" s="59" t="inlineStr">
+        <is>
+          <t>那边抬出来一个人。</t>
         </is>
       </c>
       <c r="K268" s="50" t="inlineStr"/>
@@ -20696,23 +20682,23 @@
     <row r="269" hidden="1">
       <c r="A269" s="50" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>018</t>
         </is>
       </c>
       <c r="B269" s="50" t="inlineStr">
         <is>
-          <t>赵顺来访</t>
+          <t>库房失火</t>
         </is>
       </c>
       <c r="C269" s="50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D269" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E269" s="53" t="inlineStr">
+      <c r="E269" s="59" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
@@ -20722,15 +20708,15 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G269" s="51" t="inlineStr"/>
-      <c r="H269" s="52" t="inlineStr"/>
-      <c r="I269" s="51" t="inlineStr"/>
-      <c r="J269" s="53" t="inlineStr">
-        <is>
-          <t>敢问来小馆有何贵干？</t>
-        </is>
-      </c>
-      <c r="K269" s="50" t="inlineStr"/>
+      <c r="G269" s="55" t="inlineStr"/>
+      <c r="H269" s="55" t="inlineStr"/>
+      <c r="I269" s="55" t="inlineStr"/>
+      <c r="J269" s="61" t="inlineStr">
+        <is>
+          <t>……是杨善泉。</t>
+        </is>
+      </c>
+      <c r="K269" s="55" t="inlineStr"/>
     </row>
     <row r="270" hidden="1">
       <c r="A270" s="50" t="inlineStr">
@@ -20744,7 +20730,7 @@
         </is>
       </c>
       <c r="C270" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D270" s="50" t="inlineStr">
         <is>
@@ -20763,10 +20749,14 @@
       </c>
       <c r="G270" s="51" t="inlineStr"/>
       <c r="H270" s="52" t="inlineStr"/>
-      <c r="I270" s="51" t="inlineStr"/>
+      <c r="I270" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J270" s="53" t="inlineStr">
         <is>
-          <t>啊，哈哈，没事没事，就来看看，听说咱蕲州有一位李神医，来瞻仰瞻仰。</t>
+          <t>掌柜的生意兴隆啊(四处打量...)，那扇门是通后院的吧？</t>
         </is>
       </c>
       <c r="K270" s="50" t="inlineStr"/>
@@ -20783,7 +20773,7 @@
         </is>
       </c>
       <c r="C271" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D271" s="50" t="inlineStr">
         <is>
@@ -20801,11 +20791,11 @@
         </is>
       </c>
       <c r="G271" s="51" t="inlineStr"/>
-      <c r="H271" s="51" t="inlineStr"/>
+      <c r="H271" s="52" t="inlineStr"/>
       <c r="I271" s="51" t="inlineStr"/>
       <c r="J271" s="53" t="inlineStr">
         <is>
-          <t>小馆还要接待病患，无事便请回吧。</t>
+          <t>敢问来小馆有何贵干？</t>
         </is>
       </c>
       <c r="K271" s="50" t="inlineStr"/>
@@ -20822,7 +20812,7 @@
         </is>
       </c>
       <c r="C272" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D272" s="50" t="inlineStr">
         <is>
@@ -20840,11 +20830,11 @@
         </is>
       </c>
       <c r="G272" s="51" t="inlineStr"/>
-      <c r="H272" s="51" t="inlineStr"/>
+      <c r="H272" s="52" t="inlineStr"/>
       <c r="I272" s="51" t="inlineStr"/>
       <c r="J272" s="53" t="inlineStr">
         <is>
-          <t>切，那咱们就后会有期了。</t>
+          <t>啊，哈哈，没事没事，就来看看，听说咱蕲州有一位李神医，来瞻仰瞻仰。</t>
         </is>
       </c>
       <c r="K272" s="50" t="inlineStr"/>
@@ -20852,77 +20842,77 @@
     <row r="273">
       <c r="A273" s="50" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B273" s="50" t="inlineStr">
         <is>
-          <t>夜晚遇刺</t>
+          <t>赵顺来访</t>
         </is>
       </c>
       <c r="C273" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D273" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E273" s="59" t="inlineStr"/>
-      <c r="F273" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E273" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F273" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G273" s="51" t="inlineStr"/>
-      <c r="H273" s="52" t="inlineStr"/>
-      <c r="I273" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J273" s="59" t="inlineStr">
-        <is>
-          <t>咯噔</t>
-        </is>
-      </c>
-      <c r="K273" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Music/Story/020/圍剿夜襲.mp3</t>
-        </is>
-      </c>
+      <c r="H273" s="51" t="inlineStr"/>
+      <c r="I273" s="51" t="inlineStr"/>
+      <c r="J273" s="53" t="inlineStr">
+        <is>
+          <t>小馆还要接待病患，无事便请回吧。</t>
+        </is>
+      </c>
+      <c r="K273" s="50" t="inlineStr"/>
     </row>
     <row r="274" hidden="1">
       <c r="A274" s="50" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B274" s="50" t="inlineStr">
         <is>
-          <t>夜晚遇刺</t>
+          <t>赵顺来访</t>
         </is>
       </c>
       <c r="C274" s="50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D274" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E274" s="59" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F274" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
+      <c r="E274" s="53" t="inlineStr">
+        <is>
+          <t>赵顺</t>
+        </is>
+      </c>
+      <c r="F274" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G274" s="51" t="inlineStr"/>
-      <c r="H274" s="52" t="inlineStr"/>
+      <c r="H274" s="51" t="inlineStr"/>
       <c r="I274" s="51" t="inlineStr"/>
-      <c r="J274" s="59" t="inlineStr">
-        <is>
-          <t>谁！</t>
+      <c r="J274" s="53" t="inlineStr">
+        <is>
+          <t>切，那咱们就后会有期了。</t>
         </is>
       </c>
       <c r="K274" s="50" t="inlineStr"/>
@@ -20939,36 +20929,32 @@
         </is>
       </c>
       <c r="C275" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D275" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E275" s="59" t="inlineStr">
-        <is>
-          <t>黑衣人</t>
-        </is>
-      </c>
-      <c r="F275" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E275" s="59" t="inlineStr"/>
+      <c r="F275" s="51" t="inlineStr"/>
       <c r="G275" s="51" t="inlineStr"/>
       <c r="H275" s="52" t="inlineStr"/>
       <c r="I275" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/020/020_01.png</t>
+          <t>current_scene</t>
         </is>
       </c>
       <c r="J275" s="59" t="inlineStr">
         <is>
-          <t>李大夫，我来送你上路啦。</t>
-        </is>
-      </c>
-      <c r="K275" s="50" t="inlineStr"/>
+          <t>咯噔</t>
+        </is>
+      </c>
+      <c r="K275" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/020/圍剿夜襲.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="50" t="inlineStr">
@@ -20982,7 +20968,7 @@
         </is>
       </c>
       <c r="C276" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D276" s="50" t="inlineStr">
         <is>
@@ -21000,15 +20986,11 @@
         </is>
       </c>
       <c r="G276" s="51" t="inlineStr"/>
-      <c r="H276" s="51" t="inlineStr"/>
-      <c r="I276" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/020/020_02.png</t>
-        </is>
-      </c>
+      <c r="H276" s="52" t="inlineStr"/>
+      <c r="I276" s="51" t="inlineStr"/>
       <c r="J276" s="59" t="inlineStr">
         <is>
-          <t>！！！</t>
+          <t>谁！</t>
         </is>
       </c>
       <c r="K276" s="50" t="inlineStr"/>
@@ -21025,25 +21007,33 @@
         </is>
       </c>
       <c r="C277" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D277" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E277" s="50" t="inlineStr"/>
-      <c r="F277" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E277" s="59" t="inlineStr">
+        <is>
+          <t>黑衣人</t>
+        </is>
+      </c>
+      <c r="F277" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="G277" s="51" t="inlineStr"/>
-      <c r="H277" s="51" t="inlineStr"/>
+      <c r="H277" s="52" t="inlineStr"/>
       <c r="I277" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/020/020_03.png</t>
+          <t>res://Assets/Background/020/020_01.png</t>
         </is>
       </c>
       <c r="J277" s="59" t="inlineStr">
         <is>
-          <t>砰！</t>
+          <t>李大夫，我来送你上路啦。</t>
         </is>
       </c>
       <c r="K277" s="50" t="inlineStr"/>
@@ -21060,7 +21050,7 @@
         </is>
       </c>
       <c r="C278" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D278" s="50" t="inlineStr">
         <is>
@@ -21069,23 +21059,27 @@
       </c>
       <c r="E278" s="59" t="inlineStr">
         <is>
-          <t>黑衣人</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F278" s="51" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G278" s="55" t="inlineStr"/>
-      <c r="H278" s="55" t="inlineStr"/>
-      <c r="I278" s="55" t="inlineStr"/>
-      <c r="J278" s="61" t="inlineStr">
-        <is>
-          <t>哎哟！</t>
-        </is>
-      </c>
-      <c r="K278" s="55" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G278" s="51" t="inlineStr"/>
+      <c r="H278" s="51" t="inlineStr"/>
+      <c r="I278" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/020/020_02.png</t>
+        </is>
+      </c>
+      <c r="J278" s="59" t="inlineStr">
+        <is>
+          <t>！！！</t>
+        </is>
+      </c>
+      <c r="K278" s="50" t="inlineStr"/>
     </row>
     <row r="279" hidden="1">
       <c r="A279" s="50" t="inlineStr">
@@ -21099,36 +21093,28 @@
         </is>
       </c>
       <c r="C279" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D279" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E279" s="59" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F279" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E279" s="50" t="inlineStr"/>
+      <c r="F279" s="51" t="inlineStr"/>
       <c r="G279" s="51" t="inlineStr"/>
-      <c r="H279" s="56" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I279" s="51" t="inlineStr"/>
+      <c r="H279" s="51" t="inlineStr"/>
+      <c r="I279" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/020/020_03.png</t>
+        </is>
+      </c>
       <c r="J279" s="59" t="inlineStr">
         <is>
-          <t>！！！</t>
-        </is>
-      </c>
-      <c r="K279" s="55" t="inlineStr"/>
+          <t>砰！</t>
+        </is>
+      </c>
+      <c r="K279" s="50" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="50" t="inlineStr">
@@ -21142,37 +21128,29 @@
         </is>
       </c>
       <c r="C280" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D280" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E280" s="61" t="inlineStr">
-        <is>
-          <t>雷万钧</t>
-        </is>
-      </c>
-      <c r="F280" s="60" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E280" s="59" t="inlineStr">
+        <is>
+          <t>黑衣人</t>
+        </is>
+      </c>
+      <c r="F280" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G280" s="55" t="inlineStr"/>
-      <c r="H280" s="56" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I280" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="H280" s="55" t="inlineStr"/>
+      <c r="I280" s="55" t="inlineStr"/>
       <c r="J280" s="61" t="inlineStr">
         <is>
-          <t>贤弟，你没事吧？王爷听说沈修文和杨善泉都被灭口了，猜想下一个就是你，便派我们在暗中保护。</t>
+          <t>哎哟！</t>
         </is>
       </c>
       <c r="K280" s="55" t="inlineStr"/>
@@ -21189,29 +21167,33 @@
         </is>
       </c>
       <c r="C281" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D281" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E281" s="61" t="inlineStr">
-        <is>
-          <t>王府护卫</t>
-        </is>
-      </c>
-      <c r="F281" s="60" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G281" s="55" t="inlineStr"/>
-      <c r="H281" s="55" t="inlineStr"/>
-      <c r="I281" s="55" t="inlineStr"/>
-      <c r="J281" s="61" t="inlineStr">
-        <is>
-          <t>把他绑起来。</t>
+      <c r="E281" s="59" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F281" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G281" s="51" t="inlineStr"/>
+      <c r="H281" s="56" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I281" s="51" t="inlineStr"/>
+      <c r="J281" s="59" t="inlineStr">
+        <is>
+          <t>！！！</t>
         </is>
       </c>
       <c r="K281" s="55" t="inlineStr"/>
@@ -21228,7 +21210,7 @@
         </is>
       </c>
       <c r="C282" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D282" s="50" t="inlineStr">
         <is>
@@ -21237,28 +21219,28 @@
       </c>
       <c r="E282" s="61" t="inlineStr">
         <is>
-          <t>赵顺</t>
-        </is>
-      </c>
-      <c r="F282" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G282" s="61" t="inlineStr">
-        <is>
-          <t>hei</t>
-        </is>
-      </c>
+          <t>雷万钧</t>
+        </is>
+      </c>
+      <c r="F282" s="60" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G282" s="55" t="inlineStr"/>
       <c r="H282" s="56" t="inlineStr">
         <is>
           <t>hide</t>
         </is>
       </c>
-      <c r="I282" s="55" t="inlineStr"/>
+      <c r="I282" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J282" s="61" t="inlineStr">
         <is>
-          <t>误会啊大人，误会。</t>
+          <t>贤弟，你没事吧？王爷听说沈修文和杨善泉都被灭口了，猜想下一个就是你，便派我们在暗中保护。</t>
         </is>
       </c>
       <c r="K282" s="55" t="inlineStr"/>
@@ -21275,25 +21257,29 @@
         </is>
       </c>
       <c r="C283" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D283" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E283" s="55" t="inlineStr"/>
-      <c r="F283" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E283" s="61" t="inlineStr">
+        <is>
+          <t>王府护卫</t>
+        </is>
+      </c>
+      <c r="F283" s="60" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="G283" s="55" t="inlineStr"/>
       <c r="H283" s="55" t="inlineStr"/>
-      <c r="I283" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/020/020_04.png</t>
-        </is>
-      </c>
-      <c r="J283" s="56" t="inlineStr">
-        <is>
-          <t>一行人来到王府</t>
+      <c r="I283" s="55" t="inlineStr"/>
+      <c r="J283" s="61" t="inlineStr">
+        <is>
+          <t>把他绑起来。</t>
         </is>
       </c>
       <c r="K283" s="55" t="inlineStr"/>
@@ -21310,7 +21296,7 @@
         </is>
       </c>
       <c r="C284" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D284" s="50" t="inlineStr">
         <is>
@@ -21319,7 +21305,7 @@
       </c>
       <c r="E284" s="61" t="inlineStr">
         <is>
-          <t>王府护卫</t>
+          <t>赵顺</t>
         </is>
       </c>
       <c r="F284" s="51" t="inlineStr">
@@ -21327,12 +21313,20 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G284" s="55" t="inlineStr"/>
-      <c r="H284" s="55" t="inlineStr"/>
+      <c r="G284" s="61" t="inlineStr">
+        <is>
+          <t>hei</t>
+        </is>
+      </c>
+      <c r="H284" s="56" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I284" s="55" t="inlineStr"/>
-      <c r="J284" s="56" t="inlineStr">
-        <is>
-          <t>启禀王爷，人都带来了。</t>
+      <c r="J284" s="61" t="inlineStr">
+        <is>
+          <t>误会啊大人，误会。</t>
         </is>
       </c>
       <c r="K284" s="55" t="inlineStr"/>
@@ -21349,29 +21343,25 @@
         </is>
       </c>
       <c r="C285" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D285" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E285" s="56" t="inlineStr">
-        <is>
-          <t>楚王</t>
-        </is>
-      </c>
-      <c r="F285" s="60" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E285" s="55" t="inlineStr"/>
+      <c r="F285" s="51" t="inlineStr"/>
       <c r="G285" s="55" t="inlineStr"/>
       <c r="H285" s="55" t="inlineStr"/>
-      <c r="I285" s="55" t="inlineStr"/>
+      <c r="I285" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/020/020_04.png</t>
+        </is>
+      </c>
       <c r="J285" s="56" t="inlineStr">
         <is>
-          <t>这几位是朝廷派来查赈灾药材案的钦差。</t>
+          <t>一行人来到王府</t>
         </is>
       </c>
       <c r="K285" s="55" t="inlineStr"/>
@@ -21388,21 +21378,21 @@
         </is>
       </c>
       <c r="C286" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D286" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E286" s="56" t="inlineStr">
-        <is>
-          <t>陆丁</t>
-        </is>
-      </c>
-      <c r="F286" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+      <c r="E286" s="61" t="inlineStr">
+        <is>
+          <t>王府护卫</t>
+        </is>
+      </c>
+      <c r="F286" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G286" s="55" t="inlineStr"/>
@@ -21410,7 +21400,7 @@
       <c r="I286" s="55" t="inlineStr"/>
       <c r="J286" s="56" t="inlineStr">
         <is>
-          <t>北镇抚司陆丁，你就是李东璧？</t>
+          <t>启禀王爷，人都带来了。</t>
         </is>
       </c>
       <c r="K286" s="55" t="inlineStr"/>
@@ -21427,21 +21417,21 @@
         </is>
       </c>
       <c r="C287" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D287" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E287" s="59" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F287" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E287" s="56" t="inlineStr">
+        <is>
+          <t>楚王</t>
+        </is>
+      </c>
+      <c r="F287" s="60" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G287" s="55" t="inlineStr"/>
@@ -21449,7 +21439,7 @@
       <c r="I287" s="55" t="inlineStr"/>
       <c r="J287" s="56" t="inlineStr">
         <is>
-          <t>正是草民。</t>
+          <t>这几位是朝廷派来查赈灾药材案的钦差。</t>
         </is>
       </c>
       <c r="K287" s="55" t="inlineStr"/>
@@ -21466,21 +21456,29 @@
         </is>
       </c>
       <c r="C288" s="50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D288" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E288" s="55" t="inlineStr"/>
-      <c r="F288" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E288" s="56" t="inlineStr">
+        <is>
+          <t>陆丁</t>
+        </is>
+      </c>
+      <c r="F288" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="G288" s="55" t="inlineStr"/>
       <c r="H288" s="55" t="inlineStr"/>
       <c r="I288" s="55" t="inlineStr"/>
       <c r="J288" s="56" t="inlineStr">
         <is>
-          <t>李东璧将前前后后发生的事情一五一十地禀明钦差</t>
+          <t>北镇抚司陆丁，你就是李东璧？</t>
         </is>
       </c>
       <c r="K288" s="55" t="inlineStr"/>
@@ -21488,72 +21486,72 @@
     <row r="289">
       <c r="A289" s="50" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>020</t>
         </is>
       </c>
       <c r="B289" s="50" t="inlineStr">
         <is>
-          <t>结案</t>
+          <t>夜晚遇刺</t>
         </is>
       </c>
       <c r="C289" s="50" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D289" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E289" s="50" t="inlineStr"/>
-      <c r="F289" s="51" t="inlineStr"/>
-      <c r="G289" s="51" t="inlineStr"/>
-      <c r="H289" s="52" t="inlineStr"/>
-      <c r="I289" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/021/021.png</t>
-        </is>
-      </c>
-      <c r="J289" s="53" t="inlineStr">
-        <is>
-          <t>蕲州赈灾药材贪污案惊动朝廷，锦衣卫奉旨查办，地方涉案官员数十人，贪污银钱近万两。</t>
-        </is>
-      </c>
-      <c r="K289" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Music/Story/021/问斩.mp3</t>
-        </is>
-      </c>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E289" s="59" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F289" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G289" s="55" t="inlineStr"/>
+      <c r="H289" s="55" t="inlineStr"/>
+      <c r="I289" s="55" t="inlineStr"/>
+      <c r="J289" s="56" t="inlineStr">
+        <is>
+          <t>正是草民。</t>
+        </is>
+      </c>
+      <c r="K289" s="55" t="inlineStr"/>
     </row>
     <row r="290" hidden="1">
       <c r="A290" s="50" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>020</t>
         </is>
       </c>
       <c r="B290" s="50" t="inlineStr">
         <is>
-          <t>结案</t>
+          <t>夜晚遇刺</t>
         </is>
       </c>
       <c r="C290" s="50" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D290" s="50" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="E290" s="50" t="inlineStr"/>
+      <c r="E290" s="55" t="inlineStr"/>
       <c r="F290" s="51" t="inlineStr"/>
-      <c r="G290" s="51" t="inlineStr"/>
-      <c r="H290" s="52" t="inlineStr"/>
-      <c r="I290" s="51" t="inlineStr"/>
-      <c r="J290" s="53" t="inlineStr">
-        <is>
-          <t>主犯吴世良、赵顺等即刻斩首。湖广巡抚陈仕贤等，连坐失察，官降两级。</t>
-        </is>
-      </c>
-      <c r="K290" s="50" t="inlineStr"/>
+      <c r="G290" s="55" t="inlineStr"/>
+      <c r="H290" s="55" t="inlineStr"/>
+      <c r="I290" s="55" t="inlineStr"/>
+      <c r="J290" s="56" t="inlineStr">
+        <is>
+          <t>李东璧将前前后后发生的事情一五一十地禀明钦差</t>
+        </is>
+      </c>
+      <c r="K290" s="55" t="inlineStr"/>
     </row>
     <row r="291" hidden="1">
       <c r="A291" s="50" t="inlineStr">
@@ -21567,7 +21565,7 @@
         </is>
       </c>
       <c r="C291" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D291" s="50" t="inlineStr">
         <is>
@@ -21575,16 +21573,24 @@
         </is>
       </c>
       <c r="E291" s="50" t="inlineStr"/>
-      <c r="F291" s="52" t="inlineStr"/>
+      <c r="F291" s="51" t="inlineStr"/>
       <c r="G291" s="51" t="inlineStr"/>
       <c r="H291" s="52" t="inlineStr"/>
-      <c r="I291" s="51" t="inlineStr"/>
+      <c r="I291" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/021/021.png</t>
+        </is>
+      </c>
       <c r="J291" s="53" t="inlineStr">
         <is>
-          <t>蕲州所需赈灾药材由太医院调拨，重新发放。</t>
-        </is>
-      </c>
-      <c r="K291" s="50" t="inlineStr"/>
+          <t>蕲州赈灾药材贪污案惊动朝廷，锦衣卫奉旨查办，地方涉案官员数十人，贪污银钱近万两。</t>
+        </is>
+      </c>
+      <c r="K291" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/021/问斩.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="292" hidden="1">
       <c r="A292" s="50" t="inlineStr">
@@ -21598,29 +21604,21 @@
         </is>
       </c>
       <c r="C292" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D292" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E292" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F292" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E292" s="50" t="inlineStr"/>
+      <c r="F292" s="51" t="inlineStr"/>
       <c r="G292" s="51" t="inlineStr"/>
-      <c r="H292" s="51" t="inlineStr"/>
+      <c r="H292" s="52" t="inlineStr"/>
       <c r="I292" s="51" t="inlineStr"/>
       <c r="J292" s="53" t="inlineStr">
         <is>
-          <t>到头来这吴世良不过是个被推出来顶罪的罢了。</t>
+          <t>主犯吴世良、赵顺等即刻斩首。湖广巡抚陈仕贤等，连坐失察，官降两级。</t>
         </is>
       </c>
       <c r="K292" s="50" t="inlineStr"/>
@@ -21637,29 +21635,21 @@
         </is>
       </c>
       <c r="C293" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D293" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E293" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F293" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E293" s="50" t="inlineStr"/>
+      <c r="F293" s="52" t="inlineStr"/>
       <c r="G293" s="51" t="inlineStr"/>
-      <c r="H293" s="51" t="inlineStr"/>
+      <c r="H293" s="52" t="inlineStr"/>
       <c r="I293" s="51" t="inlineStr"/>
       <c r="J293" s="53" t="inlineStr">
         <is>
-          <t>朝政被严党把持，这些做官的你中有我，我中有你，真细究起来又是一笔糊涂账。</t>
+          <t>蕲州所需赈灾药材由太医院调拨，重新发放。</t>
         </is>
       </c>
       <c r="K293" s="50" t="inlineStr"/>
@@ -21676,29 +21666,29 @@
         </is>
       </c>
       <c r="C294" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D294" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E294" s="56" t="inlineStr">
-        <is>
-          <t>楚王</t>
+      <c r="E294" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F294" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G294" s="55" t="inlineStr"/>
-      <c r="H294" s="55" t="inlineStr"/>
-      <c r="I294" s="55" t="inlineStr"/>
-      <c r="J294" s="55" t="inlineStr">
-        <is>
-          <t>李先生。</t>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G294" s="51" t="inlineStr"/>
+      <c r="H294" s="51" t="inlineStr"/>
+      <c r="I294" s="51" t="inlineStr"/>
+      <c r="J294" s="53" t="inlineStr">
+        <is>
+          <t>到头来这吴世良不过是个被推出来顶罪的罢了。</t>
         </is>
       </c>
       <c r="K294" s="50" t="inlineStr"/>
@@ -21715,7 +21705,7 @@
         </is>
       </c>
       <c r="C295" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D295" s="50" t="inlineStr">
         <is>
@@ -21724,20 +21714,20 @@
       </c>
       <c r="E295" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F295" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G295" s="55" t="inlineStr"/>
-      <c r="H295" s="55" t="inlineStr"/>
-      <c r="I295" s="55" t="inlineStr"/>
-      <c r="J295" s="56" t="inlineStr">
-        <is>
-          <t>楚王殿下。</t>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G295" s="51" t="inlineStr"/>
+      <c r="H295" s="51" t="inlineStr"/>
+      <c r="I295" s="51" t="inlineStr"/>
+      <c r="J295" s="53" t="inlineStr">
+        <is>
+          <t>朝政被严党把持，这些做官的你中有我，我中有你，真细究起来又是一笔糊涂账。</t>
         </is>
       </c>
       <c r="K295" s="50" t="inlineStr"/>
@@ -21754,7 +21744,7 @@
         </is>
       </c>
       <c r="C296" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D296" s="50" t="inlineStr">
         <is>
@@ -21774,9 +21764,9 @@
       <c r="G296" s="55" t="inlineStr"/>
       <c r="H296" s="55" t="inlineStr"/>
       <c r="I296" s="55" t="inlineStr"/>
-      <c r="J296" s="56" t="inlineStr">
-        <is>
-          <t>这次我上奏皇上，除了赈灾药材一案，还将先生举荐给朝廷。正好太医院院判一职空缺，特批先生赴任。</t>
+      <c r="J296" s="55" t="inlineStr">
+        <is>
+          <t>李先生。</t>
         </is>
       </c>
       <c r="K296" s="50" t="inlineStr"/>
@@ -21793,7 +21783,7 @@
         </is>
       </c>
       <c r="C297" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D297" s="50" t="inlineStr">
         <is>
@@ -21815,7 +21805,7 @@
       <c r="I297" s="55" t="inlineStr"/>
       <c r="J297" s="56" t="inlineStr">
         <is>
-          <t>多谢王爷提拔，可草民荆楚鄙人，幼多羸疾，质成钝椎，实在是力不从心。</t>
+          <t>楚王殿下。</t>
         </is>
       </c>
       <c r="K297" s="50" t="inlineStr"/>
@@ -21832,7 +21822,7 @@
         </is>
       </c>
       <c r="C298" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D298" s="50" t="inlineStr">
         <is>
@@ -21854,50 +21844,46 @@
       <c r="I298" s="55" t="inlineStr"/>
       <c r="J298" s="56" t="inlineStr">
         <is>
-          <t>……既然如此，那本王就不强人所难了。</t>
+          <t>这次我上奏皇上，除了赈灾药材一案，还将先生举荐给朝廷。正好太医院院判一职空缺，特批先生赴任。</t>
         </is>
       </c>
       <c r="K298" s="50" t="inlineStr"/>
     </row>
-    <row r="299" ht="34.5" customHeight="1">
+    <row r="299">
       <c r="A299" s="50" t="inlineStr">
         <is>
-          <t>022_01</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B299" s="50" t="inlineStr">
         <is>
-          <t>柳敬亭温燥证</t>
+          <t>结案</t>
         </is>
       </c>
       <c r="C299" s="50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D299" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E299" s="50" t="inlineStr">
-        <is>
-          <t>柳敬亭</t>
-        </is>
-      </c>
-      <c r="F299" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G299" s="51" t="inlineStr"/>
-      <c r="H299" s="52" t="inlineStr"/>
-      <c r="I299" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J299" s="50" t="inlineStr">
-        <is>
-          <t>咳咳咳，咳咳，大夫，我这嗓子嗓子也不知怎么了，又疼又痒，咳得嗓子都哑了。</t>
+      <c r="E299" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F299" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G299" s="55" t="inlineStr"/>
+      <c r="H299" s="55" t="inlineStr"/>
+      <c r="I299" s="55" t="inlineStr"/>
+      <c r="J299" s="56" t="inlineStr">
+        <is>
+          <t>多谢王爷提拔，可草民荆楚鄙人，幼多羸疾，质成钝椎，实在是力不从心。</t>
         </is>
       </c>
       <c r="K299" s="50" t="inlineStr"/>
@@ -21905,61 +21891,61 @@
     <row r="300" hidden="1">
       <c r="A300" s="50" t="inlineStr">
         <is>
+          <t>021</t>
+        </is>
+      </c>
+      <c r="B300" s="50" t="inlineStr">
+        <is>
+          <t>结案</t>
+        </is>
+      </c>
+      <c r="C300" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="D300" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E300" s="56" t="inlineStr">
+        <is>
+          <t>楚王</t>
+        </is>
+      </c>
+      <c r="F300" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G300" s="55" t="inlineStr"/>
+      <c r="H300" s="55" t="inlineStr"/>
+      <c r="I300" s="55" t="inlineStr"/>
+      <c r="J300" s="56" t="inlineStr">
+        <is>
+          <t>……既然如此，那本王就不强人所难了。</t>
+        </is>
+      </c>
+      <c r="K300" s="50" t="inlineStr"/>
+    </row>
+    <row r="301" ht="34.5" customHeight="1">
+      <c r="A301" s="50" t="inlineStr">
+        <is>
           <t>022_01</t>
         </is>
       </c>
-      <c r="B300" s="50" t="inlineStr">
+      <c r="B301" s="50" t="inlineStr">
         <is>
           <t>柳敬亭温燥证</t>
         </is>
       </c>
-      <c r="C300" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D300" s="50" t="inlineStr">
+      <c r="C301" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D301" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E300" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F300" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G300" s="51" t="inlineStr"/>
-      <c r="H300" s="52" t="inlineStr"/>
-      <c r="I300" s="51" t="inlineStr"/>
-      <c r="J300" s="50" t="inlineStr">
-        <is>
-          <t>是柳先生啊，快请坐。</t>
-        </is>
-      </c>
-      <c r="K300" s="50" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="50" t="inlineStr">
-        <is>
-          <t>022_02</t>
-        </is>
-      </c>
-      <c r="B301" s="50" t="inlineStr">
-        <is>
-          <t>022治疗成功</t>
-        </is>
-      </c>
-      <c r="C301" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D301" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
       <c r="E301" s="50" t="inlineStr">
         <is>
           <t>柳敬亭</t>
@@ -21967,7 +21953,7 @@
       </c>
       <c r="F301" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G301" s="51" t="inlineStr"/>
@@ -21979,7 +21965,7 @@
       </c>
       <c r="J301" s="50" t="inlineStr">
         <is>
-          <t>哎呀，舒服多了。</t>
+          <t>咳咳咳，咳咳，大夫，我这嗓子嗓子也不知怎么了，又疼又痒，咳得嗓子都哑了。</t>
         </is>
       </c>
       <c r="K301" s="50" t="inlineStr"/>
@@ -21987,12 +21973,12 @@
     <row r="302" hidden="1">
       <c r="A302" s="50" t="inlineStr">
         <is>
-          <t>022_02</t>
+          <t>022_01</t>
         </is>
       </c>
       <c r="B302" s="50" t="inlineStr">
         <is>
-          <t>022治疗成功</t>
+          <t>柳敬亭温燥证</t>
         </is>
       </c>
       <c r="C302" s="50" t="n">
@@ -22008,9 +21994,9 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F302" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
+      <c r="F302" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G302" s="51" t="inlineStr"/>
@@ -22018,7 +22004,7 @@
       <c r="I302" s="51" t="inlineStr"/>
       <c r="J302" s="50" t="inlineStr">
         <is>
-          <t>您这是温燥证，整日说书久坐少动，伤津耗气，易生内热。</t>
+          <t>是柳先生啊，快请坐。</t>
         </is>
       </c>
       <c r="K302" s="50" t="inlineStr"/>
@@ -22035,7 +22021,7 @@
         </is>
       </c>
       <c r="C303" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D303" s="50" t="inlineStr">
         <is>
@@ -22044,20 +22030,24 @@
       </c>
       <c r="E303" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F303" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G303" s="51" t="inlineStr"/>
       <c r="H303" s="52" t="inlineStr"/>
-      <c r="I303" s="51" t="inlineStr"/>
-      <c r="J303" s="67" t="inlineStr">
-        <is>
-          <t>给您开一副桑杏汤，一天三服，也记得多喝水。</t>
+      <c r="I303" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J303" s="50" t="inlineStr">
+        <is>
+          <t>哎呀，舒服多了。</t>
         </is>
       </c>
       <c r="K303" s="50" t="inlineStr"/>
@@ -22074,7 +22064,7 @@
         </is>
       </c>
       <c r="C304" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D304" s="50" t="inlineStr">
         <is>
@@ -22083,20 +22073,20 @@
       </c>
       <c r="E304" s="50" t="inlineStr">
         <is>
-          <t>陈皮</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F304" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G304" s="51" t="inlineStr"/>
-      <c r="H304" s="51" t="inlineStr"/>
+      <c r="H304" s="52" t="inlineStr"/>
       <c r="I304" s="51" t="inlineStr"/>
       <c r="J304" s="50" t="inlineStr">
         <is>
-          <t>柳先生，我最喜欢听您说书啦，您真是啥都知道啥都会，讲什么像什么。</t>
+          <t>您这是温燥证，整日说书久坐少动，伤津耗气，易生内热。</t>
         </is>
       </c>
       <c r="K304" s="50" t="inlineStr"/>
@@ -22113,7 +22103,7 @@
         </is>
       </c>
       <c r="C305" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D305" s="50" t="inlineStr">
         <is>
@@ -22122,20 +22112,20 @@
       </c>
       <c r="E305" s="50" t="inlineStr">
         <is>
-          <t>柳敬亭</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F305" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G305" s="51" t="inlineStr"/>
-      <c r="H305" s="51" t="inlineStr"/>
+      <c r="H305" s="52" t="inlineStr"/>
       <c r="I305" s="51" t="inlineStr"/>
       <c r="J305" s="67" t="inlineStr">
         <is>
-          <t>诶嘿嘿，小兄弟过奖了，我只是说些王侯将相，才子佳人的故事，来听书的客官喜欢什么，我就讲什么。</t>
+          <t>给您开一副桑杏汤，一天三服，也记得多喝水。</t>
         </is>
       </c>
       <c r="K305" s="50" t="inlineStr"/>
@@ -22152,7 +22142,7 @@
         </is>
       </c>
       <c r="C306" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D306" s="50" t="inlineStr">
         <is>
@@ -22169,15 +22159,15 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G306" s="55" t="inlineStr"/>
-      <c r="H306" s="55" t="inlineStr"/>
-      <c r="I306" s="55" t="inlineStr"/>
-      <c r="J306" s="55" t="inlineStr">
-        <is>
-          <t>先生，您现在就在这讲一段吧。</t>
-        </is>
-      </c>
-      <c r="K306" s="55" t="inlineStr"/>
+      <c r="G306" s="51" t="inlineStr"/>
+      <c r="H306" s="51" t="inlineStr"/>
+      <c r="I306" s="51" t="inlineStr"/>
+      <c r="J306" s="50" t="inlineStr">
+        <is>
+          <t>柳先生，我最喜欢听您说书啦，您真是啥都知道啥都会，讲什么像什么。</t>
+        </is>
+      </c>
+      <c r="K306" s="50" t="inlineStr"/>
     </row>
     <row r="307" hidden="1">
       <c r="A307" s="50" t="inlineStr">
@@ -22191,7 +22181,7 @@
         </is>
       </c>
       <c r="C307" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D307" s="50" t="inlineStr">
         <is>
@@ -22200,23 +22190,23 @@
       </c>
       <c r="E307" s="50" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F307" s="51" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G307" s="55" t="inlineStr"/>
-      <c r="H307" s="55" t="inlineStr"/>
-      <c r="I307" s="55" t="inlineStr"/>
-      <c r="J307" s="62" t="inlineStr">
-        <is>
-          <t>是啊是啊，讲一段吧。</t>
-        </is>
-      </c>
-      <c r="K307" s="55" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G307" s="51" t="inlineStr"/>
+      <c r="H307" s="51" t="inlineStr"/>
+      <c r="I307" s="51" t="inlineStr"/>
+      <c r="J307" s="67" t="inlineStr">
+        <is>
+          <t>诶嘿嘿，小兄弟过奖了，我只是说些王侯将相，才子佳人的故事，来听书的客官喜欢什么，我就讲什么。</t>
+        </is>
+      </c>
+      <c r="K307" s="50" t="inlineStr"/>
     </row>
     <row r="308" hidden="1">
       <c r="A308" s="50" t="inlineStr">
@@ -22230,7 +22220,7 @@
         </is>
       </c>
       <c r="C308" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D308" s="50" t="inlineStr">
         <is>
@@ -22239,12 +22229,12 @@
       </c>
       <c r="E308" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>陈皮</t>
         </is>
       </c>
       <c r="F308" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G308" s="55" t="inlineStr"/>
@@ -22252,7 +22242,7 @@
       <c r="I308" s="55" t="inlineStr"/>
       <c r="J308" s="55" t="inlineStr">
         <is>
-          <t>人家柳先生还病着呢，你们别在这胡闹。</t>
+          <t>先生，您现在就在这讲一段吧。</t>
         </is>
       </c>
       <c r="K308" s="55" t="inlineStr"/>
@@ -22269,7 +22259,7 @@
         </is>
       </c>
       <c r="C309" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D309" s="50" t="inlineStr">
         <is>
@@ -22278,20 +22268,20 @@
       </c>
       <c r="E309" s="50" t="inlineStr">
         <is>
-          <t>柳敬亭</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F309" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G309" s="55" t="inlineStr"/>
       <c r="H309" s="55" t="inlineStr"/>
       <c r="I309" s="55" t="inlineStr"/>
-      <c r="J309" s="55" t="inlineStr">
-        <is>
-          <t>无妨，呵呵，那就说一个王道士胡诌妒妇方。</t>
+      <c r="J309" s="62" t="inlineStr">
+        <is>
+          <t>是啊是啊，讲一段吧。</t>
         </is>
       </c>
       <c r="K309" s="55" t="inlineStr"/>
@@ -22308,7 +22298,7 @@
         </is>
       </c>
       <c r="C310" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D310" s="50" t="inlineStr">
         <is>
@@ -22317,12 +22307,12 @@
       </c>
       <c r="E310" s="50" t="inlineStr">
         <is>
-          <t>柳敬亭</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F310" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G310" s="55" t="inlineStr"/>
@@ -22330,7 +22320,7 @@
       <c r="I310" s="55" t="inlineStr"/>
       <c r="J310" s="55" t="inlineStr">
         <is>
-          <t>说京城有一富商，娶了位善妒的夫人，家中鸡飞狗跳无一日安宁。他的朋友觉得这是病，得找人医治。</t>
+          <t>人家柳先生还病着呢，你们别在这胡闹。</t>
         </is>
       </c>
       <c r="K310" s="55" t="inlineStr"/>
@@ -22347,7 +22337,7 @@
         </is>
       </c>
       <c r="C311" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D311" s="50" t="inlineStr">
         <is>
@@ -22369,7 +22359,7 @@
       <c r="I311" s="55" t="inlineStr"/>
       <c r="J311" s="55" t="inlineStr">
         <is>
-          <t>正巧天齐庙有位摆摊卖膏药的王道士，因膏药灵验得名王一贴，富商的朋友便去求方问药。</t>
+          <t>无妨，呵呵，那就说一个王道士胡诌妒妇方。</t>
         </is>
       </c>
       <c r="K311" s="55" t="inlineStr"/>
@@ -22386,7 +22376,7 @@
         </is>
       </c>
       <c r="C312" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D312" s="50" t="inlineStr">
         <is>
@@ -22408,7 +22398,7 @@
       <c r="I312" s="55" t="inlineStr"/>
       <c r="J312" s="55" t="inlineStr">
         <is>
-          <t>王一贴道：“这贴妒的膏药倒没经过。有一种汤药，或者可医，只是慢些儿，不能立刻见效的。”</t>
+          <t>说京城有一富商，娶了位善妒的夫人，家中鸡飞狗跳无一日安宁。他的朋友觉得这是病，得找人医治。</t>
         </is>
       </c>
       <c r="K312" s="55" t="inlineStr"/>
@@ -22425,7 +22415,7 @@
         </is>
       </c>
       <c r="C313" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D313" s="50" t="inlineStr">
         <is>
@@ -22447,7 +22437,7 @@
       <c r="I313" s="55" t="inlineStr"/>
       <c r="J313" s="55" t="inlineStr">
         <is>
-          <t>朋友问：“什么汤？怎么吃法？”</t>
+          <t>正巧天齐庙有位摆摊卖膏药的王道士，因膏药灵验得名王一贴，富商的朋友便去求方问药。</t>
         </is>
       </c>
       <c r="K313" s="55" t="inlineStr"/>
@@ -22464,7 +22454,7 @@
         </is>
       </c>
       <c r="C314" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D314" s="50" t="inlineStr">
         <is>
@@ -22486,7 +22476,7 @@
       <c r="I314" s="55" t="inlineStr"/>
       <c r="J314" s="55" t="inlineStr">
         <is>
-          <t>王一贴道：“这叫做‘疗妒汤’。用极好的秋梨一个，二钱冰糖，一钱陈皮，水三碗，梨熟为度。每日清晨吃这一个梨，吃来吃去就好了。”</t>
+          <t>王一贴道：“这贴妒的膏药倒没经过。有一种汤药，或者可医，只是慢些儿，不能立刻见效的。”</t>
         </is>
       </c>
       <c r="K314" s="55" t="inlineStr"/>
@@ -22503,7 +22493,7 @@
         </is>
       </c>
       <c r="C315" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D315" s="50" t="inlineStr">
         <is>
@@ -22525,7 +22515,7 @@
       <c r="I315" s="55" t="inlineStr"/>
       <c r="J315" s="55" t="inlineStr">
         <is>
-          <t>朋友道：“这也不值什么。只怕未必见效。”</t>
+          <t>朋友问：“什么汤？怎么吃法？”</t>
         </is>
       </c>
       <c r="K315" s="55" t="inlineStr"/>
@@ -22542,7 +22532,7 @@
         </is>
       </c>
       <c r="C316" s="50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D316" s="50" t="inlineStr">
         <is>
@@ -22564,7 +22554,7 @@
       <c r="I316" s="55" t="inlineStr"/>
       <c r="J316" s="55" t="inlineStr">
         <is>
-          <t>王一贴道：“一剂不效，吃十剂；今日不效，明日再吃；今年不效，明年再吃。”</t>
+          <t>王一贴道：“这叫做‘疗妒汤’。用极好的秋梨一个，二钱冰糖，一钱陈皮，水三碗，梨熟为度。每日清晨吃这一个梨，吃来吃去就好了。”</t>
         </is>
       </c>
       <c r="K316" s="55" t="inlineStr"/>
@@ -22581,7 +22571,7 @@
         </is>
       </c>
       <c r="C317" s="50" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D317" s="50" t="inlineStr">
         <is>
@@ -22603,7 +22593,7 @@
       <c r="I317" s="55" t="inlineStr"/>
       <c r="J317" s="55" t="inlineStr">
         <is>
-          <t>“横竖这三味药都是润肺开胃不伤人的，甜丝丝的，又止咳嗽，又好吃。吃过一百岁，人横竖是要死的，死了还妒什么？那时就见效了。”</t>
+          <t>朋友道：“这也不值什么。只怕未必见效。”</t>
         </is>
       </c>
       <c r="K317" s="55" t="inlineStr"/>
@@ -22620,7 +22610,7 @@
         </is>
       </c>
       <c r="C318" s="50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D318" s="50" t="inlineStr">
         <is>
@@ -22629,12 +22619,12 @@
       </c>
       <c r="E318" s="50" t="inlineStr">
         <is>
-          <t>陈皮</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F318" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G318" s="55" t="inlineStr"/>
@@ -22642,24 +22632,24 @@
       <c r="I318" s="55" t="inlineStr"/>
       <c r="J318" s="55" t="inlineStr">
         <is>
-          <t>哈哈哈，还有这种方子。</t>
+          <t>王一贴道：“一剂不效，吃十剂；今日不效，明日再吃；今年不效，明年再吃。”</t>
         </is>
       </c>
       <c r="K318" s="55" t="inlineStr"/>
     </row>
     <row r="319" hidden="1">
-      <c r="A319" s="55" t="inlineStr">
+      <c r="A319" s="50" t="inlineStr">
         <is>
           <t>022_02</t>
         </is>
       </c>
-      <c r="B319" s="55" t="inlineStr">
+      <c r="B319" s="50" t="inlineStr">
         <is>
           <t>022治疗成功</t>
         </is>
       </c>
-      <c r="C319" s="55" t="n">
-        <v>19</v>
+      <c r="C319" s="50" t="n">
+        <v>17</v>
       </c>
       <c r="D319" s="50" t="inlineStr">
         <is>
@@ -22668,12 +22658,12 @@
       </c>
       <c r="E319" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>柳敬亭</t>
         </is>
       </c>
       <c r="F319" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G319" s="55" t="inlineStr"/>
@@ -22681,7 +22671,7 @@
       <c r="I319" s="55" t="inlineStr"/>
       <c r="J319" s="55" t="inlineStr">
         <is>
-          <t>哈哈哈，这道士说的也不无道理。</t>
+          <t>“横竖这三味药都是润肺开胃不伤人的，甜丝丝的，又止咳嗽，又好吃。吃过一百岁，人横竖是要死的，死了还妒什么？那时就见效了。”</t>
         </is>
       </c>
       <c r="K319" s="55" t="inlineStr"/>
@@ -22689,16 +22679,16 @@
     <row r="320">
       <c r="A320" s="50" t="inlineStr">
         <is>
-          <t>022_03</t>
+          <t>022_02</t>
         </is>
       </c>
       <c r="B320" s="50" t="inlineStr">
         <is>
-          <t>022治疗失败</t>
+          <t>022治疗成功</t>
         </is>
       </c>
       <c r="C320" s="50" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D320" s="50" t="inlineStr">
         <is>
@@ -22707,84 +22697,76 @@
       </c>
       <c r="E320" s="50" t="inlineStr">
         <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F320" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G320" s="55" t="inlineStr"/>
+      <c r="H320" s="55" t="inlineStr"/>
+      <c r="I320" s="55" t="inlineStr"/>
+      <c r="J320" s="55" t="inlineStr">
+        <is>
+          <t>哈哈哈，还有这种方子。</t>
+        </is>
+      </c>
+      <c r="K320" s="55" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="55" t="inlineStr">
+        <is>
+          <t>022_02</t>
+        </is>
+      </c>
+      <c r="B321" s="55" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C321" s="55" t="n">
+        <v>19</v>
+      </c>
+      <c r="D321" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E321" s="50" t="inlineStr">
+        <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F320" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G320" s="51" t="inlineStr"/>
-      <c r="H320" s="52" t="inlineStr"/>
-      <c r="I320" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J320" s="53" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
-        </is>
-      </c>
-      <c r="K320" s="50" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="50" t="inlineStr">
-        <is>
-          <t>023_01</t>
-        </is>
-      </c>
-      <c r="B321" s="50" t="inlineStr">
-        <is>
-          <t>谢飞燕肺气虚</t>
-        </is>
-      </c>
-      <c r="C321" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D321" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E321" s="50" t="inlineStr">
-        <is>
-          <t>金姨妈</t>
-        </is>
-      </c>
       <c r="F321" s="51" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G321" s="51" t="inlineStr"/>
-      <c r="H321" s="52" t="inlineStr"/>
-      <c r="I321" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J321" s="50" t="inlineStr">
-        <is>
-          <t>李大夫，您快给我女儿瞧瞧吧，这孩子整日茶饭不进，愁眉苦脸咳个不停。</t>
-        </is>
-      </c>
-      <c r="K321" s="50" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G321" s="55" t="inlineStr"/>
+      <c r="H321" s="55" t="inlineStr"/>
+      <c r="I321" s="55" t="inlineStr"/>
+      <c r="J321" s="55" t="inlineStr">
+        <is>
+          <t>哈哈哈，这道士说的也不无道理。</t>
+        </is>
+      </c>
+      <c r="K321" s="55" t="inlineStr"/>
     </row>
     <row r="322" hidden="1">
       <c r="A322" s="50" t="inlineStr">
         <is>
-          <t>023_01</t>
+          <t>022_03</t>
         </is>
       </c>
       <c r="B322" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕肺气虚</t>
+          <t>022治疗失败</t>
         </is>
       </c>
       <c r="C322" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D322" s="50" t="inlineStr">
         <is>
@@ -22793,7 +22775,7 @@
       </c>
       <c r="E322" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F322" s="52" t="inlineStr">
@@ -22801,16 +22783,16 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G322" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+      <c r="G322" s="51" t="inlineStr"/>
       <c r="H322" s="52" t="inlineStr"/>
-      <c r="I322" s="51" t="inlineStr"/>
-      <c r="J322" s="50" t="inlineStr">
-        <is>
-          <t>…</t>
+      <c r="I322" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J322" s="53" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K322" s="50" t="inlineStr"/>
@@ -22827,7 +22809,7 @@
         </is>
       </c>
       <c r="C323" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D323" s="50" t="inlineStr">
         <is>
@@ -22836,20 +22818,24 @@
       </c>
       <c r="E323" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>金姨妈</t>
         </is>
       </c>
       <c r="F323" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G323" s="51" t="inlineStr"/>
       <c r="H323" s="52" t="inlineStr"/>
-      <c r="I323" s="51" t="inlineStr"/>
+      <c r="I323" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J323" s="50" t="inlineStr">
         <is>
-          <t>这是您女儿？</t>
+          <t>李大夫，您快给我女儿瞧瞧吧，这孩子整日茶饭不进，愁眉苦脸咳个不停。</t>
         </is>
       </c>
       <c r="K323" s="50" t="inlineStr"/>
@@ -22866,7 +22852,7 @@
         </is>
       </c>
       <c r="C324" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D324" s="50" t="inlineStr">
         <is>
@@ -22875,20 +22861,24 @@
       </c>
       <c r="E324" s="50" t="inlineStr">
         <is>
-          <t>金姨妈</t>
-        </is>
-      </c>
-      <c r="F324" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G324" s="51" t="inlineStr"/>
-      <c r="H324" s="51" t="inlineStr"/>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F324" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G324" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H324" s="52" t="inlineStr"/>
       <c r="I324" s="51" t="inlineStr"/>
       <c r="J324" s="50" t="inlineStr">
         <is>
-          <t>哎呀，可不是嘛，这孩子随我学艺两年又半载，尤善歌舞，是咱柳月坊的花魁。</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K324" s="50" t="inlineStr"/>
@@ -22905,7 +22895,7 @@
         </is>
       </c>
       <c r="C325" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D325" s="50" t="inlineStr">
         <is>
@@ -22914,98 +22904,98 @@
       </c>
       <c r="E325" s="50" t="inlineStr">
         <is>
-          <t>金姨妈</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F325" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G325" s="51" t="inlineStr"/>
-      <c r="H325" s="51" t="inlineStr"/>
+      <c r="H325" s="52" t="inlineStr"/>
       <c r="I325" s="51" t="inlineStr"/>
       <c r="J325" s="50" t="inlineStr">
         <is>
+          <t>这是您女儿？</t>
+        </is>
+      </c>
+      <c r="K325" s="50" t="inlineStr"/>
+    </row>
+    <row r="326" hidden="1">
+      <c r="A326" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B326" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C326" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D326" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E326" s="50" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F326" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G326" s="51" t="inlineStr"/>
+      <c r="H326" s="51" t="inlineStr"/>
+      <c r="I326" s="51" t="inlineStr"/>
+      <c r="J326" s="50" t="inlineStr">
+        <is>
+          <t>哎呀，可不是嘛，这孩子随我学艺两年又半载，尤善歌舞，是咱柳月坊的花魁。</t>
+        </is>
+      </c>
+      <c r="K326" s="50" t="inlineStr"/>
+    </row>
+    <row r="327" hidden="1">
+      <c r="A327" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B327" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C327" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D327" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E327" s="50" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F327" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G327" s="51" t="inlineStr"/>
+      <c r="H327" s="51" t="inlineStr"/>
+      <c r="I327" s="51" t="inlineStr"/>
+      <c r="J327" s="50" t="inlineStr">
+        <is>
           <t>可你看她现在这个样子，还怎么接待客人啊。</t>
-        </is>
-      </c>
-      <c r="K325" s="50" t="inlineStr"/>
-    </row>
-    <row r="326" hidden="1">
-      <c r="A326" s="55" t="inlineStr">
-        <is>
-          <t>023_01</t>
-        </is>
-      </c>
-      <c r="B326" s="55" t="inlineStr">
-        <is>
-          <t>谢飞燕肺气虚</t>
-        </is>
-      </c>
-      <c r="C326" s="55" t="n">
-        <v>6</v>
-      </c>
-      <c r="D326" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E326" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F326" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G326" s="55" t="inlineStr"/>
-      <c r="H326" s="55" t="inlineStr"/>
-      <c r="I326" s="55" t="inlineStr"/>
-      <c r="J326" s="55" t="inlineStr">
-        <is>
-          <t>姑娘你坐下，我给你把把脉。哎，半夏你在这干什么？</t>
-        </is>
-      </c>
-      <c r="K326" s="50" t="inlineStr"/>
-    </row>
-    <row r="327" hidden="1">
-      <c r="A327" s="55" t="inlineStr">
-        <is>
-          <t>023_01</t>
-        </is>
-      </c>
-      <c r="B327" s="55" t="inlineStr">
-        <is>
-          <t>谢飞燕肺气虚</t>
-        </is>
-      </c>
-      <c r="C327" s="55" t="n">
-        <v>7</v>
-      </c>
-      <c r="D327" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E327" s="53" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F327" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G327" s="55" t="inlineStr"/>
-      <c r="H327" s="55" t="inlineStr"/>
-      <c r="I327" s="55" t="inlineStr"/>
-      <c r="J327" s="56" t="inlineStr">
-        <is>
-          <t>我替少夫人来看着你。</t>
         </is>
       </c>
       <c r="K327" s="50" t="inlineStr"/>
@@ -23022,7 +23012,7 @@
         </is>
       </c>
       <c r="C328" s="55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D328" s="50" t="inlineStr">
         <is>
@@ -23042,112 +23032,104 @@
       <c r="G328" s="55" t="inlineStr"/>
       <c r="H328" s="55" t="inlineStr"/>
       <c r="I328" s="55" t="inlineStr"/>
-      <c r="J328" s="56" t="inlineStr">
+      <c r="J328" s="55" t="inlineStr">
+        <is>
+          <t>姑娘你坐下，我给你把把脉。哎，半夏你在这干什么？</t>
+        </is>
+      </c>
+      <c r="K328" s="50" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="55" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B329" s="55" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C329" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D329" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E329" s="53" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F329" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G329" s="55" t="inlineStr"/>
+      <c r="H329" s="55" t="inlineStr"/>
+      <c r="I329" s="55" t="inlineStr"/>
+      <c r="J329" s="56" t="inlineStr">
+        <is>
+          <t>我替少夫人来看着你。</t>
+        </is>
+      </c>
+      <c r="K329" s="50" t="inlineStr"/>
+    </row>
+    <row r="330" hidden="1">
+      <c r="A330" s="55" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B330" s="55" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C330" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D330" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E330" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F330" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G330" s="55" t="inlineStr"/>
+      <c r="H330" s="55" t="inlineStr"/>
+      <c r="I330" s="55" t="inlineStr"/>
+      <c r="J330" s="56" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="K328" s="50" t="inlineStr"/>
-    </row>
-    <row r="329" ht="33" customHeight="1">
-      <c r="A329" s="50" t="inlineStr">
+      <c r="K330" s="50" t="inlineStr"/>
+    </row>
+    <row r="331" hidden="1" ht="33" customHeight="1">
+      <c r="A331" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
         </is>
       </c>
-      <c r="B329" s="50" t="inlineStr">
+      <c r="B331" s="50" t="inlineStr">
         <is>
           <t>023治疗成功</t>
         </is>
       </c>
-      <c r="C329" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D329" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E329" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F329" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G329" s="51" t="inlineStr"/>
-      <c r="H329" s="52" t="inlineStr"/>
-      <c r="I329" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J329" s="50" t="inlineStr">
-        <is>
-          <t>姑娘这病是肺气虚，平日注意避风避寒，开副补肺汤调养调养。早上练练六字诀中的呬字诀，舒畅胸中气机。</t>
-        </is>
-      </c>
-      <c r="K329" s="50" t="inlineStr"/>
-    </row>
-    <row r="330" hidden="1">
-      <c r="A330" s="50" t="inlineStr">
-        <is>
-          <t>023_02</t>
-        </is>
-      </c>
-      <c r="B330" s="50" t="inlineStr">
-        <is>
-          <t>023治疗成功</t>
-        </is>
-      </c>
-      <c r="C330" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D330" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E330" s="50" t="inlineStr">
-        <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F330" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G330" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H330" s="52" t="inlineStr"/>
-      <c r="I330" s="51" t="inlineStr"/>
-      <c r="J330" s="50" t="inlineStr">
-        <is>
-          <t>…多谢先生。</t>
-        </is>
-      </c>
-      <c r="K330" s="50" t="inlineStr"/>
-    </row>
-    <row r="331" hidden="1">
-      <c r="A331" s="50" t="inlineStr">
-        <is>
-          <t>023_02</t>
-        </is>
-      </c>
-      <c r="B331" s="50" t="inlineStr">
-        <is>
-          <t>023治疗成功</t>
-        </is>
-      </c>
       <c r="C331" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D331" s="50" t="inlineStr">
         <is>
@@ -23166,10 +23148,14 @@
       </c>
       <c r="G331" s="51" t="inlineStr"/>
       <c r="H331" s="52" t="inlineStr"/>
-      <c r="I331" s="51" t="inlineStr"/>
+      <c r="I331" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J331" s="50" t="inlineStr">
         <is>
-          <t>姑娘可是有什么心事？</t>
+          <t>姑娘这病是肺气虚，平日注意避风避寒，开副补肺汤调养调养。早上练练六字诀中的呬字诀，舒畅胸中气机。</t>
         </is>
       </c>
       <c r="K331" s="50" t="inlineStr"/>
@@ -23186,7 +23172,7 @@
         </is>
       </c>
       <c r="C332" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D332" s="50" t="inlineStr">
         <is>
@@ -23195,20 +23181,24 @@
       </c>
       <c r="E332" s="50" t="inlineStr">
         <is>
-          <t>金姨妈</t>
-        </is>
-      </c>
-      <c r="F332" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G332" s="51" t="inlineStr"/>
-      <c r="H332" s="51" t="inlineStr"/>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F332" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G332" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H332" s="52" t="inlineStr"/>
       <c r="I332" s="51" t="inlineStr"/>
       <c r="J332" s="50" t="inlineStr">
         <is>
-          <t>成天好吃好喝的伺候着，她能有什么心事。</t>
+          <t>…多谢先生。</t>
         </is>
       </c>
       <c r="K332" s="50" t="inlineStr"/>
@@ -23225,7 +23215,7 @@
         </is>
       </c>
       <c r="C333" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D333" s="50" t="inlineStr">
         <is>
@@ -23234,20 +23224,20 @@
       </c>
       <c r="E333" s="50" t="inlineStr">
         <is>
-          <t>金姨妈</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F333" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G333" s="51" t="inlineStr"/>
-      <c r="H333" s="51" t="inlineStr"/>
+      <c r="H333" s="52" t="inlineStr"/>
       <c r="I333" s="51" t="inlineStr"/>
       <c r="J333" s="50" t="inlineStr">
         <is>
-          <t>那就多谢大夫了，走吧女儿。</t>
+          <t>姑娘可是有什么心事？</t>
         </is>
       </c>
       <c r="K333" s="50" t="inlineStr"/>
@@ -23264,7 +23254,7 @@
         </is>
       </c>
       <c r="C334" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D334" s="50" t="inlineStr">
         <is>
@@ -23273,24 +23263,20 @@
       </c>
       <c r="E334" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F334" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G334" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H334" s="55" t="inlineStr"/>
-      <c r="I334" s="55" t="inlineStr"/>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F334" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G334" s="51" t="inlineStr"/>
+      <c r="H334" s="51" t="inlineStr"/>
+      <c r="I334" s="51" t="inlineStr"/>
       <c r="J334" s="50" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>成天好吃好喝的伺候着，她能有什么心事。</t>
         </is>
       </c>
       <c r="K334" s="50" t="inlineStr"/>
@@ -23307,25 +23293,29 @@
         </is>
       </c>
       <c r="C335" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D335" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E335" s="55" t="inlineStr"/>
-      <c r="F335" s="51" t="inlineStr"/>
-      <c r="G335" s="55" t="inlineStr"/>
-      <c r="H335" s="55" t="inlineStr"/>
-      <c r="I335" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/black.png</t>
-        </is>
-      </c>
-      <c r="J335" s="88" t="inlineStr">
-        <is>
-          <t>收入一两白银</t>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E335" s="50" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F335" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G335" s="51" t="inlineStr"/>
+      <c r="H335" s="51" t="inlineStr"/>
+      <c r="I335" s="51" t="inlineStr"/>
+      <c r="J335" s="50" t="inlineStr">
+        <is>
+          <t>那就多谢大夫了，走吧女儿。</t>
         </is>
       </c>
       <c r="K335" s="50" t="inlineStr"/>
@@ -23342,33 +23332,33 @@
         </is>
       </c>
       <c r="C336" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D336" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E336" s="55" t="inlineStr">
-        <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F336" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G336" s="55" t="inlineStr"/>
+      <c r="E336" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F336" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G336" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H336" s="55" t="inlineStr"/>
-      <c r="I336" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J336" s="68" t="inlineStr">
-        <is>
-          <t>大夫，刚才那姑娘是得了什么病啊？</t>
+      <c r="I336" s="55" t="inlineStr"/>
+      <c r="J336" s="50" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="K336" s="50" t="inlineStr"/>
@@ -23385,29 +23375,25 @@
         </is>
       </c>
       <c r="C337" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D337" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E337" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F337" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E337" s="55" t="inlineStr"/>
+      <c r="F337" s="51" t="inlineStr"/>
       <c r="G337" s="55" t="inlineStr"/>
       <c r="H337" s="55" t="inlineStr"/>
-      <c r="I337" s="55" t="inlineStr"/>
-      <c r="J337" s="55" t="inlineStr">
-        <is>
-          <t>您是？</t>
+      <c r="I337" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/black.png</t>
+        </is>
+      </c>
+      <c r="J337" s="88" t="inlineStr">
+        <is>
+          <t>收入一两白银</t>
         </is>
       </c>
       <c r="K337" s="50" t="inlineStr"/>
@@ -23424,7 +23410,7 @@
         </is>
       </c>
       <c r="C338" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D338" s="50" t="inlineStr">
         <is>
@@ -23443,10 +23429,14 @@
       </c>
       <c r="G338" s="55" t="inlineStr"/>
       <c r="H338" s="55" t="inlineStr"/>
-      <c r="I338" s="55" t="inlineStr"/>
-      <c r="J338" s="55" t="inlineStr">
-        <is>
-          <t>小生是姑娘的一位相识，担心姑娘身体，来问问大夫。</t>
+      <c r="I338" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J338" s="68" t="inlineStr">
+        <is>
+          <t>大夫，刚才那姑娘是得了什么病啊？</t>
         </is>
       </c>
       <c r="K338" s="50" t="inlineStr"/>
@@ -23463,7 +23453,7 @@
         </is>
       </c>
       <c r="C339" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D339" s="50" t="inlineStr">
         <is>
@@ -23485,7 +23475,7 @@
       <c r="I339" s="55" t="inlineStr"/>
       <c r="J339" s="55" t="inlineStr">
         <is>
-          <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
+          <t>您是？</t>
         </is>
       </c>
       <c r="K339" s="50" t="inlineStr"/>
@@ -23502,7 +23492,7 @@
         </is>
       </c>
       <c r="C340" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D340" s="50" t="inlineStr">
         <is>
@@ -23511,12 +23501,12 @@
       </c>
       <c r="E340" s="55" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F340" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G340" s="55" t="inlineStr"/>
@@ -23524,7 +23514,7 @@
       <c r="I340" s="55" t="inlineStr"/>
       <c r="J340" s="55" t="inlineStr">
         <is>
-          <t>哎哟？这里面有事儿，快说来听听。</t>
+          <t>小生是姑娘的一位相识，担心姑娘身体，来问问大夫。</t>
         </is>
       </c>
       <c r="K340" s="50" t="inlineStr"/>
@@ -23541,29 +23531,29 @@
         </is>
       </c>
       <c r="C341" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D341" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E341" s="55" t="inlineStr">
-        <is>
-          <t>王百堂</t>
+      <c r="E341" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F341" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G341" s="55" t="inlineStr"/>
       <c r="H341" s="55" t="inlineStr"/>
       <c r="I341" s="55" t="inlineStr"/>
-      <c r="J341" s="68" t="inlineStr">
-        <is>
-          <t>实不相瞒，小生在柳月坊与飞燕相识，一见倾心，私底下定了终身。</t>
+      <c r="J341" s="55" t="inlineStr">
+        <is>
+          <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
         </is>
       </c>
       <c r="K341" s="50" t="inlineStr"/>
@@ -23580,7 +23570,7 @@
         </is>
       </c>
       <c r="C342" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D342" s="50" t="inlineStr">
         <is>
@@ -23589,12 +23579,12 @@
       </c>
       <c r="E342" s="55" t="inlineStr">
         <is>
-          <t>王百堂</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F342" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G342" s="55" t="inlineStr"/>
@@ -23602,7 +23592,7 @@
       <c r="I342" s="55" t="inlineStr"/>
       <c r="J342" s="55" t="inlineStr">
         <is>
-          <t>原想着凑够五百两银子，给她赎身。可那老鸨坐地起价，张口就要一千两，这让我们上哪去凑这么多银子啊…</t>
+          <t>哎哟？这里面有事儿，快说来听听。</t>
         </is>
       </c>
       <c r="K342" s="50" t="inlineStr"/>
@@ -23619,29 +23609,29 @@
         </is>
       </c>
       <c r="C343" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D343" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E343" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E343" s="55" t="inlineStr">
+        <is>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F343" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G343" s="55" t="inlineStr"/>
       <c r="H343" s="55" t="inlineStr"/>
       <c r="I343" s="55" t="inlineStr"/>
-      <c r="J343" s="55" t="inlineStr">
-        <is>
-          <t>想必姑娘是因为这事急坏了身子。</t>
+      <c r="J343" s="68" t="inlineStr">
+        <is>
+          <t>实不相瞒，小生在柳月坊与飞燕相识，一见倾心，私底下定了终身。</t>
         </is>
       </c>
       <c r="K343" s="50" t="inlineStr"/>
@@ -23658,7 +23648,7 @@
         </is>
       </c>
       <c r="C344" s="50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D344" s="50" t="inlineStr">
         <is>
@@ -23667,12 +23657,12 @@
       </c>
       <c r="E344" s="55" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F344" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G344" s="55" t="inlineStr"/>
@@ -23680,7 +23670,7 @@
       <c r="I344" s="55" t="inlineStr"/>
       <c r="J344" s="55" t="inlineStr">
         <is>
-          <t>唉，又是一对儿苦命的鸳鸯。</t>
+          <t>原想着凑够五百两银子，给她赎身。可那老鸨坐地起价，张口就要一千两，这让我们上哪去凑这么多银子啊…</t>
         </is>
       </c>
       <c r="K344" s="50" t="inlineStr"/>
@@ -23697,29 +23687,29 @@
         </is>
       </c>
       <c r="C345" s="50" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D345" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E345" s="56" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E345" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F345" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G345" s="55" t="inlineStr"/>
       <c r="H345" s="55" t="inlineStr"/>
       <c r="I345" s="55" t="inlineStr"/>
-      <c r="J345" s="56" t="inlineStr">
-        <is>
-          <t>相公咱想办法帮帮他们吧。</t>
+      <c r="J345" s="55" t="inlineStr">
+        <is>
+          <t>想必姑娘是因为这事急坏了身子。</t>
         </is>
       </c>
       <c r="K345" s="50" t="inlineStr"/>
@@ -23736,21 +23726,21 @@
         </is>
       </c>
       <c r="C346" s="50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D346" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E346" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E346" s="55" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F346" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G346" s="55" t="inlineStr"/>
@@ -23758,7 +23748,7 @@
       <c r="I346" s="55" t="inlineStr"/>
       <c r="J346" s="55" t="inlineStr">
         <is>
-          <t>我也想帮他们，可怎么帮呢？</t>
+          <t>唉，又是一对儿苦命的鸳鸯。</t>
         </is>
       </c>
       <c r="K346" s="50" t="inlineStr"/>
@@ -23766,42 +23756,38 @@
     <row r="347">
       <c r="A347" s="50" t="inlineStr">
         <is>
-          <t>023_03</t>
+          <t>023_02</t>
         </is>
       </c>
       <c r="B347" s="50" t="inlineStr">
         <is>
-          <t>023治疗失败</t>
+          <t>023治疗成功</t>
         </is>
       </c>
       <c r="C347" s="50" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D347" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E347" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E347" s="56" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F347" s="51" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G347" s="51" t="inlineStr"/>
-      <c r="H347" s="52" t="inlineStr"/>
-      <c r="I347" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J347" s="53" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G347" s="55" t="inlineStr"/>
+      <c r="H347" s="55" t="inlineStr"/>
+      <c r="I347" s="55" t="inlineStr"/>
+      <c r="J347" s="56" t="inlineStr">
+        <is>
+          <t>相公咱想办法帮帮他们吧。</t>
         </is>
       </c>
       <c r="K347" s="50" t="inlineStr"/>
@@ -23809,42 +23795,38 @@
     <row r="348">
       <c r="A348" s="50" t="inlineStr">
         <is>
-          <t>024_01</t>
+          <t>023_02</t>
         </is>
       </c>
       <c r="B348" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕肺阴虚</t>
+          <t>023治疗成功</t>
         </is>
       </c>
       <c r="C348" s="50" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D348" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E348" s="53" t="inlineStr">
+      <c r="E348" s="50" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F348" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G348" s="51" t="inlineStr"/>
-      <c r="H348" s="52" t="inlineStr"/>
-      <c r="I348" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J348" s="53" t="inlineStr">
-        <is>
-          <t>姑娘你来啦，病好点了吗？</t>
+      <c r="F348" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G348" s="55" t="inlineStr"/>
+      <c r="H348" s="55" t="inlineStr"/>
+      <c r="I348" s="55" t="inlineStr"/>
+      <c r="J348" s="55" t="inlineStr">
+        <is>
+          <t>我也想帮他们，可怎么帮呢？</t>
         </is>
       </c>
       <c r="K348" s="50" t="inlineStr"/>
@@ -23852,16 +23834,16 @@
     <row r="349" hidden="1">
       <c r="A349" s="50" t="inlineStr">
         <is>
-          <t>024_01</t>
+          <t>023_03</t>
         </is>
       </c>
       <c r="B349" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕肺阴虚</t>
+          <t>023治疗失败</t>
         </is>
       </c>
       <c r="C349" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D349" s="50" t="inlineStr">
         <is>
@@ -23870,24 +23852,24 @@
       </c>
       <c r="E349" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F349" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G349" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F349" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G349" s="51" t="inlineStr"/>
       <c r="H349" s="52" t="inlineStr"/>
-      <c r="I349" s="51" t="inlineStr"/>
+      <c r="I349" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J349" s="53" t="inlineStr">
         <is>
-          <t>唉，这些日子一直不太好，前天还咳出血丝来了…</t>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K349" s="50" t="inlineStr"/>
@@ -23904,7 +23886,7 @@
         </is>
       </c>
       <c r="C350" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D350" s="50" t="inlineStr">
         <is>
@@ -23923,10 +23905,14 @@
       </c>
       <c r="G350" s="51" t="inlineStr"/>
       <c r="H350" s="52" t="inlineStr"/>
-      <c r="I350" s="51" t="inlineStr"/>
+      <c r="I350" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J350" s="53" t="inlineStr">
         <is>
-          <t>请坐，我再给你看看。</t>
+          <t>姑娘你来啦，病好点了吗？</t>
         </is>
       </c>
       <c r="K350" s="50" t="inlineStr"/>
@@ -23934,16 +23920,16 @@
     <row r="351">
       <c r="A351" s="50" t="inlineStr">
         <is>
-          <t>024_02</t>
+          <t>024_01</t>
         </is>
       </c>
       <c r="B351" s="50" t="inlineStr">
         <is>
-          <t>024治疗成功</t>
+          <t>谢飞燕肺阴虚</t>
         </is>
       </c>
       <c r="C351" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351" s="50" t="inlineStr">
         <is>
@@ -23952,24 +23938,24 @@
       </c>
       <c r="E351" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F351" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G351" s="51" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G351" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H351" s="52" t="inlineStr"/>
-      <c r="I351" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I351" s="51" t="inlineStr"/>
       <c r="J351" s="53" t="inlineStr">
         <is>
-          <t>姑娘你这病，因气虚日久，气不化津，已经恶化为肺阴虚了。给你开些沙参麦冬汤补津养肺。</t>
+          <t>唉，这些日子一直不太好，前天还咳出血丝来了…</t>
         </is>
       </c>
       <c r="K351" s="50" t="inlineStr"/>
@@ -23977,16 +23963,16 @@
     <row r="352" hidden="1">
       <c r="A352" s="50" t="inlineStr">
         <is>
-          <t>024_02</t>
+          <t>024_01</t>
         </is>
       </c>
       <c r="B352" s="50" t="inlineStr">
         <is>
-          <t>024治疗成功</t>
+          <t>谢飞燕肺阴虚</t>
         </is>
       </c>
       <c r="C352" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D352" s="50" t="inlineStr">
         <is>
@@ -23995,24 +23981,20 @@
       </c>
       <c r="E352" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F352" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G352" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G352" s="51" t="inlineStr"/>
       <c r="H352" s="52" t="inlineStr"/>
       <c r="I352" s="51" t="inlineStr"/>
       <c r="J352" s="53" t="inlineStr">
         <is>
-          <t>多谢先生…</t>
+          <t>请坐，我再给你看看。</t>
         </is>
       </c>
       <c r="K352" s="50" t="inlineStr"/>
@@ -24029,7 +24011,7 @@
         </is>
       </c>
       <c r="C353" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D353" s="50" t="inlineStr">
         <is>
@@ -24038,20 +24020,24 @@
       </c>
       <c r="E353" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F353" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G353" s="51" t="inlineStr"/>
       <c r="H353" s="52" t="inlineStr"/>
-      <c r="I353" s="51" t="inlineStr"/>
+      <c r="I353" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J353" s="53" t="inlineStr">
         <is>
-          <t>可这药只能医肺病，不能医心病，心病还须心药医。</t>
+          <t>姑娘你这病，因气虚日久，气不化津，已经恶化为肺阴虚了。给你开些沙参麦冬汤补津养肺。</t>
         </is>
       </c>
       <c r="K353" s="50" t="inlineStr"/>
@@ -24068,7 +24054,7 @@
         </is>
       </c>
       <c r="C354" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D354" s="50" t="inlineStr">
         <is>
@@ -24090,11 +24076,11 @@
           <t>sick</t>
         </is>
       </c>
-      <c r="H354" s="51" t="inlineStr"/>
+      <c r="H354" s="52" t="inlineStr"/>
       <c r="I354" s="51" t="inlineStr"/>
       <c r="J354" s="53" t="inlineStr">
         <is>
-          <t>夫人这是何意味？</t>
+          <t>多谢先生…</t>
         </is>
       </c>
       <c r="K354" s="50" t="inlineStr"/>
@@ -24111,7 +24097,7 @@
         </is>
       </c>
       <c r="C355" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D355" s="50" t="inlineStr">
         <is>
@@ -24129,11 +24115,11 @@
         </is>
       </c>
       <c r="G355" s="51" t="inlineStr"/>
-      <c r="H355" s="51" t="inlineStr"/>
+      <c r="H355" s="52" t="inlineStr"/>
       <c r="I355" s="51" t="inlineStr"/>
       <c r="J355" s="53" t="inlineStr">
         <is>
-          <t>前些天你来看病，你前脚刚走，王公子就来这问你的病情，很是担心你。</t>
+          <t>可这药只能医肺病，不能医心病，心病还须心药医。</t>
         </is>
       </c>
       <c r="K355" s="50" t="inlineStr"/>
@@ -24150,7 +24136,7 @@
         </is>
       </c>
       <c r="C356" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D356" s="50" t="inlineStr">
         <is>
@@ -24172,11 +24158,11 @@
           <t>sick</t>
         </is>
       </c>
-      <c r="H356" s="55" t="inlineStr"/>
-      <c r="I356" s="55" t="inlineStr"/>
-      <c r="J356" s="56" t="inlineStr">
-        <is>
-          <t>唉，我们这行当是做不长久的，只盼着有个如意的郎君，趁着年轻嫁入好人家。</t>
+      <c r="H356" s="51" t="inlineStr"/>
+      <c r="I356" s="51" t="inlineStr"/>
+      <c r="J356" s="53" t="inlineStr">
+        <is>
+          <t>夫人这是何意味？</t>
         </is>
       </c>
       <c r="K356" s="50" t="inlineStr"/>
@@ -24193,7 +24179,7 @@
         </is>
       </c>
       <c r="C357" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D357" s="50" t="inlineStr">
         <is>
@@ -24202,24 +24188,20 @@
       </c>
       <c r="E357" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F357" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G357" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H357" s="55" t="inlineStr"/>
-      <c r="I357" s="55" t="inlineStr"/>
-      <c r="J357" s="56" t="inlineStr">
-        <is>
-          <t>王郎待我真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G357" s="51" t="inlineStr"/>
+      <c r="H357" s="51" t="inlineStr"/>
+      <c r="I357" s="51" t="inlineStr"/>
+      <c r="J357" s="53" t="inlineStr">
+        <is>
+          <t>前些天你来看病，你前脚刚走，王公子就来这问你的病情，很是担心你。</t>
         </is>
       </c>
       <c r="K357" s="50" t="inlineStr"/>
@@ -24236,7 +24218,7 @@
         </is>
       </c>
       <c r="C358" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D358" s="50" t="inlineStr">
         <is>
@@ -24245,20 +24227,24 @@
       </c>
       <c r="E358" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F358" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G358" s="55" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G358" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H358" s="55" t="inlineStr"/>
       <c r="I358" s="55" t="inlineStr"/>
       <c r="J358" s="56" t="inlineStr">
         <is>
-          <t>我有一计，可使你二人有情人终成眷属。</t>
+          <t>唉，我们这行当是做不长久的，只盼着有个如意的郎君，趁着年轻嫁入好人家。</t>
         </is>
       </c>
       <c r="K358" s="50" t="inlineStr"/>
@@ -24275,33 +24261,33 @@
         </is>
       </c>
       <c r="C359" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D359" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E359" s="56" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E359" s="53" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F359" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G359" s="55" t="inlineStr"/>
-      <c r="H359" s="55" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G359" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H359" s="55" t="inlineStr"/>
       <c r="I359" s="55" t="inlineStr"/>
       <c r="J359" s="56" t="inlineStr">
         <is>
-          <t>少夫人你有什么主意呀？快说快说！</t>
+          <t>王郎待我真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
         </is>
       </c>
       <c r="K359" s="50" t="inlineStr"/>
@@ -24318,7 +24304,7 @@
         </is>
       </c>
       <c r="C360" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D360" s="50" t="inlineStr">
         <is>
@@ -24336,15 +24322,11 @@
         </is>
       </c>
       <c r="G360" s="55" t="inlineStr"/>
-      <c r="H360" s="55" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H360" s="55" t="inlineStr"/>
       <c r="I360" s="55" t="inlineStr"/>
       <c r="J360" s="56" t="inlineStr">
         <is>
-          <t>明日你让金姨妈来一趟，如此这般….</t>
+          <t>我有一计，可使你二人有情人终成眷属。</t>
         </is>
       </c>
       <c r="K360" s="50" t="inlineStr"/>
@@ -24361,21 +24343,33 @@
         </is>
       </c>
       <c r="C361" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D361" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E361" s="53" t="inlineStr"/>
-      <c r="F361" s="52" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E361" s="56" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F361" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G361" s="55" t="inlineStr"/>
-      <c r="H361" s="55" t="inlineStr"/>
+      <c r="H361" s="55" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I361" s="55" t="inlineStr"/>
       <c r="J361" s="56" t="inlineStr">
         <is>
-          <t>吴芷兰和众人说出了自己的主意</t>
+          <t>少夫人你有什么主意呀？快说快说！</t>
         </is>
       </c>
       <c r="K361" s="50" t="inlineStr"/>
@@ -24392,7 +24386,7 @@
         </is>
       </c>
       <c r="C362" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D362" s="50" t="inlineStr">
         <is>
@@ -24401,20 +24395,24 @@
       </c>
       <c r="E362" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F362" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G362" s="55" t="inlineStr"/>
-      <c r="H362" s="55" t="inlineStr"/>
+      <c r="H362" s="55" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I362" s="55" t="inlineStr"/>
       <c r="J362" s="56" t="inlineStr">
         <is>
-          <t>先生若是能帮我们渡此难关，便是再造父母。</t>
+          <t>明日你让金姨妈来一趟，如此这般….</t>
         </is>
       </c>
       <c r="K362" s="50" t="inlineStr"/>
@@ -24431,7 +24429,7 @@
         </is>
       </c>
       <c r="C363" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D363" s="50" t="inlineStr">
         <is>
@@ -24442,14 +24440,10 @@
       <c r="F363" s="52" t="inlineStr"/>
       <c r="G363" s="55" t="inlineStr"/>
       <c r="H363" s="55" t="inlineStr"/>
-      <c r="I363" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/black.png</t>
-        </is>
-      </c>
+      <c r="I363" s="55" t="inlineStr"/>
       <c r="J363" s="56" t="inlineStr">
         <is>
-          <t>收入二两白银</t>
+          <t>吴芷兰和众人说出了自己的主意</t>
         </is>
       </c>
       <c r="K363" s="50" t="inlineStr"/>
@@ -24466,25 +24460,29 @@
         </is>
       </c>
       <c r="C364" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D364" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E364" s="55" t="inlineStr"/>
-      <c r="F364" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E364" s="53" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F364" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="G364" s="55" t="inlineStr"/>
       <c r="H364" s="55" t="inlineStr"/>
-      <c r="I364" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I364" s="55" t="inlineStr"/>
       <c r="J364" s="56" t="inlineStr">
         <is>
-          <t>次日</t>
+          <t>先生若是能帮我们渡此难关，便是再造父母。</t>
         </is>
       </c>
       <c r="K364" s="50" t="inlineStr"/>
@@ -24501,29 +24499,25 @@
         </is>
       </c>
       <c r="C365" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D365" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E365" s="56" t="inlineStr">
-        <is>
-          <t>金姨妈</t>
-        </is>
-      </c>
-      <c r="F365" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E365" s="53" t="inlineStr"/>
+      <c r="F365" s="52" t="inlineStr"/>
       <c r="G365" s="55" t="inlineStr"/>
       <c r="H365" s="55" t="inlineStr"/>
-      <c r="I365" s="55" t="inlineStr"/>
+      <c r="I365" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/black.png</t>
+        </is>
+      </c>
       <c r="J365" s="56" t="inlineStr">
         <is>
-          <t>李大夫，你叫我来是什么事儿啊？</t>
+          <t>收入一两白银</t>
         </is>
       </c>
       <c r="K365" s="50" t="inlineStr"/>
@@ -24540,29 +24534,25 @@
         </is>
       </c>
       <c r="C366" s="50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D366" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E366" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F366" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E366" s="55" t="inlineStr"/>
+      <c r="F366" s="51" t="inlineStr"/>
       <c r="G366" s="55" t="inlineStr"/>
       <c r="H366" s="55" t="inlineStr"/>
-      <c r="I366" s="55" t="inlineStr"/>
+      <c r="I366" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J366" s="56" t="inlineStr">
         <is>
-          <t>昨日经我仔细检查，谢姑娘的病乃是肺痨，此病只能缓解，不能根治，而且身边之人都有可能沾染。</t>
+          <t>次日</t>
         </is>
       </c>
       <c r="K366" s="50" t="inlineStr"/>
@@ -24579,7 +24569,7 @@
         </is>
       </c>
       <c r="C367" s="50" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D367" s="50" t="inlineStr">
         <is>
@@ -24601,7 +24591,7 @@
       <c r="I367" s="55" t="inlineStr"/>
       <c r="J367" s="56" t="inlineStr">
         <is>
-          <t>啊？这可如何是好？</t>
+          <t>李大夫，你叫我来是什么事儿啊？</t>
         </is>
       </c>
       <c r="K367" s="50" t="inlineStr"/>
@@ -24618,7 +24608,7 @@
         </is>
       </c>
       <c r="C368" s="50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D368" s="50" t="inlineStr">
         <is>
@@ -24640,7 +24630,7 @@
       <c r="I368" s="55" t="inlineStr"/>
       <c r="J368" s="56" t="inlineStr">
         <is>
-          <t>您还是早做打算，给女儿寻觅个好归宿吧。</t>
+          <t>昨日经我仔细检查，谢姑娘的病乃是肺痨，此病只能缓解，不能根治，而且身边之人都有可能沾染。</t>
         </is>
       </c>
       <c r="K368" s="50" t="inlineStr"/>
@@ -24657,7 +24647,7 @@
         </is>
       </c>
       <c r="C369" s="50" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D369" s="50" t="inlineStr">
         <is>
@@ -24679,7 +24669,7 @@
       <c r="I369" s="55" t="inlineStr"/>
       <c r="J369" s="56" t="inlineStr">
         <is>
-          <t>(若是这样，不如趁那小子不知情，便宜与了他去….)</t>
+          <t>啊？这可如何是好？</t>
         </is>
       </c>
       <c r="K369" s="50" t="inlineStr"/>
@@ -24687,16 +24677,16 @@
     <row r="370">
       <c r="A370" s="50" t="inlineStr">
         <is>
-          <t>024_03</t>
+          <t>024_02</t>
         </is>
       </c>
       <c r="B370" s="50" t="inlineStr">
         <is>
-          <t>024治疗失败</t>
+          <t>024治疗成功</t>
         </is>
       </c>
       <c r="C370" s="50" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D370" s="50" t="inlineStr">
         <is>
@@ -24713,16 +24703,12 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G370" s="51" t="inlineStr"/>
-      <c r="H370" s="52" t="inlineStr"/>
-      <c r="I370" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J370" s="50" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
+      <c r="G370" s="55" t="inlineStr"/>
+      <c r="H370" s="55" t="inlineStr"/>
+      <c r="I370" s="55" t="inlineStr"/>
+      <c r="J370" s="56" t="inlineStr">
+        <is>
+          <t>您还是早做打算，给女儿寻觅个好归宿吧。</t>
         </is>
       </c>
       <c r="K370" s="50" t="inlineStr"/>
@@ -24730,42 +24716,38 @@
     <row r="371">
       <c r="A371" s="50" t="inlineStr">
         <is>
-          <t>024_04</t>
+          <t>024_02</t>
         </is>
       </c>
       <c r="B371" s="50" t="inlineStr">
         <is>
-          <t>王百堂来访</t>
+          <t>024治疗成功</t>
         </is>
       </c>
       <c r="C371" s="50" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D371" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E371" s="50" t="inlineStr">
-        <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F371" s="51" t="inlineStr">
+      <c r="E371" s="56" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F371" s="52" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="G371" s="51" t="inlineStr"/>
-      <c r="H371" s="54" t="inlineStr"/>
-      <c r="I371" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J371" s="50" t="inlineStr">
-        <is>
-          <t>恩公！小生拜见恩公。</t>
+      <c r="G371" s="55" t="inlineStr"/>
+      <c r="H371" s="55" t="inlineStr"/>
+      <c r="I371" s="55" t="inlineStr"/>
+      <c r="J371" s="56" t="inlineStr">
+        <is>
+          <t>(若是这样，不如趁那小子不知情，便宜与了他去….)</t>
         </is>
       </c>
       <c r="K371" s="50" t="inlineStr"/>
@@ -24773,38 +24755,42 @@
     <row r="372" hidden="1">
       <c r="A372" s="50" t="inlineStr">
         <is>
-          <t>024_04</t>
+          <t>024_03</t>
         </is>
       </c>
       <c r="B372" s="50" t="inlineStr">
         <is>
-          <t>王百堂来访</t>
+          <t>024治疗失败</t>
         </is>
       </c>
       <c r="C372" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D372" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E372" s="50" t="inlineStr">
+      <c r="E372" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F372" s="54" t="inlineStr">
+      <c r="F372" s="52" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
       <c r="G372" s="51" t="inlineStr"/>
-      <c r="H372" s="54" t="inlineStr"/>
-      <c r="I372" s="51" t="inlineStr"/>
+      <c r="H372" s="52" t="inlineStr"/>
+      <c r="I372" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J372" s="50" t="inlineStr">
         <is>
-          <t>是你啊，快请起。你和谢姑娘怎么样了？</t>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K372" s="50" t="inlineStr"/>
@@ -24821,7 +24807,7 @@
         </is>
       </c>
       <c r="C373" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D373" s="50" t="inlineStr">
         <is>
@@ -24840,10 +24826,14 @@
       </c>
       <c r="G373" s="51" t="inlineStr"/>
       <c r="H373" s="54" t="inlineStr"/>
-      <c r="I373" s="51" t="inlineStr"/>
+      <c r="I373" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J373" s="50" t="inlineStr">
         <is>
-          <t>承蒙恩公出手相助，我二人已结为夫妻，在城外安顿下来，今日特来拜谢。</t>
+          <t>恩公！小生拜见恩公。</t>
         </is>
       </c>
       <c r="K373" s="50" t="inlineStr"/>
@@ -24860,7 +24850,7 @@
         </is>
       </c>
       <c r="C374" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D374" s="50" t="inlineStr">
         <is>
@@ -24869,20 +24859,20 @@
       </c>
       <c r="E374" s="50" t="inlineStr">
         <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F374" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F374" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G374" s="51" t="inlineStr"/>
-      <c r="H374" s="51" t="inlineStr"/>
+      <c r="H374" s="54" t="inlineStr"/>
       <c r="I374" s="51" t="inlineStr"/>
       <c r="J374" s="50" t="inlineStr">
         <is>
-          <t>听闻恩公酷好青囊之书，先父也是一生行医，家中有不少先父留下的笔记心得，今日便赠予恩公。</t>
+          <t>是你啊，快请起。你和谢姑娘怎么样了？</t>
         </is>
       </c>
       <c r="K374" s="50" t="inlineStr"/>
@@ -24899,7 +24889,7 @@
         </is>
       </c>
       <c r="C375" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D375" s="50" t="inlineStr">
         <is>
@@ -24908,37 +24898,37 @@
       </c>
       <c r="E375" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F375" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F375" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G375" s="51" t="inlineStr"/>
-      <c r="H375" s="51" t="inlineStr"/>
+      <c r="H375" s="54" t="inlineStr"/>
       <c r="I375" s="51" t="inlineStr"/>
       <c r="J375" s="50" t="inlineStr">
         <is>
-          <t>哎呀，这可太好了，真是求之不得啊。</t>
+          <t>承蒙恩公出手相助，我二人已结为夫妻，在城外安顿下来，今日特来拜谢。</t>
         </is>
       </c>
       <c r="K375" s="50" t="inlineStr"/>
     </row>
-    <row r="376" ht="34.5" customHeight="1">
+    <row r="376">
       <c r="A376" s="50" t="inlineStr">
         <is>
-          <t>025_01</t>
+          <t>024_04</t>
         </is>
       </c>
       <c r="B376" s="50" t="inlineStr">
         <is>
-          <t>和尚肾精不足</t>
+          <t>王百堂来访</t>
         </is>
       </c>
       <c r="C376" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D376" s="50" t="inlineStr">
         <is>
@@ -24947,7 +24937,7 @@
       </c>
       <c r="E376" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F376" s="51" t="inlineStr">
@@ -24955,20 +24945,12 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G376" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H376" s="52" t="inlineStr"/>
-      <c r="I376" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J376" s="67" t="inlineStr">
-        <is>
-          <t>阿弥陀佛，贫僧法号性空，《中论》曰："众因缘生法，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
+      <c r="G376" s="51" t="inlineStr"/>
+      <c r="H376" s="51" t="inlineStr"/>
+      <c r="I376" s="51" t="inlineStr"/>
+      <c r="J376" s="50" t="inlineStr">
+        <is>
+          <t>听闻恩公酷好青囊之书，先父也是一生行医，家中有不少先父留下的笔记心得，今日便赠予恩公。</t>
         </is>
       </c>
       <c r="K376" s="50" t="inlineStr"/>
@@ -24976,61 +24958,61 @@
     <row r="377" hidden="1">
       <c r="A377" s="50" t="inlineStr">
         <is>
+          <t>024_04</t>
+        </is>
+      </c>
+      <c r="B377" s="50" t="inlineStr">
+        <is>
+          <t>王百堂来访</t>
+        </is>
+      </c>
+      <c r="C377" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D377" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E377" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F377" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G377" s="51" t="inlineStr"/>
+      <c r="H377" s="51" t="inlineStr"/>
+      <c r="I377" s="51" t="inlineStr"/>
+      <c r="J377" s="50" t="inlineStr">
+        <is>
+          <t>哎呀，这可太好了，真是求之不得啊。</t>
+        </is>
+      </c>
+      <c r="K377" s="50" t="inlineStr"/>
+    </row>
+    <row r="378" hidden="1" ht="34.5" customHeight="1">
+      <c r="A378" s="50" t="inlineStr">
+        <is>
           <t>025_01</t>
         </is>
       </c>
-      <c r="B377" s="50" t="inlineStr">
+      <c r="B378" s="50" t="inlineStr">
         <is>
           <t>和尚肾精不足</t>
         </is>
       </c>
-      <c r="C377" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D377" s="50" t="inlineStr">
+      <c r="C378" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D378" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E377" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F377" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G377" s="51" t="inlineStr"/>
-      <c r="H377" s="52" t="inlineStr"/>
-      <c r="I377" s="51" t="inlineStr"/>
-      <c r="J377" s="67" t="inlineStr">
-        <is>
-          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
-        </is>
-      </c>
-      <c r="K377" s="50" t="inlineStr"/>
-    </row>
-    <row r="378" hidden="1">
-      <c r="A378" s="50" t="inlineStr">
-        <is>
-          <t>025_01</t>
-        </is>
-      </c>
-      <c r="B378" s="50" t="inlineStr">
-        <is>
-          <t>和尚肾精不足</t>
-        </is>
-      </c>
-      <c r="C378" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D378" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
       <c r="E378" s="50" t="inlineStr">
         <is>
           <t>性空</t>
@@ -25047,10 +25029,14 @@
         </is>
       </c>
       <c r="H378" s="52" t="inlineStr"/>
-      <c r="I378" s="51" t="inlineStr"/>
-      <c r="J378" s="50" t="inlineStr">
-        <is>
-          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
+      <c r="I378" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J378" s="67" t="inlineStr">
+        <is>
+          <t>阿弥陀佛，贫僧法号性空，《中论》曰："众因缘生法，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
         </is>
       </c>
       <c r="K378" s="50" t="inlineStr"/>
@@ -25058,16 +25044,16 @@
     <row r="379">
       <c r="A379" s="50" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>025_01</t>
         </is>
       </c>
       <c r="B379" s="50" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>和尚肾精不足</t>
         </is>
       </c>
       <c r="C379" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D379" s="50" t="inlineStr">
         <is>
@@ -25086,14 +25072,10 @@
       </c>
       <c r="G379" s="51" t="inlineStr"/>
       <c r="H379" s="52" t="inlineStr"/>
-      <c r="I379" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I379" s="51" t="inlineStr"/>
       <c r="J379" s="67" t="inlineStr">
         <is>
-          <t>师父所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
+          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
         </is>
       </c>
       <c r="K379" s="50" t="inlineStr"/>
@@ -25101,16 +25083,16 @@
     <row r="380" hidden="1">
       <c r="A380" s="50" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>025_01</t>
         </is>
       </c>
       <c r="B380" s="50" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>和尚肾精不足</t>
         </is>
       </c>
       <c r="C380" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D380" s="50" t="inlineStr">
         <is>
@@ -25129,14 +25111,14 @@
       </c>
       <c r="G380" s="51" t="inlineStr">
         <is>
-          <t>after</t>
+          <t>sick</t>
         </is>
       </c>
       <c r="H380" s="52" t="inlineStr"/>
       <c r="I380" s="51" t="inlineStr"/>
       <c r="J380" s="50" t="inlineStr">
         <is>
-          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
+          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
         </is>
       </c>
       <c r="K380" s="50" t="inlineStr"/>
@@ -25153,7 +25135,7 @@
         </is>
       </c>
       <c r="C381" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D381" s="50" t="inlineStr">
         <is>
@@ -25172,10 +25154,14 @@
       </c>
       <c r="G381" s="51" t="inlineStr"/>
       <c r="H381" s="52" t="inlineStr"/>
-      <c r="I381" s="51" t="inlineStr"/>
-      <c r="J381" s="50" t="inlineStr">
-        <is>
-          <t>…</t>
+      <c r="I381" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J381" s="67" t="inlineStr">
+        <is>
+          <t>师父所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
         </is>
       </c>
       <c r="K381" s="50" t="inlineStr"/>
@@ -25192,7 +25178,7 @@
         </is>
       </c>
       <c r="C382" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D382" s="50" t="inlineStr">
         <is>
@@ -25214,11 +25200,11 @@
           <t>after</t>
         </is>
       </c>
-      <c r="H382" s="51" t="inlineStr"/>
+      <c r="H382" s="52" t="inlineStr"/>
       <c r="I382" s="51" t="inlineStr"/>
       <c r="J382" s="50" t="inlineStr">
         <is>
-          <t>一定是我晚上念经太过用功，着凉了。</t>
+          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
         </is>
       </c>
       <c r="K382" s="50" t="inlineStr"/>
@@ -25235,7 +25221,7 @@
         </is>
       </c>
       <c r="C383" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D383" s="50" t="inlineStr">
         <is>
@@ -25253,11 +25239,11 @@
         </is>
       </c>
       <c r="G383" s="51" t="inlineStr"/>
-      <c r="H383" s="51" t="inlineStr"/>
+      <c r="H383" s="52" t="inlineStr"/>
       <c r="I383" s="51" t="inlineStr"/>
       <c r="J383" s="50" t="inlineStr">
         <is>
-          <t>是是是，师父说得对，也不是没有这个可能。</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K383" s="50" t="inlineStr"/>
@@ -25274,7 +25260,7 @@
         </is>
       </c>
       <c r="C384" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D384" s="50" t="inlineStr">
         <is>
@@ -25296,15 +25282,11 @@
           <t>after</t>
         </is>
       </c>
-      <c r="H384" s="55" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I384" s="55" t="inlineStr"/>
-      <c r="J384" s="73" t="inlineStr">
-        <is>
-          <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
+      <c r="H384" s="51" t="inlineStr"/>
+      <c r="I384" s="51" t="inlineStr"/>
+      <c r="J384" s="50" t="inlineStr">
+        <is>
+          <t>一定是我晚上念经太过用功，着凉了。</t>
         </is>
       </c>
       <c r="K384" s="50" t="inlineStr"/>
@@ -25321,21 +25303,29 @@
         </is>
       </c>
       <c r="C385" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D385" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E385" s="50" t="inlineStr"/>
-      <c r="F385" s="51" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E385" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F385" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G385" s="51" t="inlineStr"/>
-      <c r="H385" s="55" t="inlineStr"/>
-      <c r="I385" s="55" t="inlineStr"/>
-      <c r="J385" s="56" t="inlineStr">
-        <is>
-          <t>金钱+2两</t>
+      <c r="H385" s="51" t="inlineStr"/>
+      <c r="I385" s="51" t="inlineStr"/>
+      <c r="J385" s="50" t="inlineStr">
+        <is>
+          <t>是是是，师父说得对，也不是没有这个可能。</t>
         </is>
       </c>
       <c r="K385" s="50" t="inlineStr"/>
@@ -25352,29 +25342,37 @@
         </is>
       </c>
       <c r="C386" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D386" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E386" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F386" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G386" s="55" t="inlineStr"/>
-      <c r="H386" s="55" t="inlineStr"/>
+      <c r="E386" s="50" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F386" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G386" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H386" s="55" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I386" s="55" t="inlineStr"/>
-      <c r="J386" s="55" t="inlineStr">
-        <is>
-          <t>哇，这就是传说中的花和尚吗？</t>
+      <c r="J386" s="68" t="inlineStr">
+        <is>
+          <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
         </is>
       </c>
       <c r="K386" s="50" t="inlineStr"/>
@@ -25391,29 +25389,21 @@
         </is>
       </c>
       <c r="C387" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D387" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E387" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F387" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G387" s="55" t="inlineStr"/>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E387" s="50" t="inlineStr"/>
+      <c r="F387" s="51" t="inlineStr"/>
+      <c r="G387" s="51" t="inlineStr"/>
       <c r="H387" s="55" t="inlineStr"/>
       <c r="I387" s="55" t="inlineStr"/>
-      <c r="J387" s="55" t="inlineStr">
-        <is>
-          <t>…</t>
+      <c r="J387" s="56" t="inlineStr">
+        <is>
+          <t>收入二两白银</t>
         </is>
       </c>
       <c r="K387" s="50" t="inlineStr"/>
@@ -25430,7 +25420,7 @@
         </is>
       </c>
       <c r="C388" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D388" s="50" t="inlineStr">
         <is>
@@ -25439,12 +25429,12 @@
       </c>
       <c r="E388" s="55" t="inlineStr">
         <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F388" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F388" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G388" s="55" t="inlineStr"/>
@@ -25452,7 +25442,7 @@
       <c r="I388" s="55" t="inlineStr"/>
       <c r="J388" s="55" t="inlineStr">
         <is>
-          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+          <t>哇，这就是传说中的花和尚吗？</t>
         </is>
       </c>
       <c r="K388" s="50" t="inlineStr"/>
@@ -25469,21 +25459,21 @@
         </is>
       </c>
       <c r="C389" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D389" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E389" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E389" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F389" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G389" s="55" t="inlineStr"/>
@@ -25491,7 +25481,7 @@
       <c r="I389" s="55" t="inlineStr"/>
       <c r="J389" s="55" t="inlineStr">
         <is>
-          <t>找打！</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K389" s="50" t="inlineStr"/>
@@ -25508,7 +25498,7 @@
         </is>
       </c>
       <c r="C390" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D390" s="50" t="inlineStr">
         <is>
@@ -25530,7 +25520,7 @@
       <c r="I390" s="55" t="inlineStr"/>
       <c r="J390" s="55" t="inlineStr">
         <is>
-          <t>哎哟！</t>
+          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
         </is>
       </c>
       <c r="K390" s="50" t="inlineStr"/>
@@ -25538,42 +25528,38 @@
     <row r="391">
       <c r="A391" s="50" t="inlineStr">
         <is>
-          <t>025_03</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B391" s="50" t="inlineStr">
         <is>
-          <t>025治疗失败</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C391" s="50" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D391" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E391" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E391" s="55" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F391" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G391" s="51" t="inlineStr"/>
-      <c r="H391" s="52" t="inlineStr"/>
-      <c r="I391" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J391" s="50" t="inlineStr">
-        <is>
-          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G391" s="55" t="inlineStr"/>
+      <c r="H391" s="55" t="inlineStr"/>
+      <c r="I391" s="55" t="inlineStr"/>
+      <c r="J391" s="55" t="inlineStr">
+        <is>
+          <t>找打！</t>
         </is>
       </c>
       <c r="K391" s="50" t="inlineStr"/>
@@ -25581,42 +25567,38 @@
     <row r="392">
       <c r="A392" s="50" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B392" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C392" s="50" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D392" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E392" s="53" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F392" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G392" s="51" t="inlineStr"/>
-      <c r="H392" s="52" t="inlineStr"/>
-      <c r="I392" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J392" s="53" t="inlineStr">
-        <is>
-          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
+      <c r="E392" s="55" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F392" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G392" s="55" t="inlineStr"/>
+      <c r="H392" s="55" t="inlineStr"/>
+      <c r="I392" s="55" t="inlineStr"/>
+      <c r="J392" s="55" t="inlineStr">
+        <is>
+          <t>哎哟！</t>
         </is>
       </c>
       <c r="K392" s="50" t="inlineStr"/>
@@ -25624,23 +25606,23 @@
     <row r="393" hidden="1">
       <c r="A393" s="50" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_03</t>
         </is>
       </c>
       <c r="B393" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗失败</t>
         </is>
       </c>
       <c r="C393" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D393" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E393" s="53" t="inlineStr">
+      <c r="E393" s="50" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
@@ -25652,10 +25634,14 @@
       </c>
       <c r="G393" s="51" t="inlineStr"/>
       <c r="H393" s="52" t="inlineStr"/>
-      <c r="I393" s="51" t="inlineStr"/>
-      <c r="J393" s="53" t="inlineStr">
-        <is>
-          <t>芷兰！！！</t>
+      <c r="I393" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J393" s="50" t="inlineStr">
+        <is>
+          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
         </is>
       </c>
       <c r="K393" s="50" t="inlineStr"/>
@@ -25672,7 +25658,7 @@
         </is>
       </c>
       <c r="C394" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D394" s="50" t="inlineStr">
         <is>
@@ -25681,7 +25667,7 @@
       </c>
       <c r="E394" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F394" s="52" t="inlineStr">
@@ -25689,20 +25675,16 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G394" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+      <c r="G394" s="51" t="inlineStr"/>
       <c r="H394" s="52" t="inlineStr"/>
       <c r="I394" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/026/026.png</t>
+          <t>current_scene</t>
         </is>
       </c>
       <c r="J394" s="53" t="inlineStr">
         <is>
-          <t>…...</t>
+          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
         </is>
       </c>
       <c r="K394" s="50" t="inlineStr"/>
@@ -25719,7 +25701,7 @@
         </is>
       </c>
       <c r="C395" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D395" s="50" t="inlineStr">
         <is>
@@ -25728,24 +25710,20 @@
       </c>
       <c r="E395" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F395" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G395" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G395" s="51" t="inlineStr"/>
       <c r="H395" s="52" t="inlineStr"/>
       <c r="I395" s="51" t="inlineStr"/>
       <c r="J395" s="53" t="inlineStr">
         <is>
-          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+          <t>芷兰！！！</t>
         </is>
       </c>
       <c r="K395" s="50" t="inlineStr"/>
@@ -25762,7 +25740,7 @@
         </is>
       </c>
       <c r="C396" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D396" s="50" t="inlineStr">
         <is>
@@ -25771,20 +25749,28 @@
       </c>
       <c r="E396" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F396" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G396" s="51" t="inlineStr"/>
-      <c r="H396" s="51" t="inlineStr"/>
-      <c r="I396" s="51" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G396" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H396" s="52" t="inlineStr"/>
+      <c r="I396" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
       <c r="J396" s="53" t="inlineStr">
         <is>
-          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
+          <t>…...</t>
         </is>
       </c>
       <c r="K396" s="50" t="inlineStr"/>
@@ -25792,42 +25778,42 @@
     <row r="397">
       <c r="A397" s="50" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B397" s="50" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C397" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D397" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E397" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E397" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F397" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G397" s="51" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G397" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H397" s="52" t="inlineStr"/>
-      <c r="I397" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J397" s="67" t="inlineStr">
-        <is>
-          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
+      <c r="I397" s="51" t="inlineStr"/>
+      <c r="J397" s="53" t="inlineStr">
+        <is>
+          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
         </is>
       </c>
       <c r="K397" s="50" t="inlineStr"/>
@@ -25835,38 +25821,38 @@
     <row r="398" hidden="1">
       <c r="A398" s="50" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B398" s="50" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C398" s="50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D398" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E398" s="50" t="inlineStr">
+      <c r="E398" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F398" s="51" t="inlineStr">
+      <c r="F398" s="52" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
       <c r="G398" s="51" t="inlineStr"/>
-      <c r="H398" s="52" t="inlineStr"/>
+      <c r="H398" s="51" t="inlineStr"/>
       <c r="I398" s="51" t="inlineStr"/>
-      <c r="J398" s="50" t="inlineStr">
-        <is>
-          <t>芷兰…我们有孩子了…</t>
+      <c r="J398" s="53" t="inlineStr">
+        <is>
+          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
         </is>
       </c>
       <c r="K398" s="50" t="inlineStr"/>
@@ -25883,7 +25869,7 @@
         </is>
       </c>
       <c r="C399" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D399" s="50" t="inlineStr">
         <is>
@@ -25892,20 +25878,24 @@
       </c>
       <c r="E399" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F399" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G399" s="51" t="inlineStr"/>
       <c r="H399" s="52" t="inlineStr"/>
-      <c r="I399" s="51" t="inlineStr"/>
-      <c r="J399" s="50" t="inlineStr">
-        <is>
-          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+      <c r="I399" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J399" s="67" t="inlineStr">
+        <is>
+          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
         </is>
       </c>
       <c r="K399" s="50" t="inlineStr"/>
@@ -25922,7 +25912,7 @@
         </is>
       </c>
       <c r="C400" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D400" s="50" t="inlineStr">
         <is>
@@ -25940,11 +25930,11 @@
         </is>
       </c>
       <c r="G400" s="51" t="inlineStr"/>
-      <c r="H400" s="51" t="inlineStr"/>
+      <c r="H400" s="52" t="inlineStr"/>
       <c r="I400" s="51" t="inlineStr"/>
-      <c r="J400" s="67" t="inlineStr">
-        <is>
-          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+      <c r="J400" s="50" t="inlineStr">
+        <is>
+          <t>芷兰…我们有孩子了…</t>
         </is>
       </c>
       <c r="K400" s="50" t="inlineStr"/>
@@ -25961,7 +25951,7 @@
         </is>
       </c>
       <c r="C401" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D401" s="50" t="inlineStr">
         <is>
@@ -25970,20 +25960,20 @@
       </c>
       <c r="E401" s="50" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F401" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G401" s="51" t="inlineStr"/>
-      <c r="H401" s="51" t="inlineStr"/>
+      <c r="H401" s="52" t="inlineStr"/>
       <c r="I401" s="51" t="inlineStr"/>
       <c r="J401" s="50" t="inlineStr">
         <is>
-          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
+          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
         </is>
       </c>
       <c r="K401" s="50" t="inlineStr"/>
@@ -25991,16 +25981,16 @@
     <row r="402">
       <c r="A402" s="50" t="inlineStr">
         <is>
-          <t>026_03</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B402" s="50" t="inlineStr">
         <is>
-          <t>026治疗失败</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C402" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D402" s="50" t="inlineStr">
         <is>
@@ -26012,21 +26002,17 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F402" s="52" t="inlineStr">
+      <c r="F402" s="51" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
       <c r="G402" s="51" t="inlineStr"/>
-      <c r="H402" s="52" t="inlineStr"/>
-      <c r="I402" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J402" s="50" t="inlineStr">
-        <is>
-          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
+      <c r="H402" s="51" t="inlineStr"/>
+      <c r="I402" s="51" t="inlineStr"/>
+      <c r="J402" s="67" t="inlineStr">
+        <is>
+          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
         </is>
       </c>
       <c r="K402" s="50" t="inlineStr"/>
@@ -26034,85 +26020,81 @@
     <row r="403">
       <c r="A403" s="50" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B403" s="50" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C403" s="50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D403" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E403" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E403" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F403" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G403" s="51" t="inlineStr"/>
-      <c r="H403" s="54" t="inlineStr"/>
-      <c r="I403" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/004/004.png</t>
-        </is>
-      </c>
-      <c r="J403" s="53" t="inlineStr">
-        <is>
-          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
-        </is>
-      </c>
-      <c r="K403" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
-        </is>
-      </c>
+      <c r="H403" s="51" t="inlineStr"/>
+      <c r="I403" s="51" t="inlineStr"/>
+      <c r="J403" s="50" t="inlineStr">
+        <is>
+          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
+        </is>
+      </c>
+      <c r="K403" s="50" t="inlineStr"/>
     </row>
     <row r="404" hidden="1">
       <c r="A404" s="50" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_03</t>
         </is>
       </c>
       <c r="B404" s="50" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗失败</t>
         </is>
       </c>
       <c r="C404" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D404" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E404" s="53" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F404" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
+      <c r="E404" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F404" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G404" s="51" t="inlineStr"/>
-      <c r="H404" s="54" t="inlineStr"/>
-      <c r="I404" s="51" t="inlineStr"/>
-      <c r="J404" s="53" t="inlineStr">
-        <is>
-          <t>太好了，咱们快出发吧。</t>
+      <c r="H404" s="52" t="inlineStr"/>
+      <c r="I404" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J404" s="50" t="inlineStr">
+        <is>
+          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
         </is>
       </c>
       <c r="K404" s="50" t="inlineStr"/>
@@ -26129,7 +26111,7 @@
         </is>
       </c>
       <c r="C405" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D405" s="50" t="inlineStr">
         <is>
@@ -26138,23 +26120,31 @@
       </c>
       <c r="E405" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F405" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F405" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G405" s="51" t="inlineStr"/>
       <c r="H405" s="54" t="inlineStr"/>
-      <c r="I405" s="51" t="inlineStr"/>
+      <c r="I405" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/004/004.png</t>
+        </is>
+      </c>
       <c r="J405" s="53" t="inlineStr">
         <is>
-          <t>走。</t>
-        </is>
-      </c>
-      <c r="K405" s="50" t="inlineStr"/>
+          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
+        </is>
+      </c>
+      <c r="K405" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="50" t="inlineStr">
@@ -26168,33 +26158,29 @@
         </is>
       </c>
       <c r="C406" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D406" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E406" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F406" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E406" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F406" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G406" s="51" t="inlineStr"/>
-      <c r="H406" s="52" t="inlineStr"/>
-      <c r="I406" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_01.png</t>
-        </is>
-      </c>
+      <c r="H406" s="54" t="inlineStr"/>
+      <c r="I406" s="51" t="inlineStr"/>
       <c r="J406" s="53" t="inlineStr">
         <is>
-          <t>哇，好多人啊！好热闹啊！</t>
+          <t>太好了，咱们快出发吧。</t>
         </is>
       </c>
       <c r="K406" s="50" t="inlineStr"/>
@@ -26211,7 +26197,7 @@
         </is>
       </c>
       <c r="C407" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D407" s="50" t="inlineStr">
         <is>
@@ -26220,7 +26206,7 @@
       </c>
       <c r="E407" s="53" t="inlineStr">
         <is>
-          <t>陈皮</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F407" s="54" t="inlineStr">
@@ -26229,15 +26215,11 @@
         </is>
       </c>
       <c r="G407" s="51" t="inlineStr"/>
-      <c r="H407" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H407" s="54" t="inlineStr"/>
       <c r="I407" s="51" t="inlineStr"/>
       <c r="J407" s="53" t="inlineStr">
         <is>
-          <t>看你那没见过世面的样子。</t>
+          <t>走。</t>
         </is>
       </c>
       <c r="K407" s="50" t="inlineStr"/>
@@ -26254,7 +26236,7 @@
         </is>
       </c>
       <c r="C408" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D408" s="50" t="inlineStr">
         <is>
@@ -26271,19 +26253,19 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="G408" s="55" t="inlineStr"/>
-      <c r="H408" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I408" s="55" t="inlineStr"/>
-      <c r="J408" s="56" t="inlineStr">
-        <is>
-          <t>找打，你别跑！</t>
-        </is>
-      </c>
-      <c r="K408" s="55" t="inlineStr"/>
+      <c r="G408" s="51" t="inlineStr"/>
+      <c r="H408" s="52" t="inlineStr"/>
+      <c r="I408" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_01.png</t>
+        </is>
+      </c>
+      <c r="J408" s="53" t="inlineStr">
+        <is>
+          <t>哇，好多人啊！好热闹啊！</t>
+        </is>
+      </c>
+      <c r="K408" s="50" t="inlineStr"/>
     </row>
     <row r="409" hidden="1">
       <c r="A409" s="50" t="inlineStr">
@@ -26297,7 +26279,7 @@
         </is>
       </c>
       <c r="C409" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D409" s="50" t="inlineStr">
         <is>
@@ -26306,23 +26288,27 @@
       </c>
       <c r="E409" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F409" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G409" s="55" t="inlineStr"/>
-      <c r="H409" s="55" t="inlineStr"/>
-      <c r="I409" s="55" t="inlineStr"/>
-      <c r="J409" s="56" t="inlineStr">
-        <is>
-          <t>那边好像有唱戏的，咱们去那边看看。</t>
-        </is>
-      </c>
-      <c r="K409" s="55" t="inlineStr"/>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F409" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G409" s="51" t="inlineStr"/>
+      <c r="H409" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I409" s="51" t="inlineStr"/>
+      <c r="J409" s="53" t="inlineStr">
+        <is>
+          <t>看你那没见过世面的样子。</t>
+        </is>
+      </c>
+      <c r="K409" s="50" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="50" t="inlineStr">
@@ -26336,7 +26322,7 @@
         </is>
       </c>
       <c r="C410" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D410" s="50" t="inlineStr">
         <is>
@@ -26350,7 +26336,7 @@
       </c>
       <c r="F410" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G410" s="55" t="inlineStr"/>
@@ -26359,14 +26345,10 @@
           <t>hide</t>
         </is>
       </c>
-      <c r="I410" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_02.png</t>
-        </is>
-      </c>
+      <c r="I410" s="55" t="inlineStr"/>
       <c r="J410" s="56" t="inlineStr">
         <is>
-          <t>夫人，那边有座桥，咱们去走百病！</t>
+          <t>找打，你别跑！</t>
         </is>
       </c>
       <c r="K410" s="55" t="inlineStr"/>
@@ -26383,7 +26365,7 @@
         </is>
       </c>
       <c r="C411" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D411" s="50" t="inlineStr">
         <is>
@@ -26392,7 +26374,7 @@
       </c>
       <c r="E411" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F411" s="52" t="inlineStr">
@@ -26401,15 +26383,11 @@
         </is>
       </c>
       <c r="G411" s="55" t="inlineStr"/>
-      <c r="H411" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H411" s="55" t="inlineStr"/>
       <c r="I411" s="55" t="inlineStr"/>
       <c r="J411" s="56" t="inlineStr">
         <is>
-          <t>走，今夜走三桥，一年无灾病。</t>
+          <t>那边好像有唱戏的，咱们去那边看看。</t>
         </is>
       </c>
       <c r="K411" s="55" t="inlineStr"/>
@@ -26426,29 +26404,37 @@
         </is>
       </c>
       <c r="C412" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D412" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E412" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E412" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F412" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G412" s="55" t="inlineStr"/>
-      <c r="H412" s="55" t="inlineStr"/>
-      <c r="I412" s="55" t="inlineStr"/>
+      <c r="H412" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
+      <c r="I412" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_02.png</t>
+        </is>
+      </c>
       <c r="J412" s="56" t="inlineStr">
         <is>
-          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
+          <t>夫人，那边有座桥，咱们去走百病！</t>
         </is>
       </c>
       <c r="K412" s="55" t="inlineStr"/>
@@ -26465,7 +26451,7 @@
         </is>
       </c>
       <c r="C413" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D413" s="50" t="inlineStr">
         <is>
@@ -26474,20 +26460,24 @@
       </c>
       <c r="E413" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F413" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F413" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G413" s="55" t="inlineStr"/>
-      <c r="H413" s="55" t="inlineStr"/>
+      <c r="H413" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I413" s="55" t="inlineStr"/>
       <c r="J413" s="56" t="inlineStr">
         <is>
-          <t>哎哟，爹，您就别操心了。</t>
+          <t>走，今夜走三桥，一年无灾病。</t>
         </is>
       </c>
       <c r="K413" s="55" t="inlineStr"/>
@@ -26504,7 +26494,7 @@
         </is>
       </c>
       <c r="C414" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D414" s="50" t="inlineStr">
         <is>
@@ -26526,7 +26516,7 @@
       <c r="I414" s="55" t="inlineStr"/>
       <c r="J414" s="56" t="inlineStr">
         <is>
-          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
+          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
         </is>
       </c>
       <c r="K414" s="55" t="inlineStr"/>
@@ -26543,7 +26533,7 @@
         </is>
       </c>
       <c r="C415" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D415" s="50" t="inlineStr">
         <is>
@@ -26565,7 +26555,7 @@
       <c r="I415" s="55" t="inlineStr"/>
       <c r="J415" s="56" t="inlineStr">
         <is>
-          <t>别说了爹，咱们看戏去吧。</t>
+          <t>哎哟，爹，您就别操心了。</t>
         </is>
       </c>
       <c r="K415" s="55" t="inlineStr"/>
@@ -26582,7 +26572,7 @@
         </is>
       </c>
       <c r="C416" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D416" s="50" t="inlineStr">
         <is>
@@ -26591,20 +26581,20 @@
       </c>
       <c r="E416" s="53" t="inlineStr">
         <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F416" s="54" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F416" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G416" s="55" t="inlineStr"/>
       <c r="H416" s="55" t="inlineStr"/>
-      <c r="I416" s="51" t="inlineStr"/>
+      <c r="I416" s="55" t="inlineStr"/>
       <c r="J416" s="56" t="inlineStr">
         <is>
-          <t>老爷，那边儿在唱紫钗记呢。</t>
+          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
         </is>
       </c>
       <c r="K416" s="55" t="inlineStr"/>
@@ -26621,25 +26611,29 @@
         </is>
       </c>
       <c r="C417" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D417" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E417" s="55" t="inlineStr"/>
-      <c r="F417" s="50" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E417" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F417" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="G417" s="55" t="inlineStr"/>
       <c r="H417" s="55" t="inlineStr"/>
-      <c r="I417" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_03.png</t>
-        </is>
-      </c>
+      <c r="I417" s="55" t="inlineStr"/>
       <c r="J417" s="56" t="inlineStr">
         <is>
-          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
+          <t>别说了爹，咱们看戏去吧。</t>
         </is>
       </c>
       <c r="K417" s="55" t="inlineStr"/>
@@ -26656,7 +26650,7 @@
         </is>
       </c>
       <c r="C418" s="50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D418" s="50" t="inlineStr">
         <is>
@@ -26665,20 +26659,20 @@
       </c>
       <c r="E418" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F418" s="52" t="inlineStr">
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F418" s="54" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
       <c r="G418" s="55" t="inlineStr"/>
       <c r="H418" s="55" t="inlineStr"/>
-      <c r="I418" s="55" t="inlineStr"/>
-      <c r="J418" s="55" t="inlineStr">
-        <is>
-          <t>相公，咱们去猜灯谜吧！</t>
+      <c r="I418" s="51" t="inlineStr"/>
+      <c r="J418" s="56" t="inlineStr">
+        <is>
+          <t>老爷，那边儿在唱紫钗记呢。</t>
         </is>
       </c>
       <c r="K418" s="55" t="inlineStr"/>
@@ -26695,29 +26689,25 @@
         </is>
       </c>
       <c r="C419" s="50" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D419" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E419" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F419" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E419" s="55" t="inlineStr"/>
+      <c r="F419" s="50" t="inlineStr"/>
       <c r="G419" s="55" t="inlineStr"/>
       <c r="H419" s="55" t="inlineStr"/>
-      <c r="I419" s="55" t="inlineStr"/>
-      <c r="J419" s="55" t="inlineStr">
-        <is>
-          <t>走！</t>
+      <c r="I419" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_03.png</t>
+        </is>
+      </c>
+      <c r="J419" s="56" t="inlineStr">
+        <is>
+          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
         </is>
       </c>
       <c r="K419" s="55" t="inlineStr"/>
@@ -26734,7 +26724,7 @@
         </is>
       </c>
       <c r="C420" s="50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D420" s="50" t="inlineStr">
         <is>
@@ -26743,24 +26733,20 @@
       </c>
       <c r="E420" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F420" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F420" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G420" s="55" t="inlineStr"/>
       <c r="H420" s="55" t="inlineStr"/>
-      <c r="I420" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_04.png</t>
-        </is>
-      </c>
-      <c r="J420" s="68" t="inlineStr">
-        <is>
-          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
+      <c r="I420" s="55" t="inlineStr"/>
+      <c r="J420" s="55" t="inlineStr">
+        <is>
+          <t>相公，咱们去猜灯谜吧！</t>
         </is>
       </c>
       <c r="K420" s="55" t="inlineStr"/>
@@ -26777,7 +26763,7 @@
         </is>
       </c>
       <c r="C421" s="50" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D421" s="50" t="inlineStr">
         <is>
@@ -26786,12 +26772,12 @@
       </c>
       <c r="E421" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F421" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F421" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G421" s="55" t="inlineStr"/>
@@ -26799,7 +26785,7 @@
       <c r="I421" s="55" t="inlineStr"/>
       <c r="J421" s="55" t="inlineStr">
         <is>
-          <t>我知道，这是个"府"字。</t>
+          <t>走！</t>
         </is>
       </c>
       <c r="K421" s="55" t="inlineStr"/>
@@ -26816,7 +26802,7 @@
         </is>
       </c>
       <c r="C422" s="50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D422" s="50" t="inlineStr">
         <is>
@@ -26835,10 +26821,14 @@
       </c>
       <c r="G422" s="55" t="inlineStr"/>
       <c r="H422" s="55" t="inlineStr"/>
-      <c r="I422" s="55" t="inlineStr"/>
-      <c r="J422" s="55" t="inlineStr">
-        <is>
-          <t>还是娘子聪慧啊，哈哈。</t>
+      <c r="I422" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_04.png</t>
+        </is>
+      </c>
+      <c r="J422" s="68" t="inlineStr">
+        <is>
+          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
         </is>
       </c>
       <c r="K422" s="55" t="inlineStr"/>
@@ -26855,7 +26845,7 @@
         </is>
       </c>
       <c r="C423" s="50" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D423" s="50" t="inlineStr">
         <is>
@@ -26877,7 +26867,7 @@
       <c r="I423" s="55" t="inlineStr"/>
       <c r="J423" s="55" t="inlineStr">
         <is>
-          <t>你看这个，"大雪压青松"，打一味药材。</t>
+          <t>我知道，这是个"府"字。</t>
         </is>
       </c>
       <c r="K423" s="55" t="inlineStr"/>
@@ -26894,7 +26884,7 @@
         </is>
       </c>
       <c r="C424" s="50" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D424" s="50" t="inlineStr">
         <is>
@@ -26914,9 +26904,9 @@
       <c r="G424" s="55" t="inlineStr"/>
       <c r="H424" s="55" t="inlineStr"/>
       <c r="I424" s="55" t="inlineStr"/>
-      <c r="J424" s="68" t="inlineStr">
-        <is>
-          <t>这个我会，是"忍冬"。</t>
+      <c r="J424" s="55" t="inlineStr">
+        <is>
+          <t>还是娘子聪慧啊，哈哈。</t>
         </is>
       </c>
       <c r="K424" s="55" t="inlineStr"/>
@@ -26933,7 +26923,7 @@
         </is>
       </c>
       <c r="C425" s="50" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D425" s="50" t="inlineStr">
         <is>
@@ -26942,20 +26932,20 @@
       </c>
       <c r="E425" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F425" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G425" s="55" t="inlineStr"/>
       <c r="H425" s="55" t="inlineStr"/>
       <c r="I425" s="55" t="inlineStr"/>
-      <c r="J425" s="68" t="inlineStr">
-        <is>
-          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
+      <c r="J425" s="55" t="inlineStr">
+        <is>
+          <t>你看这个，"大雪压青松"，打一味药材。</t>
         </is>
       </c>
       <c r="K425" s="55" t="inlineStr"/>
@@ -26972,7 +26962,7 @@
         </is>
       </c>
       <c r="C426" s="50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D426" s="50" t="inlineStr">
         <is>
@@ -26981,24 +26971,20 @@
       </c>
       <c r="E426" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F426" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F426" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G426" s="55" t="inlineStr"/>
       <c r="H426" s="55" t="inlineStr"/>
-      <c r="I426" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_05.png</t>
-        </is>
-      </c>
-      <c r="J426" s="55" t="inlineStr">
-        <is>
-          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
+      <c r="I426" s="55" t="inlineStr"/>
+      <c r="J426" s="68" t="inlineStr">
+        <is>
+          <t>这个我会，是"忍冬"。</t>
         </is>
       </c>
       <c r="K426" s="55" t="inlineStr"/>
@@ -27015,7 +27001,7 @@
         </is>
       </c>
       <c r="C427" s="50" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D427" s="50" t="inlineStr">
         <is>
@@ -27024,20 +27010,20 @@
       </c>
       <c r="E427" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F427" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F427" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G427" s="55" t="inlineStr"/>
       <c r="H427" s="55" t="inlineStr"/>
       <c r="I427" s="55" t="inlineStr"/>
-      <c r="J427" s="55" t="inlineStr">
-        <is>
-          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
+      <c r="J427" s="68" t="inlineStr">
+        <is>
+          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
         </is>
       </c>
       <c r="K427" s="55" t="inlineStr"/>
@@ -27054,7 +27040,7 @@
         </is>
       </c>
       <c r="C428" s="50" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D428" s="50" t="inlineStr">
         <is>
@@ -27063,20 +27049,24 @@
       </c>
       <c r="E428" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F428" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G428" s="55" t="inlineStr"/>
       <c r="H428" s="55" t="inlineStr"/>
-      <c r="I428" s="55" t="inlineStr"/>
+      <c r="I428" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_05.png</t>
+        </is>
+      </c>
       <c r="J428" s="55" t="inlineStr">
         <is>
-          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
         </is>
       </c>
       <c r="K428" s="55" t="inlineStr"/>
@@ -27093,7 +27083,7 @@
         </is>
       </c>
       <c r="C429" s="50" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D429" s="50" t="inlineStr">
         <is>
@@ -27102,12 +27092,12 @@
       </c>
       <c r="E429" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F429" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F429" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G429" s="55" t="inlineStr"/>
@@ -27115,7 +27105,7 @@
       <c r="I429" s="55" t="inlineStr"/>
       <c r="J429" s="55" t="inlineStr">
         <is>
-          <t>是啊，一家人平平安安就好啊。</t>
+          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
         </is>
       </c>
       <c r="K429" s="55" t="inlineStr"/>
@@ -27132,7 +27122,7 @@
         </is>
       </c>
       <c r="C430" s="50" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D430" s="50" t="inlineStr">
         <is>
@@ -27141,12 +27131,12 @@
       </c>
       <c r="E430" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F430" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G430" s="55" t="inlineStr"/>
@@ -27154,24 +27144,24 @@
       <c r="I430" s="55" t="inlineStr"/>
       <c r="J430" s="55" t="inlineStr">
         <is>
-          <t>好了，不早了，咱们该回家了。</t>
+          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
         </is>
       </c>
       <c r="K430" s="55" t="inlineStr"/>
     </row>
-    <row r="431" ht="30" customHeight="1">
+    <row r="431">
       <c r="A431" s="50" t="inlineStr">
         <is>
-          <t>028_01</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B431" s="50" t="inlineStr">
         <is>
-          <t>曾题名痰火扰心</t>
+          <t>上元灯节</t>
         </is>
       </c>
       <c r="C431" s="50" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D431" s="50" t="inlineStr">
         <is>
@@ -27180,102 +27170,102 @@
       </c>
       <c r="E431" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F431" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G431" s="51" t="inlineStr"/>
-      <c r="H431" s="54" t="inlineStr"/>
-      <c r="I431" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J431" s="53" t="inlineStr">
-        <is>
-          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
-        </is>
-      </c>
-      <c r="K431" s="50" t="inlineStr"/>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F431" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G431" s="55" t="inlineStr"/>
+      <c r="H431" s="55" t="inlineStr"/>
+      <c r="I431" s="55" t="inlineStr"/>
+      <c r="J431" s="55" t="inlineStr">
+        <is>
+          <t>是啊，一家人平平安安就好啊。</t>
+        </is>
+      </c>
+      <c r="K431" s="55" t="inlineStr"/>
     </row>
     <row r="432" hidden="1">
       <c r="A432" s="50" t="inlineStr">
         <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B432" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C432" s="50" t="n">
+        <v>28</v>
+      </c>
+      <c r="D432" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E432" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F432" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G432" s="55" t="inlineStr"/>
+      <c r="H432" s="55" t="inlineStr"/>
+      <c r="I432" s="55" t="inlineStr"/>
+      <c r="J432" s="55" t="inlineStr">
+        <is>
+          <t>好了，不早了，咱们该回家了。</t>
+        </is>
+      </c>
+      <c r="K432" s="55" t="inlineStr"/>
+    </row>
+    <row r="433" hidden="1" ht="30" customHeight="1">
+      <c r="A433" s="50" t="inlineStr">
+        <is>
           <t>028_01</t>
         </is>
       </c>
-      <c r="B432" s="50" t="inlineStr">
+      <c r="B433" s="50" t="inlineStr">
         <is>
           <t>曾题名痰火扰心</t>
         </is>
       </c>
-      <c r="C432" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D432" s="50" t="inlineStr">
+      <c r="C433" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D433" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E432" s="53" t="inlineStr">
-        <is>
-          <t>曾题名</t>
-        </is>
-      </c>
-      <c r="F432" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G432" s="51" t="inlineStr"/>
-      <c r="H432" s="54" t="inlineStr"/>
-      <c r="I432" s="51" t="inlineStr"/>
-      <c r="J432" s="53" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K432" s="50" t="inlineStr"/>
-    </row>
-    <row r="433" hidden="1">
-      <c r="A433" s="50" t="inlineStr">
-        <is>
-          <t>028_01</t>
-        </is>
-      </c>
-      <c r="B433" s="50" t="inlineStr">
-        <is>
-          <t>曾题名痰火扰心</t>
-        </is>
-      </c>
-      <c r="C433" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D433" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
       <c r="E433" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F433" s="54" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F433" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G433" s="51" t="inlineStr"/>
       <c r="H433" s="54" t="inlineStr"/>
-      <c r="I433" s="51" t="inlineStr"/>
+      <c r="I433" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J433" s="53" t="inlineStr">
         <is>
-          <t>别急，坐下来让我看看。</t>
+          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
         </is>
       </c>
       <c r="K433" s="50" t="inlineStr"/>
@@ -27292,34 +27282,46 @@
         </is>
       </c>
       <c r="C434" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D434" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E434" s="50" t="inlineStr"/>
-      <c r="F434" s="51" t="inlineStr"/>
+      <c r="E434" s="53" t="inlineStr">
+        <is>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F434" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G434" s="51" t="inlineStr"/>
-      <c r="H434" s="51" t="inlineStr"/>
+      <c r="H434" s="54" t="inlineStr"/>
       <c r="I434" s="51" t="inlineStr"/>
-      <c r="J434" s="50" t="inlineStr"/>
+      <c r="J434" s="53" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
       <c r="K434" s="50" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B435" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C435" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D435" s="50" t="inlineStr">
         <is>
@@ -27331,21 +27333,17 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F435" s="52" t="inlineStr">
+      <c r="F435" s="54" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
       <c r="G435" s="51" t="inlineStr"/>
       <c r="H435" s="54" t="inlineStr"/>
-      <c r="I435" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I435" s="51" t="inlineStr"/>
       <c r="J435" s="53" t="inlineStr">
         <is>
-          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
+          <t>别急，坐下来让我看看。</t>
         </is>
       </c>
       <c r="K435" s="50" t="inlineStr"/>
@@ -27353,40 +27351,28 @@
     <row r="436" hidden="1">
       <c r="A436" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B436" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C436" s="50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D436" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E436" s="53" t="inlineStr">
-        <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F436" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="E436" s="50" t="inlineStr"/>
+      <c r="F436" s="51" t="inlineStr"/>
       <c r="G436" s="51" t="inlineStr"/>
-      <c r="H436" s="54" t="inlineStr"/>
+      <c r="H436" s="51" t="inlineStr"/>
       <c r="I436" s="51" t="inlineStr"/>
-      <c r="J436" s="53" t="inlineStr">
-        <is>
-          <t>好好的怎么就得了这怪病呢？</t>
-        </is>
-      </c>
+      <c r="J436" s="50" t="inlineStr"/>
       <c r="K436" s="50" t="inlineStr"/>
     </row>
     <row r="437" hidden="1">
@@ -27401,7 +27387,7 @@
         </is>
       </c>
       <c r="C437" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D437" s="50" t="inlineStr">
         <is>
@@ -27419,11 +27405,15 @@
         </is>
       </c>
       <c r="G437" s="51" t="inlineStr"/>
-      <c r="H437" s="51" t="inlineStr"/>
-      <c r="I437" s="51" t="inlineStr"/>
+      <c r="H437" s="54" t="inlineStr"/>
+      <c r="I437" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J437" s="53" t="inlineStr">
         <is>
-          <t>是不是读书压力太大了呀？</t>
+          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
         </is>
       </c>
       <c r="K437" s="50" t="inlineStr"/>
@@ -27440,7 +27430,7 @@
         </is>
       </c>
       <c r="C438" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D438" s="50" t="inlineStr">
         <is>
@@ -27449,20 +27439,20 @@
       </c>
       <c r="E438" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F438" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G438" s="51" t="inlineStr"/>
-      <c r="H438" s="51" t="inlineStr"/>
+      <c r="H438" s="54" t="inlineStr"/>
       <c r="I438" s="51" t="inlineStr"/>
       <c r="J438" s="53" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>好好的怎么就得了这怪病呢？</t>
         </is>
       </c>
       <c r="K438" s="50" t="inlineStr"/>
@@ -27479,7 +27469,7 @@
         </is>
       </c>
       <c r="C439" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D439" s="50" t="inlineStr">
         <is>
@@ -27488,12 +27478,12 @@
       </c>
       <c r="E439" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F439" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F439" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G439" s="51" t="inlineStr"/>
@@ -27501,7 +27491,7 @@
       <c r="I439" s="51" t="inlineStr"/>
       <c r="J439" s="53" t="inlineStr">
         <is>
-          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+          <t>是不是读书压力太大了呀？</t>
         </is>
       </c>
       <c r="K439" s="50" t="inlineStr"/>
@@ -27518,7 +27508,7 @@
         </is>
       </c>
       <c r="C440" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D440" s="50" t="inlineStr">
         <is>
@@ -27527,23 +27517,23 @@
       </c>
       <c r="E440" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F440" s="54" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G440" s="55" t="inlineStr"/>
-      <c r="H440" s="55" t="inlineStr"/>
-      <c r="I440" s="55" t="inlineStr"/>
-      <c r="J440" s="56" t="inlineStr">
-        <is>
-          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
-        </is>
-      </c>
-      <c r="K440" s="55" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G440" s="51" t="inlineStr"/>
+      <c r="H440" s="51" t="inlineStr"/>
+      <c r="I440" s="51" t="inlineStr"/>
+      <c r="J440" s="53" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K440" s="50" t="inlineStr"/>
     </row>
     <row r="441" hidden="1">
       <c r="A441" s="50" t="inlineStr">
@@ -27557,7 +27547,7 @@
         </is>
       </c>
       <c r="C441" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D441" s="50" t="inlineStr">
         <is>
@@ -27566,12 +27556,12 @@
       </c>
       <c r="E441" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F441" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G441" s="51" t="inlineStr"/>
@@ -27579,10 +27569,10 @@
       <c r="I441" s="51" t="inlineStr"/>
       <c r="J441" s="53" t="inlineStr">
         <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K441" s="55" t="inlineStr"/>
+          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+        </is>
+      </c>
+      <c r="K441" s="50" t="inlineStr"/>
     </row>
     <row r="442" hidden="1">
       <c r="A442" s="50" t="inlineStr">
@@ -27596,7 +27586,7 @@
         </is>
       </c>
       <c r="C442" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D442" s="50" t="inlineStr">
         <is>
@@ -27605,20 +27595,20 @@
       </c>
       <c r="E442" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F442" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F442" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G442" s="55" t="inlineStr"/>
       <c r="H442" s="55" t="inlineStr"/>
       <c r="I442" s="55" t="inlineStr"/>
-      <c r="J442" s="53" t="inlineStr">
-        <is>
-          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
+      <c r="J442" s="56" t="inlineStr">
+        <is>
+          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
         </is>
       </c>
       <c r="K442" s="55" t="inlineStr"/>
@@ -27635,7 +27625,7 @@
         </is>
       </c>
       <c r="C443" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D443" s="50" t="inlineStr">
         <is>
@@ -27644,20 +27634,20 @@
       </c>
       <c r="E443" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F443" s="54" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G443" s="55" t="inlineStr"/>
-      <c r="H443" s="55" t="inlineStr"/>
-      <c r="I443" s="55" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G443" s="51" t="inlineStr"/>
+      <c r="H443" s="51" t="inlineStr"/>
+      <c r="I443" s="51" t="inlineStr"/>
       <c r="J443" s="53" t="inlineStr">
         <is>
-          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K443" s="55" t="inlineStr"/>
@@ -27674,7 +27664,7 @@
         </is>
       </c>
       <c r="C444" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D444" s="50" t="inlineStr">
         <is>
@@ -27683,12 +27673,12 @@
       </c>
       <c r="E444" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F444" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F444" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G444" s="55" t="inlineStr"/>
@@ -27696,7 +27686,7 @@
       <c r="I444" s="55" t="inlineStr"/>
       <c r="J444" s="53" t="inlineStr">
         <is>
-          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
+          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
         </is>
       </c>
       <c r="K444" s="55" t="inlineStr"/>
@@ -27713,7 +27703,7 @@
         </is>
       </c>
       <c r="C445" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D445" s="50" t="inlineStr">
         <is>
@@ -27722,12 +27712,12 @@
       </c>
       <c r="E445" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F445" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G445" s="55" t="inlineStr"/>
@@ -27735,7 +27725,7 @@
       <c r="I445" s="55" t="inlineStr"/>
       <c r="J445" s="53" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
         </is>
       </c>
       <c r="K445" s="55" t="inlineStr"/>
@@ -27752,7 +27742,7 @@
         </is>
       </c>
       <c r="C446" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D446" s="50" t="inlineStr">
         <is>
@@ -27761,20 +27751,20 @@
       </c>
       <c r="E446" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F446" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F446" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G446" s="55" t="inlineStr"/>
       <c r="H446" s="55" t="inlineStr"/>
       <c r="I446" s="55" t="inlineStr"/>
-      <c r="J446" s="87" t="inlineStr">
-        <is>
-          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
+      <c r="J446" s="53" t="inlineStr">
+        <is>
+          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
         </is>
       </c>
       <c r="K446" s="55" t="inlineStr"/>
@@ -27791,7 +27781,7 @@
         </is>
       </c>
       <c r="C447" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D447" s="50" t="inlineStr">
         <is>
@@ -27800,20 +27790,20 @@
       </c>
       <c r="E447" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F447" s="54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G447" s="55" t="inlineStr"/>
       <c r="H447" s="55" t="inlineStr"/>
       <c r="I447" s="55" t="inlineStr"/>
-      <c r="J447" s="87" t="inlineStr">
-        <is>
-          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+      <c r="J447" s="53" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
       <c r="K447" s="55" t="inlineStr"/>
@@ -27830,7 +27820,7 @@
         </is>
       </c>
       <c r="C448" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D448" s="50" t="inlineStr">
         <is>
@@ -27839,12 +27829,12 @@
       </c>
       <c r="E448" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F448" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F448" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G448" s="55" t="inlineStr"/>
@@ -27852,7 +27842,7 @@
       <c r="I448" s="55" t="inlineStr"/>
       <c r="J448" s="87" t="inlineStr">
         <is>
-          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
         </is>
       </c>
       <c r="K448" s="55" t="inlineStr"/>
@@ -27869,7 +27859,7 @@
         </is>
       </c>
       <c r="C449" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D449" s="50" t="inlineStr">
         <is>
@@ -27878,12 +27868,12 @@
       </c>
       <c r="E449" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F449" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F449" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G449" s="55" t="inlineStr"/>
@@ -27891,7 +27881,7 @@
       <c r="I449" s="55" t="inlineStr"/>
       <c r="J449" s="87" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
         </is>
       </c>
       <c r="K449" s="55" t="inlineStr"/>
@@ -27899,45 +27889,123 @@
     <row r="450">
       <c r="A450" s="50" t="inlineStr">
         <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B450" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C450" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D450" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E450" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F450" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G450" s="55" t="inlineStr"/>
+      <c r="H450" s="55" t="inlineStr"/>
+      <c r="I450" s="55" t="inlineStr"/>
+      <c r="J450" s="87" t="inlineStr">
+        <is>
+          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+        </is>
+      </c>
+      <c r="K450" s="55" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B451" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C451" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D451" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E451" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F451" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G451" s="55" t="inlineStr"/>
+      <c r="H451" s="55" t="inlineStr"/>
+      <c r="I451" s="55" t="inlineStr"/>
+      <c r="J451" s="87" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K451" s="55" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="50" t="inlineStr">
+        <is>
           <t>028_03</t>
         </is>
       </c>
-      <c r="B450" s="50" t="inlineStr">
+      <c r="B452" s="50" t="inlineStr">
         <is>
           <t>028治疗失败</t>
         </is>
       </c>
-      <c r="C450" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D450" s="50" t="inlineStr">
+      <c r="C452" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D452" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E450" s="53" t="inlineStr">
+      <c r="E452" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F450" s="52" t="inlineStr">
+      <c r="F452" s="52" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G450" s="51" t="inlineStr"/>
-      <c r="H450" s="54" t="inlineStr"/>
-      <c r="I450" s="51" t="inlineStr">
+      <c r="G452" s="51" t="inlineStr"/>
+      <c r="H452" s="54" t="inlineStr"/>
+      <c r="I452" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J450" s="53" t="inlineStr">
+      <c r="J452" s="53" t="inlineStr">
         <is>
           <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
-      <c r="K450" s="50" t="inlineStr"/>
+      <c r="K452" s="50" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BI450">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -164,13 +164,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
       <family val="2"/>
@@ -182,6 +175,13 @@
       <charset val="134"/>
       <family val="3"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -309,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -483,9 +483,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -514,16 +511,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2434,8 +2428,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="88"/>
-    <col width="9.125" customWidth="1" style="23" min="89" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="89"/>
+    <col width="9.125" customWidth="1" style="23" min="90" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -4316,7 +4310,7 @@
           <t>先生啊，俺这几天</t>
         </is>
       </c>
-      <c r="G52" s="75" t="inlineStr">
+      <c r="G52" s="74" t="inlineStr">
         <is>
           <t>请您给俺看看。</t>
         </is>
@@ -4406,7 +4400,7 @@
           <t>我这几日</t>
         </is>
       </c>
-      <c r="G54" s="75" t="inlineStr">
+      <c r="G54" s="74" t="inlineStr">
         <is>
           <t>劳烦先生您给小妇看看。</t>
         </is>
@@ -5643,7 +5637,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="11.125" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11.375" bestFit="1" customWidth="1" style="83" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" style="82" min="5" max="5"/>
     <col width="14.25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5668,7 +5662,7 @@
           <t>BookID</t>
         </is>
       </c>
-      <c r="E1" s="84" t="inlineStr">
+      <c r="E1" s="83" t="inlineStr">
         <is>
           <t>sort_index</t>
         </is>
@@ -5698,7 +5692,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E2" s="85" t="n">
+      <c r="E2" s="84" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="48" t="inlineStr">
@@ -5723,12 +5717,12 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="74" t="inlineStr">
+      <c r="A3" s="73" t="inlineStr">
         <is>
           <t>ba_gang_bian_zheng</t>
         </is>
       </c>
-      <c r="B3" s="74" t="inlineStr">
+      <c r="B3" s="73" t="inlineStr">
         <is>
           <t>八纲辨证</t>
         </is>
@@ -5741,10 +5735,10 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E3" s="85" t="n">
+      <c r="E3" s="84" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="74" t="inlineStr">
+      <c r="F3" s="73" t="inlineStr">
         <is>
           <t>【八纲辨证】
 八纲辨证是中医分析病情的基本方法。医者通过望、闻、问、切收集症状，再以阴、阳、表、里、寒、热、虚、实八项纲领进行归纳，从而判断疾病的位置、性质以及正邪力量的盛衰。
@@ -5757,12 +5751,12 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="73" t="inlineStr">
         <is>
           <t>yin_yang</t>
         </is>
       </c>
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>阴阳</t>
         </is>
@@ -5775,10 +5769,10 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E4" s="85" t="n">
+      <c r="E4" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="74" t="inlineStr">
+      <c r="F4" s="73" t="inlineStr">
         <is>
           <t>【阴阳】
 阴阳是中医认识人体与自然变化的基本方法。阴代表相对安静、寒凉、内守的一面，阳代表相对活动、温热、外发的一面。二者相互对立，又彼此依存，并会随着时间与环境不断消长变化。
@@ -5792,7 +5786,7 @@
           <t>biao_li</t>
         </is>
       </c>
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B5" s="73" t="inlineStr">
         <is>
           <t>表里</t>
         </is>
@@ -5805,7 +5799,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E5" s="85" t="n">
+      <c r="E5" s="84" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -5837,7 +5831,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E6" s="85" t="n">
+      <c r="E6" s="84" t="n">
         <v>5</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -5869,7 +5863,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E7" s="85" t="n">
+      <c r="E7" s="84" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -5883,12 +5877,12 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="74" t="inlineStr">
+      <c r="A8" s="73" t="inlineStr">
         <is>
           <t>wu_xing</t>
         </is>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="73" t="inlineStr">
         <is>
           <t>五行</t>
         </is>
@@ -5901,7 +5895,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E8" s="85" t="n">
+      <c r="E8" s="84" t="n">
         <v>7</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -5946,7 +5940,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E9" s="85" t="n">
+      <c r="E9" s="84" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -5977,7 +5971,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E10" s="85" t="n">
+      <c r="E10" s="84" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -6008,7 +6002,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E11" s="85" t="n">
+      <c r="E11" s="84" t="n">
         <v>10</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -6039,7 +6033,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E12" s="85" t="n">
+      <c r="E12" s="84" t="n">
         <v>11</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -6070,7 +6064,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E13" s="85" t="n">
+      <c r="E13" s="84" t="n">
         <v>12</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -6101,7 +6095,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E14" s="85" t="n">
+      <c r="E14" s="84" t="n">
         <v>13</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -6132,7 +6126,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E15" s="85" t="n">
+      <c r="E15" s="84" t="n">
         <v>14</v>
       </c>
       <c r="F15" s="48" t="inlineStr">
@@ -6163,7 +6157,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E16" s="85" t="n">
+      <c r="E16" s="84" t="n">
         <v>15</v>
       </c>
       <c r="F16" s="48" t="inlineStr">
@@ -6194,7 +6188,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E17" s="85" t="n">
+      <c r="E17" s="84" t="n">
         <v>16</v>
       </c>
       <c r="F17" s="48" t="inlineStr">
@@ -6225,7 +6219,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E18" s="85" t="n">
+      <c r="E18" s="84" t="n">
         <v>17</v>
       </c>
       <c r="F18" s="48" t="inlineStr">
@@ -6256,7 +6250,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E19" s="85" t="n">
+      <c r="E19" s="84" t="n">
         <v>18</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -6287,7 +6281,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E20" s="85" t="n">
+      <c r="E20" s="84" t="n">
         <v>19</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -6318,7 +6312,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E21" s="85" t="n">
+      <c r="E21" s="84" t="n">
         <v>20</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -6349,7 +6343,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E22" s="85" t="n">
+      <c r="E22" s="84" t="n">
         <v>21</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -6380,7 +6374,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E23" s="85" t="n">
+      <c r="E23" s="84" t="n">
         <v>22</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -6411,7 +6405,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E24" s="85" t="n">
+      <c r="E24" s="84" t="n">
         <v>23</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -6442,7 +6436,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E25" s="85" t="n">
+      <c r="E25" s="84" t="n">
         <v>24</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -6473,7 +6467,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E26" s="85" t="n">
+      <c r="E26" s="84" t="n">
         <v>25</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -6505,7 +6499,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E27" s="85" t="n">
+      <c r="E27" s="84" t="n">
         <v>26</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -6536,7 +6530,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E28" s="85" t="n">
+      <c r="E28" s="84" t="n">
         <v>27</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -6567,7 +6561,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E29" s="85" t="n">
+      <c r="E29" s="84" t="n">
         <v>28</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -6598,7 +6592,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E30" s="85" t="n">
+      <c r="E30" s="84" t="n">
         <v>29</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -6629,7 +6623,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E31" s="85" t="n">
+      <c r="E31" s="84" t="n">
         <v>30</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -6660,7 +6654,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E32" s="85" t="n">
+      <c r="E32" s="84" t="n">
         <v>31</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -6691,7 +6685,7 @@
           <t>huang_di_nei_jing</t>
         </is>
       </c>
-      <c r="E33" s="85" t="n">
+      <c r="E33" s="84" t="n">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -6708,7 +6702,7 @@
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="n"/>
-      <c r="E34" s="85" t="n"/>
+      <c r="E34" s="84" t="n"/>
       <c r="F34" s="7" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6716,7 +6710,7 @@
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
-      <c r="E35" s="85" t="n"/>
+      <c r="E35" s="84" t="n"/>
       <c r="F35" s="7" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6724,7 +6718,7 @@
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="n"/>
-      <c r="E36" s="85" t="n"/>
+      <c r="E36" s="84" t="n"/>
       <c r="F36" s="7" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6732,7 +6726,7 @@
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="n"/>
-      <c r="E37" s="85" t="n"/>
+      <c r="E37" s="84" t="n"/>
       <c r="F37" s="7" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -6740,7 +6734,7 @@
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="n"/>
-      <c r="E38" s="85" t="n"/>
+      <c r="E38" s="84" t="n"/>
       <c r="F38" s="7" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6748,7 +6742,7 @@
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="n"/>
-      <c r="E39" s="85" t="n"/>
+      <c r="E39" s="84" t="n"/>
       <c r="F39" s="7" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -6756,7 +6750,7 @@
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="n"/>
-      <c r="E40" s="85" t="n"/>
+      <c r="E40" s="84" t="n"/>
       <c r="F40" s="7" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6764,7 +6758,7 @@
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="n"/>
-      <c r="E41" s="85" t="n"/>
+      <c r="E41" s="84" t="n"/>
       <c r="F41" s="7" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6772,7 +6766,7 @@
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="n"/>
-      <c r="E42" s="85" t="n"/>
+      <c r="E42" s="84" t="n"/>
       <c r="F42" s="7" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6780,7 +6774,7 @@
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
-      <c r="E43" s="85" t="n"/>
+      <c r="E43" s="84" t="n"/>
       <c r="F43" s="7" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6788,7 +6782,7 @@
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
-      <c r="E44" s="85" t="n"/>
+      <c r="E44" s="84" t="n"/>
       <c r="F44" s="7" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6796,7 +6790,7 @@
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="n"/>
-      <c r="E45" s="85" t="n"/>
+      <c r="E45" s="84" t="n"/>
       <c r="F45" s="7" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6841,107 +6835,107 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="38"/>
-    <col width="9" customWidth="1" style="47" min="39" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="39"/>
+    <col width="9" customWidth="1" style="47" min="40" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>剧情ID</t>
         </is>
       </c>
-      <c r="B1" s="77" t="inlineStr">
+      <c r="B1" s="76" t="inlineStr">
         <is>
           <t>剧情名</t>
         </is>
       </c>
-      <c r="C1" s="78" t="inlineStr">
+      <c r="C1" s="77" t="inlineStr">
         <is>
           <t>触发场景</t>
         </is>
       </c>
-      <c r="D1" s="78" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>触发天数</t>
         </is>
       </c>
-      <c r="E1" s="79" t="inlineStr">
+      <c r="E1" s="78" t="inlineStr">
         <is>
           <t>金钱判定</t>
         </is>
       </c>
-      <c r="F1" s="79" t="inlineStr">
+      <c r="F1" s="78" t="inlineStr">
         <is>
           <t>触发金钱</t>
         </is>
       </c>
-      <c r="G1" s="79" t="inlineStr">
+      <c r="G1" s="78" t="inlineStr">
         <is>
           <t>名望判定</t>
         </is>
       </c>
-      <c r="H1" s="79" t="inlineStr">
+      <c r="H1" s="78" t="inlineStr">
         <is>
           <t>触发名望</t>
         </is>
       </c>
-      <c r="I1" s="79" t="inlineStr">
+      <c r="I1" s="78" t="inlineStr">
         <is>
           <t>触发条目</t>
         </is>
       </c>
-      <c r="J1" s="79" t="inlineStr">
+      <c r="J1" s="78" t="inlineStr">
         <is>
           <t>触发剧情ID</t>
         </is>
       </c>
-      <c r="K1" s="79" t="inlineStr">
+      <c r="K1" s="78" t="inlineStr">
         <is>
           <t>触发治疗结果</t>
         </is>
       </c>
-      <c r="L1" s="80" t="inlineStr">
+      <c r="L1" s="79" t="inlineStr">
         <is>
           <t>播放后</t>
         </is>
       </c>
-      <c r="M1" s="81" t="inlineStr">
+      <c r="M1" s="80" t="inlineStr">
         <is>
           <t>人物ID</t>
         </is>
       </c>
-      <c r="N1" s="81" t="inlineStr">
+      <c r="N1" s="80" t="inlineStr">
         <is>
           <t>疾病</t>
         </is>
       </c>
-      <c r="O1" s="81" t="inlineStr">
+      <c r="O1" s="80" t="inlineStr">
         <is>
           <t>人物立绘路径</t>
         </is>
       </c>
-      <c r="P1" s="81" t="inlineStr">
+      <c r="P1" s="80" t="inlineStr">
         <is>
           <t>奖励金钱</t>
         </is>
       </c>
-      <c r="Q1" s="81" t="inlineStr">
+      <c r="Q1" s="80" t="inlineStr">
         <is>
           <t>奖励名望</t>
         </is>
       </c>
-      <c r="R1" s="81" t="inlineStr">
+      <c r="R1" s="80" t="inlineStr">
         <is>
           <t>奖励心得</t>
         </is>
       </c>
-      <c r="S1" s="82" t="inlineStr">
+      <c r="S1" s="81" t="inlineStr">
         <is>
           <t>PlayOnce</t>
         </is>
       </c>
-      <c r="T1" s="82" t="inlineStr">
+      <c r="T1" s="81" t="inlineStr">
         <is>
           <t>SortIndex</t>
         </is>
@@ -6995,7 +6989,7 @@
       <c r="S2" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T2" s="83" t="inlineStr"/>
+      <c r="T2" s="82" t="inlineStr"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="48" t="inlineStr">
@@ -7041,7 +7035,7 @@
       <c r="S3" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T3" s="83" t="inlineStr"/>
+      <c r="T3" s="82" t="inlineStr"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="48" t="inlineStr">
@@ -7087,7 +7081,7 @@
       <c r="S4" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T4" s="83" t="inlineStr"/>
+      <c r="T4" s="82" t="inlineStr"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="48" t="inlineStr">
@@ -7133,7 +7127,7 @@
       <c r="S5" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T5" s="83" t="inlineStr"/>
+      <c r="T5" s="82" t="inlineStr"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="48" t="inlineStr">
@@ -7158,7 +7152,7 @@
         </is>
       </c>
       <c r="F6" s="48" t="n">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="G6" s="48" t="inlineStr"/>
       <c r="H6" s="48" t="inlineStr"/>
@@ -7183,7 +7177,7 @@
       <c r="S6" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T6" s="83" t="inlineStr"/>
+      <c r="T6" s="82" t="inlineStr"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="48" t="inlineStr">
@@ -7229,7 +7223,7 @@
       <c r="S7" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T7" s="83" t="inlineStr"/>
+      <c r="T7" s="82" t="inlineStr"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="48" t="inlineStr">
@@ -7275,7 +7269,7 @@
       <c r="S8" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T8" s="83" t="inlineStr"/>
+      <c r="T8" s="82" t="inlineStr"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="48" t="inlineStr">
@@ -7317,7 +7311,7 @@
       <c r="S9" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T9" s="83" t="inlineStr"/>
+      <c r="T9" s="82" t="inlineStr"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="48" t="inlineStr">
@@ -7359,7 +7353,7 @@
       <c r="S10" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T10" s="83" t="inlineStr"/>
+      <c r="T10" s="82" t="inlineStr"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="48" t="inlineStr">
@@ -7401,7 +7395,7 @@
       <c r="S11" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T11" s="83" t="inlineStr"/>
+      <c r="T11" s="82" t="inlineStr"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="48" t="inlineStr">
@@ -7443,7 +7437,7 @@
       <c r="S12" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T12" s="83" t="inlineStr"/>
+      <c r="T12" s="82" t="inlineStr"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="48" t="inlineStr">
@@ -7497,7 +7491,7 @@
       <c r="S13" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T13" s="83" t="inlineStr"/>
+      <c r="T13" s="82" t="inlineStr"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="48" t="inlineStr">
@@ -7545,7 +7539,7 @@
       <c r="S14" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T14" s="83" t="inlineStr"/>
+      <c r="T14" s="82" t="inlineStr"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="48" t="inlineStr">
@@ -7605,7 +7599,7 @@
       <c r="S15" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="83" t="inlineStr"/>
+      <c r="T15" s="82" t="inlineStr"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="48" t="inlineStr">
@@ -7651,7 +7645,7 @@
       <c r="S16" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T16" s="83" t="inlineStr"/>
+      <c r="T16" s="82" t="inlineStr"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="48" t="inlineStr">
@@ -7707,7 +7701,7 @@
       <c r="S17" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T17" s="83" t="inlineStr"/>
+      <c r="T17" s="82" t="inlineStr"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="48" t="inlineStr">
@@ -7755,7 +7749,7 @@
       <c r="S18" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T18" s="83" t="inlineStr"/>
+      <c r="T18" s="82" t="inlineStr"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="48" t="inlineStr">
@@ -7799,7 +7793,7 @@
       <c r="S19" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="83" t="inlineStr"/>
+      <c r="T19" s="82" t="inlineStr"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="48" t="inlineStr">
@@ -7843,7 +7837,7 @@
       <c r="S20" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T20" s="83" t="inlineStr"/>
+      <c r="T20" s="82" t="inlineStr"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="48" t="inlineStr">
@@ -7899,7 +7893,7 @@
       <c r="S21" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T21" s="83" t="inlineStr"/>
+      <c r="T21" s="82" t="inlineStr"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="48" t="inlineStr">
@@ -7943,7 +7937,7 @@
       <c r="S22" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T22" s="83" t="inlineStr"/>
+      <c r="T22" s="82" t="inlineStr"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="48" t="inlineStr">
@@ -7999,7 +7993,7 @@
       <c r="S23" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="83" t="inlineStr"/>
+      <c r="T23" s="82" t="inlineStr"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="48" t="inlineStr">
@@ -8059,7 +8053,7 @@
       <c r="S24" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="83" t="inlineStr"/>
+      <c r="T24" s="82" t="inlineStr"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="48" t="inlineStr">
@@ -8103,7 +8097,7 @@
       <c r="S25" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T25" s="83" t="inlineStr"/>
+      <c r="T25" s="82" t="inlineStr"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="48" t="inlineStr">
@@ -8159,7 +8153,7 @@
       <c r="S26" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T26" s="83" t="inlineStr"/>
+      <c r="T26" s="82" t="inlineStr"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="48" t="inlineStr">
@@ -8209,7 +8203,7 @@
       <c r="S27" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T27" s="83" t="inlineStr"/>
+      <c r="T27" s="82" t="inlineStr"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="48" t="inlineStr">
@@ -8255,7 +8249,7 @@
       <c r="S28" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T28" s="83" t="inlineStr"/>
+      <c r="T28" s="82" t="inlineStr"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="48" t="inlineStr">
@@ -8301,7 +8295,7 @@
       <c r="S29" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T29" s="83" t="inlineStr"/>
+      <c r="T29" s="82" t="inlineStr"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="48" t="inlineStr">
@@ -8347,7 +8341,7 @@
       <c r="S30" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T30" s="83" t="inlineStr"/>
+      <c r="T30" s="82" t="inlineStr"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="48" t="inlineStr">
@@ -8393,7 +8387,7 @@
       <c r="S31" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T31" s="83" t="inlineStr"/>
+      <c r="T31" s="82" t="inlineStr"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="48" t="inlineStr">
@@ -8455,7 +8449,7 @@
       <c r="S32" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T32" s="83" t="inlineStr"/>
+      <c r="T32" s="82" t="inlineStr"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="48" t="inlineStr">
@@ -8501,7 +8495,7 @@
       <c r="S33" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T33" s="83" t="inlineStr"/>
+      <c r="T33" s="82" t="inlineStr"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
@@ -8557,7 +8551,7 @@
       <c r="S34" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T34" s="83" t="inlineStr"/>
+      <c r="T34" s="82" t="inlineStr"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="48" t="inlineStr">
@@ -8603,7 +8597,7 @@
       <c r="S35" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T35" s="83" t="inlineStr"/>
+      <c r="T35" s="82" t="inlineStr"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="48" t="inlineStr">
@@ -8649,7 +8643,7 @@
       <c r="S36" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T36" s="83" t="inlineStr"/>
+      <c r="T36" s="82" t="inlineStr"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="48" t="inlineStr">
@@ -8711,7 +8705,7 @@
       <c r="S37" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T37" s="83" t="inlineStr"/>
+      <c r="T37" s="82" t="inlineStr"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="48" t="inlineStr">
@@ -8757,7 +8751,7 @@
       <c r="S38" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T38" s="83" t="inlineStr"/>
+      <c r="T38" s="82" t="inlineStr"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="48" t="inlineStr">
@@ -8813,7 +8807,7 @@
       <c r="S39" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T39" s="83" t="inlineStr"/>
+      <c r="T39" s="82" t="inlineStr"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="48" t="inlineStr">
@@ -8859,7 +8853,7 @@
       <c r="S40" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T40" s="83" t="inlineStr"/>
+      <c r="T40" s="82" t="inlineStr"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="48" t="inlineStr">
@@ -8905,7 +8899,7 @@
       <c r="S41" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T41" s="83" t="inlineStr"/>
+      <c r="T41" s="82" t="inlineStr"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="48" t="inlineStr">
@@ -8951,7 +8945,7 @@
       <c r="S42" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T42" s="83" t="inlineStr"/>
+      <c r="T42" s="82" t="inlineStr"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="48" t="inlineStr">
@@ -8997,7 +8991,7 @@
       <c r="S43" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T43" s="83" t="inlineStr"/>
+      <c r="T43" s="82" t="inlineStr"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="48" t="inlineStr">
@@ -9053,7 +9047,7 @@
       <c r="S44" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T44" s="83" t="inlineStr"/>
+      <c r="T44" s="82" t="inlineStr"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="48" t="inlineStr">
@@ -9091,13 +9085,15 @@
       <c r="M45" s="48" t="inlineStr"/>
       <c r="N45" s="48" t="inlineStr"/>
       <c r="O45" s="48" t="inlineStr"/>
-      <c r="P45" s="48" t="inlineStr"/>
+      <c r="P45" s="48" t="n">
+        <v>1000</v>
+      </c>
       <c r="Q45" s="48" t="inlineStr"/>
       <c r="R45" s="48" t="inlineStr"/>
       <c r="S45" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T45" s="83" t="inlineStr"/>
+      <c r="T45" s="82" t="inlineStr"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="48" t="inlineStr">
@@ -9153,7 +9149,7 @@
       <c r="S46" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T46" s="83" t="inlineStr"/>
+      <c r="T46" s="82" t="inlineStr"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="48" t="inlineStr">
@@ -9209,7 +9205,7 @@
       <c r="S47" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T47" s="83" t="inlineStr"/>
+      <c r="T47" s="82" t="inlineStr"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="48" t="inlineStr">
@@ -9259,7 +9255,7 @@
       <c r="S48" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T48" s="83" t="inlineStr"/>
+      <c r="T48" s="82" t="inlineStr"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="48" t="inlineStr">
@@ -9315,7 +9311,7 @@
       <c r="S49" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T49" s="83" t="inlineStr"/>
+      <c r="T49" s="82" t="inlineStr"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="48" t="inlineStr">
@@ -9377,7 +9373,7 @@
       <c r="S50" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T50" s="83" t="inlineStr"/>
+      <c r="T50" s="82" t="inlineStr"/>
     </row>
     <row r="51" ht="17.65" customHeight="1">
       <c r="A51" s="48" t="inlineStr">
@@ -9423,7 +9419,7 @@
       <c r="S51" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T51" s="83" t="inlineStr"/>
+      <c r="T51" s="82" t="inlineStr"/>
     </row>
     <row r="52" ht="17.65" customHeight="1">
       <c r="A52" s="48" t="inlineStr">
@@ -9479,7 +9475,7 @@
       <c r="S52" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T52" s="83" t="inlineStr"/>
+      <c r="T52" s="82" t="inlineStr"/>
     </row>
     <row r="53" ht="17.65" customHeight="1">
       <c r="A53" s="48" t="inlineStr">
@@ -9527,7 +9523,7 @@
       <c r="S53" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T53" s="83" t="inlineStr"/>
+      <c r="T53" s="82" t="inlineStr"/>
     </row>
     <row r="54" ht="17.65" customHeight="1">
       <c r="A54" s="48" t="inlineStr">
@@ -9583,7 +9579,7 @@
       <c r="S54" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T54" s="83" t="inlineStr"/>
+      <c r="T54" s="82" t="inlineStr"/>
     </row>
     <row r="55" ht="17.65" customHeight="1">
       <c r="A55" s="48" t="inlineStr">
@@ -9629,7 +9625,7 @@
       <c r="S55" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T55" s="83" t="inlineStr"/>
+      <c r="T55" s="82" t="inlineStr"/>
     </row>
     <row r="56" ht="17.65" customHeight="1">
       <c r="A56" s="48" t="inlineStr">
@@ -9685,7 +9681,7 @@
       <c r="S56" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T56" s="83" t="inlineStr"/>
+      <c r="T56" s="82" t="inlineStr"/>
     </row>
     <row r="57" ht="17.65" customHeight="1">
       <c r="A57" s="48" t="inlineStr">
@@ -9747,7 +9743,7 @@
       <c r="S57" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T57" s="83" t="inlineStr"/>
+      <c r="T57" s="82" t="inlineStr"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="48" t="inlineStr">
@@ -9791,7 +9787,7 @@
       <c r="S58" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T58" s="83" t="inlineStr"/>
+      <c r="T58" s="82" t="inlineStr"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" s="48" t="inlineStr">
@@ -9847,7 +9843,7 @@
       <c r="S59" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="T59" s="83" t="inlineStr"/>
+      <c r="T59" s="82" t="inlineStr"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" s="48" t="inlineStr">
@@ -9889,163 +9885,163 @@
       <c r="S60" s="48" t="b">
         <v>1</v>
       </c>
-      <c r="T60" s="83" t="inlineStr"/>
-    </row>
-    <row r="61" ht="17.65" customHeight="1">
-      <c r="A61" t="inlineStr">
+      <c r="T60" s="82" t="inlineStr"/>
+    </row>
+    <row r="61" ht="18.75" customHeight="1">
+      <c r="A61" s="48" t="inlineStr">
         <is>
           <t>028_01</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="48" t="inlineStr">
         <is>
           <t>曾题名痰火扰心</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="48" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
+      <c r="D61" s="48" t="inlineStr"/>
+      <c r="E61" s="48" t="inlineStr"/>
+      <c r="F61" s="48" t="inlineStr"/>
+      <c r="G61" s="48" t="inlineStr"/>
+      <c r="H61" s="48" t="inlineStr"/>
+      <c r="I61" s="48" t="inlineStr">
         <is>
           <t>痰迷心窍</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
+      <c r="J61" s="48" t="inlineStr"/>
+      <c r="K61" s="48" t="inlineStr"/>
+      <c r="L61" s="48" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M61" s="48" t="inlineStr">
         <is>
           <t>zeng_ti_ming</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N61" s="48" t="inlineStr">
         <is>
           <t>痰迷心窍</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O61" s="48" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/zeng_ti_ming/zeng_ti_ming.png</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="b">
-        <v>1</v>
-      </c>
-      <c r="T61" t="inlineStr"/>
-    </row>
-    <row r="62" ht="17.65" customHeight="1">
-      <c r="A62" t="inlineStr">
+      <c r="P61" s="48" t="inlineStr"/>
+      <c r="Q61" s="48" t="inlineStr"/>
+      <c r="R61" s="48" t="inlineStr"/>
+      <c r="S61" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" s="82" t="inlineStr"/>
+    </row>
+    <row r="62" ht="18.75" customHeight="1">
+      <c r="A62" s="48" t="inlineStr">
         <is>
           <t>028_02</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="48" t="inlineStr">
         <is>
           <t>028治疗成功</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
+      <c r="C62" s="48" t="inlineStr"/>
+      <c r="D62" s="48" t="inlineStr"/>
+      <c r="E62" s="48" t="inlineStr"/>
+      <c r="F62" s="48" t="inlineStr"/>
+      <c r="G62" s="48" t="inlineStr"/>
+      <c r="H62" s="48" t="inlineStr"/>
+      <c r="I62" s="48" t="inlineStr"/>
+      <c r="J62" s="48" t="inlineStr">
         <is>
           <t>028_01</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="48" t="inlineStr">
         <is>
           <t>cured</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L62" s="48" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="b">
-        <v>1</v>
-      </c>
-      <c r="T62" t="inlineStr"/>
-    </row>
-    <row r="63" ht="17.65" customHeight="1">
-      <c r="A63" t="inlineStr">
+      <c r="M62" s="48" t="inlineStr"/>
+      <c r="N62" s="48" t="inlineStr"/>
+      <c r="O62" s="48" t="inlineStr"/>
+      <c r="P62" s="48" t="inlineStr"/>
+      <c r="Q62" s="48" t="inlineStr"/>
+      <c r="R62" s="48" t="inlineStr"/>
+      <c r="S62" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" s="82" t="inlineStr"/>
+    </row>
+    <row r="63" ht="18.75" customHeight="1">
+      <c r="A63" s="48" t="inlineStr">
         <is>
           <t>028_03</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="48" t="inlineStr">
         <is>
           <t>028治疗失败</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
+      <c r="C63" s="48" t="inlineStr"/>
+      <c r="D63" s="48" t="inlineStr"/>
+      <c r="E63" s="48" t="inlineStr"/>
+      <c r="F63" s="48" t="inlineStr"/>
+      <c r="G63" s="48" t="inlineStr"/>
+      <c r="H63" s="48" t="inlineStr"/>
+      <c r="I63" s="48" t="inlineStr"/>
+      <c r="J63" s="48" t="inlineStr">
         <is>
           <t>028_01</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" s="48" t="inlineStr">
         <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L63" s="48" t="inlineStr">
         <is>
           <t>clinic</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M63" s="48" t="inlineStr">
         <is>
           <t>zeng_ti_ming</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N63" s="48" t="inlineStr">
         <is>
           <t>痰迷心窍</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O63" s="48" t="inlineStr">
         <is>
           <t>res://Assets/Portrait/StoryNpc/zeng_ti_ming/zeng_ti_ming.png</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="b">
-        <v>1</v>
-      </c>
-      <c r="T63" t="inlineStr"/>
+      <c r="P63" s="48" t="inlineStr"/>
+      <c r="Q63" s="48" t="inlineStr"/>
+      <c r="R63" s="48" t="inlineStr"/>
+      <c r="S63" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" s="82" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA60"/>
@@ -10059,7 +10055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K452"/>
+  <dimension ref="A1:K453"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -10073,8 +10069,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="62"/>
-    <col width="8.875" customWidth="1" style="36" min="63" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="63"/>
+    <col width="8.875" customWidth="1" style="36" min="64" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12286,7 +12282,7 @@
       <c r="I56" s="51" t="inlineStr"/>
       <c r="J56" s="67" t="inlineStr">
         <is>
-          <t>......也罢，科举考功名的学子千千万，可真能博取个功名的又有几人呢？东璧呀，你若真的想从医，今日起便随为父从《内经》、《本草》学起吧。</t>
+          <t>唉......也罢，科举考功名的学子千千万，可真能博取个功名的又有几人呢？东璧呀，你若真的想从医，今日起便随为父从《内经》、《本草》学起吧。</t>
         </is>
       </c>
       <c r="K56" s="55" t="inlineStr"/>
@@ -12345,7 +12341,7 @@
       <c r="F58" s="52" t="inlineStr"/>
       <c r="G58" s="51" t="inlineStr"/>
       <c r="H58" s="52" t="inlineStr"/>
-      <c r="I58" s="90" t="inlineStr">
+      <c r="I58" s="88" t="inlineStr">
         <is>
           <t>res://Assets/Background/clinic/spring_night.png</t>
         </is>
@@ -12388,7 +12384,7 @@
       </c>
       <c r="G59" s="51" t="inlineStr"/>
       <c r="H59" s="52" t="inlineStr"/>
-      <c r="I59" s="90" t="inlineStr"/>
+      <c r="I59" s="88" t="inlineStr"/>
       <c r="J59" s="57" t="inlineStr">
         <is>
           <t>麻桂相须，增强发汗散寒之力，专治表实无汗。麻杏相使，宣降相配，专治寒邪闭肺之喘逆…</t>
@@ -12505,7 +12501,7 @@
       </c>
       <c r="G62" s="51" t="inlineStr"/>
       <c r="H62" s="52" t="inlineStr"/>
-      <c r="I62" s="90" t="inlineStr">
+      <c r="I62" s="88" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -14171,7 +14167,7 @@
         </is>
       </c>
       <c r="H104" s="52" t="inlineStr"/>
-      <c r="I104" s="90" t="inlineStr"/>
+      <c r="I104" s="88" t="inlineStr"/>
       <c r="J104" s="56" t="inlineStr">
         <is>
           <t>咳咳咳，父王…</t>
@@ -22755,57 +22751,45 @@
       <c r="K321" s="55" t="inlineStr"/>
     </row>
     <row r="322" hidden="1">
-      <c r="A322" s="50" t="inlineStr">
-        <is>
-          <t>022_03</t>
-        </is>
-      </c>
-      <c r="B322" s="50" t="inlineStr">
-        <is>
-          <t>022治疗失败</t>
-        </is>
-      </c>
-      <c r="C322" s="50" t="n">
-        <v>1</v>
+      <c r="A322" s="55" t="inlineStr">
+        <is>
+          <t>022_02</t>
+        </is>
+      </c>
+      <c r="B322" s="55" t="inlineStr">
+        <is>
+          <t>022治疗成功</t>
+        </is>
+      </c>
+      <c r="C322" s="55" t="n">
+        <v>20</v>
       </c>
       <c r="D322" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E322" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F322" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G322" s="51" t="inlineStr"/>
-      <c r="H322" s="52" t="inlineStr"/>
-      <c r="I322" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J322" s="53" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
-        </is>
-      </c>
-      <c r="K322" s="50" t="inlineStr"/>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E322" s="50" t="inlineStr"/>
+      <c r="F322" s="51" t="inlineStr"/>
+      <c r="G322" s="55" t="inlineStr"/>
+      <c r="H322" s="55" t="inlineStr"/>
+      <c r="I322" s="55" t="inlineStr"/>
+      <c r="J322" s="55" t="inlineStr">
+        <is>
+          <t>收入一两白银</t>
+        </is>
+      </c>
+      <c r="K322" s="55" t="inlineStr"/>
     </row>
     <row r="323" hidden="1">
       <c r="A323" s="50" t="inlineStr">
         <is>
-          <t>023_01</t>
+          <t>022_03</t>
         </is>
       </c>
       <c r="B323" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕肺气虚</t>
+          <t>022治疗失败</t>
         </is>
       </c>
       <c r="C323" s="50" t="n">
@@ -22818,12 +22802,12 @@
       </c>
       <c r="E323" s="50" t="inlineStr">
         <is>
-          <t>金姨妈</t>
-        </is>
-      </c>
-      <c r="F323" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F323" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G323" s="51" t="inlineStr"/>
@@ -22833,9 +22817,9 @@
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J323" s="50" t="inlineStr">
-        <is>
-          <t>李大夫，您快给我女儿瞧瞧吧，这孩子整日茶饭不进，愁眉苦脸咳个不停。</t>
+      <c r="J323" s="53" t="inlineStr">
+        <is>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K323" s="50" t="inlineStr"/>
@@ -22852,7 +22836,7 @@
         </is>
       </c>
       <c r="C324" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D324" s="50" t="inlineStr">
         <is>
@@ -22861,24 +22845,24 @@
       </c>
       <c r="E324" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F324" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G324" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F324" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G324" s="51" t="inlineStr"/>
       <c r="H324" s="52" t="inlineStr"/>
-      <c r="I324" s="51" t="inlineStr"/>
+      <c r="I324" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J324" s="50" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>李大夫，您快给我女儿瞧瞧吧，这孩子整日茶饭不进，愁眉苦脸咳个不停。</t>
         </is>
       </c>
       <c r="K324" s="50" t="inlineStr"/>
@@ -22895,7 +22879,7 @@
         </is>
       </c>
       <c r="C325" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D325" s="50" t="inlineStr">
         <is>
@@ -22904,20 +22888,24 @@
       </c>
       <c r="E325" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F325" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G325" s="51" t="inlineStr"/>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F325" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G325" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H325" s="52" t="inlineStr"/>
       <c r="I325" s="51" t="inlineStr"/>
       <c r="J325" s="50" t="inlineStr">
         <is>
-          <t>这是您女儿？</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K325" s="50" t="inlineStr"/>
@@ -22934,7 +22922,7 @@
         </is>
       </c>
       <c r="C326" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D326" s="50" t="inlineStr">
         <is>
@@ -22943,20 +22931,20 @@
       </c>
       <c r="E326" s="50" t="inlineStr">
         <is>
-          <t>金姨妈</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F326" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G326" s="51" t="inlineStr"/>
-      <c r="H326" s="51" t="inlineStr"/>
+      <c r="H326" s="52" t="inlineStr"/>
       <c r="I326" s="51" t="inlineStr"/>
       <c r="J326" s="50" t="inlineStr">
         <is>
-          <t>哎呀，可不是嘛，这孩子随我学艺两年又半载，尤善歌舞，是咱柳月坊的花魁。</t>
+          <t>这是您女儿？</t>
         </is>
       </c>
       <c r="K326" s="50" t="inlineStr"/>
@@ -22973,7 +22961,7 @@
         </is>
       </c>
       <c r="C327" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D327" s="50" t="inlineStr">
         <is>
@@ -22995,46 +22983,46 @@
       <c r="I327" s="51" t="inlineStr"/>
       <c r="J327" s="50" t="inlineStr">
         <is>
+          <t>哎呀，可不是嘛，这孩子随我学艺两年又半载，尤善歌舞，是咱柳月坊的花魁。</t>
+        </is>
+      </c>
+      <c r="K327" s="50" t="inlineStr"/>
+    </row>
+    <row r="328" hidden="1">
+      <c r="A328" s="50" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B328" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C328" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D328" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E328" s="50" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F328" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G328" s="51" t="inlineStr"/>
+      <c r="H328" s="51" t="inlineStr"/>
+      <c r="I328" s="51" t="inlineStr"/>
+      <c r="J328" s="50" t="inlineStr">
+        <is>
           <t>可你看她现在这个样子，还怎么接待客人啊。</t>
-        </is>
-      </c>
-      <c r="K327" s="50" t="inlineStr"/>
-    </row>
-    <row r="328" hidden="1">
-      <c r="A328" s="55" t="inlineStr">
-        <is>
-          <t>023_01</t>
-        </is>
-      </c>
-      <c r="B328" s="55" t="inlineStr">
-        <is>
-          <t>谢飞燕肺气虚</t>
-        </is>
-      </c>
-      <c r="C328" s="55" t="n">
-        <v>6</v>
-      </c>
-      <c r="D328" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E328" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F328" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G328" s="55" t="inlineStr"/>
-      <c r="H328" s="55" t="inlineStr"/>
-      <c r="I328" s="55" t="inlineStr"/>
-      <c r="J328" s="55" t="inlineStr">
-        <is>
-          <t>姑娘你坐下，我给你把把脉。哎，半夏你在这干什么？</t>
         </is>
       </c>
       <c r="K328" s="50" t="inlineStr"/>
@@ -23051,29 +23039,29 @@
         </is>
       </c>
       <c r="C329" s="55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D329" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E329" s="53" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E329" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F329" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G329" s="55" t="inlineStr"/>
       <c r="H329" s="55" t="inlineStr"/>
       <c r="I329" s="55" t="inlineStr"/>
-      <c r="J329" s="56" t="inlineStr">
-        <is>
-          <t>我替少夫人来看着你。</t>
+      <c r="J329" s="55" t="inlineStr">
+        <is>
+          <t>姑娘你坐下，我给你把把脉。哎，半夏你在这干什么？</t>
         </is>
       </c>
       <c r="K329" s="50" t="inlineStr"/>
@@ -23090,21 +23078,21 @@
         </is>
       </c>
       <c r="C330" s="55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D330" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E330" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E330" s="53" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F330" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G330" s="55" t="inlineStr"/>
@@ -23112,93 +23100,89 @@
       <c r="I330" s="55" t="inlineStr"/>
       <c r="J330" s="56" t="inlineStr">
         <is>
+          <t>我替少夫人来看着你。</t>
+        </is>
+      </c>
+      <c r="K330" s="50" t="inlineStr"/>
+    </row>
+    <row r="331" hidden="1">
+      <c r="A331" s="55" t="inlineStr">
+        <is>
+          <t>023_01</t>
+        </is>
+      </c>
+      <c r="B331" s="55" t="inlineStr">
+        <is>
+          <t>谢飞燕肺气虚</t>
+        </is>
+      </c>
+      <c r="C331" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D331" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E331" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F331" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G331" s="55" t="inlineStr"/>
+      <c r="H331" s="55" t="inlineStr"/>
+      <c r="I331" s="55" t="inlineStr"/>
+      <c r="J331" s="56" t="inlineStr">
+        <is>
           <t>…</t>
         </is>
       </c>
-      <c r="K330" s="50" t="inlineStr"/>
-    </row>
-    <row r="331" hidden="1" ht="33" customHeight="1">
-      <c r="A331" s="50" t="inlineStr">
+      <c r="K331" s="50" t="inlineStr"/>
+    </row>
+    <row r="332" hidden="1" ht="33" customHeight="1">
+      <c r="A332" s="50" t="inlineStr">
         <is>
           <t>023_02</t>
         </is>
       </c>
-      <c r="B331" s="50" t="inlineStr">
+      <c r="B332" s="50" t="inlineStr">
         <is>
           <t>023治疗成功</t>
         </is>
       </c>
-      <c r="C331" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D331" s="50" t="inlineStr">
+      <c r="C332" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D332" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E331" s="50" t="inlineStr">
+      <c r="E332" s="50" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F331" s="51" t="inlineStr">
+      <c r="F332" s="51" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G331" s="51" t="inlineStr"/>
-      <c r="H331" s="52" t="inlineStr"/>
-      <c r="I331" s="51" t="inlineStr">
+      <c r="G332" s="51" t="inlineStr"/>
+      <c r="H332" s="52" t="inlineStr"/>
+      <c r="I332" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J331" s="50" t="inlineStr">
+      <c r="J332" s="50" t="inlineStr">
         <is>
           <t>姑娘这病是肺气虚，平日注意避风避寒，开副补肺汤调养调养。早上练练六字诀中的呬字诀，舒畅胸中气机。</t>
-        </is>
-      </c>
-      <c r="K331" s="50" t="inlineStr"/>
-    </row>
-    <row r="332" hidden="1">
-      <c r="A332" s="50" t="inlineStr">
-        <is>
-          <t>023_02</t>
-        </is>
-      </c>
-      <c r="B332" s="50" t="inlineStr">
-        <is>
-          <t>023治疗成功</t>
-        </is>
-      </c>
-      <c r="C332" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D332" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E332" s="50" t="inlineStr">
-        <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F332" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G332" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H332" s="52" t="inlineStr"/>
-      <c r="I332" s="51" t="inlineStr"/>
-      <c r="J332" s="50" t="inlineStr">
-        <is>
-          <t>…多谢先生。</t>
         </is>
       </c>
       <c r="K332" s="50" t="inlineStr"/>
@@ -23215,7 +23199,7 @@
         </is>
       </c>
       <c r="C333" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D333" s="50" t="inlineStr">
         <is>
@@ -23224,20 +23208,24 @@
       </c>
       <c r="E333" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F333" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G333" s="51" t="inlineStr"/>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F333" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G333" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H333" s="52" t="inlineStr"/>
       <c r="I333" s="51" t="inlineStr"/>
       <c r="J333" s="50" t="inlineStr">
         <is>
-          <t>姑娘可是有什么心事？</t>
+          <t>…多谢先生。</t>
         </is>
       </c>
       <c r="K333" s="50" t="inlineStr"/>
@@ -23254,7 +23242,7 @@
         </is>
       </c>
       <c r="C334" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D334" s="50" t="inlineStr">
         <is>
@@ -23263,20 +23251,20 @@
       </c>
       <c r="E334" s="50" t="inlineStr">
         <is>
-          <t>金姨妈</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F334" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G334" s="51" t="inlineStr"/>
-      <c r="H334" s="51" t="inlineStr"/>
+      <c r="H334" s="52" t="inlineStr"/>
       <c r="I334" s="51" t="inlineStr"/>
       <c r="J334" s="50" t="inlineStr">
         <is>
-          <t>成天好吃好喝的伺候着，她能有什么心事。</t>
+          <t>姑娘可是有什么心事？</t>
         </is>
       </c>
       <c r="K334" s="50" t="inlineStr"/>
@@ -23293,7 +23281,7 @@
         </is>
       </c>
       <c r="C335" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D335" s="50" t="inlineStr">
         <is>
@@ -23315,7 +23303,7 @@
       <c r="I335" s="51" t="inlineStr"/>
       <c r="J335" s="50" t="inlineStr">
         <is>
-          <t>那就多谢大夫了，走吧女儿。</t>
+          <t>成天好吃好喝的伺候着，她能有什么心事。</t>
         </is>
       </c>
       <c r="K335" s="50" t="inlineStr"/>
@@ -23332,7 +23320,7 @@
         </is>
       </c>
       <c r="C336" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D336" s="50" t="inlineStr">
         <is>
@@ -23341,24 +23329,20 @@
       </c>
       <c r="E336" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F336" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G336" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H336" s="55" t="inlineStr"/>
-      <c r="I336" s="55" t="inlineStr"/>
+          <t>金姨妈</t>
+        </is>
+      </c>
+      <c r="F336" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G336" s="51" t="inlineStr"/>
+      <c r="H336" s="51" t="inlineStr"/>
+      <c r="I336" s="51" t="inlineStr"/>
       <c r="J336" s="50" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>那就多谢大夫了，走吧女儿。</t>
         </is>
       </c>
       <c r="K336" s="50" t="inlineStr"/>
@@ -23375,25 +23359,33 @@
         </is>
       </c>
       <c r="C337" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D337" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E337" s="55" t="inlineStr"/>
-      <c r="F337" s="51" t="inlineStr"/>
-      <c r="G337" s="55" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E337" s="50" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F337" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G337" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H337" s="55" t="inlineStr"/>
-      <c r="I337" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/black.png</t>
-        </is>
-      </c>
-      <c r="J337" s="88" t="inlineStr">
-        <is>
-          <t>收入一两白银</t>
+      <c r="I337" s="55" t="inlineStr"/>
+      <c r="J337" s="50" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="K337" s="50" t="inlineStr"/>
@@ -23410,33 +23402,25 @@
         </is>
       </c>
       <c r="C338" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D338" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E338" s="55" t="inlineStr">
-        <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F338" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E338" s="55" t="inlineStr"/>
+      <c r="F338" s="51" t="inlineStr"/>
       <c r="G338" s="55" t="inlineStr"/>
       <c r="H338" s="55" t="inlineStr"/>
       <c r="I338" s="51" t="inlineStr">
         <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J338" s="68" t="inlineStr">
-        <is>
-          <t>大夫，刚才那姑娘是得了什么病啊？</t>
+          <t>res://Assets/Background/black.png</t>
+        </is>
+      </c>
+      <c r="J338" s="86" t="inlineStr">
+        <is>
+          <t>收入一两白银</t>
         </is>
       </c>
       <c r="K338" s="50" t="inlineStr"/>
@@ -23453,29 +23437,33 @@
         </is>
       </c>
       <c r="C339" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D339" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E339" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E339" s="55" t="inlineStr">
+        <is>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F339" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G339" s="55" t="inlineStr"/>
       <c r="H339" s="55" t="inlineStr"/>
-      <c r="I339" s="55" t="inlineStr"/>
-      <c r="J339" s="55" t="inlineStr">
-        <is>
-          <t>您是？</t>
+      <c r="I339" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J339" s="68" t="inlineStr">
+        <is>
+          <t>大夫，刚才那姑娘是得了什么病啊？</t>
         </is>
       </c>
       <c r="K339" s="50" t="inlineStr"/>
@@ -23492,21 +23480,21 @@
         </is>
       </c>
       <c r="C340" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D340" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E340" s="55" t="inlineStr">
-        <is>
-          <t>王百堂</t>
+      <c r="E340" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F340" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G340" s="55" t="inlineStr"/>
@@ -23514,7 +23502,7 @@
       <c r="I340" s="55" t="inlineStr"/>
       <c r="J340" s="55" t="inlineStr">
         <is>
-          <t>小生是姑娘的一位相识，担心姑娘身体，来问问大夫。</t>
+          <t>您是？</t>
         </is>
       </c>
       <c r="K340" s="50" t="inlineStr"/>
@@ -23531,21 +23519,21 @@
         </is>
       </c>
       <c r="C341" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D341" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E341" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E341" s="55" t="inlineStr">
+        <is>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F341" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G341" s="55" t="inlineStr"/>
@@ -23553,7 +23541,7 @@
       <c r="I341" s="55" t="inlineStr"/>
       <c r="J341" s="55" t="inlineStr">
         <is>
-          <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
+          <t>小生是姑娘的一位相识，担心姑娘身体，来问问大夫。</t>
         </is>
       </c>
       <c r="K341" s="50" t="inlineStr"/>
@@ -23570,21 +23558,21 @@
         </is>
       </c>
       <c r="C342" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D342" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E342" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E342" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F342" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G342" s="55" t="inlineStr"/>
@@ -23592,7 +23580,7 @@
       <c r="I342" s="55" t="inlineStr"/>
       <c r="J342" s="55" t="inlineStr">
         <is>
-          <t>哎哟？这里面有事儿，快说来听听。</t>
+          <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
         </is>
       </c>
       <c r="K342" s="50" t="inlineStr"/>
@@ -23609,7 +23597,7 @@
         </is>
       </c>
       <c r="C343" s="50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D343" s="50" t="inlineStr">
         <is>
@@ -23618,20 +23606,20 @@
       </c>
       <c r="E343" s="55" t="inlineStr">
         <is>
-          <t>王百堂</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F343" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G343" s="55" t="inlineStr"/>
       <c r="H343" s="55" t="inlineStr"/>
       <c r="I343" s="55" t="inlineStr"/>
-      <c r="J343" s="68" t="inlineStr">
-        <is>
-          <t>实不相瞒，小生在柳月坊与飞燕相识，一见倾心，私底下定了终身。</t>
+      <c r="J343" s="55" t="inlineStr">
+        <is>
+          <t>哎哟？这里面有事儿，快说来听听。</t>
         </is>
       </c>
       <c r="K343" s="50" t="inlineStr"/>
@@ -23648,7 +23636,7 @@
         </is>
       </c>
       <c r="C344" s="50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D344" s="50" t="inlineStr">
         <is>
@@ -23668,9 +23656,9 @@
       <c r="G344" s="55" t="inlineStr"/>
       <c r="H344" s="55" t="inlineStr"/>
       <c r="I344" s="55" t="inlineStr"/>
-      <c r="J344" s="55" t="inlineStr">
-        <is>
-          <t>原想着凑够五百两银子，给她赎身。可那老鸨坐地起价，张口就要一千两，这让我们上哪去凑这么多银子啊…</t>
+      <c r="J344" s="68" t="inlineStr">
+        <is>
+          <t>实不相瞒，小生在柳月坊与飞燕相识，一见倾心，私底下定了终身。</t>
         </is>
       </c>
       <c r="K344" s="50" t="inlineStr"/>
@@ -23687,21 +23675,21 @@
         </is>
       </c>
       <c r="C345" s="50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D345" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E345" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E345" s="55" t="inlineStr">
+        <is>
+          <t>王百堂</t>
         </is>
       </c>
       <c r="F345" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G345" s="55" t="inlineStr"/>
@@ -23709,7 +23697,7 @@
       <c r="I345" s="55" t="inlineStr"/>
       <c r="J345" s="55" t="inlineStr">
         <is>
-          <t>想必姑娘是因为这事急坏了身子。</t>
+          <t>原想着凑够五百两银子，给她赎身。可那老鸨坐地起价，张口就要一千两，这让我们上哪去凑这么多银子啊…</t>
         </is>
       </c>
       <c r="K345" s="50" t="inlineStr"/>
@@ -23726,21 +23714,21 @@
         </is>
       </c>
       <c r="C346" s="50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D346" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E346" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E346" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F346" s="51" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G346" s="55" t="inlineStr"/>
@@ -23748,7 +23736,7 @@
       <c r="I346" s="55" t="inlineStr"/>
       <c r="J346" s="55" t="inlineStr">
         <is>
-          <t>唉，又是一对儿苦命的鸳鸯。</t>
+          <t>想必姑娘是因为这事急坏了身子。</t>
         </is>
       </c>
       <c r="K346" s="50" t="inlineStr"/>
@@ -23765,29 +23753,29 @@
         </is>
       </c>
       <c r="C347" s="50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D347" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E347" s="56" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E347" s="55" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F347" s="51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G347" s="55" t="inlineStr"/>
       <c r="H347" s="55" t="inlineStr"/>
       <c r="I347" s="55" t="inlineStr"/>
-      <c r="J347" s="56" t="inlineStr">
-        <is>
-          <t>相公咱想办法帮帮他们吧。</t>
+      <c r="J347" s="55" t="inlineStr">
+        <is>
+          <t>唉，又是一对儿苦命的鸳鸯。</t>
         </is>
       </c>
       <c r="K347" s="50" t="inlineStr"/>
@@ -23804,29 +23792,29 @@
         </is>
       </c>
       <c r="C348" s="50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D348" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E348" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E348" s="56" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F348" s="51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G348" s="55" t="inlineStr"/>
       <c r="H348" s="55" t="inlineStr"/>
       <c r="I348" s="55" t="inlineStr"/>
-      <c r="J348" s="55" t="inlineStr">
-        <is>
-          <t>我也想帮他们，可怎么帮呢？</t>
+      <c r="J348" s="56" t="inlineStr">
+        <is>
+          <t>相公咱想办法帮帮他们吧。</t>
         </is>
       </c>
       <c r="K348" s="50" t="inlineStr"/>
@@ -23834,23 +23822,23 @@
     <row r="349" hidden="1">
       <c r="A349" s="50" t="inlineStr">
         <is>
-          <t>023_03</t>
+          <t>023_02</t>
         </is>
       </c>
       <c r="B349" s="50" t="inlineStr">
         <is>
-          <t>023治疗失败</t>
+          <t>023治疗成功</t>
         </is>
       </c>
       <c r="C349" s="50" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D349" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E349" s="53" t="inlineStr">
+      <c r="E349" s="50" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
@@ -23860,16 +23848,12 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G349" s="51" t="inlineStr"/>
-      <c r="H349" s="52" t="inlineStr"/>
-      <c r="I349" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J349" s="53" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
+      <c r="G349" s="55" t="inlineStr"/>
+      <c r="H349" s="55" t="inlineStr"/>
+      <c r="I349" s="55" t="inlineStr"/>
+      <c r="J349" s="55" t="inlineStr">
+        <is>
+          <t>我也想帮他们，可怎么帮呢？</t>
         </is>
       </c>
       <c r="K349" s="50" t="inlineStr"/>
@@ -23877,12 +23861,12 @@
     <row r="350" hidden="1">
       <c r="A350" s="50" t="inlineStr">
         <is>
-          <t>024_01</t>
+          <t>023_03</t>
         </is>
       </c>
       <c r="B350" s="50" t="inlineStr">
         <is>
-          <t>谢飞燕肺阴虚</t>
+          <t>023治疗失败</t>
         </is>
       </c>
       <c r="C350" s="50" t="n">
@@ -23898,9 +23882,9 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F350" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="F350" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G350" s="51" t="inlineStr"/>
@@ -23912,7 +23896,7 @@
       </c>
       <c r="J350" s="53" t="inlineStr">
         <is>
-          <t>姑娘你来啦，病好点了吗？</t>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K350" s="50" t="inlineStr"/>
@@ -23929,7 +23913,7 @@
         </is>
       </c>
       <c r="C351" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D351" s="50" t="inlineStr">
         <is>
@@ -23938,24 +23922,24 @@
       </c>
       <c r="E351" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F351" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G351" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G351" s="51" t="inlineStr"/>
       <c r="H351" s="52" t="inlineStr"/>
-      <c r="I351" s="51" t="inlineStr"/>
+      <c r="I351" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J351" s="53" t="inlineStr">
         <is>
-          <t>唉，这些日子一直不太好，前天还咳出血丝来了…</t>
+          <t>姑娘你来啦，病好点了吗？</t>
         </is>
       </c>
       <c r="K351" s="50" t="inlineStr"/>
@@ -23972,7 +23956,7 @@
         </is>
       </c>
       <c r="C352" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D352" s="50" t="inlineStr">
         <is>
@@ -23981,20 +23965,24 @@
       </c>
       <c r="E352" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F352" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G352" s="51" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G352" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H352" s="52" t="inlineStr"/>
       <c r="I352" s="51" t="inlineStr"/>
       <c r="J352" s="53" t="inlineStr">
         <is>
-          <t>请坐，我再给你看看。</t>
+          <t>唉，这些日子一直不太好，前天还咳出血丝来了…</t>
         </is>
       </c>
       <c r="K352" s="50" t="inlineStr"/>
@@ -24002,16 +23990,16 @@
     <row r="353" hidden="1">
       <c r="A353" s="50" t="inlineStr">
         <is>
-          <t>024_02</t>
+          <t>024_01</t>
         </is>
       </c>
       <c r="B353" s="50" t="inlineStr">
         <is>
-          <t>024治疗成功</t>
+          <t>谢飞燕肺阴虚</t>
         </is>
       </c>
       <c r="C353" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D353" s="50" t="inlineStr">
         <is>
@@ -24030,14 +24018,10 @@
       </c>
       <c r="G353" s="51" t="inlineStr"/>
       <c r="H353" s="52" t="inlineStr"/>
-      <c r="I353" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I353" s="51" t="inlineStr"/>
       <c r="J353" s="53" t="inlineStr">
         <is>
-          <t>姑娘你这病，因气虚日久，气不化津，已经恶化为肺阴虚了。给你开些沙参麦冬汤补津养肺。</t>
+          <t>请坐，我再给你看看。</t>
         </is>
       </c>
       <c r="K353" s="50" t="inlineStr"/>
@@ -24054,7 +24038,7 @@
         </is>
       </c>
       <c r="C354" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D354" s="50" t="inlineStr">
         <is>
@@ -24063,24 +24047,24 @@
       </c>
       <c r="E354" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F354" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G354" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G354" s="51" t="inlineStr"/>
       <c r="H354" s="52" t="inlineStr"/>
-      <c r="I354" s="51" t="inlineStr"/>
+      <c r="I354" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J354" s="53" t="inlineStr">
         <is>
-          <t>多谢先生…</t>
+          <t>姑娘你这病，因气虚日久，气不化津，已经恶化为肺阴虚了。给你开些沙参麦冬汤补津养肺。</t>
         </is>
       </c>
       <c r="K354" s="50" t="inlineStr"/>
@@ -24097,7 +24081,7 @@
         </is>
       </c>
       <c r="C355" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D355" s="50" t="inlineStr">
         <is>
@@ -24106,20 +24090,24 @@
       </c>
       <c r="E355" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F355" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G355" s="51" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G355" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H355" s="52" t="inlineStr"/>
       <c r="I355" s="51" t="inlineStr"/>
       <c r="J355" s="53" t="inlineStr">
         <is>
-          <t>可这药只能医肺病，不能医心病，心病还须心药医。</t>
+          <t>多谢先生…</t>
         </is>
       </c>
       <c r="K355" s="50" t="inlineStr"/>
@@ -24136,7 +24124,7 @@
         </is>
       </c>
       <c r="C356" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D356" s="50" t="inlineStr">
         <is>
@@ -24145,24 +24133,20 @@
       </c>
       <c r="E356" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F356" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G356" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H356" s="51" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G356" s="51" t="inlineStr"/>
+      <c r="H356" s="52" t="inlineStr"/>
       <c r="I356" s="51" t="inlineStr"/>
       <c r="J356" s="53" t="inlineStr">
         <is>
-          <t>夫人这是何意味？</t>
+          <t>可这药只能医肺病，不能医心病，心病还须心药医。</t>
         </is>
       </c>
       <c r="K356" s="50" t="inlineStr"/>
@@ -24179,7 +24163,7 @@
         </is>
       </c>
       <c r="C357" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D357" s="50" t="inlineStr">
         <is>
@@ -24188,20 +24172,24 @@
       </c>
       <c r="E357" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F357" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G357" s="51" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G357" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H357" s="51" t="inlineStr"/>
       <c r="I357" s="51" t="inlineStr"/>
       <c r="J357" s="53" t="inlineStr">
         <is>
-          <t>前些天你来看病，你前脚刚走，王公子就来这问你的病情，很是担心你。</t>
+          <t>夫人这是何意味？</t>
         </is>
       </c>
       <c r="K357" s="50" t="inlineStr"/>
@@ -24218,7 +24206,7 @@
         </is>
       </c>
       <c r="C358" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D358" s="50" t="inlineStr">
         <is>
@@ -24227,24 +24215,20 @@
       </c>
       <c r="E358" s="53" t="inlineStr">
         <is>
-          <t>谢飞燕</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F358" s="52" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G358" s="52" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
-      <c r="H358" s="55" t="inlineStr"/>
-      <c r="I358" s="55" t="inlineStr"/>
-      <c r="J358" s="56" t="inlineStr">
-        <is>
-          <t>唉，我们这行当是做不长久的，只盼着有个如意的郎君，趁着年轻嫁入好人家。</t>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G358" s="51" t="inlineStr"/>
+      <c r="H358" s="51" t="inlineStr"/>
+      <c r="I358" s="51" t="inlineStr"/>
+      <c r="J358" s="53" t="inlineStr">
+        <is>
+          <t>前些天你来看病，你前脚刚走，王公子就来这问你的病情，很是担心你。</t>
         </is>
       </c>
       <c r="K358" s="50" t="inlineStr"/>
@@ -24261,7 +24245,7 @@
         </is>
       </c>
       <c r="C359" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D359" s="50" t="inlineStr">
         <is>
@@ -24287,7 +24271,7 @@
       <c r="I359" s="55" t="inlineStr"/>
       <c r="J359" s="56" t="inlineStr">
         <is>
-          <t>王郎待我真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
+          <t>唉，我们这行当是做不长久的，只盼着有个如意的郎君，趁着年轻嫁入好人家。</t>
         </is>
       </c>
       <c r="K359" s="50" t="inlineStr"/>
@@ -24304,7 +24288,7 @@
         </is>
       </c>
       <c r="C360" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D360" s="50" t="inlineStr">
         <is>
@@ -24313,20 +24297,24 @@
       </c>
       <c r="E360" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>谢飞燕</t>
         </is>
       </c>
       <c r="F360" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G360" s="55" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G360" s="52" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H360" s="55" t="inlineStr"/>
       <c r="I360" s="55" t="inlineStr"/>
       <c r="J360" s="56" t="inlineStr">
         <is>
-          <t>我有一计，可使你二人有情人终成眷属。</t>
+          <t>王郎待我真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
         </is>
       </c>
       <c r="K360" s="50" t="inlineStr"/>
@@ -24343,33 +24331,29 @@
         </is>
       </c>
       <c r="C361" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D361" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E361" s="56" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E361" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F361" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G361" s="55" t="inlineStr"/>
-      <c r="H361" s="55" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
+      <c r="H361" s="55" t="inlineStr"/>
       <c r="I361" s="55" t="inlineStr"/>
       <c r="J361" s="56" t="inlineStr">
         <is>
-          <t>少夫人你有什么主意呀？快说快说！</t>
+          <t>我有一计，可使你二人有情人终成眷属。</t>
         </is>
       </c>
       <c r="K361" s="50" t="inlineStr"/>
@@ -24386,21 +24370,21 @@
         </is>
       </c>
       <c r="C362" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D362" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E362" s="53" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E362" s="56" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F362" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G362" s="55" t="inlineStr"/>
@@ -24412,7 +24396,7 @@
       <c r="I362" s="55" t="inlineStr"/>
       <c r="J362" s="56" t="inlineStr">
         <is>
-          <t>明日你让金姨妈来一趟，如此这般….</t>
+          <t>少夫人你有什么主意呀？快说快说！</t>
         </is>
       </c>
       <c r="K362" s="50" t="inlineStr"/>
@@ -24429,21 +24413,33 @@
         </is>
       </c>
       <c r="C363" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D363" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E363" s="53" t="inlineStr"/>
-      <c r="F363" s="52" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E363" s="53" t="inlineStr">
+        <is>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F363" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="G363" s="55" t="inlineStr"/>
-      <c r="H363" s="55" t="inlineStr"/>
+      <c r="H363" s="55" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I363" s="55" t="inlineStr"/>
       <c r="J363" s="56" t="inlineStr">
         <is>
-          <t>吴芷兰和众人说出了自己的主意</t>
+          <t>明日你让金姨妈来一趟，如此这般….</t>
         </is>
       </c>
       <c r="K363" s="50" t="inlineStr"/>
@@ -24460,29 +24456,21 @@
         </is>
       </c>
       <c r="C364" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D364" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E364" s="53" t="inlineStr">
-        <is>
-          <t>谢飞燕</t>
-        </is>
-      </c>
-      <c r="F364" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E364" s="53" t="inlineStr"/>
+      <c r="F364" s="52" t="inlineStr"/>
       <c r="G364" s="55" t="inlineStr"/>
       <c r="H364" s="55" t="inlineStr"/>
       <c r="I364" s="55" t="inlineStr"/>
       <c r="J364" s="56" t="inlineStr">
         <is>
-          <t>先生若是能帮我们渡此难关，便是再造父母。</t>
+          <t>吴芷兰和众人说出了自己的主意</t>
         </is>
       </c>
       <c r="K364" s="50" t="inlineStr"/>
@@ -24499,25 +24487,29 @@
         </is>
       </c>
       <c r="C365" s="50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D365" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E365" s="53" t="inlineStr"/>
-      <c r="F365" s="52" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E365" s="53" t="inlineStr">
+        <is>
+          <t>谢飞燕</t>
+        </is>
+      </c>
+      <c r="F365" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="G365" s="55" t="inlineStr"/>
       <c r="H365" s="55" t="inlineStr"/>
-      <c r="I365" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/black.png</t>
-        </is>
-      </c>
+      <c r="I365" s="55" t="inlineStr"/>
       <c r="J365" s="56" t="inlineStr">
         <is>
-          <t>收入一两白银</t>
+          <t>先生若是能帮我们渡此难关，便是再造父母。</t>
         </is>
       </c>
       <c r="K365" s="50" t="inlineStr"/>
@@ -24534,25 +24526,25 @@
         </is>
       </c>
       <c r="C366" s="50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D366" s="50" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="E366" s="55" t="inlineStr"/>
-      <c r="F366" s="51" t="inlineStr"/>
+      <c r="E366" s="53" t="inlineStr"/>
+      <c r="F366" s="52" t="inlineStr"/>
       <c r="G366" s="55" t="inlineStr"/>
       <c r="H366" s="55" t="inlineStr"/>
       <c r="I366" s="51" t="inlineStr">
         <is>
-          <t>current_scene</t>
+          <t>res://Assets/Background/black.png</t>
         </is>
       </c>
       <c r="J366" s="56" t="inlineStr">
         <is>
-          <t>次日</t>
+          <t>收入一两白银</t>
         </is>
       </c>
       <c r="K366" s="50" t="inlineStr"/>
@@ -24569,29 +24561,25 @@
         </is>
       </c>
       <c r="C367" s="50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D367" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E367" s="56" t="inlineStr">
-        <is>
-          <t>金姨妈</t>
-        </is>
-      </c>
-      <c r="F367" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E367" s="55" t="inlineStr"/>
+      <c r="F367" s="51" t="inlineStr"/>
       <c r="G367" s="55" t="inlineStr"/>
       <c r="H367" s="55" t="inlineStr"/>
-      <c r="I367" s="55" t="inlineStr"/>
+      <c r="I367" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J367" s="56" t="inlineStr">
         <is>
-          <t>李大夫，你叫我来是什么事儿啊？</t>
+          <t>次日</t>
         </is>
       </c>
       <c r="K367" s="50" t="inlineStr"/>
@@ -24608,21 +24596,21 @@
         </is>
       </c>
       <c r="C368" s="50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D368" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E368" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E368" s="56" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
         </is>
       </c>
       <c r="F368" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G368" s="55" t="inlineStr"/>
@@ -24630,7 +24618,7 @@
       <c r="I368" s="55" t="inlineStr"/>
       <c r="J368" s="56" t="inlineStr">
         <is>
-          <t>昨日经我仔细检查，谢姑娘的病乃是肺痨，此病只能缓解，不能根治，而且身边之人都有可能沾染。</t>
+          <t>李大夫，你叫我来是什么事儿啊？</t>
         </is>
       </c>
       <c r="K368" s="50" t="inlineStr"/>
@@ -24647,21 +24635,21 @@
         </is>
       </c>
       <c r="C369" s="50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D369" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E369" s="56" t="inlineStr">
-        <is>
-          <t>金姨妈</t>
+      <c r="E369" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F369" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G369" s="55" t="inlineStr"/>
@@ -24669,7 +24657,7 @@
       <c r="I369" s="55" t="inlineStr"/>
       <c r="J369" s="56" t="inlineStr">
         <is>
-          <t>啊？这可如何是好？</t>
+          <t>昨日经我仔细检查，谢姑娘的病乃是肺痨，此病只能缓解，不能根治，而且身边之人都有可能沾染。</t>
         </is>
       </c>
       <c r="K369" s="50" t="inlineStr"/>
@@ -24686,21 +24674,21 @@
         </is>
       </c>
       <c r="C370" s="50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D370" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E370" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E370" s="56" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
         </is>
       </c>
       <c r="F370" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G370" s="55" t="inlineStr"/>
@@ -24708,7 +24696,7 @@
       <c r="I370" s="55" t="inlineStr"/>
       <c r="J370" s="56" t="inlineStr">
         <is>
-          <t>您还是早做打算，给女儿寻觅个好归宿吧。</t>
+          <t>啊？这可如何是好？</t>
         </is>
       </c>
       <c r="K370" s="50" t="inlineStr"/>
@@ -24725,21 +24713,21 @@
         </is>
       </c>
       <c r="C371" s="50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D371" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E371" s="56" t="inlineStr">
-        <is>
-          <t>金姨妈</t>
+      <c r="E371" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F371" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G371" s="55" t="inlineStr"/>
@@ -24747,7 +24735,7 @@
       <c r="I371" s="55" t="inlineStr"/>
       <c r="J371" s="56" t="inlineStr">
         <is>
-          <t>(若是这样，不如趁那小子不知情，便宜与了他去….)</t>
+          <t>您还是早做打算，给女儿寻觅个好归宿吧。</t>
         </is>
       </c>
       <c r="K371" s="50" t="inlineStr"/>
@@ -24755,42 +24743,38 @@
     <row r="372" hidden="1">
       <c r="A372" s="50" t="inlineStr">
         <is>
-          <t>024_03</t>
+          <t>024_02</t>
         </is>
       </c>
       <c r="B372" s="50" t="inlineStr">
         <is>
-          <t>024治疗失败</t>
+          <t>024治疗成功</t>
         </is>
       </c>
       <c r="C372" s="50" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D372" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E372" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E372" s="56" t="inlineStr">
+        <is>
+          <t>金姨妈</t>
         </is>
       </c>
       <c r="F372" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G372" s="51" t="inlineStr"/>
-      <c r="H372" s="52" t="inlineStr"/>
-      <c r="I372" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J372" s="50" t="inlineStr">
-        <is>
-          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G372" s="55" t="inlineStr"/>
+      <c r="H372" s="55" t="inlineStr"/>
+      <c r="I372" s="55" t="inlineStr"/>
+      <c r="J372" s="56" t="inlineStr">
+        <is>
+          <t>(若是这样，不如趁那小子不知情，便宜与了他去….)</t>
         </is>
       </c>
       <c r="K372" s="50" t="inlineStr"/>
@@ -24798,12 +24782,12 @@
     <row r="373" hidden="1">
       <c r="A373" s="50" t="inlineStr">
         <is>
-          <t>024_04</t>
+          <t>024_03</t>
         </is>
       </c>
       <c r="B373" s="50" t="inlineStr">
         <is>
-          <t>王百堂来访</t>
+          <t>024治疗失败</t>
         </is>
       </c>
       <c r="C373" s="50" t="n">
@@ -24814,18 +24798,18 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E373" s="50" t="inlineStr">
-        <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F373" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E373" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F373" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G373" s="51" t="inlineStr"/>
-      <c r="H373" s="54" t="inlineStr"/>
+      <c r="H373" s="52" t="inlineStr"/>
       <c r="I373" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
@@ -24833,7 +24817,7 @@
       </c>
       <c r="J373" s="50" t="inlineStr">
         <is>
-          <t>恩公！小生拜见恩公。</t>
+          <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
       <c r="K373" s="50" t="inlineStr"/>
@@ -24850,7 +24834,7 @@
         </is>
       </c>
       <c r="C374" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D374" s="50" t="inlineStr">
         <is>
@@ -24859,20 +24843,24 @@
       </c>
       <c r="E374" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F374" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F374" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G374" s="51" t="inlineStr"/>
       <c r="H374" s="54" t="inlineStr"/>
-      <c r="I374" s="51" t="inlineStr"/>
+      <c r="I374" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J374" s="50" t="inlineStr">
         <is>
-          <t>是你啊，快请起。你和谢姑娘怎么样了？</t>
+          <t>恩公！小生拜见恩公。</t>
         </is>
       </c>
       <c r="K374" s="50" t="inlineStr"/>
@@ -24889,7 +24877,7 @@
         </is>
       </c>
       <c r="C375" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D375" s="50" t="inlineStr">
         <is>
@@ -24898,12 +24886,12 @@
       </c>
       <c r="E375" s="50" t="inlineStr">
         <is>
-          <t>王百堂</t>
-        </is>
-      </c>
-      <c r="F375" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F375" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G375" s="51" t="inlineStr"/>
@@ -24911,7 +24899,7 @@
       <c r="I375" s="51" t="inlineStr"/>
       <c r="J375" s="50" t="inlineStr">
         <is>
-          <t>承蒙恩公出手相助，我二人已结为夫妻，在城外安顿下来，今日特来拜谢。</t>
+          <t>是你啊，快请起。你和谢姑娘怎么样了？</t>
         </is>
       </c>
       <c r="K375" s="50" t="inlineStr"/>
@@ -24928,7 +24916,7 @@
         </is>
       </c>
       <c r="C376" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D376" s="50" t="inlineStr">
         <is>
@@ -24946,11 +24934,11 @@
         </is>
       </c>
       <c r="G376" s="51" t="inlineStr"/>
-      <c r="H376" s="51" t="inlineStr"/>
+      <c r="H376" s="54" t="inlineStr"/>
       <c r="I376" s="51" t="inlineStr"/>
       <c r="J376" s="50" t="inlineStr">
         <is>
-          <t>听闻恩公酷好青囊之书，先父也是一生行医，家中有不少先父留下的笔记心得，今日便赠予恩公。</t>
+          <t>承蒙恩公出手相助，我二人已结为夫妻，在城外安顿下来，今日特来拜谢。</t>
         </is>
       </c>
       <c r="K376" s="50" t="inlineStr"/>
@@ -24967,7 +24955,7 @@
         </is>
       </c>
       <c r="C377" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D377" s="50" t="inlineStr">
         <is>
@@ -24976,12 +24964,12 @@
       </c>
       <c r="E377" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F377" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>王百堂</t>
+        </is>
+      </c>
+      <c r="F377" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G377" s="51" t="inlineStr"/>
@@ -24989,93 +24977,93 @@
       <c r="I377" s="51" t="inlineStr"/>
       <c r="J377" s="50" t="inlineStr">
         <is>
+          <t>听闻恩公酷好青囊之书，先父也是一生行医，家中有不少先父留下的笔记心得，今日便赠予恩公。</t>
+        </is>
+      </c>
+      <c r="K377" s="50" t="inlineStr"/>
+    </row>
+    <row r="378" hidden="1">
+      <c r="A378" s="50" t="inlineStr">
+        <is>
+          <t>024_04</t>
+        </is>
+      </c>
+      <c r="B378" s="50" t="inlineStr">
+        <is>
+          <t>王百堂来访</t>
+        </is>
+      </c>
+      <c r="C378" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D378" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E378" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F378" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G378" s="51" t="inlineStr"/>
+      <c r="H378" s="51" t="inlineStr"/>
+      <c r="I378" s="51" t="inlineStr"/>
+      <c r="J378" s="50" t="inlineStr">
+        <is>
           <t>哎呀，这可太好了，真是求之不得啊。</t>
         </is>
       </c>
-      <c r="K377" s="50" t="inlineStr"/>
-    </row>
-    <row r="378" hidden="1" ht="34.5" customHeight="1">
-      <c r="A378" s="50" t="inlineStr">
+      <c r="K378" s="50" t="inlineStr"/>
+    </row>
+    <row r="379" ht="34.5" customHeight="1">
+      <c r="A379" s="50" t="inlineStr">
         <is>
           <t>025_01</t>
         </is>
       </c>
-      <c r="B378" s="50" t="inlineStr">
+      <c r="B379" s="50" t="inlineStr">
         <is>
           <t>和尚肾精不足</t>
         </is>
       </c>
-      <c r="C378" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D378" s="50" t="inlineStr">
+      <c r="C379" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D379" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E378" s="50" t="inlineStr">
+      <c r="E379" s="50" t="inlineStr">
         <is>
           <t>性空</t>
         </is>
       </c>
-      <c r="F378" s="51" t="inlineStr">
+      <c r="F379" s="51" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="G378" s="51" t="inlineStr">
+      <c r="G379" s="51" t="inlineStr">
         <is>
           <t>sick</t>
         </is>
       </c>
-      <c r="H378" s="52" t="inlineStr"/>
-      <c r="I378" s="51" t="inlineStr">
+      <c r="H379" s="52" t="inlineStr"/>
+      <c r="I379" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J378" s="67" t="inlineStr">
+      <c r="J379" s="67" t="inlineStr">
         <is>
           <t>阿弥陀佛，贫僧法号性空，《中论》曰："众因缘生法，我说即是空，亦为是假名，亦是中道义。"正所谓缘起性空是也。</t>
-        </is>
-      </c>
-      <c r="K378" s="50" t="inlineStr"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="50" t="inlineStr">
-        <is>
-          <t>025_01</t>
-        </is>
-      </c>
-      <c r="B379" s="50" t="inlineStr">
-        <is>
-          <t>和尚肾精不足</t>
-        </is>
-      </c>
-      <c r="C379" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D379" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E379" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F379" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G379" s="51" t="inlineStr"/>
-      <c r="H379" s="52" t="inlineStr"/>
-      <c r="I379" s="51" t="inlineStr"/>
-      <c r="J379" s="67" t="inlineStr">
-        <is>
-          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
         </is>
       </c>
       <c r="K379" s="50" t="inlineStr"/>
@@ -25092,7 +25080,7 @@
         </is>
       </c>
       <c r="C380" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D380" s="50" t="inlineStr">
         <is>
@@ -25101,24 +25089,20 @@
       </c>
       <c r="E380" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F380" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G380" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F380" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G380" s="51" t="inlineStr"/>
       <c r="H380" s="52" t="inlineStr"/>
       <c r="I380" s="51" t="inlineStr"/>
-      <c r="J380" s="50" t="inlineStr">
-        <is>
-          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
+      <c r="J380" s="67" t="inlineStr">
+        <is>
+          <t>师父请坐，今日来小馆是？(这和尚身上好大的酒味啊...)</t>
         </is>
       </c>
       <c r="K380" s="50" t="inlineStr"/>
@@ -25126,16 +25110,16 @@
     <row r="381" hidden="1">
       <c r="A381" s="50" t="inlineStr">
         <is>
-          <t>025_02</t>
+          <t>025_01</t>
         </is>
       </c>
       <c r="B381" s="50" t="inlineStr">
         <is>
-          <t>025治疗成功</t>
+          <t>和尚肾精不足</t>
         </is>
       </c>
       <c r="C381" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D381" s="50" t="inlineStr">
         <is>
@@ -25144,24 +25128,24 @@
       </c>
       <c r="E381" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F381" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G381" s="51" t="inlineStr"/>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F381" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G381" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
       <c r="H381" s="52" t="inlineStr"/>
-      <c r="I381" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J381" s="67" t="inlineStr">
-        <is>
-          <t>师父所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
+      <c r="I381" s="51" t="inlineStr"/>
+      <c r="J381" s="50" t="inlineStr">
+        <is>
+          <t>最近身体不太舒服，老是耳鸣头晕，请大夫给贫僧看看。</t>
         </is>
       </c>
       <c r="K381" s="50" t="inlineStr"/>
@@ -25178,7 +25162,7 @@
         </is>
       </c>
       <c r="C382" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D382" s="50" t="inlineStr">
         <is>
@@ -25187,24 +25171,24 @@
       </c>
       <c r="E382" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F382" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G382" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F382" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G382" s="51" t="inlineStr"/>
       <c r="H382" s="52" t="inlineStr"/>
-      <c r="I382" s="51" t="inlineStr"/>
-      <c r="J382" s="50" t="inlineStr">
-        <is>
-          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
+      <c r="I382" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
+      <c r="J382" s="67" t="inlineStr">
+        <is>
+          <t>师父所患的乃是肾精不足之症，嗯…是房事过劳所致…</t>
         </is>
       </c>
       <c r="K382" s="50" t="inlineStr"/>
@@ -25221,7 +25205,7 @@
         </is>
       </c>
       <c r="C383" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D383" s="50" t="inlineStr">
         <is>
@@ -25230,20 +25214,24 @@
       </c>
       <c r="E383" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F383" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G383" s="51" t="inlineStr"/>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F383" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G383" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
       <c r="H383" s="52" t="inlineStr"/>
       <c r="I383" s="51" t="inlineStr"/>
       <c r="J383" s="50" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
         </is>
       </c>
       <c r="K383" s="50" t="inlineStr"/>
@@ -25260,7 +25248,7 @@
         </is>
       </c>
       <c r="C384" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D384" s="50" t="inlineStr">
         <is>
@@ -25269,24 +25257,20 @@
       </c>
       <c r="E384" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F384" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G384" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
-      <c r="H384" s="51" t="inlineStr"/>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F384" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G384" s="51" t="inlineStr"/>
+      <c r="H384" s="52" t="inlineStr"/>
       <c r="I384" s="51" t="inlineStr"/>
       <c r="J384" s="50" t="inlineStr">
         <is>
-          <t>一定是我晚上念经太过用功，着凉了。</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K384" s="50" t="inlineStr"/>
@@ -25303,7 +25287,7 @@
         </is>
       </c>
       <c r="C385" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D385" s="50" t="inlineStr">
         <is>
@@ -25312,20 +25296,24 @@
       </c>
       <c r="E385" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F385" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G385" s="51" t="inlineStr"/>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F385" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G385" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
       <c r="H385" s="51" t="inlineStr"/>
       <c r="I385" s="51" t="inlineStr"/>
       <c r="J385" s="50" t="inlineStr">
         <is>
-          <t>是是是，师父说得对，也不是没有这个可能。</t>
+          <t>一定是我晚上念经太过用功，着凉了。</t>
         </is>
       </c>
       <c r="K385" s="50" t="inlineStr"/>
@@ -25342,7 +25330,7 @@
         </is>
       </c>
       <c r="C386" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D386" s="50" t="inlineStr">
         <is>
@@ -25351,28 +25339,20 @@
       </c>
       <c r="E386" s="50" t="inlineStr">
         <is>
-          <t>性空</t>
-        </is>
-      </c>
-      <c r="F386" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G386" s="51" t="inlineStr">
-        <is>
-          <t>after</t>
-        </is>
-      </c>
-      <c r="H386" s="55" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I386" s="55" t="inlineStr"/>
-      <c r="J386" s="68" t="inlineStr">
-        <is>
-          <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F386" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G386" s="51" t="inlineStr"/>
+      <c r="H386" s="51" t="inlineStr"/>
+      <c r="I386" s="51" t="inlineStr"/>
+      <c r="J386" s="50" t="inlineStr">
+        <is>
+          <t>是是是，师父说得对，也不是没有这个可能。</t>
         </is>
       </c>
       <c r="K386" s="50" t="inlineStr"/>
@@ -25389,21 +25369,37 @@
         </is>
       </c>
       <c r="C387" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D387" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E387" s="50" t="inlineStr"/>
-      <c r="F387" s="51" t="inlineStr"/>
-      <c r="G387" s="51" t="inlineStr"/>
-      <c r="H387" s="55" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E387" s="50" t="inlineStr">
+        <is>
+          <t>性空</t>
+        </is>
+      </c>
+      <c r="F387" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G387" s="51" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="H387" s="55" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I387" s="55" t="inlineStr"/>
-      <c r="J387" s="56" t="inlineStr">
-        <is>
-          <t>收入二两白银</t>
+      <c r="J387" s="68" t="inlineStr">
+        <is>
+          <t>嗯，可别到处乱说啊，这钱你拿着吧，这小郎中真是…</t>
         </is>
       </c>
       <c r="K387" s="50" t="inlineStr"/>
@@ -25420,29 +25416,21 @@
         </is>
       </c>
       <c r="C388" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D388" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E388" s="55" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F388" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G388" s="55" t="inlineStr"/>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E388" s="50" t="inlineStr"/>
+      <c r="F388" s="51" t="inlineStr"/>
+      <c r="G388" s="51" t="inlineStr"/>
       <c r="H388" s="55" t="inlineStr"/>
       <c r="I388" s="55" t="inlineStr"/>
-      <c r="J388" s="55" t="inlineStr">
-        <is>
-          <t>哇，这就是传说中的花和尚吗？</t>
+      <c r="J388" s="56" t="inlineStr">
+        <is>
+          <t>收入二两白银</t>
         </is>
       </c>
       <c r="K388" s="50" t="inlineStr"/>
@@ -25459,21 +25447,21 @@
         </is>
       </c>
       <c r="C389" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D389" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E389" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
+      <c r="E389" s="55" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F389" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G389" s="55" t="inlineStr"/>
@@ -25481,7 +25469,7 @@
       <c r="I389" s="55" t="inlineStr"/>
       <c r="J389" s="55" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>哇，这就是传说中的花和尚吗？</t>
         </is>
       </c>
       <c r="K389" s="50" t="inlineStr"/>
@@ -25498,21 +25486,21 @@
         </is>
       </c>
       <c r="C390" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D390" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E390" s="55" t="inlineStr">
-        <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F390" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E390" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F390" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G390" s="55" t="inlineStr"/>
@@ -25520,7 +25508,7 @@
       <c r="I390" s="55" t="inlineStr"/>
       <c r="J390" s="55" t="inlineStr">
         <is>
-          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K390" s="50" t="inlineStr"/>
@@ -25537,7 +25525,7 @@
         </is>
       </c>
       <c r="C391" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D391" s="50" t="inlineStr">
         <is>
@@ -25546,12 +25534,12 @@
       </c>
       <c r="E391" s="55" t="inlineStr">
         <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F391" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F391" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G391" s="55" t="inlineStr"/>
@@ -25559,7 +25547,7 @@
       <c r="I391" s="55" t="inlineStr"/>
       <c r="J391" s="55" t="inlineStr">
         <is>
-          <t>找打！</t>
+          <t>他是花和尚，你是花痴，正好凑一对儿。</t>
         </is>
       </c>
       <c r="K391" s="50" t="inlineStr"/>
@@ -25576,7 +25564,7 @@
         </is>
       </c>
       <c r="C392" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D392" s="50" t="inlineStr">
         <is>
@@ -25585,12 +25573,12 @@
       </c>
       <c r="E392" s="55" t="inlineStr">
         <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F392" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F392" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G392" s="55" t="inlineStr"/>
@@ -25598,7 +25586,7 @@
       <c r="I392" s="55" t="inlineStr"/>
       <c r="J392" s="55" t="inlineStr">
         <is>
-          <t>哎哟！</t>
+          <t>找打！</t>
         </is>
       </c>
       <c r="K392" s="50" t="inlineStr"/>
@@ -25606,42 +25594,38 @@
     <row r="393" hidden="1">
       <c r="A393" s="50" t="inlineStr">
         <is>
-          <t>025_03</t>
+          <t>025_02</t>
         </is>
       </c>
       <c r="B393" s="50" t="inlineStr">
         <is>
-          <t>025治疗失败</t>
+          <t>025治疗成功</t>
         </is>
       </c>
       <c r="C393" s="50" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D393" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E393" s="50" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F393" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G393" s="51" t="inlineStr"/>
-      <c r="H393" s="52" t="inlineStr"/>
-      <c r="I393" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J393" s="50" t="inlineStr">
-        <is>
-          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
+      <c r="E393" s="55" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F393" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G393" s="55" t="inlineStr"/>
+      <c r="H393" s="55" t="inlineStr"/>
+      <c r="I393" s="55" t="inlineStr"/>
+      <c r="J393" s="55" t="inlineStr">
+        <is>
+          <t>哎哟！</t>
         </is>
       </c>
       <c r="K393" s="50" t="inlineStr"/>
@@ -25649,12 +25633,12 @@
     <row r="394">
       <c r="A394" s="50" t="inlineStr">
         <is>
-          <t>026_01</t>
+          <t>025_03</t>
         </is>
       </c>
       <c r="B394" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰妊娠</t>
+          <t>025治疗失败</t>
         </is>
       </c>
       <c r="C394" s="50" t="n">
@@ -25665,14 +25649,14 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E394" s="53" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E394" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F394" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G394" s="51" t="inlineStr"/>
@@ -25682,9 +25666,9 @@
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J394" s="53" t="inlineStr">
-        <is>
-          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
+      <c r="J394" s="50" t="inlineStr">
+        <is>
+          <t>虽然这不是个正经和尚，但还是得好好想想他得的是什么病。</t>
         </is>
       </c>
       <c r="K394" s="50" t="inlineStr"/>
@@ -25701,7 +25685,7 @@
         </is>
       </c>
       <c r="C395" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D395" s="50" t="inlineStr">
         <is>
@@ -25710,20 +25694,24 @@
       </c>
       <c r="E395" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F395" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G395" s="51" t="inlineStr"/>
       <c r="H395" s="52" t="inlineStr"/>
-      <c r="I395" s="51" t="inlineStr"/>
+      <c r="I395" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J395" s="53" t="inlineStr">
         <is>
-          <t>芷兰！！！</t>
+          <t>少掌柜的，少夫人在屋里晕倒了，您快来看看啊！</t>
         </is>
       </c>
       <c r="K395" s="50" t="inlineStr"/>
@@ -25740,7 +25728,7 @@
         </is>
       </c>
       <c r="C396" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D396" s="50" t="inlineStr">
         <is>
@@ -25749,28 +25737,20 @@
       </c>
       <c r="E396" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F396" s="52" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G396" s="51" t="inlineStr">
-        <is>
-          <t>sick</t>
-        </is>
-      </c>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G396" s="51" t="inlineStr"/>
       <c r="H396" s="52" t="inlineStr"/>
-      <c r="I396" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
+      <c r="I396" s="51" t="inlineStr"/>
       <c r="J396" s="53" t="inlineStr">
         <is>
-          <t>…...</t>
+          <t>芷兰！！！</t>
         </is>
       </c>
       <c r="K396" s="50" t="inlineStr"/>
@@ -25787,7 +25767,7 @@
         </is>
       </c>
       <c r="C397" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D397" s="50" t="inlineStr">
         <is>
@@ -25810,10 +25790,14 @@
         </is>
       </c>
       <c r="H397" s="52" t="inlineStr"/>
-      <c r="I397" s="51" t="inlineStr"/>
+      <c r="I397" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
       <c r="J397" s="53" t="inlineStr">
         <is>
-          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
+          <t>…...</t>
         </is>
       </c>
       <c r="K397" s="50" t="inlineStr"/>
@@ -25830,7 +25814,7 @@
         </is>
       </c>
       <c r="C398" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D398" s="50" t="inlineStr">
         <is>
@@ -25839,20 +25823,24 @@
       </c>
       <c r="E398" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F398" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G398" s="51" t="inlineStr"/>
-      <c r="H398" s="51" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G398" s="51" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H398" s="52" t="inlineStr"/>
       <c r="I398" s="51" t="inlineStr"/>
       <c r="J398" s="53" t="inlineStr">
         <is>
-          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
+          <t>相公，我最近头晕目眩，时不时的还恶心想吐，不知是怎么了…</t>
         </is>
       </c>
       <c r="K398" s="50" t="inlineStr"/>
@@ -25860,42 +25848,38 @@
     <row r="399" hidden="1">
       <c r="A399" s="50" t="inlineStr">
         <is>
-          <t>026_02</t>
+          <t>026_01</t>
         </is>
       </c>
       <c r="B399" s="50" t="inlineStr">
         <is>
-          <t>026治疗成功</t>
+          <t>吴芷兰妊娠</t>
         </is>
       </c>
       <c r="C399" s="50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D399" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E399" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E399" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F399" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G399" s="51" t="inlineStr"/>
-      <c r="H399" s="52" t="inlineStr"/>
-      <c r="I399" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
-      <c r="J399" s="67" t="inlineStr">
-        <is>
-          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
+      <c r="H399" s="51" t="inlineStr"/>
+      <c r="I399" s="51" t="inlineStr"/>
+      <c r="J399" s="53" t="inlineStr">
+        <is>
+          <t>夫人一定是操持家务太过劳累，我给你把把脉。</t>
         </is>
       </c>
       <c r="K399" s="50" t="inlineStr"/>
@@ -25912,7 +25896,7 @@
         </is>
       </c>
       <c r="C400" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D400" s="50" t="inlineStr">
         <is>
@@ -25921,20 +25905,24 @@
       </c>
       <c r="E400" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F400" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F400" s="52" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G400" s="51" t="inlineStr"/>
       <c r="H400" s="52" t="inlineStr"/>
-      <c r="I400" s="51" t="inlineStr"/>
-      <c r="J400" s="50" t="inlineStr">
-        <is>
-          <t>芷兰…我们有孩子了…</t>
+      <c r="I400" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J400" s="67" t="inlineStr">
+        <is>
+          <t>呜呜呜，少夫人到底是得了什么病啊。</t>
         </is>
       </c>
       <c r="K400" s="50" t="inlineStr"/>
@@ -25951,7 +25939,7 @@
         </is>
       </c>
       <c r="C401" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D401" s="50" t="inlineStr">
         <is>
@@ -25960,12 +25948,12 @@
       </c>
       <c r="E401" s="50" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F401" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F401" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G401" s="51" t="inlineStr"/>
@@ -25973,7 +25961,7 @@
       <c r="I401" s="51" t="inlineStr"/>
       <c r="J401" s="50" t="inlineStr">
         <is>
-          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
+          <t>芷兰…我们有孩子了…</t>
         </is>
       </c>
       <c r="K401" s="50" t="inlineStr"/>
@@ -25990,7 +25978,7 @@
         </is>
       </c>
       <c r="C402" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D402" s="50" t="inlineStr">
         <is>
@@ -25999,20 +25987,20 @@
       </c>
       <c r="E402" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F402" s="51" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F402" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G402" s="51" t="inlineStr"/>
-      <c r="H402" s="51" t="inlineStr"/>
+      <c r="H402" s="52" t="inlineStr"/>
       <c r="I402" s="51" t="inlineStr"/>
-      <c r="J402" s="67" t="inlineStr">
-        <is>
-          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
+      <c r="J402" s="50" t="inlineStr">
+        <is>
+          <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
         </is>
       </c>
       <c r="K402" s="50" t="inlineStr"/>
@@ -26029,7 +26017,7 @@
         </is>
       </c>
       <c r="C403" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D403" s="50" t="inlineStr">
         <is>
@@ -26038,20 +26026,20 @@
       </c>
       <c r="E403" s="50" t="inlineStr">
         <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F403" s="52" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F403" s="51" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G403" s="51" t="inlineStr"/>
       <c r="H403" s="51" t="inlineStr"/>
       <c r="I403" s="51" t="inlineStr"/>
-      <c r="J403" s="50" t="inlineStr">
-        <is>
-          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
+      <c r="J403" s="67" t="inlineStr">
+        <is>
+          <t>现在还看不出来，男孩儿女孩儿都一样，我们要当爹当娘了。</t>
         </is>
       </c>
       <c r="K403" s="50" t="inlineStr"/>
@@ -26059,16 +26047,16 @@
     <row r="404" hidden="1">
       <c r="A404" s="50" t="inlineStr">
         <is>
-          <t>026_03</t>
+          <t>026_02</t>
         </is>
       </c>
       <c r="B404" s="50" t="inlineStr">
         <is>
-          <t>026治疗失败</t>
+          <t>026治疗成功</t>
         </is>
       </c>
       <c r="C404" s="50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D404" s="50" t="inlineStr">
         <is>
@@ -26077,24 +26065,20 @@
       </c>
       <c r="E404" s="50" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F404" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G404" s="51" t="inlineStr"/>
-      <c r="H404" s="52" t="inlineStr"/>
-      <c r="I404" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/026/026.png</t>
-        </is>
-      </c>
+      <c r="H404" s="51" t="inlineStr"/>
+      <c r="I404" s="51" t="inlineStr"/>
       <c r="J404" s="50" t="inlineStr">
         <is>
-          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
+          <t>哇，恭喜恭喜，真是菩萨保佑，我去把这喜事告诉老爷去！</t>
         </is>
       </c>
       <c r="K404" s="50" t="inlineStr"/>
@@ -26102,12 +26086,12 @@
     <row r="405" hidden="1">
       <c r="A405" s="50" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026_03</t>
         </is>
       </c>
       <c r="B405" s="50" t="inlineStr">
         <is>
-          <t>上元灯节</t>
+          <t>026治疗失败</t>
         </is>
       </c>
       <c r="C405" s="50" t="n">
@@ -26118,9 +26102,9 @@
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E405" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E405" s="50" t="inlineStr">
+        <is>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F405" s="52" t="inlineStr">
@@ -26129,22 +26113,18 @@
         </is>
       </c>
       <c r="G405" s="51" t="inlineStr"/>
-      <c r="H405" s="54" t="inlineStr"/>
+      <c r="H405" s="52" t="inlineStr"/>
       <c r="I405" s="51" t="inlineStr">
         <is>
-          <t>res://Assets/Background/004/004.png</t>
-        </is>
-      </c>
-      <c r="J405" s="53" t="inlineStr">
-        <is>
-          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
-        </is>
-      </c>
-      <c r="K405" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
-        </is>
-      </c>
+          <t>res://Assets/Background/026/026.png</t>
+        </is>
+      </c>
+      <c r="J405" s="50" t="inlineStr">
+        <is>
+          <t>不对不对，我在干什么呀，冷静冷静，再好好想想。</t>
+        </is>
+      </c>
+      <c r="K405" s="50" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="50" t="inlineStr">
@@ -26158,7 +26138,7 @@
         </is>
       </c>
       <c r="C406" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D406" s="50" t="inlineStr">
         <is>
@@ -26167,23 +26147,31 @@
       </c>
       <c r="E406" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F406" s="51" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F406" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G406" s="51" t="inlineStr"/>
       <c r="H406" s="54" t="inlineStr"/>
-      <c r="I406" s="51" t="inlineStr"/>
+      <c r="I406" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/004/004.png</t>
+        </is>
+      </c>
       <c r="J406" s="53" t="inlineStr">
         <is>
-          <t>太好了，咱们快出发吧。</t>
-        </is>
-      </c>
-      <c r="K406" s="50" t="inlineStr"/>
+          <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
+        </is>
+      </c>
+      <c r="K406" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="407" hidden="1">
       <c r="A407" s="50" t="inlineStr">
@@ -26197,7 +26185,7 @@
         </is>
       </c>
       <c r="C407" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D407" s="50" t="inlineStr">
         <is>
@@ -26206,12 +26194,12 @@
       </c>
       <c r="E407" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F407" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F407" s="51" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G407" s="51" t="inlineStr"/>
@@ -26219,7 +26207,7 @@
       <c r="I407" s="51" t="inlineStr"/>
       <c r="J407" s="53" t="inlineStr">
         <is>
-          <t>走。</t>
+          <t>太好了，咱们快出发吧。</t>
         </is>
       </c>
       <c r="K407" s="50" t="inlineStr"/>
@@ -26236,33 +26224,29 @@
         </is>
       </c>
       <c r="C408" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D408" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E408" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F408" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+      <c r="E408" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F408" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G408" s="51" t="inlineStr"/>
-      <c r="H408" s="52" t="inlineStr"/>
-      <c r="I408" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_01.png</t>
-        </is>
-      </c>
+      <c r="H408" s="54" t="inlineStr"/>
+      <c r="I408" s="51" t="inlineStr"/>
       <c r="J408" s="53" t="inlineStr">
         <is>
-          <t>哇，好多人啊！好热闹啊！</t>
+          <t>走。</t>
         </is>
       </c>
       <c r="K408" s="50" t="inlineStr"/>
@@ -26279,33 +26263,33 @@
         </is>
       </c>
       <c r="C409" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D409" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E409" s="53" t="inlineStr">
-        <is>
-          <t>陈皮</t>
-        </is>
-      </c>
-      <c r="F409" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+      <c r="E409" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
+        </is>
+      </c>
+      <c r="F409" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G409" s="51" t="inlineStr"/>
-      <c r="H409" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I409" s="51" t="inlineStr"/>
+      <c r="H409" s="52" t="inlineStr"/>
+      <c r="I409" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_01.png</t>
+        </is>
+      </c>
       <c r="J409" s="53" t="inlineStr">
         <is>
-          <t>看你那没见过世面的样子。</t>
+          <t>哇，好多人啊！好热闹啊！</t>
         </is>
       </c>
       <c r="K409" s="50" t="inlineStr"/>
@@ -26322,36 +26306,36 @@
         </is>
       </c>
       <c r="C410" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D410" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E410" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
-        </is>
-      </c>
-      <c r="F410" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G410" s="55" t="inlineStr"/>
+      <c r="E410" s="53" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F410" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G410" s="51" t="inlineStr"/>
       <c r="H410" s="52" t="inlineStr">
         <is>
           <t>hide</t>
         </is>
       </c>
-      <c r="I410" s="55" t="inlineStr"/>
-      <c r="J410" s="56" t="inlineStr">
-        <is>
-          <t>找打，你别跑！</t>
-        </is>
-      </c>
-      <c r="K410" s="55" t="inlineStr"/>
+      <c r="I410" s="51" t="inlineStr"/>
+      <c r="J410" s="53" t="inlineStr">
+        <is>
+          <t>看你那没见过世面的样子。</t>
+        </is>
+      </c>
+      <c r="K410" s="50" t="inlineStr"/>
     </row>
     <row r="411" hidden="1">
       <c r="A411" s="50" t="inlineStr">
@@ -26365,16 +26349,16 @@
         </is>
       </c>
       <c r="C411" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D411" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E411" s="53" t="inlineStr">
-        <is>
-          <t>李言闻</t>
+      <c r="E411" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F411" s="52" t="inlineStr">
@@ -26383,11 +26367,15 @@
         </is>
       </c>
       <c r="G411" s="55" t="inlineStr"/>
-      <c r="H411" s="55" t="inlineStr"/>
+      <c r="H411" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I411" s="55" t="inlineStr"/>
       <c r="J411" s="56" t="inlineStr">
         <is>
-          <t>那边好像有唱戏的，咱们去那边看看。</t>
+          <t>找打，你别跑！</t>
         </is>
       </c>
       <c r="K411" s="55" t="inlineStr"/>
@@ -26404,37 +26392,29 @@
         </is>
       </c>
       <c r="C412" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D412" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E412" s="50" t="inlineStr">
-        <is>
-          <t>半夏</t>
+      <c r="E412" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F412" s="52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G412" s="55" t="inlineStr"/>
-      <c r="H412" s="52" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="I412" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_02.png</t>
-        </is>
-      </c>
+      <c r="H412" s="55" t="inlineStr"/>
+      <c r="I412" s="55" t="inlineStr"/>
       <c r="J412" s="56" t="inlineStr">
         <is>
-          <t>夫人，那边有座桥，咱们去走百病！</t>
+          <t>那边好像有唱戏的，咱们去那边看看。</t>
         </is>
       </c>
       <c r="K412" s="55" t="inlineStr"/>
@@ -26451,21 +26431,21 @@
         </is>
       </c>
       <c r="C413" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D413" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E413" s="53" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
+      <c r="E413" s="50" t="inlineStr">
+        <is>
+          <t>半夏</t>
         </is>
       </c>
       <c r="F413" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G413" s="55" t="inlineStr"/>
@@ -26474,10 +26454,14 @@
           <t>hide</t>
         </is>
       </c>
-      <c r="I413" s="55" t="inlineStr"/>
+      <c r="I413" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_02.png</t>
+        </is>
+      </c>
       <c r="J413" s="56" t="inlineStr">
         <is>
-          <t>走，今夜走三桥，一年无灾病。</t>
+          <t>夫人，那边有座桥，咱们去走百病！</t>
         </is>
       </c>
       <c r="K413" s="55" t="inlineStr"/>
@@ -26494,7 +26478,7 @@
         </is>
       </c>
       <c r="C414" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D414" s="50" t="inlineStr">
         <is>
@@ -26503,7 +26487,7 @@
       </c>
       <c r="E414" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F414" s="52" t="inlineStr">
@@ -26512,11 +26496,15 @@
         </is>
       </c>
       <c r="G414" s="55" t="inlineStr"/>
-      <c r="H414" s="55" t="inlineStr"/>
+      <c r="H414" s="52" t="inlineStr">
+        <is>
+          <t>hide</t>
+        </is>
+      </c>
       <c r="I414" s="55" t="inlineStr"/>
       <c r="J414" s="56" t="inlineStr">
         <is>
-          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
+          <t>走，今夜走三桥，一年无灾病。</t>
         </is>
       </c>
       <c r="K414" s="55" t="inlineStr"/>
@@ -26533,7 +26521,7 @@
         </is>
       </c>
       <c r="C415" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D415" s="50" t="inlineStr">
         <is>
@@ -26542,12 +26530,12 @@
       </c>
       <c r="E415" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F415" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F415" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G415" s="55" t="inlineStr"/>
@@ -26555,7 +26543,7 @@
       <c r="I415" s="55" t="inlineStr"/>
       <c r="J415" s="56" t="inlineStr">
         <is>
-          <t>哎哟，爹，您就别操心了。</t>
+          <t>儿子啊，你和芷兰准备啥时候要孩子啊？</t>
         </is>
       </c>
       <c r="K415" s="55" t="inlineStr"/>
@@ -26572,7 +26560,7 @@
         </is>
       </c>
       <c r="C416" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D416" s="50" t="inlineStr">
         <is>
@@ -26581,12 +26569,12 @@
       </c>
       <c r="E416" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F416" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F416" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G416" s="55" t="inlineStr"/>
@@ -26594,7 +26582,7 @@
       <c r="I416" s="55" t="inlineStr"/>
       <c r="J416" s="56" t="inlineStr">
         <is>
-          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
+          <t>哎哟，爹，您就别操心了。</t>
         </is>
       </c>
       <c r="K416" s="55" t="inlineStr"/>
@@ -26611,7 +26599,7 @@
         </is>
       </c>
       <c r="C417" s="50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D417" s="50" t="inlineStr">
         <is>
@@ -26620,12 +26608,12 @@
       </c>
       <c r="E417" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F417" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F417" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G417" s="55" t="inlineStr"/>
@@ -26633,7 +26621,7 @@
       <c r="I417" s="55" t="inlineStr"/>
       <c r="J417" s="56" t="inlineStr">
         <is>
-          <t>别说了爹，咱们看戏去吧。</t>
+          <t>你们俩一会儿去南门摸摸福气去，听说可灵了。</t>
         </is>
       </c>
       <c r="K417" s="55" t="inlineStr"/>
@@ -26650,7 +26638,7 @@
         </is>
       </c>
       <c r="C418" s="50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D418" s="50" t="inlineStr">
         <is>
@@ -26659,20 +26647,20 @@
       </c>
       <c r="E418" s="53" t="inlineStr">
         <is>
-          <t>陈皮</t>
+          <t>李东璧</t>
         </is>
       </c>
       <c r="F418" s="54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G418" s="55" t="inlineStr"/>
       <c r="H418" s="55" t="inlineStr"/>
-      <c r="I418" s="51" t="inlineStr"/>
+      <c r="I418" s="55" t="inlineStr"/>
       <c r="J418" s="56" t="inlineStr">
         <is>
-          <t>老爷，那边儿在唱紫钗记呢。</t>
+          <t>别说了爹，咱们看戏去吧。</t>
         </is>
       </c>
       <c r="K418" s="55" t="inlineStr"/>
@@ -26689,25 +26677,29 @@
         </is>
       </c>
       <c r="C419" s="50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D419" s="50" t="inlineStr">
         <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="E419" s="55" t="inlineStr"/>
-      <c r="F419" s="50" t="inlineStr"/>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E419" s="53" t="inlineStr">
+        <is>
+          <t>陈皮</t>
+        </is>
+      </c>
+      <c r="F419" s="54" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="G419" s="55" t="inlineStr"/>
       <c r="H419" s="55" t="inlineStr"/>
-      <c r="I419" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_03.png</t>
-        </is>
-      </c>
+      <c r="I419" s="51" t="inlineStr"/>
       <c r="J419" s="56" t="inlineStr">
         <is>
-          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
+          <t>老爷，那边儿在唱紫钗记呢。</t>
         </is>
       </c>
       <c r="K419" s="55" t="inlineStr"/>
@@ -26724,29 +26716,25 @@
         </is>
       </c>
       <c r="C420" s="50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D420" s="50" t="inlineStr">
         <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E420" s="53" t="inlineStr">
-        <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F420" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="E420" s="55" t="inlineStr"/>
+      <c r="F420" s="50" t="inlineStr"/>
       <c r="G420" s="55" t="inlineStr"/>
       <c r="H420" s="55" t="inlineStr"/>
-      <c r="I420" s="55" t="inlineStr"/>
-      <c r="J420" s="55" t="inlineStr">
-        <is>
-          <t>相公，咱们去猜灯谜吧！</t>
+      <c r="I420" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_03.png</t>
+        </is>
+      </c>
+      <c r="J420" s="56" t="inlineStr">
+        <is>
+          <t>谢皇恩灯华月华，谢天恩春华岁华，遍写着国泰民安天下，遨头去唱声哗。好灯也，说灯花南天门最佳，香车隘挑笼绛纱，喝道转身停马，尘影里看谁家。</t>
         </is>
       </c>
       <c r="K420" s="55" t="inlineStr"/>
@@ -26763,7 +26751,7 @@
         </is>
       </c>
       <c r="C421" s="50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D421" s="50" t="inlineStr">
         <is>
@@ -26772,12 +26760,12 @@
       </c>
       <c r="E421" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F421" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F421" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G421" s="55" t="inlineStr"/>
@@ -26785,7 +26773,7 @@
       <c r="I421" s="55" t="inlineStr"/>
       <c r="J421" s="55" t="inlineStr">
         <is>
-          <t>走！</t>
+          <t>相公，咱们去猜灯谜吧！</t>
         </is>
       </c>
       <c r="K421" s="55" t="inlineStr"/>
@@ -26802,7 +26790,7 @@
         </is>
       </c>
       <c r="C422" s="50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D422" s="50" t="inlineStr">
         <is>
@@ -26821,14 +26809,10 @@
       </c>
       <c r="G422" s="55" t="inlineStr"/>
       <c r="H422" s="55" t="inlineStr"/>
-      <c r="I422" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_04.png</t>
-        </is>
-      </c>
-      <c r="J422" s="68" t="inlineStr">
-        <is>
-          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
+      <c r="I422" s="55" t="inlineStr"/>
+      <c r="J422" s="55" t="inlineStr">
+        <is>
+          <t>走！</t>
         </is>
       </c>
       <c r="K422" s="55" t="inlineStr"/>
@@ -26845,7 +26829,7 @@
         </is>
       </c>
       <c r="C423" s="50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D423" s="50" t="inlineStr">
         <is>
@@ -26854,20 +26838,24 @@
       </c>
       <c r="E423" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F423" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F423" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G423" s="55" t="inlineStr"/>
       <c r="H423" s="55" t="inlineStr"/>
-      <c r="I423" s="55" t="inlineStr"/>
-      <c r="J423" s="55" t="inlineStr">
-        <is>
-          <t>我知道，这是个"府"字。</t>
+      <c r="I423" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_04.png</t>
+        </is>
+      </c>
+      <c r="J423" s="68" t="inlineStr">
+        <is>
+          <t>这么多灯谜，"一点一横长，一撇到南洋，南阳有个人，只有一寸长"，打一个字…</t>
         </is>
       </c>
       <c r="K423" s="55" t="inlineStr"/>
@@ -26884,7 +26872,7 @@
         </is>
       </c>
       <c r="C424" s="50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D424" s="50" t="inlineStr">
         <is>
@@ -26893,12 +26881,12 @@
       </c>
       <c r="E424" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F424" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F424" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G424" s="55" t="inlineStr"/>
@@ -26906,7 +26894,7 @@
       <c r="I424" s="55" t="inlineStr"/>
       <c r="J424" s="55" t="inlineStr">
         <is>
-          <t>还是娘子聪慧啊，哈哈。</t>
+          <t>我知道，这是个"府"字。</t>
         </is>
       </c>
       <c r="K424" s="55" t="inlineStr"/>
@@ -26923,7 +26911,7 @@
         </is>
       </c>
       <c r="C425" s="50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D425" s="50" t="inlineStr">
         <is>
@@ -26932,12 +26920,12 @@
       </c>
       <c r="E425" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F425" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F425" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G425" s="55" t="inlineStr"/>
@@ -26945,7 +26933,7 @@
       <c r="I425" s="55" t="inlineStr"/>
       <c r="J425" s="55" t="inlineStr">
         <is>
-          <t>你看这个，"大雪压青松"，打一味药材。</t>
+          <t>还是娘子聪慧啊，哈哈。</t>
         </is>
       </c>
       <c r="K425" s="55" t="inlineStr"/>
@@ -26962,7 +26950,7 @@
         </is>
       </c>
       <c r="C426" s="50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D426" s="50" t="inlineStr">
         <is>
@@ -26971,20 +26959,20 @@
       </c>
       <c r="E426" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F426" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>吴芷兰</t>
+        </is>
+      </c>
+      <c r="F426" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G426" s="55" t="inlineStr"/>
       <c r="H426" s="55" t="inlineStr"/>
       <c r="I426" s="55" t="inlineStr"/>
-      <c r="J426" s="68" t="inlineStr">
-        <is>
-          <t>这个我会，是"忍冬"。</t>
+      <c r="J426" s="55" t="inlineStr">
+        <is>
+          <t>你看这个，"大雪压青松"，打一味药材。</t>
         </is>
       </c>
       <c r="K426" s="55" t="inlineStr"/>
@@ -27001,7 +26989,7 @@
         </is>
       </c>
       <c r="C427" s="50" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D427" s="50" t="inlineStr">
         <is>
@@ -27010,12 +26998,12 @@
       </c>
       <c r="E427" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F427" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F427" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G427" s="55" t="inlineStr"/>
@@ -27023,7 +27011,7 @@
       <c r="I427" s="55" t="inlineStr"/>
       <c r="J427" s="68" t="inlineStr">
         <is>
-          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
+          <t>这个我会，是"忍冬"。</t>
         </is>
       </c>
       <c r="K427" s="55" t="inlineStr"/>
@@ -27040,7 +27028,7 @@
         </is>
       </c>
       <c r="C428" s="50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D428" s="50" t="inlineStr">
         <is>
@@ -27059,14 +27047,10 @@
       </c>
       <c r="G428" s="55" t="inlineStr"/>
       <c r="H428" s="55" t="inlineStr"/>
-      <c r="I428" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_05.png</t>
-        </is>
-      </c>
-      <c r="J428" s="55" t="inlineStr">
-        <is>
-          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
+      <c r="I428" s="55" t="inlineStr"/>
+      <c r="J428" s="68" t="inlineStr">
+        <is>
+          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
         </is>
       </c>
       <c r="K428" s="55" t="inlineStr"/>
@@ -27083,7 +27067,7 @@
         </is>
       </c>
       <c r="C429" s="50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D429" s="50" t="inlineStr">
         <is>
@@ -27092,20 +27076,24 @@
       </c>
       <c r="E429" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F429" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F429" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G429" s="55" t="inlineStr"/>
       <c r="H429" s="55" t="inlineStr"/>
-      <c r="I429" s="55" t="inlineStr"/>
+      <c r="I429" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_05.png</t>
+        </is>
+      </c>
       <c r="J429" s="55" t="inlineStr">
         <is>
-          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
+          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
         </is>
       </c>
       <c r="K429" s="55" t="inlineStr"/>
@@ -27122,7 +27110,7 @@
         </is>
       </c>
       <c r="C430" s="50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D430" s="50" t="inlineStr">
         <is>
@@ -27131,12 +27119,12 @@
       </c>
       <c r="E430" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
-        </is>
-      </c>
-      <c r="F430" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F430" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G430" s="55" t="inlineStr"/>
@@ -27144,7 +27132,7 @@
       <c r="I430" s="55" t="inlineStr"/>
       <c r="J430" s="55" t="inlineStr">
         <is>
-          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
         </is>
       </c>
       <c r="K430" s="55" t="inlineStr"/>
@@ -27161,7 +27149,7 @@
         </is>
       </c>
       <c r="C431" s="50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D431" s="50" t="inlineStr">
         <is>
@@ -27170,12 +27158,12 @@
       </c>
       <c r="E431" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F431" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G431" s="55" t="inlineStr"/>
@@ -27183,7 +27171,7 @@
       <c r="I431" s="55" t="inlineStr"/>
       <c r="J431" s="55" t="inlineStr">
         <is>
-          <t>是啊，一家人平平安安就好啊。</t>
+          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
         </is>
       </c>
       <c r="K431" s="55" t="inlineStr"/>
@@ -27200,7 +27188,7 @@
         </is>
       </c>
       <c r="C432" s="50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D432" s="50" t="inlineStr">
         <is>
@@ -27222,89 +27210,89 @@
       <c r="I432" s="55" t="inlineStr"/>
       <c r="J432" s="55" t="inlineStr">
         <is>
+          <t>是啊，一家人平平安安就好啊。</t>
+        </is>
+      </c>
+      <c r="K432" s="55" t="inlineStr"/>
+    </row>
+    <row r="433" hidden="1">
+      <c r="A433" s="50" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B433" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C433" s="50" t="n">
+        <v>28</v>
+      </c>
+      <c r="D433" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E433" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F433" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G433" s="55" t="inlineStr"/>
+      <c r="H433" s="55" t="inlineStr"/>
+      <c r="I433" s="55" t="inlineStr"/>
+      <c r="J433" s="55" t="inlineStr">
+        <is>
           <t>好了，不早了，咱们该回家了。</t>
         </is>
       </c>
-      <c r="K432" s="55" t="inlineStr"/>
-    </row>
-    <row r="433" hidden="1" ht="30" customHeight="1">
-      <c r="A433" s="50" t="inlineStr">
+      <c r="K433" s="55" t="inlineStr"/>
+    </row>
+    <row r="434" hidden="1" ht="30" customHeight="1">
+      <c r="A434" s="50" t="inlineStr">
         <is>
           <t>028_01</t>
         </is>
       </c>
-      <c r="B433" s="50" t="inlineStr">
+      <c r="B434" s="50" t="inlineStr">
         <is>
           <t>曾题名痰火扰心</t>
         </is>
       </c>
-      <c r="C433" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D433" s="50" t="inlineStr">
+      <c r="C434" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D434" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E433" s="53" t="inlineStr">
+      <c r="E434" s="53" t="inlineStr">
         <is>
           <t>曾和</t>
         </is>
       </c>
-      <c r="F433" s="51" t="inlineStr">
+      <c r="F434" s="51" t="inlineStr">
         <is>
           <t>left</t>
-        </is>
-      </c>
-      <c r="G433" s="51" t="inlineStr"/>
-      <c r="H433" s="54" t="inlineStr"/>
-      <c r="I433" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J433" s="53" t="inlineStr">
-        <is>
-          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
-        </is>
-      </c>
-      <c r="K433" s="50" t="inlineStr"/>
-    </row>
-    <row r="434" hidden="1">
-      <c r="A434" s="50" t="inlineStr">
-        <is>
-          <t>028_01</t>
-        </is>
-      </c>
-      <c r="B434" s="50" t="inlineStr">
-        <is>
-          <t>曾题名痰火扰心</t>
-        </is>
-      </c>
-      <c r="C434" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D434" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
-      <c r="E434" s="53" t="inlineStr">
-        <is>
-          <t>曾题名</t>
-        </is>
-      </c>
-      <c r="F434" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
         </is>
       </c>
       <c r="G434" s="51" t="inlineStr"/>
       <c r="H434" s="54" t="inlineStr"/>
-      <c r="I434" s="51" t="inlineStr"/>
+      <c r="I434" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J434" s="53" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
         </is>
       </c>
       <c r="K434" s="50" t="inlineStr"/>
@@ -27321,7 +27309,7 @@
         </is>
       </c>
       <c r="C435" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D435" s="50" t="inlineStr">
         <is>
@@ -27330,12 +27318,12 @@
       </c>
       <c r="E435" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F435" s="54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G435" s="51" t="inlineStr"/>
@@ -27343,7 +27331,7 @@
       <c r="I435" s="51" t="inlineStr"/>
       <c r="J435" s="53" t="inlineStr">
         <is>
-          <t>别急，坐下来让我看看。</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K435" s="50" t="inlineStr"/>
@@ -27360,62 +27348,58 @@
         </is>
       </c>
       <c r="C436" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D436" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E436" s="50" t="inlineStr"/>
-      <c r="F436" s="51" t="inlineStr"/>
+      <c r="E436" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F436" s="54" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="G436" s="51" t="inlineStr"/>
-      <c r="H436" s="51" t="inlineStr"/>
+      <c r="H436" s="54" t="inlineStr"/>
       <c r="I436" s="51" t="inlineStr"/>
-      <c r="J436" s="50" t="inlineStr"/>
+      <c r="J436" s="53" t="inlineStr">
+        <is>
+          <t>别急，坐下来让我看看。</t>
+        </is>
+      </c>
       <c r="K436" s="50" t="inlineStr"/>
     </row>
     <row r="437" hidden="1">
       <c r="A437" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B437" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C437" s="50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D437" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E437" s="53" t="inlineStr">
-        <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F437" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="E437" s="50" t="inlineStr"/>
+      <c r="F437" s="51" t="inlineStr"/>
       <c r="G437" s="51" t="inlineStr"/>
-      <c r="H437" s="54" t="inlineStr"/>
-      <c r="I437" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J437" s="53" t="inlineStr">
-        <is>
-          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
-        </is>
-      </c>
+      <c r="H437" s="51" t="inlineStr"/>
+      <c r="I437" s="51" t="inlineStr"/>
+      <c r="J437" s="50" t="inlineStr"/>
       <c r="K437" s="50" t="inlineStr"/>
     </row>
     <row r="438" hidden="1">
@@ -27430,7 +27414,7 @@
         </is>
       </c>
       <c r="C438" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D438" s="50" t="inlineStr">
         <is>
@@ -27439,20 +27423,24 @@
       </c>
       <c r="E438" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F438" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F438" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G438" s="51" t="inlineStr"/>
       <c r="H438" s="54" t="inlineStr"/>
-      <c r="I438" s="51" t="inlineStr"/>
+      <c r="I438" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J438" s="53" t="inlineStr">
         <is>
-          <t>好好的怎么就得了这怪病呢？</t>
+          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
         </is>
       </c>
       <c r="K438" s="50" t="inlineStr"/>
@@ -27469,7 +27457,7 @@
         </is>
       </c>
       <c r="C439" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D439" s="50" t="inlineStr">
         <is>
@@ -27478,20 +27466,20 @@
       </c>
       <c r="E439" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F439" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F439" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G439" s="51" t="inlineStr"/>
-      <c r="H439" s="51" t="inlineStr"/>
+      <c r="H439" s="54" t="inlineStr"/>
       <c r="I439" s="51" t="inlineStr"/>
       <c r="J439" s="53" t="inlineStr">
         <is>
-          <t>是不是读书压力太大了呀？</t>
+          <t>好好的怎么就得了这怪病呢？</t>
         </is>
       </c>
       <c r="K439" s="50" t="inlineStr"/>
@@ -27508,7 +27496,7 @@
         </is>
       </c>
       <c r="C440" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D440" s="50" t="inlineStr">
         <is>
@@ -27517,12 +27505,12 @@
       </c>
       <c r="E440" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
-        </is>
-      </c>
-      <c r="F440" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F440" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G440" s="51" t="inlineStr"/>
@@ -27530,7 +27518,7 @@
       <c r="I440" s="51" t="inlineStr"/>
       <c r="J440" s="53" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>是不是读书压力太大了呀？</t>
         </is>
       </c>
       <c r="K440" s="50" t="inlineStr"/>
@@ -27547,7 +27535,7 @@
         </is>
       </c>
       <c r="C441" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D441" s="50" t="inlineStr">
         <is>
@@ -27556,12 +27544,12 @@
       </c>
       <c r="E441" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F441" s="54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G441" s="51" t="inlineStr"/>
@@ -27569,7 +27557,7 @@
       <c r="I441" s="51" t="inlineStr"/>
       <c r="J441" s="53" t="inlineStr">
         <is>
-          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K441" s="50" t="inlineStr"/>
@@ -27586,7 +27574,7 @@
         </is>
       </c>
       <c r="C442" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D442" s="50" t="inlineStr">
         <is>
@@ -27603,15 +27591,15 @@
           <t>left</t>
         </is>
       </c>
-      <c r="G442" s="55" t="inlineStr"/>
-      <c r="H442" s="55" t="inlineStr"/>
-      <c r="I442" s="55" t="inlineStr"/>
-      <c r="J442" s="56" t="inlineStr">
-        <is>
-          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
-        </is>
-      </c>
-      <c r="K442" s="55" t="inlineStr"/>
+      <c r="G442" s="51" t="inlineStr"/>
+      <c r="H442" s="51" t="inlineStr"/>
+      <c r="I442" s="51" t="inlineStr"/>
+      <c r="J442" s="53" t="inlineStr">
+        <is>
+          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+        </is>
+      </c>
+      <c r="K442" s="50" t="inlineStr"/>
     </row>
     <row r="443" hidden="1">
       <c r="A443" s="50" t="inlineStr">
@@ -27625,7 +27613,7 @@
         </is>
       </c>
       <c r="C443" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D443" s="50" t="inlineStr">
         <is>
@@ -27634,20 +27622,20 @@
       </c>
       <c r="E443" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F443" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G443" s="51" t="inlineStr"/>
-      <c r="H443" s="51" t="inlineStr"/>
-      <c r="I443" s="51" t="inlineStr"/>
-      <c r="J443" s="53" t="inlineStr">
-        <is>
-          <t>…</t>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G443" s="55" t="inlineStr"/>
+      <c r="H443" s="55" t="inlineStr"/>
+      <c r="I443" s="55" t="inlineStr"/>
+      <c r="J443" s="56" t="inlineStr">
+        <is>
+          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
         </is>
       </c>
       <c r="K443" s="55" t="inlineStr"/>
@@ -27664,7 +27652,7 @@
         </is>
       </c>
       <c r="C444" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D444" s="50" t="inlineStr">
         <is>
@@ -27673,20 +27661,20 @@
       </c>
       <c r="E444" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F444" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="G444" s="55" t="inlineStr"/>
-      <c r="H444" s="55" t="inlineStr"/>
-      <c r="I444" s="55" t="inlineStr"/>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F444" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G444" s="51" t="inlineStr"/>
+      <c r="H444" s="51" t="inlineStr"/>
+      <c r="I444" s="51" t="inlineStr"/>
       <c r="J444" s="53" t="inlineStr">
         <is>
-          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K444" s="55" t="inlineStr"/>
@@ -27703,7 +27691,7 @@
         </is>
       </c>
       <c r="C445" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D445" s="50" t="inlineStr">
         <is>
@@ -27712,12 +27700,12 @@
       </c>
       <c r="E445" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F445" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F445" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G445" s="55" t="inlineStr"/>
@@ -27725,7 +27713,7 @@
       <c r="I445" s="55" t="inlineStr"/>
       <c r="J445" s="53" t="inlineStr">
         <is>
-          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
+          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
         </is>
       </c>
       <c r="K445" s="55" t="inlineStr"/>
@@ -27742,7 +27730,7 @@
         </is>
       </c>
       <c r="C446" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D446" s="50" t="inlineStr">
         <is>
@@ -27764,7 +27752,7 @@
       <c r="I446" s="55" t="inlineStr"/>
       <c r="J446" s="53" t="inlineStr">
         <is>
-          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
+          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
         </is>
       </c>
       <c r="K446" s="55" t="inlineStr"/>
@@ -27781,7 +27769,7 @@
         </is>
       </c>
       <c r="C447" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D447" s="50" t="inlineStr">
         <is>
@@ -27790,12 +27778,12 @@
       </c>
       <c r="E447" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F447" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G447" s="55" t="inlineStr"/>
@@ -27803,7 +27791,7 @@
       <c r="I447" s="55" t="inlineStr"/>
       <c r="J447" s="53" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
         </is>
       </c>
       <c r="K447" s="55" t="inlineStr"/>
@@ -27820,7 +27808,7 @@
         </is>
       </c>
       <c r="C448" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D448" s="50" t="inlineStr">
         <is>
@@ -27829,20 +27817,20 @@
       </c>
       <c r="E448" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F448" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F448" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G448" s="55" t="inlineStr"/>
       <c r="H448" s="55" t="inlineStr"/>
       <c r="I448" s="55" t="inlineStr"/>
-      <c r="J448" s="87" t="inlineStr">
-        <is>
-          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
+      <c r="J448" s="53" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
       <c r="K448" s="55" t="inlineStr"/>
@@ -27859,7 +27847,7 @@
         </is>
       </c>
       <c r="C449" s="50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D449" s="50" t="inlineStr">
         <is>
@@ -27868,20 +27856,20 @@
       </c>
       <c r="E449" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F449" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F449" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G449" s="55" t="inlineStr"/>
       <c r="H449" s="55" t="inlineStr"/>
       <c r="I449" s="55" t="inlineStr"/>
-      <c r="J449" s="87" t="inlineStr">
-        <is>
-          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+      <c r="J449" s="85" t="inlineStr">
+        <is>
+          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
         </is>
       </c>
       <c r="K449" s="55" t="inlineStr"/>
@@ -27898,7 +27886,7 @@
         </is>
       </c>
       <c r="C450" s="50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D450" s="50" t="inlineStr">
         <is>
@@ -27918,9 +27906,9 @@
       <c r="G450" s="55" t="inlineStr"/>
       <c r="H450" s="55" t="inlineStr"/>
       <c r="I450" s="55" t="inlineStr"/>
-      <c r="J450" s="87" t="inlineStr">
-        <is>
-          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+      <c r="J450" s="85" t="inlineStr">
+        <is>
+          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
         </is>
       </c>
       <c r="K450" s="55" t="inlineStr"/>
@@ -27937,7 +27925,7 @@
         </is>
       </c>
       <c r="C451" s="50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D451" s="50" t="inlineStr">
         <is>
@@ -27946,20 +27934,20 @@
       </c>
       <c r="E451" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F451" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F451" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G451" s="55" t="inlineStr"/>
       <c r="H451" s="55" t="inlineStr"/>
       <c r="I451" s="55" t="inlineStr"/>
-      <c r="J451" s="87" t="inlineStr">
-        <is>
-          <t>…</t>
+      <c r="J451" s="85" t="inlineStr">
+        <is>
+          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
         </is>
       </c>
       <c r="K451" s="55" t="inlineStr"/>
@@ -27967,45 +27955,84 @@
     <row r="452">
       <c r="A452" s="50" t="inlineStr">
         <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B452" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C452" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D452" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E452" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F452" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G452" s="55" t="inlineStr"/>
+      <c r="H452" s="55" t="inlineStr"/>
+      <c r="I452" s="55" t="inlineStr"/>
+      <c r="J452" s="85" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K452" s="55" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="50" t="inlineStr">
+        <is>
           <t>028_03</t>
         </is>
       </c>
-      <c r="B452" s="50" t="inlineStr">
+      <c r="B453" s="50" t="inlineStr">
         <is>
           <t>028治疗失败</t>
         </is>
       </c>
-      <c r="C452" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D452" s="50" t="inlineStr">
+      <c r="C453" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D453" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E452" s="53" t="inlineStr">
+      <c r="E453" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F452" s="52" t="inlineStr">
+      <c r="F453" s="52" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G452" s="51" t="inlineStr"/>
-      <c r="H452" s="54" t="inlineStr"/>
-      <c r="I452" s="51" t="inlineStr">
+      <c r="G453" s="51" t="inlineStr"/>
+      <c r="H453" s="54" t="inlineStr"/>
+      <c r="I453" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J452" s="53" t="inlineStr">
+      <c r="J453" s="53" t="inlineStr">
         <is>
           <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
-      <c r="K452" s="50" t="inlineStr"/>
+      <c r="K453" s="50" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BI450">
@@ -28034,7 +28061,7 @@
     <col width="29.5" customWidth="1" style="7" min="3" max="3"/>
     <col width="29.875" customWidth="1" style="3" min="4" max="4"/>
     <col width="31.25" customWidth="1" style="3" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" style="83" min="6" max="6"/>
+    <col width="11.375" bestFit="1" customWidth="1" style="82" min="6" max="6"/>
     <col width="20.75" customWidth="1" style="3" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -28064,7 +28091,7 @@
           <t>BookID</t>
         </is>
       </c>
-      <c r="F1" s="84" t="inlineStr">
+      <c r="F1" s="83" t="inlineStr">
         <is>
           <t>sort_index</t>
         </is>
@@ -28101,7 +28128,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F2" s="85" t="n">
+      <c r="F2" s="84" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="10" t="inlineStr">
@@ -28141,7 +28168,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F3" s="85" t="n">
+      <c r="F3" s="84" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -28181,7 +28208,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F4" s="85" t="n">
+      <c r="F4" s="84" t="n">
         <v>3</v>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -28221,7 +28248,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F5" s="85" t="n">
+      <c r="F5" s="84" t="n">
         <v>4</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -28261,7 +28288,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F6" s="85" t="n">
+      <c r="F6" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -28301,7 +28328,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F7" s="85" t="n">
+      <c r="F7" s="84" t="n">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -28341,7 +28368,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F8" s="85" t="n">
+      <c r="F8" s="84" t="n">
         <v>7</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -28381,7 +28408,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F9" s="85" t="n">
+      <c r="F9" s="84" t="n">
         <v>8</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -28421,7 +28448,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F10" s="85" t="n">
+      <c r="F10" s="84" t="n">
         <v>9</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -28462,7 +28489,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F11" s="85" t="n">
+      <c r="F11" s="84" t="n">
         <v>10</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -28502,7 +28529,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F12" s="85" t="n">
+      <c r="F12" s="84" t="n">
         <v>11</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -28542,7 +28569,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F13" s="85" t="n">
+      <c r="F13" s="84" t="n">
         <v>12</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -28582,7 +28609,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F14" s="85" t="n">
+      <c r="F14" s="84" t="n">
         <v>13</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -28622,7 +28649,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F15" s="85" t="n">
+      <c r="F15" s="84" t="n">
         <v>14</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -28662,7 +28689,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F16" s="85" t="n">
+      <c r="F16" s="84" t="n">
         <v>15</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -28702,7 +28729,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F17" s="85" t="n">
+      <c r="F17" s="84" t="n">
         <v>16</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -28743,7 +28770,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F18" s="85" t="n">
+      <c r="F18" s="84" t="n">
         <v>17</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -28784,7 +28811,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F19" s="85" t="n">
+      <c r="F19" s="84" t="n">
         <v>18</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -28824,7 +28851,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F20" s="85" t="n">
+      <c r="F20" s="84" t="n">
         <v>19</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -28864,7 +28891,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F21" s="85" t="n">
+      <c r="F21" s="84" t="n">
         <v>20</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -28904,7 +28931,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F22" s="85" t="n">
+      <c r="F22" s="84" t="n">
         <v>21</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -28944,7 +28971,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F23" s="85" t="n">
+      <c r="F23" s="84" t="n">
         <v>22</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -28985,7 +29012,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F24" s="85" t="n">
+      <c r="F24" s="84" t="n">
         <v>23</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -29025,7 +29052,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F25" s="85" t="n">
+      <c r="F25" s="84" t="n">
         <v>24</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -29065,7 +29092,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F26" s="85" t="n">
+      <c r="F26" s="84" t="n">
         <v>25</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -29105,7 +29132,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F27" s="85" t="n">
+      <c r="F27" s="84" t="n">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -29145,7 +29172,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F28" s="85" t="n">
+      <c r="F28" s="84" t="n">
         <v>27</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -29185,7 +29212,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F29" s="85" t="n">
+      <c r="F29" s="84" t="n">
         <v>28</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -29225,7 +29252,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F30" s="85" t="n">
+      <c r="F30" s="84" t="n">
         <v>29</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -29265,7 +29292,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F31" s="85" t="n">
+      <c r="F31" s="84" t="n">
         <v>30</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -29305,7 +29332,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F32" s="85" t="n">
+      <c r="F32" s="84" t="n">
         <v>31</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -29346,7 +29373,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F33" s="85" t="n">
+      <c r="F33" s="84" t="n">
         <v>32</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -29386,7 +29413,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F34" s="85" t="n">
+      <c r="F34" s="84" t="n">
         <v>33</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -29426,7 +29453,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F35" s="85" t="n">
+      <c r="F35" s="84" t="n">
         <v>34</v>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -29466,7 +29493,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F36" s="85" t="n">
+      <c r="F36" s="84" t="n">
         <v>35</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -29506,7 +29533,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F37" s="85" t="n">
+      <c r="F37" s="84" t="n">
         <v>36</v>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -29546,7 +29573,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F38" s="85" t="n">
+      <c r="F38" s="84" t="n">
         <v>37</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -29586,7 +29613,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F39" s="85" t="n">
+      <c r="F39" s="84" t="n">
         <v>38</v>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -29626,7 +29653,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F40" s="85" t="n">
+      <c r="F40" s="84" t="n">
         <v>39</v>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -29667,7 +29694,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F41" s="85" t="n">
+      <c r="F41" s="84" t="n">
         <v>40</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -29708,7 +29735,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F42" s="85" t="n">
+      <c r="F42" s="84" t="n">
         <v>41</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -29749,7 +29776,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F43" s="85" t="n">
+      <c r="F43" s="84" t="n">
         <v>42</v>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -29790,7 +29817,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F44" s="85" t="n">
+      <c r="F44" s="84" t="n">
         <v>43</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -29832,7 +29859,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F45" s="85" t="n">
+      <c r="F45" s="84" t="n">
         <v>44</v>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -29874,7 +29901,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F46" s="85" t="n">
+      <c r="F46" s="84" t="n">
         <v>45</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -29915,7 +29942,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F47" s="85" t="n">
+      <c r="F47" s="84" t="n">
         <v>46</v>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -29957,7 +29984,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F48" s="85" t="n">
+      <c r="F48" s="84" t="n">
         <v>47</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -29999,7 +30026,7 @@
           <t>zhu_bing_yuan_hou_lun</t>
         </is>
       </c>
-      <c r="F49" s="85" t="n">
+      <c r="F49" s="84" t="n">
         <v>48</v>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -30240,8 +30267,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="136"/>
-    <col width="9" customWidth="1" style="9" min="137" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="137"/>
+    <col width="9" customWidth="1" style="9" min="138" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -31057,7 +31084,7 @@
     <col width="15.125" customWidth="1" style="3" min="2" max="2"/>
     <col width="21.375" customWidth="1" style="3" min="3" max="3"/>
     <col width="49.125" customWidth="1" style="3" min="4" max="4"/>
-    <col width="11.375" bestFit="1" customWidth="1" style="83" min="5" max="5"/>
+    <col width="11.375" bestFit="1" customWidth="1" style="82" min="5" max="5"/>
     <col width="13" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -31082,7 +31109,7 @@
           <t>BookID</t>
         </is>
       </c>
-      <c r="E1" s="84" t="inlineStr">
+      <c r="E1" s="83" t="inlineStr">
         <is>
           <t>sort_index</t>
         </is>
@@ -31114,7 +31141,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E2" s="85" t="n">
+      <c r="E2" s="84" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -31156,7 +31183,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E3" s="85" t="n">
+      <c r="E3" s="84" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -31197,7 +31224,7 @@
           <t>wen_bing_tiao_bian</t>
         </is>
       </c>
-      <c r="E4" s="85" t="n">
+      <c r="E4" s="84" t="n">
         <v>3</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -31242,7 +31269,7 @@
           <t>wen_bing_tiao_bian</t>
         </is>
       </c>
-      <c r="E5" s="85" t="n">
+      <c r="E5" s="84" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -31288,7 +31315,7 @@
           <t>wen_bing_tiao_bian</t>
         </is>
       </c>
-      <c r="E6" s="85" t="n">
+      <c r="E6" s="84" t="n">
         <v>5</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -31333,7 +31360,7 @@
           <t>jiu_yuan_fang</t>
         </is>
       </c>
-      <c r="E7" s="85" t="n">
+      <c r="E7" s="84" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -31375,7 +31402,7 @@
           <t>jin_gui_yao_lue</t>
         </is>
       </c>
-      <c r="E8" s="85" t="n">
+      <c r="E8" s="84" t="n">
         <v>7</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -31419,7 +31446,7 @@
           <t>jin_gui_yao_lue</t>
         </is>
       </c>
-      <c r="E9" s="85" t="n">
+      <c r="E9" s="84" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -31462,7 +31489,7 @@
           <t>tai_yi_yuan_jing_yan_qi_xiao_liang_fang_da_quan</t>
         </is>
       </c>
-      <c r="E10" s="85" t="n">
+      <c r="E10" s="84" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -31506,7 +31533,7 @@
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E11" s="85" t="n">
+      <c r="E11" s="84" t="n">
         <v>10</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -31552,7 +31579,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E12" s="85" t="n">
+      <c r="E12" s="84" t="n">
         <v>11</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -31595,7 +31622,7 @@
           <t>bei_ji_qian_jin_yao_fang</t>
         </is>
       </c>
-      <c r="E13" s="85" t="n">
+      <c r="E13" s="84" t="n">
         <v>12</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -31638,7 +31665,7 @@
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E14" s="85" t="n">
+      <c r="E14" s="84" t="n">
         <v>13</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -31681,7 +31708,7 @@
           <t>wen_bing_tiao_bian</t>
         </is>
       </c>
-      <c r="E15" s="85" t="n">
+      <c r="E15" s="84" t="n">
         <v>14</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -31725,7 +31752,7 @@
           <t>yi_fang_kao</t>
         </is>
       </c>
-      <c r="E16" s="85" t="n">
+      <c r="E16" s="84" t="n">
         <v>15</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -31771,7 +31798,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E17" s="85" t="n">
+      <c r="E17" s="84" t="n">
         <v>16</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -31817,7 +31844,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E18" s="85" t="n">
+      <c r="E18" s="84" t="n">
         <v>17</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -31862,7 +31889,7 @@
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E19" s="85" t="n">
+      <c r="E19" s="84" t="n">
         <v>18</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -31905,7 +31932,7 @@
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E20" s="85" t="n">
+      <c r="E20" s="84" t="n">
         <v>19</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -31948,7 +31975,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E21" s="85" t="n">
+      <c r="E21" s="84" t="n">
         <v>20</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -31991,7 +32018,7 @@
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E22" s="85" t="n">
+      <c r="E22" s="84" t="n">
         <v>21</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -32035,7 +32062,7 @@
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E23" s="85" t="n">
+      <c r="E23" s="84" t="n">
         <v>22</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -32080,7 +32107,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E24" s="85" t="n">
+      <c r="E24" s="84" t="n">
         <v>23</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -32125,7 +32152,7 @@
           <t>xiao_er_yao_zheng_zhi_jue</t>
         </is>
       </c>
-      <c r="E25" s="85" t="n">
+      <c r="E25" s="84" t="n">
         <v>24</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -32168,7 +32195,7 @@
           <t>tai_yi_yuan_jing_yan_qi_xiao_liang_fang_da_quan</t>
         </is>
       </c>
-      <c r="E26" s="85" t="n">
+      <c r="E26" s="84" t="n">
         <v>25</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -32214,7 +32241,7 @@
           <t>ren_zhai_zhi_zhi_fang_lun</t>
         </is>
       </c>
-      <c r="E27" s="85" t="n">
+      <c r="E27" s="84" t="n">
         <v>26</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -32260,7 +32287,7 @@
           <t>yi_lin_gai_cuo</t>
         </is>
       </c>
-      <c r="E28" s="85" t="n">
+      <c r="E28" s="84" t="n">
         <v>27</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -32306,7 +32333,7 @@
           <t>jin_gui_yao_lue</t>
         </is>
       </c>
-      <c r="E29" s="85" t="n">
+      <c r="E29" s="84" t="n">
         <v>28</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -32352,7 +32379,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E30" s="85" t="n">
+      <c r="E30" s="84" t="n">
         <v>29</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -32393,7 +32420,7 @@
           <t>bei_ji_qian_jin_yao_fang</t>
         </is>
       </c>
-      <c r="E31" s="85" t="n">
+      <c r="E31" s="84" t="n">
         <v>30</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -32441,7 +32468,7 @@
           <t>yan_shi_ji_sheng_fang</t>
         </is>
       </c>
-      <c r="E32" s="85" t="n">
+      <c r="E32" s="84" t="n">
         <v>31</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -32487,7 +32514,7 @@
           <t>lan_shi_mi_cang</t>
         </is>
       </c>
-      <c r="E33" s="85" t="n">
+      <c r="E33" s="84" t="n">
         <v>32</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -32532,7 +32559,7 @@
           <t>jing_yue_quan_shu</t>
         </is>
       </c>
-      <c r="E34" s="85" t="n">
+      <c r="E34" s="84" t="n">
         <v>33</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -32578,7 +32605,7 @@
           <t>jing_yue_quan_shu</t>
         </is>
       </c>
-      <c r="E35" s="85" t="n">
+      <c r="E35" s="84" t="n">
         <v>34</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -32622,7 +32649,7 @@
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E36" s="85" t="n">
+      <c r="E36" s="84" t="n">
         <v>35</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -32665,7 +32692,7 @@
           <t>yi_lin_gai_cuo</t>
         </is>
       </c>
-      <c r="E37" s="85" t="n">
+      <c r="E37" s="84" t="n">
         <v>36</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -32714,7 +32741,7 @@
           <t>liu_zhou_yi_hua</t>
         </is>
       </c>
-      <c r="E38" s="85" t="n">
+      <c r="E38" s="84" t="n">
         <v>37</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -32758,7 +32785,7 @@
           <t>pu_ji_ben_shi_fang</t>
         </is>
       </c>
-      <c r="E39" s="85" t="n">
+      <c r="E39" s="84" t="n">
         <v>38</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -32804,7 +32831,7 @@
           <t>tai_ping_hui_min_he_ji_ju_fang</t>
         </is>
       </c>
-      <c r="E40" s="85" t="n">
+      <c r="E40" s="84" t="n">
         <v>39</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -32849,7 +32876,7 @@
           <t>wang_shi_bo_ji_fang</t>
         </is>
       </c>
-      <c r="E41" s="85" t="n">
+      <c r="E41" s="84" t="n">
         <v>40</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -32894,7 +32921,7 @@
           <t>xiao_er_yao_zheng_zhi_jue</t>
         </is>
       </c>
-      <c r="E42" s="85" t="n">
+      <c r="E42" s="84" t="n">
         <v>41</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -32939,7 +32966,7 @@
           <t>jin_gui_yao_lue</t>
         </is>
       </c>
-      <c r="E43" s="85" t="n">
+      <c r="E43" s="84" t="n">
         <v>42</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -32981,7 +33008,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E44" s="85" t="n">
+      <c r="E44" s="84" t="n">
         <v>43</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -33025,7 +33052,7 @@
           <t>jing_yue_quan_shu</t>
         </is>
       </c>
-      <c r="E45" s="85" t="n">
+      <c r="E45" s="84" t="n">
         <v>44</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -33069,7 +33096,7 @@
           <t>yi_fang_ji_jie</t>
         </is>
       </c>
-      <c r="E46" s="85" t="n">
+      <c r="E46" s="84" t="n">
         <v>45</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -33113,7 +33140,7 @@
           <t>jing_yue_quan_shu</t>
         </is>
       </c>
-      <c r="E47" s="85" t="n">
+      <c r="E47" s="84" t="n">
         <v>46</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -33159,7 +33186,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E48" s="85" t="n">
+      <c r="E48" s="84" t="n">
         <v>47</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -33203,7 +33230,7 @@
           <t>shang_han_lun</t>
         </is>
       </c>
-      <c r="E49" s="85" t="n">
+      <c r="E49" s="84" t="n">
         <v>48</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -45094,7 +45121,7 @@
     <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
     <col width="11.125" customWidth="1" style="7" min="7" max="7"/>
     <col width="24.25" customWidth="1" style="3" min="8" max="8"/>
-    <col width="11.375" bestFit="1" customWidth="1" style="83" min="9" max="9"/>
+    <col width="11.375" bestFit="1" customWidth="1" style="82" min="9" max="9"/>
     <col width="41.75" customWidth="1" style="3" min="10" max="10"/>
     <col width="8.75" customWidth="1" style="7" min="11" max="11"/>
     <col width="14.25" customWidth="1" style="7" min="12" max="12"/>
@@ -45142,7 +45169,7 @@
           <t>BookID</t>
         </is>
       </c>
-      <c r="I1" s="84" t="inlineStr">
+      <c r="I1" s="83" t="inlineStr">
         <is>
           <t>sort_index</t>
         </is>
@@ -45202,7 +45229,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I2" s="85" t="n">
+      <c r="I2" s="84" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -45272,7 +45299,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I3" s="85" t="n">
+      <c r="I3" s="84" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
@@ -45342,7 +45369,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I4" s="85" t="n">
+      <c r="I4" s="84" t="n">
         <v>3</v>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -45411,7 +45438,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I5" s="85" t="n">
+      <c r="I5" s="84" t="n">
         <v>4</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -45483,7 +45510,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I6" s="85" t="n">
+      <c r="I6" s="84" t="n">
         <v>5</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -45559,7 +45586,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I7" s="85" t="n">
+      <c r="I7" s="84" t="n">
         <v>6</v>
       </c>
       <c r="J7" s="25" t="inlineStr">
@@ -45630,7 +45657,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I8" s="85" t="n">
+      <c r="I8" s="84" t="n">
         <v>7</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -45702,7 +45729,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I9" s="85" t="n">
+      <c r="I9" s="84" t="n">
         <v>8</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -45770,7 +45797,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I10" s="85" t="n">
+      <c r="I10" s="84" t="n">
         <v>9</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -45842,7 +45869,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I11" s="85" t="n">
+      <c r="I11" s="84" t="n">
         <v>10</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -45910,7 +45937,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I12" s="85" t="n">
+      <c r="I12" s="84" t="n">
         <v>11</v>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -45984,7 +46011,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I13" s="85" t="n">
+      <c r="I13" s="84" t="n">
         <v>12</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -46056,7 +46083,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I14" s="85" t="n">
+      <c r="I14" s="84" t="n">
         <v>13</v>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -46124,7 +46151,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I15" s="85" t="n">
+      <c r="I15" s="84" t="n">
         <v>14</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -46194,7 +46221,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I16" s="85" t="n">
+      <c r="I16" s="84" t="n">
         <v>15</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
@@ -46261,7 +46288,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I17" s="85" t="n">
+      <c r="I17" s="84" t="n">
         <v>16</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -46331,7 +46358,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I18" s="85" t="n">
+      <c r="I18" s="84" t="n">
         <v>17</v>
       </c>
       <c r="J18" s="7" t="inlineStr">
@@ -46401,7 +46428,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I19" s="85" t="n">
+      <c r="I19" s="84" t="n">
         <v>18</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -46470,7 +46497,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I20" s="85" t="n">
+      <c r="I20" s="84" t="n">
         <v>19</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -46543,7 +46570,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I21" s="85" t="n">
+      <c r="I21" s="84" t="n">
         <v>20</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -46615,7 +46642,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I22" s="85" t="n">
+      <c r="I22" s="84" t="n">
         <v>21</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -46685,7 +46712,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I23" s="85" t="n">
+      <c r="I23" s="84" t="n">
         <v>22</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -46754,7 +46781,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I24" s="85" t="n">
+      <c r="I24" s="84" t="n">
         <v>23</v>
       </c>
       <c r="J24" s="7" t="inlineStr">
@@ -46827,7 +46854,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I25" s="85" t="n">
+      <c r="I25" s="84" t="n">
         <v>24</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -46893,7 +46920,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I26" s="85" t="n">
+      <c r="I26" s="84" t="n">
         <v>25</v>
       </c>
       <c r="J26" s="7" t="inlineStr">
@@ -46964,7 +46991,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I27" s="85" t="n">
+      <c r="I27" s="84" t="n">
         <v>26</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
@@ -47037,7 +47064,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I28" s="85" t="n">
+      <c r="I28" s="84" t="n">
         <v>27</v>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -47110,7 +47137,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I29" s="85" t="n">
+      <c r="I29" s="84" t="n">
         <v>28</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
@@ -47190,7 +47217,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I30" s="85" t="n">
+      <c r="I30" s="84" t="n">
         <v>29</v>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -47259,7 +47286,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I31" s="85" t="n">
+      <c r="I31" s="84" t="n">
         <v>30</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -47325,7 +47352,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I32" s="85" t="n">
+      <c r="I32" s="84" t="n">
         <v>31</v>
       </c>
       <c r="J32" s="7" t="inlineStr">
@@ -47406,7 +47433,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I33" s="85" t="n">
+      <c r="I33" s="84" t="n">
         <v>32</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
@@ -47474,7 +47501,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I34" s="85" t="n">
+      <c r="I34" s="84" t="n">
         <v>33</v>
       </c>
       <c r="J34" s="7" t="inlineStr">
@@ -47547,7 +47574,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I35" s="85" t="n">
+      <c r="I35" s="84" t="n">
         <v>34</v>
       </c>
       <c r="J35" s="7" t="inlineStr">
@@ -47616,7 +47643,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I36" s="85" t="n">
+      <c r="I36" s="84" t="n">
         <v>35</v>
       </c>
       <c r="J36" s="7" t="inlineStr">
@@ -47687,7 +47714,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I37" s="85" t="n">
+      <c r="I37" s="84" t="n">
         <v>36</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
@@ -47757,7 +47784,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I38" s="85" t="n">
+      <c r="I38" s="84" t="n">
         <v>37</v>
       </c>
       <c r="J38" s="7" t="inlineStr">
@@ -47826,7 +47853,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I39" s="85" t="n">
+      <c r="I39" s="84" t="n">
         <v>38</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
@@ -47895,7 +47922,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I40" s="85" t="n">
+      <c r="I40" s="84" t="n">
         <v>39</v>
       </c>
       <c r="J40" s="7" t="inlineStr">
@@ -47971,7 +47998,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I41" s="85" t="n">
+      <c r="I41" s="84" t="n">
         <v>40</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
@@ -48044,7 +48071,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I42" s="85" t="n">
+      <c r="I42" s="84" t="n">
         <v>41</v>
       </c>
       <c r="J42" s="7" t="inlineStr">
@@ -48112,7 +48139,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I43" s="85" t="n">
+      <c r="I43" s="84" t="n">
         <v>42</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
@@ -48184,7 +48211,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I44" s="85" t="n">
+      <c r="I44" s="84" t="n">
         <v>43</v>
       </c>
       <c r="J44" s="7" t="inlineStr">
@@ -48255,7 +48282,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I45" s="85" t="n">
+      <c r="I45" s="84" t="n">
         <v>44</v>
       </c>
       <c r="J45" s="7" t="inlineStr">
@@ -48328,7 +48355,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I46" s="85" t="n">
+      <c r="I46" s="84" t="n">
         <v>45</v>
       </c>
       <c r="J46" s="7" t="inlineStr">
@@ -48403,7 +48430,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I47" s="85" t="n">
+      <c r="I47" s="84" t="n">
         <v>46</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
@@ -48469,7 +48496,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I48" s="85" t="n">
+      <c r="I48" s="84" t="n">
         <v>47</v>
       </c>
       <c r="J48" s="7" t="inlineStr">
@@ -48538,7 +48565,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I49" s="85" t="n">
+      <c r="I49" s="84" t="n">
         <v>48</v>
       </c>
       <c r="J49" s="7" t="inlineStr">
@@ -48608,7 +48635,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I50" s="85" t="n">
+      <c r="I50" s="84" t="n">
         <v>49</v>
       </c>
       <c r="J50" s="7" t="inlineStr">
@@ -48679,7 +48706,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I51" s="85" t="n">
+      <c r="I51" s="84" t="n">
         <v>50</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -48750,7 +48777,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I52" s="85" t="n">
+      <c r="I52" s="84" t="n">
         <v>51</v>
       </c>
       <c r="J52" s="7" t="inlineStr">
@@ -48817,7 +48844,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I53" s="85" t="n">
+      <c r="I53" s="84" t="n">
         <v>52</v>
       </c>
       <c r="J53" s="7" t="inlineStr">
@@ -48887,7 +48914,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I54" s="85" t="n">
+      <c r="I54" s="84" t="n">
         <v>53</v>
       </c>
       <c r="J54" s="7" t="inlineStr">
@@ -48957,7 +48984,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I55" s="85" t="n">
+      <c r="I55" s="84" t="n">
         <v>54</v>
       </c>
       <c r="J55" s="7" t="inlineStr">
@@ -49028,7 +49055,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I56" s="85" t="n">
+      <c r="I56" s="84" t="n">
         <v>55</v>
       </c>
       <c r="J56" s="7" t="inlineStr">
@@ -49100,7 +49127,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I57" s="85" t="n">
+      <c r="I57" s="84" t="n">
         <v>56</v>
       </c>
       <c r="J57" s="7" t="inlineStr">
@@ -49170,7 +49197,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I58" s="85" t="n">
+      <c r="I58" s="84" t="n">
         <v>57</v>
       </c>
       <c r="J58" s="7" t="inlineStr">
@@ -49243,7 +49270,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I59" s="85" t="n">
+      <c r="I59" s="84" t="n">
         <v>58</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
@@ -49316,7 +49343,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I60" s="85" t="n">
+      <c r="I60" s="84" t="n">
         <v>59</v>
       </c>
       <c r="J60" s="7" t="inlineStr">
@@ -49388,7 +49415,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I61" s="85" t="n">
+      <c r="I61" s="84" t="n">
         <v>60</v>
       </c>
       <c r="J61" s="7" t="inlineStr">
@@ -49460,7 +49487,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I62" s="85" t="n">
+      <c r="I62" s="84" t="n">
         <v>61</v>
       </c>
       <c r="J62" s="7" t="inlineStr">
@@ -49530,7 +49557,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I63" s="85" t="n">
+      <c r="I63" s="84" t="n">
         <v>62</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -49596,7 +49623,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I64" s="85" t="n">
+      <c r="I64" s="84" t="n">
         <v>63</v>
       </c>
       <c r="J64" s="7" t="inlineStr">
@@ -49664,7 +49691,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I65" s="85" t="n">
+      <c r="I65" s="84" t="n">
         <v>64</v>
       </c>
       <c r="J65" s="7" t="inlineStr">
@@ -49737,7 +49764,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I66" s="85" t="n">
+      <c r="I66" s="84" t="n">
         <v>65</v>
       </c>
       <c r="J66" s="7" t="inlineStr">
@@ -49803,7 +49830,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I67" s="85" t="n">
+      <c r="I67" s="84" t="n">
         <v>66</v>
       </c>
       <c r="J67" s="7" t="inlineStr">
@@ -49871,7 +49898,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I68" s="85" t="n">
+      <c r="I68" s="84" t="n">
         <v>67</v>
       </c>
       <c r="J68" s="7" t="inlineStr">
@@ -49943,7 +49970,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I69" s="85" t="n">
+      <c r="I69" s="84" t="n">
         <v>68</v>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -50008,7 +50035,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I70" s="85" t="n">
+      <c r="I70" s="84" t="n">
         <v>69</v>
       </c>
       <c r="J70" s="7" t="inlineStr">
@@ -50078,7 +50105,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I71" s="85" t="n">
+      <c r="I71" s="84" t="n">
         <v>70</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
@@ -50149,7 +50176,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I72" s="85" t="n">
+      <c r="I72" s="84" t="n">
         <v>71</v>
       </c>
       <c r="J72" s="7" t="inlineStr">
@@ -50217,7 +50244,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I73" s="85" t="n">
+      <c r="I73" s="84" t="n">
         <v>72</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
@@ -50287,7 +50314,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I74" s="85" t="n">
+      <c r="I74" s="84" t="n">
         <v>73</v>
       </c>
       <c r="J74" s="7" t="inlineStr">
@@ -50355,7 +50382,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I75" s="85" t="n">
+      <c r="I75" s="84" t="n">
         <v>74</v>
       </c>
       <c r="J75" s="7" t="inlineStr">
@@ -50426,7 +50453,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I76" s="85" t="n">
+      <c r="I76" s="84" t="n">
         <v>75</v>
       </c>
       <c r="J76" s="7" t="inlineStr">
@@ -50493,7 +50520,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I77" s="85" t="n">
+      <c r="I77" s="84" t="n">
         <v>76</v>
       </c>
       <c r="J77" s="7" t="inlineStr">
@@ -50559,7 +50586,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I78" s="85" t="n">
+      <c r="I78" s="84" t="n">
         <v>77</v>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -50634,7 +50661,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I79" s="85" t="n">
+      <c r="I79" s="84" t="n">
         <v>78</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -50704,7 +50731,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I80" s="85" t="n">
+      <c r="I80" s="84" t="n">
         <v>79</v>
       </c>
       <c r="J80" s="7" t="inlineStr">
@@ -50777,7 +50804,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I81" s="85" t="n">
+      <c r="I81" s="84" t="n">
         <v>80</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
@@ -50853,7 +50880,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I82" s="85" t="n">
+      <c r="I82" s="84" t="n">
         <v>81</v>
       </c>
       <c r="J82" s="7" t="inlineStr">
@@ -50921,7 +50948,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I83" s="85" t="n">
+      <c r="I83" s="84" t="n">
         <v>82</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
@@ -50988,7 +51015,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I84" s="85" t="n">
+      <c r="I84" s="84" t="n">
         <v>83</v>
       </c>
       <c r="J84" s="7" t="inlineStr">
@@ -51067,7 +51094,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I85" s="85" t="n">
+      <c r="I85" s="84" t="n">
         <v>84</v>
       </c>
       <c r="J85" s="7" t="inlineStr">
@@ -51136,7 +51163,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I86" s="85" t="n">
+      <c r="I86" s="84" t="n">
         <v>85</v>
       </c>
       <c r="J86" s="7" t="inlineStr">
@@ -51211,7 +51238,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I87" s="85" t="n">
+      <c r="I87" s="84" t="n">
         <v>86</v>
       </c>
       <c r="J87" s="7" t="inlineStr">
@@ -51279,7 +51306,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I88" s="85" t="n">
+      <c r="I88" s="84" t="n">
         <v>87</v>
       </c>
       <c r="J88" s="7" t="inlineStr">
@@ -51350,7 +51377,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I89" s="85" t="n">
+      <c r="I89" s="84" t="n">
         <v>88</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
@@ -51420,7 +51447,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I90" s="85" t="n">
+      <c r="I90" s="84" t="n">
         <v>89</v>
       </c>
       <c r="J90" s="7" t="inlineStr">
@@ -51490,7 +51517,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I91" s="85" t="n">
+      <c r="I91" s="84" t="n">
         <v>90</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
@@ -51563,7 +51590,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I92" s="85" t="n">
+      <c r="I92" s="84" t="n">
         <v>91</v>
       </c>
       <c r="J92" s="7" t="inlineStr">
@@ -51632,7 +51659,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I93" s="85" t="n">
+      <c r="I93" s="84" t="n">
         <v>92</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
@@ -51699,7 +51726,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I94" s="85" t="n">
+      <c r="I94" s="84" t="n">
         <v>93</v>
       </c>
       <c r="J94" s="7" t="inlineStr">
@@ -51767,7 +51794,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I95" s="85" t="n">
+      <c r="I95" s="84" t="n">
         <v>94</v>
       </c>
       <c r="J95" s="7" t="inlineStr">
@@ -51835,7 +51862,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I96" s="85" t="n">
+      <c r="I96" s="84" t="n">
         <v>95</v>
       </c>
       <c r="J96" s="7" t="inlineStr">
@@ -51904,7 +51931,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I97" s="85" t="n">
+      <c r="I97" s="84" t="n">
         <v>96</v>
       </c>
       <c r="J97" s="7" t="inlineStr">
@@ -51973,7 +52000,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I98" s="85" t="n">
+      <c r="I98" s="84" t="n">
         <v>97</v>
       </c>
       <c r="J98" s="7" t="inlineStr">
@@ -52041,7 +52068,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I99" s="85" t="n">
+      <c r="I99" s="84" t="n">
         <v>98</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
@@ -52108,7 +52135,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I100" s="85" t="n">
+      <c r="I100" s="84" t="n">
         <v>99</v>
       </c>
       <c r="J100" s="7" t="inlineStr">
@@ -52178,7 +52205,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I101" s="85" t="n">
+      <c r="I101" s="84" t="n">
         <v>100</v>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -52246,7 +52273,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I102" s="85" t="n">
+      <c r="I102" s="84" t="n">
         <v>101</v>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -52314,7 +52341,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I103" s="85" t="n">
+      <c r="I103" s="84" t="n">
         <v>102</v>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -52385,7 +52412,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I104" s="85" t="n">
+      <c r="I104" s="84" t="n">
         <v>103</v>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -52454,7 +52481,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I105" s="85" t="n">
+      <c r="I105" s="84" t="n">
         <v>104</v>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -52523,7 +52550,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I106" s="85" t="n">
+      <c r="I106" s="84" t="n">
         <v>105</v>
       </c>
       <c r="J106" s="7" t="inlineStr">
@@ -52594,7 +52621,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I107" s="85" t="n">
+      <c r="I107" s="84" t="n">
         <v>106</v>
       </c>
       <c r="J107" s="7" t="inlineStr">
@@ -52665,7 +52692,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I108" s="85" t="n">
+      <c r="I108" s="84" t="n">
         <v>107</v>
       </c>
       <c r="J108" s="7" t="inlineStr">
@@ -52737,7 +52764,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I109" s="85" t="n">
+      <c r="I109" s="84" t="n">
         <v>108</v>
       </c>
       <c r="J109" s="7" t="inlineStr">
@@ -52804,7 +52831,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I110" s="85" t="n">
+      <c r="I110" s="84" t="n">
         <v>109</v>
       </c>
       <c r="J110" s="7" t="inlineStr">
@@ -52877,7 +52904,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I111" s="85" t="n">
+      <c r="I111" s="84" t="n">
         <v>110</v>
       </c>
       <c r="J111" s="7" t="inlineStr">
@@ -52946,7 +52973,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I112" s="85" t="n">
+      <c r="I112" s="84" t="n">
         <v>111</v>
       </c>
       <c r="J112" s="7" t="inlineStr">
@@ -53013,7 +53040,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I113" s="85" t="n">
+      <c r="I113" s="84" t="n">
         <v>112</v>
       </c>
       <c r="J113" s="7" t="inlineStr">
@@ -53082,7 +53109,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I114" s="85" t="n">
+      <c r="I114" s="84" t="n">
         <v>113</v>
       </c>
       <c r="J114" s="7" t="inlineStr">
@@ -53152,7 +53179,7 @@
           <t>shen_nong_ben_cao_jing</t>
         </is>
       </c>
-      <c r="I115" s="85" t="n">
+      <c r="I115" s="84" t="n">
         <v>114</v>
       </c>
       <c r="J115" s="7" t="inlineStr">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story'!$A$1:$AA$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'StoryLine'!$A$1:$BI$450</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2428,8 +2428,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.75" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.875" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.125" customWidth="1" style="23" min="10" max="89"/>
-    <col width="9.125" customWidth="1" style="23" min="90" max="16384"/>
+    <col width="9.125" customWidth="1" style="23" min="10" max="90"/>
+    <col width="9.125" customWidth="1" style="23" min="91" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -6835,8 +6835,8 @@
     <col width="8.375" bestFit="1" customWidth="1" style="46" min="16" max="18"/>
     <col width="10.75" customWidth="1" style="46" min="19" max="19"/>
     <col width="10" bestFit="1" customWidth="1" style="46" min="20" max="20"/>
-    <col width="9" customWidth="1" style="47" min="21" max="39"/>
-    <col width="9" customWidth="1" style="47" min="40" max="16384"/>
+    <col width="9" customWidth="1" style="47" min="21" max="40"/>
+    <col width="9" customWidth="1" style="47" min="41" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customFormat="1" customHeight="1" s="46">
@@ -10059,7 +10059,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
-    <col width="13" customWidth="1" style="10" min="2" max="2"/>
+    <col width="15.1875" customWidth="1" style="10" min="2" max="2"/>
     <col width="11.25" customWidth="1" style="10" min="3" max="3"/>
     <col width="10.5" customWidth="1" style="10" min="4" max="4"/>
     <col width="9.5" customWidth="1" style="10" min="5" max="5"/>
@@ -10069,8 +10069,8 @@
     <col width="48" customWidth="1" style="10" min="9" max="9"/>
     <col width="150.5" customWidth="1" style="64" min="10" max="10"/>
     <col width="8.875" customWidth="1" style="66" min="11" max="11"/>
-    <col width="8.875" customWidth="1" style="36" min="12" max="63"/>
-    <col width="8.875" customWidth="1" style="36" min="64" max="16384"/>
+    <col width="8.875" customWidth="1" style="36" min="12" max="64"/>
+    <col width="8.875" customWidth="1" style="36" min="65" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30267,8 +30267,8 @@
     <col width="5.125" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.25" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="137"/>
-    <col width="9" customWidth="1" style="9" min="138" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="138"/>
+    <col width="9" customWidth="1" style="9" min="139" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276DE0B4-B88E-4DBB-9391-FC216E4CB812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0E3BF6-E884-432C-863F-C0B6513553E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7383" uniqueCount="1892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7390" uniqueCount="1897">
   <si>
     <t>NpcID</t>
   </si>
@@ -3045,7 +3045,7 @@
 【病机】风湿热邪侵袭经络关节，或风寒湿邪郁而化热，气血壅滞、经络痹阻。
 【症状】关节红肿灼热、疼痛剧烈；触之发热、拒按，得冷稍舒；发热、口渴、烦躁；肢体屈伸不利。
 【脉象】
-浮脉（表）：波峰高（轻微），脉搏次数多（剧烈），波宽宽（轻微）
+浮脉（表）：波峰高（轻微），脉搏次数多，波宽宽（轻微）
 【标准方】白虎桂枝汤</t>
   </si>
   <si>
@@ -3151,7 +3151,7 @@
 【病机】肺阴亏虚，虚火内生，肺失滋润、清肃无权。
 【症状】干咳无痰，或痰少黏稠难咯；咽干口燥、声音嘶哑；潮热盗汗、五心烦热；颧红、形体消瘦。
 【脉象】
-右寸（肺）：脉搏次数多，波宽窄
+右寸（肺）：波线细，脉搏次数多，波宽窄
 【标准方】沙参麦冬汤</t>
   </si>
   <si>
@@ -3649,8 +3649,8 @@
 【病机】久病耗伤、房劳过度、过服温燥，肾阴亏虚、虚火内生、失于滋养。
 【症状】腰膝酸痛、眩晕耳鸣、健忘；潮热盗汗、五心烦热、口燥咽干；男子遗精早泄，女子经少、闭经或崩漏；形体消瘦、失眠多梦。
 【脉象】
+右尺（肾阳）：脉搏次数多
 左尺（肾阴）：波线细，波宽窄
-右尺（肾阳）：脉搏次数多
 【标准方】六味地黄丸</t>
   </si>
   <si>
@@ -3670,8 +3670,8 @@
 【病机】年老肾亏、久病伤阳、房劳耗损，肾阳亏虚、命门火衰、温煦气化无权。
 【症状】腰膝冷痛、酸软无力；畏寒肢冷，尤以下肢为甚；精神萎靡、面色㿠白或黧黑；小便清长、夜尿多、遗尿；男子阳痿早泄，女子宫寒不孕、带下清稀；大便久泄不止、完谷不化、五更泄泻。
 【脉象】
+右尺（肾阳）：波峰低，脉搏次数少
 左尺（肾阴）：波宽宽
-右尺（肾阳）：波峰低，脉搏次数少
 【标准方】金匮肾气丸</t>
   </si>
   <si>
@@ -3691,9 +3691,9 @@
 【病机】肾阳虚衰，气化无权，水湿内停，泛溢肌肤。
 【症状】周身浮肿，腰以下肿甚，按之凹陷不起；腰膝酸软冷痛，畏寒肢冷；小便短少，或小便不利；心悸气短、喘咳痰稀如水；面色㿠白或灰黯。
 【脉象】
+右关（脾）：波宽宽
+右尺（肾阳）：波峰低，脉搏次数少
 左尺（肾阴）：波宽宽
-右尺（肾阳）：波峰低，脉搏次数少
-右关（脾）：波宽宽
 【标准方】真武汤</t>
   </si>
   <si>
@@ -3708,8 +3708,8 @@
 【症状】小儿五迟五软：立迟、行迟、语迟、发迟、齿迟；囟门迟闭、智力低下、身材矮小。
 成人脑髓失养：头晕耳鸣、健忘失眠、精神迟钝；早衰特征：发脱齿摇、须发早白；骨骼失养：腰膝酸软、足痿无力生殖亏虚：男子精少不育；女子经闭、不孕。
 【脉象】
+右尺（肾阳）：波峰低
 左尺（肾阴）：波线细
-右尺（肾阳）：波峰低
 【标准方】左归丸</t>
   </si>
   <si>
@@ -3723,8 +3723,8 @@
 【病机】久病劳损、年老体弱、房事不节，肾气亏虚、封藏固摄无权，偏虚证、无明显寒热。
 【症状】腰膝酸软、神疲乏力，耳鸣；小便频数清长、夜尿多、遗尿、小便失禁；男子：滑精、早泄；女子：带下清稀量多、胎动易滑。
 【脉象】
+右尺（肾阳）：波峰低
 左尺（肾阴）：波宽宽
-右尺（肾阳）：波峰低
 【标准方】金锁固精丸</t>
   </si>
   <si>
@@ -3741,9 +3741,9 @@
 【病机】气血下聚冲任以养胎元，母体气血为胎元之本。胎之成，成于肾；胎之养，养于脾。
 【症状】恶心呕吐，食入即吐、厌油腻、头晕倦怠；
 【脉象】
+右关（脾）：波宽宽
+右尺（肾阳）：波峰高
 左尺（肾阴）：波线粗
-右尺（肾阳）：波峰高
-右关（脾）：波宽宽
 【标准方】泰山磐石散</t>
   </si>
   <si>
@@ -8095,6 +8095,48 @@
 惊是七情之一，是人在突然遇到意外、声响或危险时产生的急剧情绪反应。惊与恐有所不同：惊通常由突发刺激引起，事先没有心理准备；恐则多是对已知或预期危险产生的害怕。
 中医认为惊主要影响心神，可使气机紊乱，称为“惊则气乱”。受到突然惊吓后，心神失去安定，气血运行也可能暂时失常，并可进一步影响肾的封藏功能。
 惊伤心神时，常见心悸、失眠、神志不宁、精神恍惚、容易受惊或注意力难以集中等表现；情况严重时，还可能出现昏厥或神志异常。判断时需要结合刺激强度、持续影响及患者原有的身心状态综合分析。</t>
+  </si>
+  <si>
+    <t>ye_chun_luo</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>田春萝</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>叶江舟</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>男</t>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <r>
+      <t>郭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>妈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>妈</t>
+    </r>
+    <phoneticPr fontId="20"/>
   </si>
 </sst>
 </file>
@@ -8244,17 +8286,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="6"/>
+      <name val="BIZ UDGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="BIZ UDGothic"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="13">
@@ -8583,7 +8625,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -10417,7 +10459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" style="23" customWidth="1"/>
@@ -10429,8 +10471,8 @@
     <col min="7" max="7" width="25.5" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.75" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="94" width="9.125" style="23" customWidth="1"/>
-    <col min="95" max="16384" width="9.125" style="23"/>
+    <col min="10" max="95" width="9.125" style="23" customWidth="1"/>
+    <col min="96" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -10971,7 +11013,7 @@
         <v>60</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>61</v>
+        <v>1896</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>11</v>
@@ -12530,10 +12572,18 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="18" customHeight="1">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
+      <c r="A81" s="7" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B81" s="73" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7"/>
       <c r="G81" s="40"/>
@@ -12542,9 +12592,15 @@
     </row>
     <row r="82" spans="1:9" ht="18" customHeight="1">
       <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
+      <c r="B82" s="73" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D82" s="73" t="s">
+        <v>1895</v>
+      </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
       <c r="G82" s="40"/>
@@ -12562,8 +12618,96 @@
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
     </row>
+    <row r="84" spans="1:9" ht="18" customHeight="1">
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="40"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" spans="1:9" ht="18" customHeight="1">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86" spans="1:9" ht="18" customHeight="1">
+      <c r="A86" s="7"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" spans="1:9" ht="18" customHeight="1">
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+    </row>
+    <row r="88" spans="1:9" ht="18" customHeight="1">
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" spans="1:9" ht="18" customHeight="1">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="40"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" spans="1:9" ht="18" customHeight="1">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="40"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" spans="1:9" ht="18" customHeight="1">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="40"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13352,7 +13496,7 @@
       <c r="F47" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -13377,8 +13521,8 @@
     <col min="16" max="18" width="8.375" style="46" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.75" style="46" customWidth="1"/>
     <col min="20" max="20" width="10" style="46" bestFit="1" customWidth="1"/>
-    <col min="21" max="44" width="9" style="47" customWidth="1"/>
-    <col min="45" max="16384" width="9" style="47"/>
+    <col min="21" max="45" width="9" style="47" customWidth="1"/>
+    <col min="46" max="16384" width="9" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="46" customFormat="1" ht="36" customHeight="1">
@@ -15781,7 +15925,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AA60" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15802,8 +15946,8 @@
     <col min="9" max="9" width="48" style="10" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="64" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="66" customWidth="1"/>
-    <col min="12" max="68" width="8.875" style="36" customWidth="1"/>
-    <col min="69" max="16384" width="8.875" style="36"/>
+    <col min="12" max="69" width="8.875" style="36" customWidth="1"/>
+    <col min="70" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -28177,7 +28321,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:BI453" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -29508,7 +29652,7 @@
       <c r="C114" s="24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -29541,8 +29685,8 @@
     <col min="27" max="27" width="5.125" style="35" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" customWidth="1"/>
-    <col min="30" max="142" width="9" style="9" customWidth="1"/>
-    <col min="143" max="16384" width="9" style="9"/>
+    <col min="30" max="143" width="9" style="9" customWidth="1"/>
+    <col min="144" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -30190,7 +30334,7 @@
       <c r="A50" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -31258,7 +31402,7 @@
     <row r="112" ht="15" customHeight="1"/>
     <row r="114" ht="15" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -39470,7 +39614,7 @@
       <c r="F357" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -44247,7 +44391,7 @@
       <c r="A129" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <conditionalFormatting sqref="A1:A8 A27 A30 A34 A40 A44 A57:A58 A67 A103 A116:A1048576">
     <cfRule type="duplicateValues" dxfId="161" priority="2013"/>
   </conditionalFormatting>
@@ -45024,7 +45168,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="21"/>
+  <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -10544,7 +10544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K454"/>
+  <dimension ref="A1:K456"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="18"/>
   <cols>
     <col width="8.75" customWidth="1" style="10" min="1" max="1"/>
@@ -10680,7 +10680,7 @@
       <c r="I3" s="51" t="inlineStr"/>
       <c r="J3" s="53" t="inlineStr">
         <is>
-          <t>李东璧去各地实地考察，采集样本，参考800多种书籍，花费27年，历经三次改写，至万历六年终于完成著作。全书共52卷，载药1892种，方剂11096首，插图1109幅，约190万字。</t>
+          <t>李东璧去各地实地考察，采集样本，参考800多种书籍，历经三次改写，终于完成著作。全书共52卷，载药1892种，方剂11096首，插图1109幅，约190万字。</t>
         </is>
       </c>
       <c r="K3" s="50" t="inlineStr"/>
@@ -27533,20 +27533,24 @@
       </c>
       <c r="E429" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F429" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G429" s="55" t="inlineStr"/>
       <c r="H429" s="55" t="inlineStr"/>
-      <c r="I429" s="55" t="inlineStr"/>
+      <c r="I429" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_06.png</t>
+        </is>
+      </c>
       <c r="J429" s="68" t="inlineStr">
         <is>
-          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
+          <t>哇，放烟花啦！</t>
         </is>
       </c>
       <c r="K429" s="55" t="inlineStr"/>
@@ -27572,24 +27576,20 @@
       </c>
       <c r="E430" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F430" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F430" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G430" s="55" t="inlineStr"/>
       <c r="H430" s="55" t="inlineStr"/>
-      <c r="I430" s="51" t="inlineStr">
-        <is>
-          <t>res://Assets/Background/027/027_05.png</t>
-        </is>
-      </c>
-      <c r="J430" s="55" t="inlineStr">
-        <is>
-          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
+      <c r="I430" s="55" t="inlineStr"/>
+      <c r="J430" s="68" t="inlineStr">
+        <is>
+          <t>真漂亮啊。</t>
         </is>
       </c>
       <c r="K430" s="55" t="inlineStr"/>
@@ -27615,20 +27615,20 @@
       </c>
       <c r="E431" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F431" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F431" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
         </is>
       </c>
       <c r="G431" s="55" t="inlineStr"/>
       <c r="H431" s="55" t="inlineStr"/>
       <c r="I431" s="55" t="inlineStr"/>
-      <c r="J431" s="55" t="inlineStr">
-        <is>
-          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
+      <c r="J431" s="68" t="inlineStr">
+        <is>
+          <t>东璧，芷兰，咱们去小摊儿坐会儿吃点元宵。</t>
         </is>
       </c>
       <c r="K431" s="55" t="inlineStr"/>
@@ -27654,20 +27654,24 @@
       </c>
       <c r="E432" s="53" t="inlineStr">
         <is>
-          <t>吴芷兰</t>
+          <t>李言闻</t>
         </is>
       </c>
       <c r="F432" s="52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G432" s="55" t="inlineStr"/>
       <c r="H432" s="55" t="inlineStr"/>
-      <c r="I432" s="55" t="inlineStr"/>
+      <c r="I432" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Background/027/027_06.png</t>
+        </is>
+      </c>
       <c r="J432" s="55" t="inlineStr">
         <is>
-          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+          <t>干了一年坐堂医，感觉怎么样，和你之前想的一样吗？</t>
         </is>
       </c>
       <c r="K432" s="55" t="inlineStr"/>
@@ -27693,12 +27697,12 @@
       </c>
       <c r="E433" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
-        </is>
-      </c>
-      <c r="F433" s="52" t="inlineStr">
-        <is>
-          <t>mid</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F433" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G433" s="55" t="inlineStr"/>
@@ -27706,7 +27710,7 @@
       <c r="I433" s="55" t="inlineStr"/>
       <c r="J433" s="55" t="inlineStr">
         <is>
-          <t>是啊，一家人平平安安就好啊。</t>
+          <t>我倒是挺喜欢这一行，只是赚不到什么钱，苦了您和芷兰了…</t>
         </is>
       </c>
       <c r="K433" s="55" t="inlineStr"/>
@@ -27732,12 +27736,12 @@
       </c>
       <c r="E434" s="53" t="inlineStr">
         <is>
-          <t>李言闻</t>
+          <t>吴芷兰</t>
         </is>
       </c>
       <c r="F434" s="52" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>right</t>
         </is>
       </c>
       <c r="G434" s="55" t="inlineStr"/>
@@ -27745,24 +27749,24 @@
       <c r="I434" s="55" t="inlineStr"/>
       <c r="J434" s="55" t="inlineStr">
         <is>
-          <t>好了，不早了，咱们该回家了。</t>
+          <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
         </is>
       </c>
       <c r="K434" s="55" t="inlineStr"/>
     </row>
-    <row r="435" ht="30" customHeight="1">
+    <row r="435">
       <c r="A435" s="50" t="inlineStr">
         <is>
-          <t>028_01</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B435" s="50" t="inlineStr">
         <is>
-          <t>曾题名痰火扰心</t>
+          <t>上元灯节</t>
         </is>
       </c>
       <c r="C435" s="50" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D435" s="50" t="inlineStr">
         <is>
@@ -27771,102 +27775,102 @@
       </c>
       <c r="E435" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F435" s="51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G435" s="51" t="inlineStr"/>
-      <c r="H435" s="54" t="inlineStr"/>
-      <c r="I435" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
-      <c r="J435" s="53" t="inlineStr">
-        <is>
-          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
-        </is>
-      </c>
-      <c r="K435" s="50" t="inlineStr"/>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F435" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G435" s="55" t="inlineStr"/>
+      <c r="H435" s="55" t="inlineStr"/>
+      <c r="I435" s="55" t="inlineStr"/>
+      <c r="J435" s="55" t="inlineStr">
+        <is>
+          <t>是啊，一家人平平安安就好啊。</t>
+        </is>
+      </c>
+      <c r="K435" s="55" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="50" t="inlineStr">
         <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B436" s="50" t="inlineStr">
+        <is>
+          <t>上元灯节</t>
+        </is>
+      </c>
+      <c r="C436" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="D436" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E436" s="53" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F436" s="52" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G436" s="55" t="inlineStr"/>
+      <c r="H436" s="55" t="inlineStr"/>
+      <c r="I436" s="55" t="inlineStr"/>
+      <c r="J436" s="55" t="inlineStr">
+        <is>
+          <t>好了，不早了，咱们该回家了。</t>
+        </is>
+      </c>
+      <c r="K436" s="55" t="inlineStr"/>
+    </row>
+    <row r="437" ht="30" customHeight="1">
+      <c r="A437" s="50" t="inlineStr">
+        <is>
           <t>028_01</t>
         </is>
       </c>
-      <c r="B436" s="50" t="inlineStr">
+      <c r="B437" s="50" t="inlineStr">
         <is>
           <t>曾题名痰火扰心</t>
         </is>
       </c>
-      <c r="C436" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D436" s="50" t="inlineStr">
+      <c r="C437" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D437" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E436" s="53" t="inlineStr">
-        <is>
-          <t>曾题名</t>
-        </is>
-      </c>
-      <c r="F436" s="54" t="inlineStr">
-        <is>
-          <t>mid</t>
-        </is>
-      </c>
-      <c r="G436" s="51" t="inlineStr"/>
-      <c r="H436" s="54" t="inlineStr"/>
-      <c r="I436" s="51" t="inlineStr"/>
-      <c r="J436" s="53" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K436" s="50" t="inlineStr"/>
-    </row>
-    <row r="437">
-      <c r="A437" s="50" t="inlineStr">
-        <is>
-          <t>028_01</t>
-        </is>
-      </c>
-      <c r="B437" s="50" t="inlineStr">
-        <is>
-          <t>曾题名痰火扰心</t>
-        </is>
-      </c>
-      <c r="C437" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D437" s="50" t="inlineStr">
-        <is>
-          <t>dialogue</t>
-        </is>
-      </c>
       <c r="E437" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F437" s="54" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F437" s="51" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G437" s="51" t="inlineStr"/>
       <c r="H437" s="54" t="inlineStr"/>
-      <c r="I437" s="51" t="inlineStr"/>
+      <c r="I437" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J437" s="53" t="inlineStr">
         <is>
-          <t>别急，坐下来让我看看。</t>
+          <t>大夫啊，您快给看看吧，这孩子整日目光呆滞，叫他也不应，就在那自言自语，嘴里不知道嘟囔这什么，怪邪乎的…</t>
         </is>
       </c>
       <c r="K437" s="50" t="inlineStr"/>
@@ -27883,34 +27887,46 @@
         </is>
       </c>
       <c r="C438" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D438" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E438" s="50" t="inlineStr"/>
-      <c r="F438" s="51" t="inlineStr"/>
+      <c r="E438" s="53" t="inlineStr">
+        <is>
+          <t>曾题名</t>
+        </is>
+      </c>
+      <c r="F438" s="54" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
       <c r="G438" s="51" t="inlineStr"/>
-      <c r="H438" s="51" t="inlineStr"/>
+      <c r="H438" s="54" t="inlineStr"/>
       <c r="I438" s="51" t="inlineStr"/>
-      <c r="J438" s="50" t="inlineStr"/>
+      <c r="J438" s="53" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
       <c r="K438" s="50" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B439" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C439" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D439" s="50" t="inlineStr">
         <is>
@@ -27922,21 +27938,17 @@
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F439" s="52" t="inlineStr">
+      <c r="F439" s="54" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
       <c r="G439" s="51" t="inlineStr"/>
       <c r="H439" s="54" t="inlineStr"/>
-      <c r="I439" s="51" t="inlineStr">
-        <is>
-          <t>current_scene</t>
-        </is>
-      </c>
+      <c r="I439" s="51" t="inlineStr"/>
       <c r="J439" s="53" t="inlineStr">
         <is>
-          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
+          <t>别急，坐下来让我看看。</t>
         </is>
       </c>
       <c r="K439" s="50" t="inlineStr"/>
@@ -27944,40 +27956,28 @@
     <row r="440">
       <c r="A440" s="50" t="inlineStr">
         <is>
-          <t>028_02</t>
+          <t>028_01</t>
         </is>
       </c>
       <c r="B440" s="50" t="inlineStr">
         <is>
-          <t>028治疗成功</t>
+          <t>曾题名痰火扰心</t>
         </is>
       </c>
       <c r="C440" s="50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D440" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E440" s="53" t="inlineStr">
-        <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F440" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="E440" s="50" t="inlineStr"/>
+      <c r="F440" s="51" t="inlineStr"/>
       <c r="G440" s="51" t="inlineStr"/>
-      <c r="H440" s="54" t="inlineStr"/>
+      <c r="H440" s="51" t="inlineStr"/>
       <c r="I440" s="51" t="inlineStr"/>
-      <c r="J440" s="53" t="inlineStr">
-        <is>
-          <t>好好的怎么就得了这怪病呢？</t>
-        </is>
-      </c>
+      <c r="J440" s="50" t="inlineStr"/>
       <c r="K440" s="50" t="inlineStr"/>
     </row>
     <row r="441">
@@ -27992,7 +27992,7 @@
         </is>
       </c>
       <c r="C441" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D441" s="50" t="inlineStr">
         <is>
@@ -28010,11 +28010,15 @@
         </is>
       </c>
       <c r="G441" s="51" t="inlineStr"/>
-      <c r="H441" s="51" t="inlineStr"/>
-      <c r="I441" s="51" t="inlineStr"/>
+      <c r="H441" s="54" t="inlineStr"/>
+      <c r="I441" s="51" t="inlineStr">
+        <is>
+          <t>current_scene</t>
+        </is>
+      </c>
       <c r="J441" s="53" t="inlineStr">
         <is>
-          <t>是不是读书压力太大了呀？</t>
+          <t>公子所患的是痰迷心窍之症，开副涤痰汤调理一下。</t>
         </is>
       </c>
       <c r="K441" s="50" t="inlineStr"/>
@@ -28031,7 +28035,7 @@
         </is>
       </c>
       <c r="C442" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D442" s="50" t="inlineStr">
         <is>
@@ -28040,20 +28044,20 @@
       </c>
       <c r="E442" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F442" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G442" s="51" t="inlineStr"/>
-      <c r="H442" s="51" t="inlineStr"/>
+      <c r="H442" s="54" t="inlineStr"/>
       <c r="I442" s="51" t="inlineStr"/>
       <c r="J442" s="53" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>好好的怎么就得了这怪病呢？</t>
         </is>
       </c>
       <c r="K442" s="50" t="inlineStr"/>
@@ -28070,7 +28074,7 @@
         </is>
       </c>
       <c r="C443" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D443" s="50" t="inlineStr">
         <is>
@@ -28079,12 +28083,12 @@
       </c>
       <c r="E443" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F443" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F443" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G443" s="51" t="inlineStr"/>
@@ -28092,7 +28096,7 @@
       <c r="I443" s="51" t="inlineStr"/>
       <c r="J443" s="53" t="inlineStr">
         <is>
-          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+          <t>是不是读书压力太大了呀？</t>
         </is>
       </c>
       <c r="K443" s="50" t="inlineStr"/>
@@ -28109,7 +28113,7 @@
         </is>
       </c>
       <c r="C444" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D444" s="50" t="inlineStr">
         <is>
@@ -28118,23 +28122,23 @@
       </c>
       <c r="E444" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F444" s="54" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G444" s="55" t="inlineStr"/>
-      <c r="H444" s="55" t="inlineStr"/>
-      <c r="I444" s="55" t="inlineStr"/>
-      <c r="J444" s="56" t="inlineStr">
-        <is>
-          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
-        </is>
-      </c>
-      <c r="K444" s="55" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G444" s="51" t="inlineStr"/>
+      <c r="H444" s="51" t="inlineStr"/>
+      <c r="I444" s="51" t="inlineStr"/>
+      <c r="J444" s="53" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K444" s="50" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="50" t="inlineStr">
@@ -28148,7 +28152,7 @@
         </is>
       </c>
       <c r="C445" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D445" s="50" t="inlineStr">
         <is>
@@ -28157,12 +28161,12 @@
       </c>
       <c r="E445" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F445" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G445" s="51" t="inlineStr"/>
@@ -28170,10 +28174,10 @@
       <c r="I445" s="51" t="inlineStr"/>
       <c r="J445" s="53" t="inlineStr">
         <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="K445" s="55" t="inlineStr"/>
+          <t>他就一门心思读书，其他的什么都不用他管，能有什么压力？</t>
+        </is>
+      </c>
+      <c r="K445" s="50" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="50" t="inlineStr">
@@ -28187,7 +28191,7 @@
         </is>
       </c>
       <c r="C446" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D446" s="50" t="inlineStr">
         <is>
@@ -28196,20 +28200,20 @@
       </c>
       <c r="E446" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F446" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F446" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G446" s="55" t="inlineStr"/>
       <c r="H446" s="55" t="inlineStr"/>
       <c r="I446" s="55" t="inlineStr"/>
-      <c r="J446" s="53" t="inlineStr">
-        <is>
-          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
+      <c r="J446" s="56" t="inlineStr">
+        <is>
+          <t>再说了天下那么多读书人，怎么就他得了这怪病？</t>
         </is>
       </c>
       <c r="K446" s="55" t="inlineStr"/>
@@ -28226,7 +28230,7 @@
         </is>
       </c>
       <c r="C447" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D447" s="50" t="inlineStr">
         <is>
@@ -28235,20 +28239,20 @@
       </c>
       <c r="E447" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F447" s="54" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="G447" s="55" t="inlineStr"/>
-      <c r="H447" s="55" t="inlineStr"/>
-      <c r="I447" s="55" t="inlineStr"/>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="G447" s="51" t="inlineStr"/>
+      <c r="H447" s="51" t="inlineStr"/>
+      <c r="I447" s="51" t="inlineStr"/>
       <c r="J447" s="53" t="inlineStr">
         <is>
-          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
+          <t>…</t>
         </is>
       </c>
       <c r="K447" s="55" t="inlineStr"/>
@@ -28265,7 +28269,7 @@
         </is>
       </c>
       <c r="C448" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D448" s="50" t="inlineStr">
         <is>
@@ -28274,12 +28278,12 @@
       </c>
       <c r="E448" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F448" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F448" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G448" s="55" t="inlineStr"/>
@@ -28287,7 +28291,7 @@
       <c r="I448" s="55" t="inlineStr"/>
       <c r="J448" s="53" t="inlineStr">
         <is>
-          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
+          <t>很多人表面上看着正常，其实都病得不轻呢。</t>
         </is>
       </c>
       <c r="K448" s="55" t="inlineStr"/>
@@ -28304,7 +28308,7 @@
         </is>
       </c>
       <c r="C449" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D449" s="50" t="inlineStr">
         <is>
@@ -28313,12 +28317,12 @@
       </c>
       <c r="E449" s="53" t="inlineStr">
         <is>
-          <t>曾题名</t>
+          <t>曾和</t>
         </is>
       </c>
       <c r="F449" s="54" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>left</t>
         </is>
       </c>
       <c r="G449" s="55" t="inlineStr"/>
@@ -28326,7 +28330,7 @@
       <c r="I449" s="55" t="inlineStr"/>
       <c r="J449" s="53" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>胡扯，我看你就是没病说成有病，骗病人买药赚钱</t>
         </is>
       </c>
       <c r="K449" s="55" t="inlineStr"/>
@@ -28343,7 +28347,7 @@
         </is>
       </c>
       <c r="C450" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D450" s="50" t="inlineStr">
         <is>
@@ -28352,20 +28356,20 @@
       </c>
       <c r="E450" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F450" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F450" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G450" s="55" t="inlineStr"/>
       <c r="H450" s="55" t="inlineStr"/>
       <c r="I450" s="55" t="inlineStr"/>
-      <c r="J450" s="85" t="inlineStr">
-        <is>
-          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
+      <c r="J450" s="53" t="inlineStr">
+        <is>
+          <t>咱们家可是花了好多钱，把地都卖了供你读书，就只望着你能出人头地，光宗耀祖。可你怎么就这么不争气呢？</t>
         </is>
       </c>
       <c r="K450" s="55" t="inlineStr"/>
@@ -28382,7 +28386,7 @@
         </is>
       </c>
       <c r="C451" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D451" s="50" t="inlineStr">
         <is>
@@ -28391,20 +28395,20 @@
       </c>
       <c r="E451" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
+          <t>曾题名</t>
         </is>
       </c>
       <c r="F451" s="54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G451" s="55" t="inlineStr"/>
       <c r="H451" s="55" t="inlineStr"/>
       <c r="I451" s="55" t="inlineStr"/>
-      <c r="J451" s="85" t="inlineStr">
-        <is>
-          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
+      <c r="J451" s="53" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
       <c r="K451" s="55" t="inlineStr"/>
@@ -28421,7 +28425,7 @@
         </is>
       </c>
       <c r="C452" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D452" s="50" t="inlineStr">
         <is>
@@ -28430,12 +28434,12 @@
       </c>
       <c r="E452" s="53" t="inlineStr">
         <is>
-          <t>曾和</t>
-        </is>
-      </c>
-      <c r="F452" s="54" t="inlineStr">
-        <is>
-          <t>left</t>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F452" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
         </is>
       </c>
       <c r="G452" s="55" t="inlineStr"/>
@@ -28443,7 +28447,7 @@
       <c r="I452" s="55" t="inlineStr"/>
       <c r="J452" s="85" t="inlineStr">
         <is>
-          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+          <t>这位仁兄，我也是读过书考过科举的，读书人其实也是有很多难处的。</t>
         </is>
       </c>
       <c r="K452" s="55" t="inlineStr"/>
@@ -28460,7 +28464,7 @@
         </is>
       </c>
       <c r="C453" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D453" s="50" t="inlineStr">
         <is>
@@ -28469,12 +28473,12 @@
       </c>
       <c r="E453" s="53" t="inlineStr">
         <is>
-          <t>李东璧</t>
-        </is>
-      </c>
-      <c r="F453" s="52" t="inlineStr">
-        <is>
-          <t>right</t>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F453" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
         </is>
       </c>
       <c r="G453" s="55" t="inlineStr"/>
@@ -28482,7 +28486,7 @@
       <c r="I453" s="55" t="inlineStr"/>
       <c r="J453" s="85" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>难？还能有我赚钱养家糊口难？天底下还能有比我们做父母更难的？</t>
         </is>
       </c>
       <c r="K453" s="55" t="inlineStr"/>
@@ -28490,45 +28494,123 @@
     <row r="454">
       <c r="A454" s="50" t="inlineStr">
         <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B454" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C454" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="D454" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E454" s="53" t="inlineStr">
+        <is>
+          <t>曾和</t>
+        </is>
+      </c>
+      <c r="F454" s="54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G454" s="55" t="inlineStr"/>
+      <c r="H454" s="55" t="inlineStr"/>
+      <c r="I454" s="55" t="inlineStr"/>
+      <c r="J454" s="85" t="inlineStr">
+        <is>
+          <t>再过半年可就要考试了，你这次无论如何也要给我好好考。</t>
+        </is>
+      </c>
+      <c r="K454" s="55" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="50" t="inlineStr">
+        <is>
+          <t>028_02</t>
+        </is>
+      </c>
+      <c r="B455" s="50" t="inlineStr">
+        <is>
+          <t>028治疗成功</t>
+        </is>
+      </c>
+      <c r="C455" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D455" s="50" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E455" s="53" t="inlineStr">
+        <is>
+          <t>李东璧</t>
+        </is>
+      </c>
+      <c r="F455" s="52" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G455" s="55" t="inlineStr"/>
+      <c r="H455" s="55" t="inlineStr"/>
+      <c r="I455" s="55" t="inlineStr"/>
+      <c r="J455" s="85" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K455" s="55" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="50" t="inlineStr">
+        <is>
           <t>028_03</t>
         </is>
       </c>
-      <c r="B454" s="50" t="inlineStr">
+      <c r="B456" s="50" t="inlineStr">
         <is>
           <t>028治疗失败</t>
         </is>
       </c>
-      <c r="C454" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D454" s="50" t="inlineStr">
+      <c r="C456" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D456" s="50" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
       </c>
-      <c r="E454" s="53" t="inlineStr">
+      <c r="E456" s="53" t="inlineStr">
         <is>
           <t>李东璧</t>
         </is>
       </c>
-      <c r="F454" s="52" t="inlineStr">
+      <c r="F456" s="52" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="G454" s="51" t="inlineStr"/>
-      <c r="H454" s="54" t="inlineStr"/>
-      <c r="I454" s="51" t="inlineStr">
+      <c r="G456" s="51" t="inlineStr"/>
+      <c r="H456" s="54" t="inlineStr"/>
+      <c r="I456" s="51" t="inlineStr">
         <is>
           <t>current_scene</t>
         </is>
       </c>
-      <c r="J454" s="53" t="inlineStr">
+      <c r="J456" s="53" t="inlineStr">
         <is>
           <t>不对，我需要好好想想这是什么病，该开什么方。</t>
         </is>
       </c>
-      <c r="K454" s="50" t="inlineStr"/>
+      <c r="K456" s="50" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BI453"/>
